--- a/reports/pro-oil/pro-oil-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-oil/pro-oil-candidate-lobby-lifetime-report.xlsx
@@ -16089,7 +16089,7 @@
         <x:v>277</x:v>
       </x:c>
       <x:c r="B223" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C223" s="1">
         <x:v>0</x:v>
@@ -16101,10 +16101,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F223" s="1">
-        <x:v>2300</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G223" s="1">
-        <x:v>2300</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="224" spans="1:7">
@@ -16112,7 +16112,7 @@
         <x:v>277</x:v>
       </x:c>
       <x:c r="B224" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C224" s="1">
         <x:v>0</x:v>
@@ -16124,10 +16124,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F224" s="1">
-        <x:v>1000</x:v>
+        <x:v>2300</x:v>
       </x:c>
       <x:c r="G224" s="1">
-        <x:v>1000</x:v>
+        <x:v>2300</x:v>
       </x:c>
     </x:row>
     <x:row r="225" spans="1:7">
@@ -19194,10 +19194,10 @@
         <x:v>412</x:v>
       </x:c>
       <x:c r="B358" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C358" s="1">
-        <x:v>163000</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D358" s="1">
         <x:v>0</x:v>
@@ -19206,10 +19206,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F358" s="1">
-        <x:v>82550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G358" s="1">
-        <x:v>245550</x:v>
+        <x:v>15000</x:v>
       </x:c>
     </x:row>
     <x:row r="359" spans="1:7">
@@ -19217,10 +19217,10 @@
         <x:v>412</x:v>
       </x:c>
       <x:c r="B359" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C359" s="1">
-        <x:v>15000</x:v>
+        <x:v>163000</x:v>
       </x:c>
       <x:c r="D359" s="1">
         <x:v>0</x:v>
@@ -19229,10 +19229,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F359" s="1">
-        <x:v>0</x:v>
+        <x:v>82550</x:v>
       </x:c>
       <x:c r="G359" s="1">
-        <x:v>15000</x:v>
+        <x:v>245550</x:v>
       </x:c>
     </x:row>
     <x:row r="360" spans="1:7">
@@ -19332,10 +19332,10 @@
         <x:v>418</x:v>
       </x:c>
       <x:c r="B364" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C364" s="1">
-        <x:v>107540</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D364" s="1">
         <x:v>0</x:v>
@@ -19344,10 +19344,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F364" s="1">
-        <x:v>59170</x:v>
+        <x:v>25150</x:v>
       </x:c>
       <x:c r="G364" s="1">
-        <x:v>166710</x:v>
+        <x:v>28150</x:v>
       </x:c>
     </x:row>
     <x:row r="365" spans="1:7">
@@ -19355,10 +19355,10 @@
         <x:v>418</x:v>
       </x:c>
       <x:c r="B365" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C365" s="1">
-        <x:v>3000</x:v>
+        <x:v>107540</x:v>
       </x:c>
       <x:c r="D365" s="1">
         <x:v>0</x:v>
@@ -19367,10 +19367,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F365" s="1">
-        <x:v>25150</x:v>
+        <x:v>59170</x:v>
       </x:c>
       <x:c r="G365" s="1">
-        <x:v>28150</x:v>
+        <x:v>166710</x:v>
       </x:c>
     </x:row>
     <x:row r="366" spans="1:7">
@@ -27152,22 +27152,22 @@
         <x:v>756</x:v>
       </x:c>
       <x:c r="B704" s="1" t="s">
-        <x:v>746</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C704" s="1">
-        <x:v>418533</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D704" s="1">
-        <x:v>118</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E704" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F704" s="1">
-        <x:v>51350</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G704" s="1">
-        <x:v>470001</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="705" spans="1:7">
@@ -27175,22 +27175,22 @@
         <x:v>756</x:v>
       </x:c>
       <x:c r="B705" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>746</x:v>
       </x:c>
       <x:c r="C705" s="1">
-        <x:v>25500</x:v>
+        <x:v>418533</x:v>
       </x:c>
       <x:c r="D705" s="1">
-        <x:v>0</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E705" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F705" s="1">
-        <x:v>0</x:v>
+        <x:v>51350</x:v>
       </x:c>
       <x:c r="G705" s="1">
-        <x:v>25500</x:v>
+        <x:v>470001</x:v>
       </x:c>
     </x:row>
     <x:row r="706" spans="1:7">
@@ -30717,10 +30717,10 @@
         <x:v>909</x:v>
       </x:c>
       <x:c r="B859" s="1" t="s">
-        <x:v>258</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C859" s="1">
-        <x:v>3000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D859" s="1">
         <x:v>0</x:v>
@@ -30729,10 +30729,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F859" s="1">
-        <x:v>12950</x:v>
+        <x:v>14450</x:v>
       </x:c>
       <x:c r="G859" s="1">
-        <x:v>15950</x:v>
+        <x:v>14450</x:v>
       </x:c>
     </x:row>
     <x:row r="860" spans="1:7">
@@ -30740,10 +30740,10 @@
         <x:v>909</x:v>
       </x:c>
       <x:c r="B860" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="C860" s="1">
-        <x:v>0</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D860" s="1">
         <x:v>0</x:v>
@@ -30752,10 +30752,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F860" s="1">
-        <x:v>14450</x:v>
+        <x:v>12950</x:v>
       </x:c>
       <x:c r="G860" s="1">
-        <x:v>14450</x:v>
+        <x:v>15950</x:v>
       </x:c>
     </x:row>
     <x:row r="861" spans="1:7">
@@ -37502,10 +37502,10 @@
         <x:v>1198</x:v>
       </x:c>
       <x:c r="B1154" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C1154" s="1">
-        <x:v>752389</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1154" s="1">
         <x:v>0</x:v>
@@ -37514,10 +37514,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1154" s="1">
-        <x:v>418794</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="G1154" s="1">
-        <x:v>1171183</x:v>
+        <x:v>10000</x:v>
       </x:c>
     </x:row>
     <x:row r="1155" spans="1:7">
@@ -37525,10 +37525,10 @@
         <x:v>1198</x:v>
       </x:c>
       <x:c r="B1155" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1155" s="1">
-        <x:v>0</x:v>
+        <x:v>752389</x:v>
       </x:c>
       <x:c r="D1155" s="1">
         <x:v>0</x:v>
@@ -37537,10 +37537,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1155" s="1">
-        <x:v>10000</x:v>
+        <x:v>418794</x:v>
       </x:c>
       <x:c r="G1155" s="1">
-        <x:v>10000</x:v>
+        <x:v>1171183</x:v>
       </x:c>
     </x:row>
     <x:row r="1156" spans="1:7">
@@ -46978,10 +46978,10 @@
         <x:v>1602</x:v>
       </x:c>
       <x:c r="B1566" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="C1566" s="1">
-        <x:v>8000</x:v>
+        <x:v>181700</x:v>
       </x:c>
       <x:c r="D1566" s="1">
         <x:v>0</x:v>
@@ -46990,10 +46990,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1566" s="1">
-        <x:v>66000</x:v>
+        <x:v>168050</x:v>
       </x:c>
       <x:c r="G1566" s="1">
-        <x:v>74000</x:v>
+        <x:v>349750</x:v>
       </x:c>
     </x:row>
     <x:row r="1567" spans="1:7">
@@ -47001,10 +47001,10 @@
         <x:v>1602</x:v>
       </x:c>
       <x:c r="B1567" s="1" t="s">
-        <x:v>416</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C1567" s="1">
-        <x:v>181700</x:v>
+        <x:v>8000</x:v>
       </x:c>
       <x:c r="D1567" s="1">
         <x:v>0</x:v>
@@ -47013,10 +47013,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1567" s="1">
-        <x:v>168050</x:v>
+        <x:v>66000</x:v>
       </x:c>
       <x:c r="G1567" s="1">
-        <x:v>349750</x:v>
+        <x:v>74000</x:v>
       </x:c>
     </x:row>
     <x:row r="1568" spans="1:7">
@@ -50589,10 +50589,10 @@
         <x:v>1756</x:v>
       </x:c>
       <x:c r="B1723" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C1723" s="1">
-        <x:v>2500</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="D1723" s="1">
         <x:v>0</x:v>
@@ -50601,10 +50601,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1723" s="1">
-        <x:v>16350</x:v>
+        <x:v>72700</x:v>
       </x:c>
       <x:c r="G1723" s="1">
-        <x:v>18850</x:v>
+        <x:v>73185</x:v>
       </x:c>
     </x:row>
     <x:row r="1724" spans="1:7">
@@ -50612,10 +50612,10 @@
         <x:v>1756</x:v>
       </x:c>
       <x:c r="B1724" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1724" s="1">
-        <x:v>485</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1724" s="1">
         <x:v>0</x:v>
@@ -50624,10 +50624,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1724" s="1">
-        <x:v>72700</x:v>
+        <x:v>16350</x:v>
       </x:c>
       <x:c r="G1724" s="1">
-        <x:v>73185</x:v>
+        <x:v>18850</x:v>
       </x:c>
     </x:row>
     <x:row r="1725" spans="1:7">
@@ -52728,10 +52728,10 @@
         <x:v>1846</x:v>
       </x:c>
       <x:c r="B1816" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C1816" s="1">
-        <x:v>-1000</x:v>
+        <x:v>147100</x:v>
       </x:c>
       <x:c r="D1816" s="1">
         <x:v>0</x:v>
@@ -52740,10 +52740,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1816" s="1">
-        <x:v>0</x:v>
+        <x:v>34550</x:v>
       </x:c>
       <x:c r="G1816" s="1">
-        <x:v>-1000</x:v>
+        <x:v>181650</x:v>
       </x:c>
     </x:row>
     <x:row r="1817" spans="1:7">
@@ -52751,10 +52751,10 @@
         <x:v>1846</x:v>
       </x:c>
       <x:c r="B1817" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C1817" s="1">
-        <x:v>147100</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="D1817" s="1">
         <x:v>0</x:v>
@@ -52763,10 +52763,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1817" s="1">
-        <x:v>34550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1817" s="1">
-        <x:v>181650</x:v>
+        <x:v>-1000</x:v>
       </x:c>
     </x:row>
     <x:row r="1818" spans="1:7">
@@ -59674,10 +59674,10 @@
         <x:v>2140</x:v>
       </x:c>
       <x:c r="B2118" s="1" t="s">
-        <x:v>190</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C2118" s="1">
-        <x:v>960100</x:v>
+        <x:v>11000</x:v>
       </x:c>
       <x:c r="D2118" s="1">
         <x:v>0</x:v>
@@ -59686,10 +59686,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2118" s="1">
-        <x:v>882230</x:v>
+        <x:v>25550</x:v>
       </x:c>
       <x:c r="G2118" s="1">
-        <x:v>1842330</x:v>
+        <x:v>36550</x:v>
       </x:c>
     </x:row>
     <x:row r="2119" spans="1:7">
@@ -59697,10 +59697,10 @@
         <x:v>2140</x:v>
       </x:c>
       <x:c r="B2119" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C2119" s="1">
-        <x:v>11000</x:v>
+        <x:v>960100</x:v>
       </x:c>
       <x:c r="D2119" s="1">
         <x:v>0</x:v>
@@ -59709,10 +59709,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2119" s="1">
-        <x:v>25550</x:v>
+        <x:v>882230</x:v>
       </x:c>
       <x:c r="G2119" s="1">
-        <x:v>36550</x:v>
+        <x:v>1842330</x:v>
       </x:c>
     </x:row>
     <x:row r="2120" spans="1:7">
@@ -59789,10 +59789,10 @@
         <x:v>2144</x:v>
       </x:c>
       <x:c r="B2123" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C2123" s="1">
-        <x:v>22450</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="D2123" s="1">
         <x:v>0</x:v>
@@ -59801,10 +59801,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2123" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G2123" s="1">
         <x:v>250</x:v>
-      </x:c>
-      <x:c r="G2123" s="1">
-        <x:v>22700</x:v>
       </x:c>
     </x:row>
     <x:row r="2124" spans="1:7">
@@ -59812,22 +59812,22 @@
         <x:v>2144</x:v>
       </x:c>
       <x:c r="B2124" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C2124" s="1">
+        <x:v>22450</x:v>
+      </x:c>
+      <x:c r="D2124" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E2124" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F2124" s="1">
         <x:v>250</x:v>
       </x:c>
-      <x:c r="D2124" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E2124" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F2124" s="1">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="G2124" s="1">
-        <x:v>250</x:v>
+        <x:v>22700</x:v>
       </x:c>
     </x:row>
     <x:row r="2125" spans="1:7">
@@ -72347,10 +72347,10 @@
         <x:v>2685</x:v>
       </x:c>
       <x:c r="B2669" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C2669" s="1">
-        <x:v>139000</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D2669" s="1">
         <x:v>0</x:v>
@@ -72359,10 +72359,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2669" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2669" s="1">
-        <x:v>139500</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="2670" spans="1:7">
@@ -72370,10 +72370,10 @@
         <x:v>2685</x:v>
       </x:c>
       <x:c r="B2670" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C2670" s="1">
-        <x:v>7000</x:v>
+        <x:v>139000</x:v>
       </x:c>
       <x:c r="D2670" s="1">
         <x:v>0</x:v>
@@ -72382,10 +72382,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2670" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G2670" s="1">
-        <x:v>7000</x:v>
+        <x:v>139500</x:v>
       </x:c>
     </x:row>
     <x:row r="2671" spans="1:7">
@@ -78028,10 +78028,10 @@
         <x:v>2926</x:v>
       </x:c>
       <x:c r="B2916" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C2916" s="1">
-        <x:v>206000</x:v>
+        <x:v>37500</x:v>
       </x:c>
       <x:c r="D2916" s="1">
         <x:v>0</x:v>
@@ -78040,10 +78040,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2916" s="1">
-        <x:v>45600</x:v>
+        <x:v>8000</x:v>
       </x:c>
       <x:c r="G2916" s="1">
-        <x:v>251600</x:v>
+        <x:v>45500</x:v>
       </x:c>
     </x:row>
     <x:row r="2917" spans="1:7">
@@ -78051,10 +78051,10 @@
         <x:v>2926</x:v>
       </x:c>
       <x:c r="B2917" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C2917" s="1">
-        <x:v>37500</x:v>
+        <x:v>206000</x:v>
       </x:c>
       <x:c r="D2917" s="1">
         <x:v>0</x:v>
@@ -78063,10 +78063,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2917" s="1">
-        <x:v>8000</x:v>
+        <x:v>45600</x:v>
       </x:c>
       <x:c r="G2917" s="1">
-        <x:v>45500</x:v>
+        <x:v>251600</x:v>
       </x:c>
     </x:row>
     <x:row r="2918" spans="1:7">
@@ -78488,22 +78488,22 @@
         <x:v>2944</x:v>
       </x:c>
       <x:c r="B2936" s="1" t="s">
-        <x:v>258</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C2936" s="1">
-        <x:v>10000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D2936" s="1">
-        <x:v>0</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E2936" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2936" s="1">
-        <x:v>4950</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2936" s="1">
-        <x:v>14950</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="2937" spans="1:7">
@@ -78511,22 +78511,22 @@
         <x:v>2944</x:v>
       </x:c>
       <x:c r="B2937" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="C2937" s="1">
-        <x:v>0</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="D2937" s="1">
-        <x:v>59</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E2937" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2937" s="1">
-        <x:v>0</x:v>
+        <x:v>4950</x:v>
       </x:c>
       <x:c r="G2937" s="1">
-        <x:v>59</x:v>
+        <x:v>14950</x:v>
       </x:c>
     </x:row>
     <x:row r="2938" spans="1:7">
@@ -79132,10 +79132,10 @@
         <x:v>2971</x:v>
       </x:c>
       <x:c r="B2964" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>746</x:v>
       </x:c>
       <x:c r="C2964" s="1">
-        <x:v>5000</x:v>
+        <x:v>286800</x:v>
       </x:c>
       <x:c r="D2964" s="1">
         <x:v>0</x:v>
@@ -79144,10 +79144,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2964" s="1">
-        <x:v>0</x:v>
+        <x:v>75150</x:v>
       </x:c>
       <x:c r="G2964" s="1">
-        <x:v>5000</x:v>
+        <x:v>361950</x:v>
       </x:c>
     </x:row>
     <x:row r="2965" spans="1:7">
@@ -79155,10 +79155,10 @@
         <x:v>2971</x:v>
       </x:c>
       <x:c r="B2965" s="1" t="s">
-        <x:v>746</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C2965" s="1">
-        <x:v>286800</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D2965" s="1">
         <x:v>0</x:v>
@@ -79167,10 +79167,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2965" s="1">
-        <x:v>75150</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2965" s="1">
-        <x:v>361950</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="2966" spans="1:7">
@@ -81478,10 +81478,10 @@
         <x:v>3070</x:v>
       </x:c>
       <x:c r="B3066" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C3066" s="1">
-        <x:v>44000</x:v>
+        <x:v>10500</x:v>
       </x:c>
       <x:c r="D3066" s="1">
         <x:v>0</x:v>
@@ -81490,10 +81490,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3066" s="1">
-        <x:v>2100</x:v>
+        <x:v>31300</x:v>
       </x:c>
       <x:c r="G3066" s="1">
-        <x:v>46100</x:v>
+        <x:v>41800</x:v>
       </x:c>
     </x:row>
     <x:row r="3067" spans="1:7">
@@ -81524,10 +81524,10 @@
         <x:v>3070</x:v>
       </x:c>
       <x:c r="B3068" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C3068" s="1">
-        <x:v>10500</x:v>
+        <x:v>44000</x:v>
       </x:c>
       <x:c r="D3068" s="1">
         <x:v>0</x:v>
@@ -81536,10 +81536,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3068" s="1">
-        <x:v>31300</x:v>
+        <x:v>2100</x:v>
       </x:c>
       <x:c r="G3068" s="1">
-        <x:v>41800</x:v>
+        <x:v>46100</x:v>
       </x:c>
     </x:row>
     <x:row r="3069" spans="1:7">
@@ -81823,7 +81823,7 @@
         <x:v>3081</x:v>
       </x:c>
       <x:c r="B3081" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C3081" s="1">
         <x:v>1000</x:v>
@@ -81835,10 +81835,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3081" s="1">
-        <x:v>4750</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3081" s="1">
-        <x:v>5750</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="3082" spans="1:7">
@@ -81846,7 +81846,7 @@
         <x:v>3081</x:v>
       </x:c>
       <x:c r="B3082" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C3082" s="1">
         <x:v>1000</x:v>
@@ -81858,10 +81858,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3082" s="1">
-        <x:v>0</x:v>
+        <x:v>4750</x:v>
       </x:c>
       <x:c r="G3082" s="1">
-        <x:v>1000</x:v>
+        <x:v>5750</x:v>
       </x:c>
     </x:row>
     <x:row r="3083" spans="1:7">
@@ -82881,10 +82881,10 @@
         <x:v>3125</x:v>
       </x:c>
       <x:c r="B3127" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="C3127" s="1">
-        <x:v>5000</x:v>
+        <x:v>48000</x:v>
       </x:c>
       <x:c r="D3127" s="1">
         <x:v>0</x:v>
@@ -82893,10 +82893,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3127" s="1">
-        <x:v>250</x:v>
+        <x:v>38300</x:v>
       </x:c>
       <x:c r="G3127" s="1">
-        <x:v>5250</x:v>
+        <x:v>86300</x:v>
       </x:c>
     </x:row>
     <x:row r="3128" spans="1:7">
@@ -82904,10 +82904,10 @@
         <x:v>3125</x:v>
       </x:c>
       <x:c r="B3128" s="1" t="s">
-        <x:v>155</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C3128" s="1">
-        <x:v>48000</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D3128" s="1">
         <x:v>0</x:v>
@@ -82916,10 +82916,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3128" s="1">
-        <x:v>38300</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G3128" s="1">
-        <x:v>86300</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="3129" spans="1:7">
@@ -84813,10 +84813,10 @@
         <x:v>3203</x:v>
       </x:c>
       <x:c r="B3211" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C3211" s="1">
-        <x:v>2300</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D3211" s="1">
         <x:v>0</x:v>
@@ -84825,10 +84825,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3211" s="1">
-        <x:v>8850</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="G3211" s="1">
-        <x:v>11150</x:v>
+        <x:v>9000</x:v>
       </x:c>
     </x:row>
     <x:row r="3212" spans="1:7">
@@ -84836,10 +84836,10 @@
         <x:v>3203</x:v>
       </x:c>
       <x:c r="B3212" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C3212" s="1">
-        <x:v>3000</x:v>
+        <x:v>2300</x:v>
       </x:c>
       <x:c r="D3212" s="1">
         <x:v>0</x:v>
@@ -84848,10 +84848,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3212" s="1">
-        <x:v>6000</x:v>
+        <x:v>8850</x:v>
       </x:c>
       <x:c r="G3212" s="1">
-        <x:v>9000</x:v>
+        <x:v>11150</x:v>
       </x:c>
     </x:row>
     <x:row r="3213" spans="1:7">
@@ -85733,22 +85733,22 @@
         <x:v>3238</x:v>
       </x:c>
       <x:c r="B3251" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C3251" s="1">
-        <x:v>25500</x:v>
+        <x:v>420650</x:v>
       </x:c>
       <x:c r="D3251" s="1">
-        <x:v>0</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="E3251" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3251" s="1">
-        <x:v>0</x:v>
+        <x:v>448881</x:v>
       </x:c>
       <x:c r="G3251" s="1">
-        <x:v>25500</x:v>
+        <x:v>869712</x:v>
       </x:c>
     </x:row>
     <x:row r="3252" spans="1:7">
@@ -85756,22 +85756,22 @@
         <x:v>3238</x:v>
       </x:c>
       <x:c r="B3252" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C3252" s="1">
-        <x:v>420650</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D3252" s="1">
-        <x:v>181</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3252" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3252" s="1">
-        <x:v>448881</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3252" s="1">
-        <x:v>869712</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="3253" spans="1:7">
@@ -87550,22 +87550,22 @@
         <x:v>3316</x:v>
       </x:c>
       <x:c r="B3330" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="C3330" s="1">
-        <x:v>332220</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D3330" s="1">
-        <x:v>0</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E3330" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3330" s="1">
-        <x:v>299023</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3330" s="1">
-        <x:v>631243</x:v>
+        <x:v>15063</x:v>
       </x:c>
     </x:row>
     <x:row r="3331" spans="1:7">
@@ -87596,22 +87596,22 @@
         <x:v>3316</x:v>
       </x:c>
       <x:c r="B3332" s="1" t="s">
-        <x:v>256</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C3332" s="1">
-        <x:v>15000</x:v>
+        <x:v>332220</x:v>
       </x:c>
       <x:c r="D3332" s="1">
-        <x:v>63</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3332" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3332" s="1">
-        <x:v>0</x:v>
+        <x:v>299023</x:v>
       </x:c>
       <x:c r="G3332" s="1">
-        <x:v>15063</x:v>
+        <x:v>631243</x:v>
       </x:c>
     </x:row>
     <x:row r="3333" spans="1:7">
@@ -88746,10 +88746,10 @@
         <x:v>3363</x:v>
       </x:c>
       <x:c r="B3382" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C3382" s="1">
-        <x:v>15000</x:v>
+        <x:v>41550</x:v>
       </x:c>
       <x:c r="D3382" s="1">
         <x:v>0</x:v>
@@ -88758,10 +88758,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3382" s="1">
-        <x:v>0</x:v>
+        <x:v>6500</x:v>
       </x:c>
       <x:c r="G3382" s="1">
-        <x:v>15000</x:v>
+        <x:v>48050</x:v>
       </x:c>
     </x:row>
     <x:row r="3383" spans="1:7">
@@ -88769,10 +88769,10 @@
         <x:v>3363</x:v>
       </x:c>
       <x:c r="B3383" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C3383" s="1">
-        <x:v>41550</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D3383" s="1">
         <x:v>0</x:v>
@@ -88781,10 +88781,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3383" s="1">
-        <x:v>6500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3383" s="1">
-        <x:v>48050</x:v>
+        <x:v>15000</x:v>
       </x:c>
     </x:row>
     <x:row r="3384" spans="1:7">
@@ -89459,22 +89459,22 @@
         <x:v>3391</x:v>
       </x:c>
       <x:c r="B3413" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C3413" s="1">
-        <x:v>0</x:v>
+        <x:v>38500</x:v>
       </x:c>
       <x:c r="D3413" s="1">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3413" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3413" s="1">
-        <x:v>10700</x:v>
+        <x:v>26250</x:v>
       </x:c>
       <x:c r="G3413" s="1">
-        <x:v>10701</x:v>
+        <x:v>64750</x:v>
       </x:c>
     </x:row>
     <x:row r="3414" spans="1:7">
@@ -89482,22 +89482,22 @@
         <x:v>3391</x:v>
       </x:c>
       <x:c r="B3414" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C3414" s="1">
-        <x:v>38500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3414" s="1">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E3414" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3414" s="1">
-        <x:v>26250</x:v>
+        <x:v>10700</x:v>
       </x:c>
       <x:c r="G3414" s="1">
-        <x:v>64750</x:v>
+        <x:v>10701</x:v>
       </x:c>
     </x:row>
     <x:row r="3415" spans="1:7">
@@ -90241,22 +90241,22 @@
         <x:v>3421</x:v>
       </x:c>
       <x:c r="B3447" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C3447" s="1">
-        <x:v>0</x:v>
+        <x:v>47850</x:v>
       </x:c>
       <x:c r="D3447" s="1">
-        <x:v>59</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3447" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3447" s="1">
-        <x:v>0</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G3447" s="1">
-        <x:v>59</x:v>
+        <x:v>52850</x:v>
       </x:c>
     </x:row>
     <x:row r="3448" spans="1:7">
@@ -90264,22 +90264,22 @@
         <x:v>3421</x:v>
       </x:c>
       <x:c r="B3448" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C3448" s="1">
-        <x:v>47850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3448" s="1">
-        <x:v>0</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3448" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3448" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3448" s="1">
-        <x:v>52850</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="3449" spans="1:7">
@@ -90494,10 +90494,10 @@
         <x:v>3431</x:v>
       </x:c>
       <x:c r="B3458" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C3458" s="1">
-        <x:v>22500</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D3458" s="1">
         <x:v>0</x:v>
@@ -90509,7 +90509,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G3458" s="1">
-        <x:v>22500</x:v>
+        <x:v>3000</x:v>
       </x:c>
     </x:row>
     <x:row r="3459" spans="1:7">
@@ -90517,10 +90517,10 @@
         <x:v>3431</x:v>
       </x:c>
       <x:c r="B3459" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C3459" s="1">
-        <x:v>3000</x:v>
+        <x:v>22500</x:v>
       </x:c>
       <x:c r="D3459" s="1">
         <x:v>0</x:v>
@@ -90532,7 +90532,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G3459" s="1">
-        <x:v>3000</x:v>
+        <x:v>22500</x:v>
       </x:c>
     </x:row>
     <x:row r="3460" spans="1:7">

--- a/reports/pro-oil/pro-oil-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-oil/pro-oil-candidate-lobby-lifetime-report.xlsx
@@ -19209,10 +19209,10 @@
         <x:v>412</x:v>
       </x:c>
       <x:c r="B358" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C358" s="1">
-        <x:v>163000</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D358" s="1">
         <x:v>0</x:v>
@@ -19221,10 +19221,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F358" s="1">
-        <x:v>82550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G358" s="1">
-        <x:v>245550</x:v>
+        <x:v>15000</x:v>
       </x:c>
     </x:row>
     <x:row r="359" spans="1:7">
@@ -19232,10 +19232,10 @@
         <x:v>412</x:v>
       </x:c>
       <x:c r="B359" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C359" s="1">
-        <x:v>15000</x:v>
+        <x:v>163000</x:v>
       </x:c>
       <x:c r="D359" s="1">
         <x:v>0</x:v>
@@ -19244,10 +19244,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F359" s="1">
-        <x:v>0</x:v>
+        <x:v>82550</x:v>
       </x:c>
       <x:c r="G359" s="1">
-        <x:v>15000</x:v>
+        <x:v>245550</x:v>
       </x:c>
     </x:row>
     <x:row r="360" spans="1:7">
@@ -21003,10 +21003,10 @@
         <x:v>488</x:v>
       </x:c>
       <x:c r="B436" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C436" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D436" s="1">
         <x:v>0</x:v>
@@ -21015,10 +21015,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F436" s="1">
-        <x:v>13450</x:v>
+        <x:v>40350</x:v>
       </x:c>
       <x:c r="G436" s="1">
-        <x:v>13500</x:v>
+        <x:v>40350</x:v>
       </x:c>
     </x:row>
     <x:row r="437" spans="1:7">
@@ -21026,11 +21026,11 @@
         <x:v>488</x:v>
       </x:c>
       <x:c r="B437" s="1" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C437" s="1">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="C437" s="1">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="D437" s="1">
         <x:v>0</x:v>
       </x:c>
@@ -21038,10 +21038,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F437" s="1">
-        <x:v>40350</x:v>
+        <x:v>13450</x:v>
       </x:c>
       <x:c r="G437" s="1">
-        <x:v>40350</x:v>
+        <x:v>13500</x:v>
       </x:c>
     </x:row>
     <x:row r="438" spans="1:7">
@@ -46349,10 +46349,10 @@
         <x:v>1577</x:v>
       </x:c>
       <x:c r="B1538" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="C1538" s="1">
-        <x:v>0</x:v>
+        <x:v>82250</x:v>
       </x:c>
       <x:c r="D1538" s="1">
         <x:v>0</x:v>
@@ -46361,10 +46361,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1538" s="1">
-        <x:v>1000</x:v>
+        <x:v>9000</x:v>
       </x:c>
       <x:c r="G1538" s="1">
-        <x:v>1000</x:v>
+        <x:v>91250</x:v>
       </x:c>
     </x:row>
     <x:row r="1539" spans="1:7">
@@ -46372,10 +46372,10 @@
         <x:v>1577</x:v>
       </x:c>
       <x:c r="B1539" s="1" t="s">
-        <x:v>164</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C1539" s="1">
-        <x:v>82250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1539" s="1">
         <x:v>0</x:v>
@@ -46384,10 +46384,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1539" s="1">
-        <x:v>9000</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1539" s="1">
-        <x:v>91250</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="1540" spans="1:7">
@@ -47039,10 +47039,10 @@
         <x:v>1604</x:v>
       </x:c>
       <x:c r="B1568" s="1" t="s">
-        <x:v>416</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C1568" s="1">
-        <x:v>181700</x:v>
+        <x:v>8000</x:v>
       </x:c>
       <x:c r="D1568" s="1">
         <x:v>0</x:v>
@@ -47051,10 +47051,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1568" s="1">
-        <x:v>168050</x:v>
+        <x:v>66000</x:v>
       </x:c>
       <x:c r="G1568" s="1">
-        <x:v>349750</x:v>
+        <x:v>74000</x:v>
       </x:c>
     </x:row>
     <x:row r="1569" spans="1:7">
@@ -47062,10 +47062,10 @@
         <x:v>1604</x:v>
       </x:c>
       <x:c r="B1569" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="C1569" s="1">
-        <x:v>8000</x:v>
+        <x:v>181700</x:v>
       </x:c>
       <x:c r="D1569" s="1">
         <x:v>0</x:v>
@@ -47074,10 +47074,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1569" s="1">
-        <x:v>66000</x:v>
+        <x:v>168050</x:v>
       </x:c>
       <x:c r="G1569" s="1">
-        <x:v>74000</x:v>
+        <x:v>349750</x:v>
       </x:c>
     </x:row>
     <x:row r="1570" spans="1:7">
@@ -50650,10 +50650,10 @@
         <x:v>1758</x:v>
       </x:c>
       <x:c r="B1725" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C1725" s="1">
-        <x:v>2500</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="D1725" s="1">
         <x:v>0</x:v>
@@ -50662,10 +50662,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1725" s="1">
-        <x:v>16350</x:v>
+        <x:v>72700</x:v>
       </x:c>
       <x:c r="G1725" s="1">
-        <x:v>18850</x:v>
+        <x:v>73185</x:v>
       </x:c>
     </x:row>
     <x:row r="1726" spans="1:7">
@@ -50673,10 +50673,10 @@
         <x:v>1758</x:v>
       </x:c>
       <x:c r="B1726" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1726" s="1">
-        <x:v>485</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1726" s="1">
         <x:v>0</x:v>
@@ -50685,10 +50685,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1726" s="1">
-        <x:v>72700</x:v>
+        <x:v>16350</x:v>
       </x:c>
       <x:c r="G1726" s="1">
-        <x:v>73185</x:v>
+        <x:v>18850</x:v>
       </x:c>
     </x:row>
     <x:row r="1727" spans="1:7">
@@ -56239,10 +56239,10 @@
         <x:v>1994</x:v>
       </x:c>
       <x:c r="B1968" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1968" s="1">
-        <x:v>187150</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1968" s="1">
         <x:v>31</x:v>
@@ -56251,10 +56251,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1968" s="1">
-        <x:v>6150</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1968" s="1">
-        <x:v>193331</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="1969" spans="1:7">
@@ -56262,10 +56262,10 @@
         <x:v>1994</x:v>
       </x:c>
       <x:c r="B1969" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C1969" s="1">
-        <x:v>0</x:v>
+        <x:v>187150</x:v>
       </x:c>
       <x:c r="D1969" s="1">
         <x:v>31</x:v>
@@ -56274,10 +56274,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1969" s="1">
-        <x:v>0</x:v>
+        <x:v>6150</x:v>
       </x:c>
       <x:c r="G1969" s="1">
-        <x:v>31</x:v>
+        <x:v>193331</x:v>
       </x:c>
     </x:row>
     <x:row r="1970" spans="1:7">
@@ -59735,10 +59735,10 @@
         <x:v>2142</x:v>
       </x:c>
       <x:c r="B2120" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C2120" s="1">
-        <x:v>11000</x:v>
+        <x:v>960100</x:v>
       </x:c>
       <x:c r="D2120" s="1">
         <x:v>0</x:v>
@@ -59747,10 +59747,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2120" s="1">
-        <x:v>25550</x:v>
+        <x:v>882230</x:v>
       </x:c>
       <x:c r="G2120" s="1">
-        <x:v>36550</x:v>
+        <x:v>1842330</x:v>
       </x:c>
     </x:row>
     <x:row r="2121" spans="1:7">
@@ -59758,10 +59758,10 @@
         <x:v>2142</x:v>
       </x:c>
       <x:c r="B2121" s="1" t="s">
-        <x:v>190</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C2121" s="1">
-        <x:v>960100</x:v>
+        <x:v>11000</x:v>
       </x:c>
       <x:c r="D2121" s="1">
         <x:v>0</x:v>
@@ -59770,10 +59770,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2121" s="1">
-        <x:v>882230</x:v>
+        <x:v>25550</x:v>
       </x:c>
       <x:c r="G2121" s="1">
-        <x:v>1842330</x:v>
+        <x:v>36550</x:v>
       </x:c>
     </x:row>
     <x:row r="2122" spans="1:7">
@@ -72293,10 +72293,10 @@
         <x:v>2683</x:v>
       </x:c>
       <x:c r="B2666" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C2666" s="1">
-        <x:v>7061</x:v>
+        <x:v>409250</x:v>
       </x:c>
       <x:c r="D2666" s="1">
         <x:v>0</x:v>
@@ -72305,10 +72305,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2666" s="1">
-        <x:v>23500</x:v>
+        <x:v>159800</x:v>
       </x:c>
       <x:c r="G2666" s="1">
-        <x:v>30561</x:v>
+        <x:v>569050</x:v>
       </x:c>
     </x:row>
     <x:row r="2667" spans="1:7">
@@ -72316,10 +72316,10 @@
         <x:v>2683</x:v>
       </x:c>
       <x:c r="B2667" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C2667" s="1">
-        <x:v>409250</x:v>
+        <x:v>7061</x:v>
       </x:c>
       <x:c r="D2667" s="1">
         <x:v>0</x:v>
@@ -72328,10 +72328,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2667" s="1">
-        <x:v>159800</x:v>
+        <x:v>23500</x:v>
       </x:c>
       <x:c r="G2667" s="1">
-        <x:v>569050</x:v>
+        <x:v>30561</x:v>
       </x:c>
     </x:row>
     <x:row r="2668" spans="1:7">
@@ -72454,10 +72454,10 @@
         <x:v>2689</x:v>
       </x:c>
       <x:c r="B2673" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C2673" s="1">
-        <x:v>7000</x:v>
+        <x:v>139000</x:v>
       </x:c>
       <x:c r="D2673" s="1">
         <x:v>0</x:v>
@@ -72466,10 +72466,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2673" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G2673" s="1">
-        <x:v>7000</x:v>
+        <x:v>139500</x:v>
       </x:c>
     </x:row>
     <x:row r="2674" spans="1:7">
@@ -72477,10 +72477,10 @@
         <x:v>2689</x:v>
       </x:c>
       <x:c r="B2674" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C2674" s="1">
-        <x:v>139000</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D2674" s="1">
         <x:v>0</x:v>
@@ -72489,10 +72489,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2674" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2674" s="1">
-        <x:v>139500</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="2675" spans="1:7">
@@ -75260,10 +75260,10 @@
         <x:v>2809</x:v>
       </x:c>
       <x:c r="B2795" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C2795" s="1">
-        <x:v>15000</x:v>
+        <x:v>163800</x:v>
       </x:c>
       <x:c r="D2795" s="1">
         <x:v>0</x:v>
@@ -75272,10 +75272,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2795" s="1">
-        <x:v>111650</x:v>
+        <x:v>277645</x:v>
       </x:c>
       <x:c r="G2795" s="1">
-        <x:v>126650</x:v>
+        <x:v>441445</x:v>
       </x:c>
     </x:row>
     <x:row r="2796" spans="1:7">
@@ -75283,10 +75283,10 @@
         <x:v>2809</x:v>
       </x:c>
       <x:c r="B2796" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C2796" s="1">
-        <x:v>206766</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D2796" s="1">
         <x:v>0</x:v>
@@ -75295,10 +75295,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2796" s="1">
-        <x:v>286825</x:v>
+        <x:v>111650</x:v>
       </x:c>
       <x:c r="G2796" s="1">
-        <x:v>493591</x:v>
+        <x:v>126650</x:v>
       </x:c>
     </x:row>
     <x:row r="2797" spans="1:7">
@@ -75306,10 +75306,10 @@
         <x:v>2809</x:v>
       </x:c>
       <x:c r="B2797" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C2797" s="1">
-        <x:v>163800</x:v>
+        <x:v>206766</x:v>
       </x:c>
       <x:c r="D2797" s="1">
         <x:v>0</x:v>
@@ -75318,10 +75318,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2797" s="1">
-        <x:v>277645</x:v>
+        <x:v>286825</x:v>
       </x:c>
       <x:c r="G2797" s="1">
-        <x:v>441445</x:v>
+        <x:v>493591</x:v>
       </x:c>
     </x:row>
     <x:row r="2798" spans="1:7">
@@ -76801,10 +76801,10 @@
         <x:v>2873</x:v>
       </x:c>
       <x:c r="B2862" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C2862" s="1">
-        <x:v>15000</x:v>
+        <x:v>102350</x:v>
       </x:c>
       <x:c r="D2862" s="1">
         <x:v>0</x:v>
@@ -76813,10 +76813,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2862" s="1">
-        <x:v>5000</x:v>
+        <x:v>106550</x:v>
       </x:c>
       <x:c r="G2862" s="1">
-        <x:v>20000</x:v>
+        <x:v>208900</x:v>
       </x:c>
     </x:row>
     <x:row r="2863" spans="1:7">
@@ -76824,10 +76824,10 @@
         <x:v>2873</x:v>
       </x:c>
       <x:c r="B2863" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C2863" s="1">
-        <x:v>102350</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D2863" s="1">
         <x:v>0</x:v>
@@ -76836,10 +76836,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2863" s="1">
-        <x:v>106550</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G2863" s="1">
-        <x:v>208900</x:v>
+        <x:v>20000</x:v>
       </x:c>
     </x:row>
     <x:row r="2864" spans="1:7">
@@ -78158,10 +78158,10 @@
         <x:v>2931</x:v>
       </x:c>
       <x:c r="B2921" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C2921" s="1">
-        <x:v>37500</x:v>
+        <x:v>206000</x:v>
       </x:c>
       <x:c r="D2921" s="1">
         <x:v>0</x:v>
@@ -78170,10 +78170,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2921" s="1">
-        <x:v>8000</x:v>
+        <x:v>45600</x:v>
       </x:c>
       <x:c r="G2921" s="1">
-        <x:v>45500</x:v>
+        <x:v>251600</x:v>
       </x:c>
     </x:row>
     <x:row r="2922" spans="1:7">
@@ -78181,10 +78181,10 @@
         <x:v>2931</x:v>
       </x:c>
       <x:c r="B2922" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C2922" s="1">
-        <x:v>206000</x:v>
+        <x:v>37500</x:v>
       </x:c>
       <x:c r="D2922" s="1">
         <x:v>0</x:v>
@@ -78193,10 +78193,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2922" s="1">
-        <x:v>45600</x:v>
+        <x:v>8000</x:v>
       </x:c>
       <x:c r="G2922" s="1">
-        <x:v>251600</x:v>
+        <x:v>45500</x:v>
       </x:c>
     </x:row>
     <x:row r="2923" spans="1:7">
@@ -78572,10 +78572,10 @@
         <x:v>2948</x:v>
       </x:c>
       <x:c r="B2939" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C2939" s="1">
-        <x:v>99950</x:v>
+        <x:v>12000</x:v>
       </x:c>
       <x:c r="D2939" s="1">
         <x:v>0</x:v>
@@ -78584,10 +78584,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2939" s="1">
-        <x:v>6650</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2939" s="1">
-        <x:v>106600</x:v>
+        <x:v>12000</x:v>
       </x:c>
     </x:row>
     <x:row r="2940" spans="1:7">
@@ -78595,10 +78595,10 @@
         <x:v>2948</x:v>
       </x:c>
       <x:c r="B2940" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C2940" s="1">
-        <x:v>12000</x:v>
+        <x:v>99950</x:v>
       </x:c>
       <x:c r="D2940" s="1">
         <x:v>0</x:v>
@@ -78607,10 +78607,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2940" s="1">
-        <x:v>0</x:v>
+        <x:v>6650</x:v>
       </x:c>
       <x:c r="G2940" s="1">
-        <x:v>12000</x:v>
+        <x:v>106600</x:v>
       </x:c>
     </x:row>
     <x:row r="2941" spans="1:7">
@@ -78618,22 +78618,22 @@
         <x:v>2949</x:v>
       </x:c>
       <x:c r="B2941" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="C2941" s="1">
-        <x:v>0</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="D2941" s="1">
-        <x:v>59</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E2941" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2941" s="1">
-        <x:v>0</x:v>
+        <x:v>4950</x:v>
       </x:c>
       <x:c r="G2941" s="1">
-        <x:v>59</x:v>
+        <x:v>14950</x:v>
       </x:c>
     </x:row>
     <x:row r="2942" spans="1:7">
@@ -78641,22 +78641,22 @@
         <x:v>2949</x:v>
       </x:c>
       <x:c r="B2942" s="1" t="s">
-        <x:v>258</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C2942" s="1">
-        <x:v>10000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D2942" s="1">
-        <x:v>0</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E2942" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2942" s="1">
-        <x:v>4950</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2942" s="1">
-        <x:v>14950</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="2943" spans="1:7">
@@ -79262,10 +79262,10 @@
         <x:v>2976</x:v>
       </x:c>
       <x:c r="B2969" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>747</x:v>
       </x:c>
       <x:c r="C2969" s="1">
-        <x:v>5000</x:v>
+        <x:v>286800</x:v>
       </x:c>
       <x:c r="D2969" s="1">
         <x:v>0</x:v>
@@ -79274,10 +79274,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2969" s="1">
-        <x:v>0</x:v>
+        <x:v>75150</x:v>
       </x:c>
       <x:c r="G2969" s="1">
-        <x:v>5000</x:v>
+        <x:v>361950</x:v>
       </x:c>
     </x:row>
     <x:row r="2970" spans="1:7">
@@ -79285,10 +79285,10 @@
         <x:v>2976</x:v>
       </x:c>
       <x:c r="B2970" s="1" t="s">
-        <x:v>747</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C2970" s="1">
-        <x:v>286800</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D2970" s="1">
         <x:v>0</x:v>
@@ -79297,10 +79297,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2970" s="1">
-        <x:v>75150</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2970" s="1">
-        <x:v>361950</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="2971" spans="1:7">
@@ -81608,10 +81608,10 @@
         <x:v>3075</x:v>
       </x:c>
       <x:c r="B3071" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C3071" s="1">
-        <x:v>5000</x:v>
+        <x:v>10500</x:v>
       </x:c>
       <x:c r="D3071" s="1">
         <x:v>0</x:v>
@@ -81620,10 +81620,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3071" s="1">
-        <x:v>33600</x:v>
+        <x:v>31300</x:v>
       </x:c>
       <x:c r="G3071" s="1">
-        <x:v>38600</x:v>
+        <x:v>41800</x:v>
       </x:c>
     </x:row>
     <x:row r="3072" spans="1:7">
@@ -81631,10 +81631,10 @@
         <x:v>3075</x:v>
       </x:c>
       <x:c r="B3072" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C3072" s="1">
-        <x:v>10500</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D3072" s="1">
         <x:v>0</x:v>
@@ -81643,10 +81643,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3072" s="1">
-        <x:v>31300</x:v>
+        <x:v>33600</x:v>
       </x:c>
       <x:c r="G3072" s="1">
-        <x:v>41800</x:v>
+        <x:v>38600</x:v>
       </x:c>
     </x:row>
     <x:row r="3073" spans="1:7">
@@ -81953,7 +81953,7 @@
         <x:v>3086</x:v>
       </x:c>
       <x:c r="B3086" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C3086" s="1">
         <x:v>1000</x:v>
@@ -81965,10 +81965,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3086" s="1">
-        <x:v>0</x:v>
+        <x:v>4750</x:v>
       </x:c>
       <x:c r="G3086" s="1">
-        <x:v>1000</x:v>
+        <x:v>5750</x:v>
       </x:c>
     </x:row>
     <x:row r="3087" spans="1:7">
@@ -81976,7 +81976,7 @@
         <x:v>3086</x:v>
       </x:c>
       <x:c r="B3087" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C3087" s="1">
         <x:v>1000</x:v>
@@ -81988,10 +81988,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3087" s="1">
-        <x:v>4750</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3087" s="1">
-        <x:v>5750</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="3088" spans="1:7">
@@ -83011,10 +83011,10 @@
         <x:v>3130</x:v>
       </x:c>
       <x:c r="B3132" s="1" t="s">
-        <x:v>155</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C3132" s="1">
-        <x:v>48000</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D3132" s="1">
         <x:v>0</x:v>
@@ -83023,10 +83023,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3132" s="1">
-        <x:v>38300</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G3132" s="1">
-        <x:v>86300</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="3133" spans="1:7">
@@ -83034,10 +83034,10 @@
         <x:v>3130</x:v>
       </x:c>
       <x:c r="B3133" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="C3133" s="1">
-        <x:v>5000</x:v>
+        <x:v>48000</x:v>
       </x:c>
       <x:c r="D3133" s="1">
         <x:v>0</x:v>
@@ -83046,10 +83046,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3133" s="1">
-        <x:v>250</x:v>
+        <x:v>38300</x:v>
       </x:c>
       <x:c r="G3133" s="1">
-        <x:v>5250</x:v>
+        <x:v>86300</x:v>
       </x:c>
     </x:row>
     <x:row r="3134" spans="1:7">
@@ -83379,10 +83379,10 @@
         <x:v>3142</x:v>
       </x:c>
       <x:c r="B3148" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C3148" s="1">
-        <x:v>157500</x:v>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="D3148" s="1">
         <x:v>0</x:v>
@@ -83391,10 +83391,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3148" s="1">
-        <x:v>45517</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="G3148" s="1">
-        <x:v>203017</x:v>
+        <x:v>26000</x:v>
       </x:c>
     </x:row>
     <x:row r="3149" spans="1:7">
@@ -83402,10 +83402,10 @@
         <x:v>3142</x:v>
       </x:c>
       <x:c r="B3149" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C3149" s="1">
-        <x:v>20000</x:v>
+        <x:v>157500</x:v>
       </x:c>
       <x:c r="D3149" s="1">
         <x:v>0</x:v>
@@ -83414,10 +83414,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3149" s="1">
-        <x:v>6000</x:v>
+        <x:v>45517</x:v>
       </x:c>
       <x:c r="G3149" s="1">
-        <x:v>26000</x:v>
+        <x:v>203017</x:v>
       </x:c>
     </x:row>
     <x:row r="3150" spans="1:7">
@@ -85242,22 +85242,22 @@
         <x:v>3219</x:v>
       </x:c>
       <x:c r="B3229" s="1" t="s">
-        <x:v>297</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C3229" s="1">
-        <x:v>533500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3229" s="1">
-        <x:v>295</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3229" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3229" s="1">
-        <x:v>227847</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3229" s="1">
-        <x:v>761642</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="3230" spans="1:7">
@@ -85265,22 +85265,22 @@
         <x:v>3219</x:v>
       </x:c>
       <x:c r="B3230" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="C3230" s="1">
-        <x:v>0</x:v>
+        <x:v>533500</x:v>
       </x:c>
       <x:c r="D3230" s="1">
-        <x:v>59</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E3230" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3230" s="1">
-        <x:v>0</x:v>
+        <x:v>227847</x:v>
       </x:c>
       <x:c r="G3230" s="1">
-        <x:v>59</x:v>
+        <x:v>761642</x:v>
       </x:c>
     </x:row>
     <x:row r="3231" spans="1:7">
@@ -85656,10 +85656,10 @@
         <x:v>3235</x:v>
       </x:c>
       <x:c r="B3247" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C3247" s="1">
-        <x:v>29500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3247" s="1">
         <x:v>0</x:v>
@@ -85668,10 +85668,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3247" s="1">
-        <x:v>12550</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G3247" s="1">
-        <x:v>42050</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="3248" spans="1:7">
@@ -85679,10 +85679,10 @@
         <x:v>3235</x:v>
       </x:c>
       <x:c r="B3248" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C3248" s="1">
-        <x:v>0</x:v>
+        <x:v>29500</x:v>
       </x:c>
       <x:c r="D3248" s="1">
         <x:v>0</x:v>
@@ -85691,10 +85691,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3248" s="1">
-        <x:v>1000</x:v>
+        <x:v>12550</x:v>
       </x:c>
       <x:c r="G3248" s="1">
-        <x:v>1000</x:v>
+        <x:v>42050</x:v>
       </x:c>
     </x:row>
     <x:row r="3249" spans="1:7">
@@ -87680,22 +87680,22 @@
         <x:v>3321</x:v>
       </x:c>
       <x:c r="B3335" s="1" t="s">
-        <x:v>256</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C3335" s="1">
-        <x:v>15000</x:v>
+        <x:v>332220</x:v>
       </x:c>
       <x:c r="D3335" s="1">
-        <x:v>63</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3335" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3335" s="1">
-        <x:v>0</x:v>
+        <x:v>299023</x:v>
       </x:c>
       <x:c r="G3335" s="1">
-        <x:v>15063</x:v>
+        <x:v>631243</x:v>
       </x:c>
     </x:row>
     <x:row r="3336" spans="1:7">
@@ -87703,22 +87703,22 @@
         <x:v>3321</x:v>
       </x:c>
       <x:c r="B3336" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C3336" s="1">
-        <x:v>332220</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3336" s="1">
-        <x:v>0</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3336" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3336" s="1">
-        <x:v>299023</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3336" s="1">
-        <x:v>631243</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="3337" spans="1:7">
@@ -87726,13 +87726,13 @@
         <x:v>3321</x:v>
       </x:c>
       <x:c r="B3337" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="C3337" s="1">
-        <x:v>0</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D3337" s="1">
-        <x:v>59</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E3337" s="1">
         <x:v>0</x:v>
@@ -87741,7 +87741,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G3337" s="1">
-        <x:v>59</x:v>
+        <x:v>15063</x:v>
       </x:c>
     </x:row>
     <x:row r="3338" spans="1:7">
@@ -90141,22 +90141,22 @@
         <x:v>3418</x:v>
       </x:c>
       <x:c r="B3442" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C3442" s="1">
-        <x:v>72750</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3442" s="1">
-        <x:v>295</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3442" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3442" s="1">
-        <x:v>25450</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3442" s="1">
-        <x:v>98495</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="3443" spans="1:7">
@@ -90164,22 +90164,22 @@
         <x:v>3418</x:v>
       </x:c>
       <x:c r="B3443" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C3443" s="1">
-        <x:v>0</x:v>
+        <x:v>72750</x:v>
       </x:c>
       <x:c r="D3443" s="1">
-        <x:v>59</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E3443" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3443" s="1">
-        <x:v>0</x:v>
+        <x:v>25450</x:v>
       </x:c>
       <x:c r="G3443" s="1">
-        <x:v>59</x:v>
+        <x:v>98495</x:v>
       </x:c>
     </x:row>
     <x:row r="3444" spans="1:7">
@@ -90233,10 +90233,10 @@
         <x:v>3421</x:v>
       </x:c>
       <x:c r="B3446" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C3446" s="1">
-        <x:v>19500</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="D3446" s="1">
         <x:v>0</x:v>
@@ -90245,10 +90245,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3446" s="1">
-        <x:v>8650</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3446" s="1">
-        <x:v>28150</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="3447" spans="1:7">
@@ -90256,10 +90256,10 @@
         <x:v>3421</x:v>
       </x:c>
       <x:c r="B3447" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C3447" s="1">
-        <x:v>500</x:v>
+        <x:v>19500</x:v>
       </x:c>
       <x:c r="D3447" s="1">
         <x:v>0</x:v>
@@ -90268,10 +90268,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3447" s="1">
-        <x:v>0</x:v>
+        <x:v>8650</x:v>
       </x:c>
       <x:c r="G3447" s="1">
-        <x:v>500</x:v>
+        <x:v>28150</x:v>
       </x:c>
     </x:row>
     <x:row r="3448" spans="1:7">
@@ -90371,22 +90371,22 @@
         <x:v>3426</x:v>
       </x:c>
       <x:c r="B3452" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C3452" s="1">
-        <x:v>47850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3452" s="1">
-        <x:v>0</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3452" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3452" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3452" s="1">
-        <x:v>52850</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="3453" spans="1:7">
@@ -90394,22 +90394,22 @@
         <x:v>3426</x:v>
       </x:c>
       <x:c r="B3453" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C3453" s="1">
-        <x:v>0</x:v>
+        <x:v>47850</x:v>
       </x:c>
       <x:c r="D3453" s="1">
-        <x:v>59</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3453" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3453" s="1">
-        <x:v>0</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G3453" s="1">
-        <x:v>59</x:v>
+        <x:v>52850</x:v>
       </x:c>
     </x:row>
     <x:row r="3454" spans="1:7">
@@ -90624,10 +90624,10 @@
         <x:v>3436</x:v>
       </x:c>
       <x:c r="B3463" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C3463" s="1">
-        <x:v>3000</x:v>
+        <x:v>22500</x:v>
       </x:c>
       <x:c r="D3463" s="1">
         <x:v>0</x:v>
@@ -90639,7 +90639,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G3463" s="1">
-        <x:v>3000</x:v>
+        <x:v>22500</x:v>
       </x:c>
     </x:row>
     <x:row r="3464" spans="1:7">
@@ -90647,22 +90647,22 @@
         <x:v>3436</x:v>
       </x:c>
       <x:c r="B3464" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="C3464" s="1">
-        <x:v>22500</x:v>
+        <x:v>437150</x:v>
       </x:c>
       <x:c r="D3464" s="1">
-        <x:v>0</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="E3464" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3464" s="1">
-        <x:v>0</x:v>
+        <x:v>348550</x:v>
       </x:c>
       <x:c r="G3464" s="1">
-        <x:v>22500</x:v>
+        <x:v>786168</x:v>
       </x:c>
     </x:row>
     <x:row r="3465" spans="1:7">
@@ -90670,22 +90670,22 @@
         <x:v>3436</x:v>
       </x:c>
       <x:c r="B3465" s="1" t="s">
-        <x:v>416</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C3465" s="1">
-        <x:v>437150</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D3465" s="1">
-        <x:v>468</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3465" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3465" s="1">
-        <x:v>348550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3465" s="1">
-        <x:v>786168</x:v>
+        <x:v>3000</x:v>
       </x:c>
     </x:row>
     <x:row r="3466" spans="1:7">
@@ -91383,22 +91383,22 @@
         <x:v>3466</x:v>
       </x:c>
       <x:c r="B3496" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C3496" s="1">
-        <x:v>0</x:v>
+        <x:v>265983</x:v>
       </x:c>
       <x:c r="D3496" s="1">
-        <x:v>59</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="E3496" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3496" s="1">
-        <x:v>44000</x:v>
+        <x:v>126150</x:v>
       </x:c>
       <x:c r="G3496" s="1">
-        <x:v>44059</x:v>
+        <x:v>392310</x:v>
       </x:c>
     </x:row>
     <x:row r="3497" spans="1:7">
@@ -91406,22 +91406,22 @@
         <x:v>3466</x:v>
       </x:c>
       <x:c r="B3497" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C3497" s="1">
-        <x:v>265983</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3497" s="1">
-        <x:v>177</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3497" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3497" s="1">
-        <x:v>126150</x:v>
+        <x:v>44000</x:v>
       </x:c>
       <x:c r="G3497" s="1">
-        <x:v>392310</x:v>
+        <x:v>44059</x:v>
       </x:c>
     </x:row>
     <x:row r="3498" spans="1:7">
@@ -92395,10 +92395,10 @@
         <x:v>3507</x:v>
       </x:c>
       <x:c r="B3540" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C3540" s="1">
-        <x:v>130750</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3540" s="1">
         <x:v>7</x:v>
@@ -92407,10 +92407,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3540" s="1">
-        <x:v>83750</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3540" s="1">
-        <x:v>214507</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="3541" spans="1:7">
@@ -92418,10 +92418,10 @@
         <x:v>3507</x:v>
       </x:c>
       <x:c r="B3541" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C3541" s="1">
-        <x:v>0</x:v>
+        <x:v>130750</x:v>
       </x:c>
       <x:c r="D3541" s="1">
         <x:v>7</x:v>
@@ -92430,10 +92430,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3541" s="1">
-        <x:v>0</x:v>
+        <x:v>83750</x:v>
       </x:c>
       <x:c r="G3541" s="1">
-        <x:v>7</x:v>
+        <x:v>214507</x:v>
       </x:c>
     </x:row>
     <x:row r="3542" spans="1:7">

--- a/reports/pro-oil/pro-oil-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-oil/pro-oil-candidate-lobby-lifetime-report.xlsx
@@ -19347,10 +19347,10 @@
         <x:v>418</x:v>
       </x:c>
       <x:c r="B364" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C364" s="1">
-        <x:v>107540</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D364" s="1">
         <x:v>0</x:v>
@@ -19359,10 +19359,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F364" s="1">
-        <x:v>59170</x:v>
+        <x:v>25150</x:v>
       </x:c>
       <x:c r="G364" s="1">
-        <x:v>166710</x:v>
+        <x:v>28150</x:v>
       </x:c>
     </x:row>
     <x:row r="365" spans="1:7">
@@ -19370,10 +19370,10 @@
         <x:v>418</x:v>
       </x:c>
       <x:c r="B365" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C365" s="1">
-        <x:v>3000</x:v>
+        <x:v>107540</x:v>
       </x:c>
       <x:c r="D365" s="1">
         <x:v>0</x:v>
@@ -19382,10 +19382,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F365" s="1">
-        <x:v>25150</x:v>
+        <x:v>59170</x:v>
       </x:c>
       <x:c r="G365" s="1">
-        <x:v>28150</x:v>
+        <x:v>166710</x:v>
       </x:c>
     </x:row>
     <x:row r="366" spans="1:7">
@@ -21003,11 +21003,11 @@
         <x:v>488</x:v>
       </x:c>
       <x:c r="B436" s="1" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C436" s="1">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="C436" s="1">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="D436" s="1">
         <x:v>0</x:v>
       </x:c>
@@ -21015,10 +21015,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F436" s="1">
-        <x:v>40350</x:v>
+        <x:v>13450</x:v>
       </x:c>
       <x:c r="G436" s="1">
-        <x:v>40350</x:v>
+        <x:v>13500</x:v>
       </x:c>
     </x:row>
     <x:row r="437" spans="1:7">
@@ -21026,10 +21026,10 @@
         <x:v>488</x:v>
       </x:c>
       <x:c r="B437" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C437" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D437" s="1">
         <x:v>0</x:v>
@@ -21038,10 +21038,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F437" s="1">
-        <x:v>13450</x:v>
+        <x:v>40350</x:v>
       </x:c>
       <x:c r="G437" s="1">
-        <x:v>13500</x:v>
+        <x:v>40350</x:v>
       </x:c>
     </x:row>
     <x:row r="438" spans="1:7">
@@ -27190,22 +27190,22 @@
         <x:v>757</x:v>
       </x:c>
       <x:c r="B705" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>747</x:v>
       </x:c>
       <x:c r="C705" s="1">
-        <x:v>25500</x:v>
+        <x:v>418533</x:v>
       </x:c>
       <x:c r="D705" s="1">
-        <x:v>0</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E705" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F705" s="1">
-        <x:v>0</x:v>
+        <x:v>51350</x:v>
       </x:c>
       <x:c r="G705" s="1">
-        <x:v>25500</x:v>
+        <x:v>470001</x:v>
       </x:c>
     </x:row>
     <x:row r="706" spans="1:7">
@@ -27213,22 +27213,22 @@
         <x:v>757</x:v>
       </x:c>
       <x:c r="B706" s="1" t="s">
-        <x:v>747</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C706" s="1">
-        <x:v>418533</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D706" s="1">
-        <x:v>118</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E706" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F706" s="1">
-        <x:v>51350</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G706" s="1">
-        <x:v>470001</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="707" spans="1:7">
@@ -31353,22 +31353,22 @@
         <x:v>934</x:v>
       </x:c>
       <x:c r="B886" s="1" t="s">
-        <x:v>297</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C886" s="1">
-        <x:v>0</x:v>
+        <x:v>91000</x:v>
       </x:c>
       <x:c r="D886" s="1">
-        <x:v>59</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E886" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F886" s="1">
-        <x:v>0</x:v>
+        <x:v>26100</x:v>
       </x:c>
       <x:c r="G886" s="1">
-        <x:v>59</x:v>
+        <x:v>117218</x:v>
       </x:c>
     </x:row>
     <x:row r="887" spans="1:7">
@@ -31376,22 +31376,22 @@
         <x:v>934</x:v>
       </x:c>
       <x:c r="B887" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="C887" s="1">
-        <x:v>91000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D887" s="1">
-        <x:v>118</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E887" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F887" s="1">
-        <x:v>26100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G887" s="1">
-        <x:v>117218</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="888" spans="1:7">
@@ -37563,10 +37563,10 @@
         <x:v>1200</x:v>
       </x:c>
       <x:c r="B1156" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C1156" s="1">
-        <x:v>752389</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1156" s="1">
         <x:v>0</x:v>
@@ -37575,10 +37575,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1156" s="1">
-        <x:v>418794</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="G1156" s="1">
-        <x:v>1171183</x:v>
+        <x:v>10000</x:v>
       </x:c>
     </x:row>
     <x:row r="1157" spans="1:7">
@@ -37586,10 +37586,10 @@
         <x:v>1200</x:v>
       </x:c>
       <x:c r="B1157" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1157" s="1">
-        <x:v>0</x:v>
+        <x:v>752389</x:v>
       </x:c>
       <x:c r="D1157" s="1">
         <x:v>0</x:v>
@@ -37598,10 +37598,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1157" s="1">
-        <x:v>10000</x:v>
+        <x:v>418794</x:v>
       </x:c>
       <x:c r="G1157" s="1">
-        <x:v>10000</x:v>
+        <x:v>1171183</x:v>
       </x:c>
     </x:row>
     <x:row r="1158" spans="1:7">
@@ -38782,10 +38782,10 @@
         <x:v>1250</x:v>
       </x:c>
       <x:c r="B1209" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C1209" s="1">
-        <x:v>12000</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D1209" s="1">
         <x:v>0</x:v>
@@ -38794,10 +38794,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1209" s="1">
-        <x:v>12450</x:v>
+        <x:v>50751</x:v>
       </x:c>
       <x:c r="G1209" s="1">
-        <x:v>24450</x:v>
+        <x:v>53751</x:v>
       </x:c>
     </x:row>
     <x:row r="1210" spans="1:7">
@@ -38805,10 +38805,10 @@
         <x:v>1250</x:v>
       </x:c>
       <x:c r="B1210" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C1210" s="1">
-        <x:v>3000</x:v>
+        <x:v>12000</x:v>
       </x:c>
       <x:c r="D1210" s="1">
         <x:v>0</x:v>
@@ -38817,10 +38817,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1210" s="1">
-        <x:v>50751</x:v>
+        <x:v>12450</x:v>
       </x:c>
       <x:c r="G1210" s="1">
-        <x:v>53751</x:v>
+        <x:v>24450</x:v>
       </x:c>
     </x:row>
     <x:row r="1211" spans="1:7">
@@ -47039,10 +47039,10 @@
         <x:v>1604</x:v>
       </x:c>
       <x:c r="B1568" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="C1568" s="1">
-        <x:v>8000</x:v>
+        <x:v>181700</x:v>
       </x:c>
       <x:c r="D1568" s="1">
         <x:v>0</x:v>
@@ -47051,10 +47051,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1568" s="1">
-        <x:v>66000</x:v>
+        <x:v>168050</x:v>
       </x:c>
       <x:c r="G1568" s="1">
-        <x:v>74000</x:v>
+        <x:v>349750</x:v>
       </x:c>
     </x:row>
     <x:row r="1569" spans="1:7">
@@ -47062,10 +47062,10 @@
         <x:v>1604</x:v>
       </x:c>
       <x:c r="B1569" s="1" t="s">
-        <x:v>416</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C1569" s="1">
-        <x:v>181700</x:v>
+        <x:v>8000</x:v>
       </x:c>
       <x:c r="D1569" s="1">
         <x:v>0</x:v>
@@ -47074,10 +47074,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1569" s="1">
-        <x:v>168050</x:v>
+        <x:v>66000</x:v>
       </x:c>
       <x:c r="G1569" s="1">
-        <x:v>349750</x:v>
+        <x:v>74000</x:v>
       </x:c>
     </x:row>
     <x:row r="1570" spans="1:7">
@@ -49684,10 +49684,10 @@
         <x:v>1717</x:v>
       </x:c>
       <x:c r="B1683" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C1683" s="1">
-        <x:v>0</x:v>
+        <x:v>27850</x:v>
       </x:c>
       <x:c r="D1683" s="1">
         <x:v>0</x:v>
@@ -49696,10 +49696,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1683" s="1">
-        <x:v>102225</x:v>
+        <x:v>19000</x:v>
       </x:c>
       <x:c r="G1683" s="1">
-        <x:v>102225</x:v>
+        <x:v>46850</x:v>
       </x:c>
     </x:row>
     <x:row r="1684" spans="1:7">
@@ -49707,10 +49707,10 @@
         <x:v>1717</x:v>
       </x:c>
       <x:c r="B1684" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C1684" s="1">
-        <x:v>27850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1684" s="1">
         <x:v>0</x:v>
@@ -49719,10 +49719,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1684" s="1">
-        <x:v>19000</x:v>
+        <x:v>102225</x:v>
       </x:c>
       <x:c r="G1684" s="1">
-        <x:v>46850</x:v>
+        <x:v>102225</x:v>
       </x:c>
     </x:row>
     <x:row r="1685" spans="1:7">
@@ -55618,22 +55618,22 @@
         <x:v>1968</x:v>
       </x:c>
       <x:c r="B1941" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="C1941" s="1">
-        <x:v>299950</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1941" s="1">
-        <x:v>295</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E1941" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1941" s="1">
-        <x:v>178350</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1941" s="1">
-        <x:v>478595</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="1942" spans="1:7">
@@ -55641,22 +55641,22 @@
         <x:v>1968</x:v>
       </x:c>
       <x:c r="B1942" s="1" t="s">
-        <x:v>155</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C1942" s="1">
-        <x:v>0</x:v>
+        <x:v>299950</x:v>
       </x:c>
       <x:c r="D1942" s="1">
-        <x:v>59</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E1942" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1942" s="1">
-        <x:v>0</x:v>
+        <x:v>178350</x:v>
       </x:c>
       <x:c r="G1942" s="1">
-        <x:v>59</x:v>
+        <x:v>478595</x:v>
       </x:c>
     </x:row>
     <x:row r="1943" spans="1:7">
@@ -56239,10 +56239,10 @@
         <x:v>1994</x:v>
       </x:c>
       <x:c r="B1968" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C1968" s="1">
-        <x:v>0</x:v>
+        <x:v>187150</x:v>
       </x:c>
       <x:c r="D1968" s="1">
         <x:v>31</x:v>
@@ -56251,10 +56251,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1968" s="1">
-        <x:v>0</x:v>
+        <x:v>6150</x:v>
       </x:c>
       <x:c r="G1968" s="1">
-        <x:v>31</x:v>
+        <x:v>193331</x:v>
       </x:c>
     </x:row>
     <x:row r="1969" spans="1:7">
@@ -56262,10 +56262,10 @@
         <x:v>1994</x:v>
       </x:c>
       <x:c r="B1969" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1969" s="1">
-        <x:v>187150</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1969" s="1">
         <x:v>31</x:v>
@@ -56274,10 +56274,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1969" s="1">
-        <x:v>6150</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1969" s="1">
-        <x:v>193331</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="1970" spans="1:7">
@@ -59735,10 +59735,10 @@
         <x:v>2142</x:v>
       </x:c>
       <x:c r="B2120" s="1" t="s">
-        <x:v>190</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C2120" s="1">
-        <x:v>960100</x:v>
+        <x:v>11000</x:v>
       </x:c>
       <x:c r="D2120" s="1">
         <x:v>0</x:v>
@@ -59747,10 +59747,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2120" s="1">
-        <x:v>882230</x:v>
+        <x:v>25550</x:v>
       </x:c>
       <x:c r="G2120" s="1">
-        <x:v>1842330</x:v>
+        <x:v>36550</x:v>
       </x:c>
     </x:row>
     <x:row r="2121" spans="1:7">
@@ -59758,10 +59758,10 @@
         <x:v>2142</x:v>
       </x:c>
       <x:c r="B2121" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C2121" s="1">
-        <x:v>11000</x:v>
+        <x:v>960100</x:v>
       </x:c>
       <x:c r="D2121" s="1">
         <x:v>0</x:v>
@@ -59770,10 +59770,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2121" s="1">
-        <x:v>25550</x:v>
+        <x:v>882230</x:v>
       </x:c>
       <x:c r="G2121" s="1">
-        <x:v>36550</x:v>
+        <x:v>1842330</x:v>
       </x:c>
     </x:row>
     <x:row r="2122" spans="1:7">
@@ -59850,10 +59850,10 @@
         <x:v>2146</x:v>
       </x:c>
       <x:c r="B2125" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C2125" s="1">
-        <x:v>22450</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="D2125" s="1">
         <x:v>0</x:v>
@@ -59862,10 +59862,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2125" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G2125" s="1">
         <x:v>250</x:v>
-      </x:c>
-      <x:c r="G2125" s="1">
-        <x:v>22700</x:v>
       </x:c>
     </x:row>
     <x:row r="2126" spans="1:7">
@@ -59873,22 +59873,22 @@
         <x:v>2146</x:v>
       </x:c>
       <x:c r="B2126" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C2126" s="1">
+        <x:v>22450</x:v>
+      </x:c>
+      <x:c r="D2126" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E2126" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F2126" s="1">
         <x:v>250</x:v>
       </x:c>
-      <x:c r="D2126" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E2126" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F2126" s="1">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="G2126" s="1">
-        <x:v>250</x:v>
+        <x:v>22700</x:v>
       </x:c>
     </x:row>
     <x:row r="2127" spans="1:7">
@@ -75283,10 +75283,10 @@
         <x:v>2809</x:v>
       </x:c>
       <x:c r="B2796" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C2796" s="1">
-        <x:v>15000</x:v>
+        <x:v>206766</x:v>
       </x:c>
       <x:c r="D2796" s="1">
         <x:v>0</x:v>
@@ -75295,10 +75295,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2796" s="1">
-        <x:v>111650</x:v>
+        <x:v>286825</x:v>
       </x:c>
       <x:c r="G2796" s="1">
-        <x:v>126650</x:v>
+        <x:v>493591</x:v>
       </x:c>
     </x:row>
     <x:row r="2797" spans="1:7">
@@ -75306,10 +75306,10 @@
         <x:v>2809</x:v>
       </x:c>
       <x:c r="B2797" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C2797" s="1">
-        <x:v>206766</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D2797" s="1">
         <x:v>0</x:v>
@@ -75318,10 +75318,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2797" s="1">
-        <x:v>286825</x:v>
+        <x:v>111650</x:v>
       </x:c>
       <x:c r="G2797" s="1">
-        <x:v>493591</x:v>
+        <x:v>126650</x:v>
       </x:c>
     </x:row>
     <x:row r="2798" spans="1:7">
@@ -76801,10 +76801,10 @@
         <x:v>2873</x:v>
       </x:c>
       <x:c r="B2862" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C2862" s="1">
-        <x:v>102350</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D2862" s="1">
         <x:v>0</x:v>
@@ -76813,10 +76813,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2862" s="1">
-        <x:v>106550</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G2862" s="1">
-        <x:v>208900</x:v>
+        <x:v>20000</x:v>
       </x:c>
     </x:row>
     <x:row r="2863" spans="1:7">
@@ -76824,10 +76824,10 @@
         <x:v>2873</x:v>
       </x:c>
       <x:c r="B2863" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C2863" s="1">
-        <x:v>15000</x:v>
+        <x:v>102350</x:v>
       </x:c>
       <x:c r="D2863" s="1">
         <x:v>0</x:v>
@@ -76836,10 +76836,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2863" s="1">
-        <x:v>5000</x:v>
+        <x:v>106550</x:v>
       </x:c>
       <x:c r="G2863" s="1">
-        <x:v>20000</x:v>
+        <x:v>208900</x:v>
       </x:c>
     </x:row>
     <x:row r="2864" spans="1:7">
@@ -78158,10 +78158,10 @@
         <x:v>2931</x:v>
       </x:c>
       <x:c r="B2921" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C2921" s="1">
-        <x:v>206000</x:v>
+        <x:v>37500</x:v>
       </x:c>
       <x:c r="D2921" s="1">
         <x:v>0</x:v>
@@ -78170,10 +78170,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2921" s="1">
-        <x:v>45600</x:v>
+        <x:v>8000</x:v>
       </x:c>
       <x:c r="G2921" s="1">
-        <x:v>251600</x:v>
+        <x:v>45500</x:v>
       </x:c>
     </x:row>
     <x:row r="2922" spans="1:7">
@@ -78181,10 +78181,10 @@
         <x:v>2931</x:v>
       </x:c>
       <x:c r="B2922" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C2922" s="1">
-        <x:v>37500</x:v>
+        <x:v>206000</x:v>
       </x:c>
       <x:c r="D2922" s="1">
         <x:v>0</x:v>
@@ -78193,10 +78193,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2922" s="1">
-        <x:v>8000</x:v>
+        <x:v>45600</x:v>
       </x:c>
       <x:c r="G2922" s="1">
-        <x:v>45500</x:v>
+        <x:v>251600</x:v>
       </x:c>
     </x:row>
     <x:row r="2923" spans="1:7">
@@ -78572,10 +78572,10 @@
         <x:v>2948</x:v>
       </x:c>
       <x:c r="B2939" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C2939" s="1">
-        <x:v>12000</x:v>
+        <x:v>99950</x:v>
       </x:c>
       <x:c r="D2939" s="1">
         <x:v>0</x:v>
@@ -78584,10 +78584,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2939" s="1">
-        <x:v>0</x:v>
+        <x:v>6650</x:v>
       </x:c>
       <x:c r="G2939" s="1">
-        <x:v>12000</x:v>
+        <x:v>106600</x:v>
       </x:c>
     </x:row>
     <x:row r="2940" spans="1:7">
@@ -78595,10 +78595,10 @@
         <x:v>2948</x:v>
       </x:c>
       <x:c r="B2940" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C2940" s="1">
-        <x:v>99950</x:v>
+        <x:v>12000</x:v>
       </x:c>
       <x:c r="D2940" s="1">
         <x:v>0</x:v>
@@ -78607,10 +78607,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2940" s="1">
-        <x:v>6650</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2940" s="1">
-        <x:v>106600</x:v>
+        <x:v>12000</x:v>
       </x:c>
     </x:row>
     <x:row r="2941" spans="1:7">
@@ -78618,22 +78618,22 @@
         <x:v>2949</x:v>
       </x:c>
       <x:c r="B2941" s="1" t="s">
-        <x:v>258</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C2941" s="1">
-        <x:v>10000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D2941" s="1">
-        <x:v>0</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E2941" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2941" s="1">
-        <x:v>4950</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2941" s="1">
-        <x:v>14950</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="2942" spans="1:7">
@@ -78641,22 +78641,22 @@
         <x:v>2949</x:v>
       </x:c>
       <x:c r="B2942" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="C2942" s="1">
-        <x:v>0</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="D2942" s="1">
-        <x:v>59</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E2942" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2942" s="1">
-        <x:v>0</x:v>
+        <x:v>4950</x:v>
       </x:c>
       <x:c r="G2942" s="1">
-        <x:v>59</x:v>
+        <x:v>14950</x:v>
       </x:c>
     </x:row>
     <x:row r="2943" spans="1:7">
@@ -82275,22 +82275,22 @@
         <x:v>3099</x:v>
       </x:c>
       <x:c r="B3100" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C3100" s="1">
-        <x:v>0</x:v>
+        <x:v>307450</x:v>
       </x:c>
       <x:c r="D3100" s="1">
-        <x:v>59</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3100" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3100" s="1">
-        <x:v>0</x:v>
+        <x:v>40550</x:v>
       </x:c>
       <x:c r="G3100" s="1">
-        <x:v>59</x:v>
+        <x:v>348000</x:v>
       </x:c>
     </x:row>
     <x:row r="3101" spans="1:7">
@@ -82298,22 +82298,22 @@
         <x:v>3099</x:v>
       </x:c>
       <x:c r="B3101" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C3101" s="1">
-        <x:v>307450</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3101" s="1">
-        <x:v>0</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3101" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3101" s="1">
-        <x:v>40550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3101" s="1">
-        <x:v>348000</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="3102" spans="1:7">
@@ -83379,10 +83379,10 @@
         <x:v>3142</x:v>
       </x:c>
       <x:c r="B3148" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C3148" s="1">
-        <x:v>20000</x:v>
+        <x:v>157500</x:v>
       </x:c>
       <x:c r="D3148" s="1">
         <x:v>0</x:v>
@@ -83391,10 +83391,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3148" s="1">
-        <x:v>6000</x:v>
+        <x:v>45517</x:v>
       </x:c>
       <x:c r="G3148" s="1">
-        <x:v>26000</x:v>
+        <x:v>203017</x:v>
       </x:c>
     </x:row>
     <x:row r="3149" spans="1:7">
@@ -83402,10 +83402,10 @@
         <x:v>3142</x:v>
       </x:c>
       <x:c r="B3149" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C3149" s="1">
-        <x:v>157500</x:v>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="D3149" s="1">
         <x:v>0</x:v>
@@ -83414,10 +83414,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3149" s="1">
-        <x:v>45517</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="G3149" s="1">
-        <x:v>203017</x:v>
+        <x:v>26000</x:v>
       </x:c>
     </x:row>
     <x:row r="3150" spans="1:7">
@@ -85242,22 +85242,22 @@
         <x:v>3219</x:v>
       </x:c>
       <x:c r="B3229" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="C3229" s="1">
-        <x:v>0</x:v>
+        <x:v>533500</x:v>
       </x:c>
       <x:c r="D3229" s="1">
-        <x:v>59</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E3229" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3229" s="1">
-        <x:v>0</x:v>
+        <x:v>227847</x:v>
       </x:c>
       <x:c r="G3229" s="1">
-        <x:v>59</x:v>
+        <x:v>761642</x:v>
       </x:c>
     </x:row>
     <x:row r="3230" spans="1:7">
@@ -85265,22 +85265,22 @@
         <x:v>3219</x:v>
       </x:c>
       <x:c r="B3230" s="1" t="s">
-        <x:v>297</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C3230" s="1">
-        <x:v>533500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3230" s="1">
-        <x:v>295</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3230" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3230" s="1">
-        <x:v>227847</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3230" s="1">
-        <x:v>761642</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="3231" spans="1:7">
@@ -87680,22 +87680,22 @@
         <x:v>3321</x:v>
       </x:c>
       <x:c r="B3335" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C3335" s="1">
-        <x:v>332220</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3335" s="1">
-        <x:v>0</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3335" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3335" s="1">
-        <x:v>299023</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3335" s="1">
-        <x:v>631243</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="3336" spans="1:7">
@@ -87703,13 +87703,13 @@
         <x:v>3321</x:v>
       </x:c>
       <x:c r="B3336" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="C3336" s="1">
-        <x:v>0</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D3336" s="1">
-        <x:v>59</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E3336" s="1">
         <x:v>0</x:v>
@@ -87718,7 +87718,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G3336" s="1">
-        <x:v>59</x:v>
+        <x:v>15063</x:v>
       </x:c>
     </x:row>
     <x:row r="3337" spans="1:7">
@@ -87726,22 +87726,22 @@
         <x:v>3321</x:v>
       </x:c>
       <x:c r="B3337" s="1" t="s">
-        <x:v>256</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C3337" s="1">
-        <x:v>15000</x:v>
+        <x:v>332220</x:v>
       </x:c>
       <x:c r="D3337" s="1">
-        <x:v>63</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3337" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3337" s="1">
-        <x:v>0</x:v>
+        <x:v>299023</x:v>
       </x:c>
       <x:c r="G3337" s="1">
-        <x:v>15063</x:v>
+        <x:v>631243</x:v>
       </x:c>
     </x:row>
     <x:row r="3338" spans="1:7">
@@ -87795,22 +87795,22 @@
         <x:v>3323</x:v>
       </x:c>
       <x:c r="B3340" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C3340" s="1">
-        <x:v>7000</x:v>
+        <x:v>116050</x:v>
       </x:c>
       <x:c r="D3340" s="1">
-        <x:v>63</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="E3340" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3340" s="1">
-        <x:v>7000</x:v>
+        <x:v>47699</x:v>
       </x:c>
       <x:c r="G3340" s="1">
-        <x:v>14063</x:v>
+        <x:v>163985</x:v>
       </x:c>
     </x:row>
     <x:row r="3341" spans="1:7">
@@ -87818,22 +87818,22 @@
         <x:v>3323</x:v>
       </x:c>
       <x:c r="B3341" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C3341" s="1">
-        <x:v>116050</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D3341" s="1">
-        <x:v>236</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E3341" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3341" s="1">
-        <x:v>47699</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="G3341" s="1">
-        <x:v>163985</x:v>
+        <x:v>14063</x:v>
       </x:c>
     </x:row>
     <x:row r="3342" spans="1:7">
@@ -90141,22 +90141,22 @@
         <x:v>3418</x:v>
       </x:c>
       <x:c r="B3442" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C3442" s="1">
-        <x:v>0</x:v>
+        <x:v>72750</x:v>
       </x:c>
       <x:c r="D3442" s="1">
-        <x:v>59</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E3442" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3442" s="1">
-        <x:v>0</x:v>
+        <x:v>25450</x:v>
       </x:c>
       <x:c r="G3442" s="1">
-        <x:v>59</x:v>
+        <x:v>98495</x:v>
       </x:c>
     </x:row>
     <x:row r="3443" spans="1:7">
@@ -90164,22 +90164,22 @@
         <x:v>3418</x:v>
       </x:c>
       <x:c r="B3443" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C3443" s="1">
-        <x:v>72750</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3443" s="1">
-        <x:v>295</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3443" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3443" s="1">
-        <x:v>25450</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3443" s="1">
-        <x:v>98495</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="3444" spans="1:7">
@@ -90371,22 +90371,22 @@
         <x:v>3426</x:v>
       </x:c>
       <x:c r="B3452" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C3452" s="1">
-        <x:v>0</x:v>
+        <x:v>47850</x:v>
       </x:c>
       <x:c r="D3452" s="1">
-        <x:v>59</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3452" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3452" s="1">
-        <x:v>0</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G3452" s="1">
-        <x:v>59</x:v>
+        <x:v>52850</x:v>
       </x:c>
     </x:row>
     <x:row r="3453" spans="1:7">
@@ -90394,22 +90394,22 @@
         <x:v>3426</x:v>
       </x:c>
       <x:c r="B3453" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C3453" s="1">
-        <x:v>47850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3453" s="1">
-        <x:v>0</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3453" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3453" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3453" s="1">
-        <x:v>52850</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="3454" spans="1:7">
@@ -90624,22 +90624,22 @@
         <x:v>3436</x:v>
       </x:c>
       <x:c r="B3463" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="C3463" s="1">
-        <x:v>22500</x:v>
+        <x:v>437150</x:v>
       </x:c>
       <x:c r="D3463" s="1">
-        <x:v>0</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="E3463" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3463" s="1">
-        <x:v>0</x:v>
+        <x:v>348550</x:v>
       </x:c>
       <x:c r="G3463" s="1">
-        <x:v>22500</x:v>
+        <x:v>786168</x:v>
       </x:c>
     </x:row>
     <x:row r="3464" spans="1:7">
@@ -90647,22 +90647,22 @@
         <x:v>3436</x:v>
       </x:c>
       <x:c r="B3464" s="1" t="s">
-        <x:v>416</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C3464" s="1">
-        <x:v>437150</x:v>
+        <x:v>22500</x:v>
       </x:c>
       <x:c r="D3464" s="1">
-        <x:v>468</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3464" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3464" s="1">
-        <x:v>348550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3464" s="1">
-        <x:v>786168</x:v>
+        <x:v>22500</x:v>
       </x:c>
     </x:row>
     <x:row r="3465" spans="1:7">
@@ -91383,22 +91383,22 @@
         <x:v>3466</x:v>
       </x:c>
       <x:c r="B3496" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C3496" s="1">
-        <x:v>265983</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3496" s="1">
-        <x:v>177</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3496" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3496" s="1">
-        <x:v>126150</x:v>
+        <x:v>44000</x:v>
       </x:c>
       <x:c r="G3496" s="1">
-        <x:v>392310</x:v>
+        <x:v>44059</x:v>
       </x:c>
     </x:row>
     <x:row r="3497" spans="1:7">
@@ -91406,22 +91406,22 @@
         <x:v>3466</x:v>
       </x:c>
       <x:c r="B3497" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C3497" s="1">
-        <x:v>0</x:v>
+        <x:v>265983</x:v>
       </x:c>
       <x:c r="D3497" s="1">
-        <x:v>59</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="E3497" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3497" s="1">
-        <x:v>44000</x:v>
+        <x:v>126150</x:v>
       </x:c>
       <x:c r="G3497" s="1">
-        <x:v>44059</x:v>
+        <x:v>392310</x:v>
       </x:c>
     </x:row>
     <x:row r="3498" spans="1:7">
@@ -91820,22 +91820,22 @@
         <x:v>3483</x:v>
       </x:c>
       <x:c r="B3515" s="1" t="s">
-        <x:v>258</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C3515" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3515" s="1">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E3515" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3515" s="1">
-        <x:v>11300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3515" s="1">
-        <x:v>12300</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="3516" spans="1:7">
@@ -91843,22 +91843,22 @@
         <x:v>3483</x:v>
       </x:c>
       <x:c r="B3516" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="C3516" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D3516" s="1">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3516" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3516" s="1">
-        <x:v>0</x:v>
+        <x:v>11300</x:v>
       </x:c>
       <x:c r="G3516" s="1">
-        <x:v>3</x:v>
+        <x:v>12300</x:v>
       </x:c>
     </x:row>
     <x:row r="3517" spans="1:7">

--- a/reports/pro-oil/pro-oil-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-oil/pro-oil-candidate-lobby-lifetime-report.xlsx
@@ -16104,7 +16104,7 @@
         <x:v>277</x:v>
       </x:c>
       <x:c r="B223" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C223" s="1">
         <x:v>0</x:v>
@@ -16116,10 +16116,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F223" s="1">
-        <x:v>2300</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G223" s="1">
-        <x:v>2300</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="224" spans="1:7">
@@ -16127,7 +16127,7 @@
         <x:v>277</x:v>
       </x:c>
       <x:c r="B224" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C224" s="1">
         <x:v>0</x:v>
@@ -16139,10 +16139,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F224" s="1">
-        <x:v>1000</x:v>
+        <x:v>2300</x:v>
       </x:c>
       <x:c r="G224" s="1">
-        <x:v>1000</x:v>
+        <x:v>2300</x:v>
       </x:c>
     </x:row>
     <x:row r="225" spans="1:7">
@@ -19209,10 +19209,10 @@
         <x:v>412</x:v>
       </x:c>
       <x:c r="B358" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C358" s="1">
-        <x:v>15000</x:v>
+        <x:v>163000</x:v>
       </x:c>
       <x:c r="D358" s="1">
         <x:v>0</x:v>
@@ -19221,10 +19221,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F358" s="1">
-        <x:v>0</x:v>
+        <x:v>82550</x:v>
       </x:c>
       <x:c r="G358" s="1">
-        <x:v>15000</x:v>
+        <x:v>245550</x:v>
       </x:c>
     </x:row>
     <x:row r="359" spans="1:7">
@@ -19232,10 +19232,10 @@
         <x:v>412</x:v>
       </x:c>
       <x:c r="B359" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C359" s="1">
-        <x:v>163000</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D359" s="1">
         <x:v>0</x:v>
@@ -19244,10 +19244,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F359" s="1">
-        <x:v>82550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G359" s="1">
-        <x:v>245550</x:v>
+        <x:v>15000</x:v>
       </x:c>
     </x:row>
     <x:row r="360" spans="1:7">
@@ -19347,10 +19347,10 @@
         <x:v>418</x:v>
       </x:c>
       <x:c r="B364" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C364" s="1">
-        <x:v>3000</x:v>
+        <x:v>107540</x:v>
       </x:c>
       <x:c r="D364" s="1">
         <x:v>0</x:v>
@@ -19359,10 +19359,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F364" s="1">
-        <x:v>25150</x:v>
+        <x:v>59170</x:v>
       </x:c>
       <x:c r="G364" s="1">
-        <x:v>28150</x:v>
+        <x:v>166710</x:v>
       </x:c>
     </x:row>
     <x:row r="365" spans="1:7">
@@ -19370,10 +19370,10 @@
         <x:v>418</x:v>
       </x:c>
       <x:c r="B365" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C365" s="1">
-        <x:v>107540</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D365" s="1">
         <x:v>0</x:v>
@@ -19382,10 +19382,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F365" s="1">
-        <x:v>59170</x:v>
+        <x:v>25150</x:v>
       </x:c>
       <x:c r="G365" s="1">
-        <x:v>166710</x:v>
+        <x:v>28150</x:v>
       </x:c>
     </x:row>
     <x:row r="366" spans="1:7">
@@ -21003,10 +21003,10 @@
         <x:v>488</x:v>
       </x:c>
       <x:c r="B436" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C436" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D436" s="1">
         <x:v>0</x:v>
@@ -21015,10 +21015,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F436" s="1">
-        <x:v>13450</x:v>
+        <x:v>40350</x:v>
       </x:c>
       <x:c r="G436" s="1">
-        <x:v>13500</x:v>
+        <x:v>40350</x:v>
       </x:c>
     </x:row>
     <x:row r="437" spans="1:7">
@@ -21026,11 +21026,11 @@
         <x:v>488</x:v>
       </x:c>
       <x:c r="B437" s="1" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C437" s="1">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="C437" s="1">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="D437" s="1">
         <x:v>0</x:v>
       </x:c>
@@ -21038,10 +21038,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F437" s="1">
-        <x:v>40350</x:v>
+        <x:v>13450</x:v>
       </x:c>
       <x:c r="G437" s="1">
-        <x:v>40350</x:v>
+        <x:v>13500</x:v>
       </x:c>
     </x:row>
     <x:row r="438" spans="1:7">
@@ -27190,22 +27190,22 @@
         <x:v>757</x:v>
       </x:c>
       <x:c r="B705" s="1" t="s">
-        <x:v>747</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C705" s="1">
-        <x:v>418533</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D705" s="1">
-        <x:v>118</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E705" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F705" s="1">
-        <x:v>51350</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G705" s="1">
-        <x:v>470001</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="706" spans="1:7">
@@ -27213,22 +27213,22 @@
         <x:v>757</x:v>
       </x:c>
       <x:c r="B706" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>747</x:v>
       </x:c>
       <x:c r="C706" s="1">
-        <x:v>25500</x:v>
+        <x:v>418533</x:v>
       </x:c>
       <x:c r="D706" s="1">
-        <x:v>0</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E706" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F706" s="1">
-        <x:v>0</x:v>
+        <x:v>51350</x:v>
       </x:c>
       <x:c r="G706" s="1">
-        <x:v>25500</x:v>
+        <x:v>470001</x:v>
       </x:c>
     </x:row>
     <x:row r="707" spans="1:7">
@@ -30755,10 +30755,10 @@
         <x:v>910</x:v>
       </x:c>
       <x:c r="B860" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="C860" s="1">
-        <x:v>0</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D860" s="1">
         <x:v>0</x:v>
@@ -30767,10 +30767,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F860" s="1">
-        <x:v>14450</x:v>
+        <x:v>12950</x:v>
       </x:c>
       <x:c r="G860" s="1">
-        <x:v>14450</x:v>
+        <x:v>15950</x:v>
       </x:c>
     </x:row>
     <x:row r="861" spans="1:7">
@@ -30778,10 +30778,10 @@
         <x:v>910</x:v>
       </x:c>
       <x:c r="B861" s="1" t="s">
-        <x:v>258</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C861" s="1">
-        <x:v>3000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D861" s="1">
         <x:v>0</x:v>
@@ -30790,10 +30790,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F861" s="1">
-        <x:v>12950</x:v>
+        <x:v>14450</x:v>
       </x:c>
       <x:c r="G861" s="1">
-        <x:v>15950</x:v>
+        <x:v>14450</x:v>
       </x:c>
     </x:row>
     <x:row r="862" spans="1:7">
@@ -46349,10 +46349,10 @@
         <x:v>1577</x:v>
       </x:c>
       <x:c r="B1538" s="1" t="s">
-        <x:v>164</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C1538" s="1">
-        <x:v>82250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1538" s="1">
         <x:v>0</x:v>
@@ -46361,10 +46361,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1538" s="1">
-        <x:v>9000</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1538" s="1">
-        <x:v>91250</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="1539" spans="1:7">
@@ -46372,10 +46372,10 @@
         <x:v>1577</x:v>
       </x:c>
       <x:c r="B1539" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="C1539" s="1">
-        <x:v>0</x:v>
+        <x:v>82250</x:v>
       </x:c>
       <x:c r="D1539" s="1">
         <x:v>0</x:v>
@@ -46384,10 +46384,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1539" s="1">
-        <x:v>1000</x:v>
+        <x:v>9000</x:v>
       </x:c>
       <x:c r="G1539" s="1">
-        <x:v>1000</x:v>
+        <x:v>91250</x:v>
       </x:c>
     </x:row>
     <x:row r="1540" spans="1:7">
@@ -50650,10 +50650,10 @@
         <x:v>1758</x:v>
       </x:c>
       <x:c r="B1725" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1725" s="1">
-        <x:v>485</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1725" s="1">
         <x:v>0</x:v>
@@ -50662,10 +50662,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1725" s="1">
-        <x:v>72700</x:v>
+        <x:v>16350</x:v>
       </x:c>
       <x:c r="G1725" s="1">
-        <x:v>73185</x:v>
+        <x:v>18850</x:v>
       </x:c>
     </x:row>
     <x:row r="1726" spans="1:7">
@@ -50673,10 +50673,10 @@
         <x:v>1758</x:v>
       </x:c>
       <x:c r="B1726" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C1726" s="1">
-        <x:v>2500</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="D1726" s="1">
         <x:v>0</x:v>
@@ -50685,10 +50685,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1726" s="1">
-        <x:v>16350</x:v>
+        <x:v>72700</x:v>
       </x:c>
       <x:c r="G1726" s="1">
-        <x:v>18850</x:v>
+        <x:v>73185</x:v>
       </x:c>
     </x:row>
     <x:row r="1727" spans="1:7">
@@ -52789,10 +52789,10 @@
         <x:v>1848</x:v>
       </x:c>
       <x:c r="B1818" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C1818" s="1">
-        <x:v>-1000</x:v>
+        <x:v>147100</x:v>
       </x:c>
       <x:c r="D1818" s="1">
         <x:v>0</x:v>
@@ -52801,10 +52801,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1818" s="1">
-        <x:v>0</x:v>
+        <x:v>34550</x:v>
       </x:c>
       <x:c r="G1818" s="1">
-        <x:v>-1000</x:v>
+        <x:v>181650</x:v>
       </x:c>
     </x:row>
     <x:row r="1819" spans="1:7">
@@ -52812,10 +52812,10 @@
         <x:v>1848</x:v>
       </x:c>
       <x:c r="B1819" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C1819" s="1">
-        <x:v>147100</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="D1819" s="1">
         <x:v>0</x:v>
@@ -52824,10 +52824,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1819" s="1">
-        <x:v>34550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1819" s="1">
-        <x:v>181650</x:v>
+        <x:v>-1000</x:v>
       </x:c>
     </x:row>
     <x:row r="1820" spans="1:7">
@@ -55618,22 +55618,22 @@
         <x:v>1968</x:v>
       </x:c>
       <x:c r="B1941" s="1" t="s">
-        <x:v>155</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C1941" s="1">
-        <x:v>0</x:v>
+        <x:v>299950</x:v>
       </x:c>
       <x:c r="D1941" s="1">
-        <x:v>59</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E1941" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1941" s="1">
-        <x:v>0</x:v>
+        <x:v>178350</x:v>
       </x:c>
       <x:c r="G1941" s="1">
-        <x:v>59</x:v>
+        <x:v>478595</x:v>
       </x:c>
     </x:row>
     <x:row r="1942" spans="1:7">
@@ -55641,22 +55641,22 @@
         <x:v>1968</x:v>
       </x:c>
       <x:c r="B1942" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="C1942" s="1">
-        <x:v>299950</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1942" s="1">
-        <x:v>295</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E1942" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1942" s="1">
-        <x:v>178350</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1942" s="1">
-        <x:v>478595</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="1943" spans="1:7">
@@ -56239,10 +56239,10 @@
         <x:v>1994</x:v>
       </x:c>
       <x:c r="B1968" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1968" s="1">
-        <x:v>187150</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1968" s="1">
         <x:v>31</x:v>
@@ -56251,10 +56251,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1968" s="1">
-        <x:v>6150</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1968" s="1">
-        <x:v>193331</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="1969" spans="1:7">
@@ -56262,10 +56262,10 @@
         <x:v>1994</x:v>
       </x:c>
       <x:c r="B1969" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C1969" s="1">
-        <x:v>0</x:v>
+        <x:v>187150</x:v>
       </x:c>
       <x:c r="D1969" s="1">
         <x:v>31</x:v>
@@ -56274,10 +56274,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1969" s="1">
-        <x:v>0</x:v>
+        <x:v>6150</x:v>
       </x:c>
       <x:c r="G1969" s="1">
-        <x:v>31</x:v>
+        <x:v>193331</x:v>
       </x:c>
     </x:row>
     <x:row r="1970" spans="1:7">
@@ -75260,10 +75260,10 @@
         <x:v>2809</x:v>
       </x:c>
       <x:c r="B2795" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C2795" s="1">
-        <x:v>163800</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D2795" s="1">
         <x:v>0</x:v>
@@ -75272,10 +75272,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2795" s="1">
-        <x:v>277645</x:v>
+        <x:v>111650</x:v>
       </x:c>
       <x:c r="G2795" s="1">
-        <x:v>441445</x:v>
+        <x:v>126650</x:v>
       </x:c>
     </x:row>
     <x:row r="2796" spans="1:7">
@@ -75283,10 +75283,10 @@
         <x:v>2809</x:v>
       </x:c>
       <x:c r="B2796" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C2796" s="1">
-        <x:v>206766</x:v>
+        <x:v>163800</x:v>
       </x:c>
       <x:c r="D2796" s="1">
         <x:v>0</x:v>
@@ -75295,10 +75295,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2796" s="1">
-        <x:v>286825</x:v>
+        <x:v>277645</x:v>
       </x:c>
       <x:c r="G2796" s="1">
-        <x:v>493591</x:v>
+        <x:v>441445</x:v>
       </x:c>
     </x:row>
     <x:row r="2797" spans="1:7">
@@ -75306,10 +75306,10 @@
         <x:v>2809</x:v>
       </x:c>
       <x:c r="B2797" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C2797" s="1">
-        <x:v>15000</x:v>
+        <x:v>206766</x:v>
       </x:c>
       <x:c r="D2797" s="1">
         <x:v>0</x:v>
@@ -75318,10 +75318,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2797" s="1">
-        <x:v>111650</x:v>
+        <x:v>286825</x:v>
       </x:c>
       <x:c r="G2797" s="1">
-        <x:v>126650</x:v>
+        <x:v>493591</x:v>
       </x:c>
     </x:row>
     <x:row r="2798" spans="1:7">
@@ -78158,10 +78158,10 @@
         <x:v>2931</x:v>
       </x:c>
       <x:c r="B2921" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C2921" s="1">
-        <x:v>37500</x:v>
+        <x:v>206000</x:v>
       </x:c>
       <x:c r="D2921" s="1">
         <x:v>0</x:v>
@@ -78170,10 +78170,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2921" s="1">
-        <x:v>8000</x:v>
+        <x:v>45600</x:v>
       </x:c>
       <x:c r="G2921" s="1">
-        <x:v>45500</x:v>
+        <x:v>251600</x:v>
       </x:c>
     </x:row>
     <x:row r="2922" spans="1:7">
@@ -78181,10 +78181,10 @@
         <x:v>2931</x:v>
       </x:c>
       <x:c r="B2922" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C2922" s="1">
-        <x:v>206000</x:v>
+        <x:v>37500</x:v>
       </x:c>
       <x:c r="D2922" s="1">
         <x:v>0</x:v>
@@ -78193,10 +78193,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2922" s="1">
-        <x:v>45600</x:v>
+        <x:v>8000</x:v>
       </x:c>
       <x:c r="G2922" s="1">
-        <x:v>251600</x:v>
+        <x:v>45500</x:v>
       </x:c>
     </x:row>
     <x:row r="2923" spans="1:7">
@@ -78618,22 +78618,22 @@
         <x:v>2949</x:v>
       </x:c>
       <x:c r="B2941" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="C2941" s="1">
-        <x:v>0</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="D2941" s="1">
-        <x:v>59</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E2941" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2941" s="1">
-        <x:v>0</x:v>
+        <x:v>4950</x:v>
       </x:c>
       <x:c r="G2941" s="1">
-        <x:v>59</x:v>
+        <x:v>14950</x:v>
       </x:c>
     </x:row>
     <x:row r="2942" spans="1:7">
@@ -78641,22 +78641,22 @@
         <x:v>2949</x:v>
       </x:c>
       <x:c r="B2942" s="1" t="s">
-        <x:v>258</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C2942" s="1">
-        <x:v>10000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D2942" s="1">
-        <x:v>0</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E2942" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2942" s="1">
-        <x:v>4950</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2942" s="1">
-        <x:v>14950</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="2943" spans="1:7">
@@ -81608,10 +81608,10 @@
         <x:v>3075</x:v>
       </x:c>
       <x:c r="B3071" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C3071" s="1">
-        <x:v>10500</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D3071" s="1">
         <x:v>0</x:v>
@@ -81620,10 +81620,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3071" s="1">
-        <x:v>31300</x:v>
+        <x:v>33600</x:v>
       </x:c>
       <x:c r="G3071" s="1">
-        <x:v>41800</x:v>
+        <x:v>38600</x:v>
       </x:c>
     </x:row>
     <x:row r="3072" spans="1:7">
@@ -81631,10 +81631,10 @@
         <x:v>3075</x:v>
       </x:c>
       <x:c r="B3072" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C3072" s="1">
-        <x:v>5000</x:v>
+        <x:v>10500</x:v>
       </x:c>
       <x:c r="D3072" s="1">
         <x:v>0</x:v>
@@ -81643,10 +81643,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3072" s="1">
-        <x:v>33600</x:v>
+        <x:v>31300</x:v>
       </x:c>
       <x:c r="G3072" s="1">
-        <x:v>38600</x:v>
+        <x:v>41800</x:v>
       </x:c>
     </x:row>
     <x:row r="3073" spans="1:7">
@@ -81953,7 +81953,7 @@
         <x:v>3086</x:v>
       </x:c>
       <x:c r="B3086" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C3086" s="1">
         <x:v>1000</x:v>
@@ -81965,10 +81965,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3086" s="1">
-        <x:v>4750</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3086" s="1">
-        <x:v>5750</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="3087" spans="1:7">
@@ -81976,7 +81976,7 @@
         <x:v>3086</x:v>
       </x:c>
       <x:c r="B3087" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C3087" s="1">
         <x:v>1000</x:v>
@@ -81988,10 +81988,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3087" s="1">
-        <x:v>0</x:v>
+        <x:v>4750</x:v>
       </x:c>
       <x:c r="G3087" s="1">
-        <x:v>1000</x:v>
+        <x:v>5750</x:v>
       </x:c>
     </x:row>
     <x:row r="3088" spans="1:7">
@@ -82275,22 +82275,22 @@
         <x:v>3099</x:v>
       </x:c>
       <x:c r="B3100" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C3100" s="1">
-        <x:v>307450</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3100" s="1">
-        <x:v>0</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3100" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3100" s="1">
-        <x:v>40550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3100" s="1">
-        <x:v>348000</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="3101" spans="1:7">
@@ -82298,22 +82298,22 @@
         <x:v>3099</x:v>
       </x:c>
       <x:c r="B3101" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C3101" s="1">
-        <x:v>0</x:v>
+        <x:v>307450</x:v>
       </x:c>
       <x:c r="D3101" s="1">
-        <x:v>59</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3101" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3101" s="1">
-        <x:v>0</x:v>
+        <x:v>40550</x:v>
       </x:c>
       <x:c r="G3101" s="1">
-        <x:v>59</x:v>
+        <x:v>348000</x:v>
       </x:c>
     </x:row>
     <x:row r="3102" spans="1:7">
@@ -85863,22 +85863,22 @@
         <x:v>3243</x:v>
       </x:c>
       <x:c r="B3256" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C3256" s="1">
-        <x:v>420650</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D3256" s="1">
-        <x:v>181</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3256" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3256" s="1">
-        <x:v>448881</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3256" s="1">
-        <x:v>869712</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="3257" spans="1:7">
@@ -85886,22 +85886,22 @@
         <x:v>3243</x:v>
       </x:c>
       <x:c r="B3257" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C3257" s="1">
-        <x:v>25500</x:v>
+        <x:v>420650</x:v>
       </x:c>
       <x:c r="D3257" s="1">
-        <x:v>0</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="E3257" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3257" s="1">
-        <x:v>0</x:v>
+        <x:v>448881</x:v>
       </x:c>
       <x:c r="G3257" s="1">
-        <x:v>25500</x:v>
+        <x:v>869712</x:v>
       </x:c>
     </x:row>
     <x:row r="3258" spans="1:7">
@@ -87703,22 +87703,22 @@
         <x:v>3321</x:v>
       </x:c>
       <x:c r="B3336" s="1" t="s">
-        <x:v>256</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C3336" s="1">
-        <x:v>15000</x:v>
+        <x:v>332220</x:v>
       </x:c>
       <x:c r="D3336" s="1">
-        <x:v>63</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3336" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3336" s="1">
-        <x:v>0</x:v>
+        <x:v>299023</x:v>
       </x:c>
       <x:c r="G3336" s="1">
-        <x:v>15063</x:v>
+        <x:v>631243</x:v>
       </x:c>
     </x:row>
     <x:row r="3337" spans="1:7">
@@ -87726,22 +87726,22 @@
         <x:v>3321</x:v>
       </x:c>
       <x:c r="B3337" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="C3337" s="1">
-        <x:v>332220</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D3337" s="1">
-        <x:v>0</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E3337" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3337" s="1">
-        <x:v>299023</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3337" s="1">
-        <x:v>631243</x:v>
+        <x:v>15063</x:v>
       </x:c>
     </x:row>
     <x:row r="3338" spans="1:7">
@@ -88876,10 +88876,10 @@
         <x:v>3368</x:v>
       </x:c>
       <x:c r="B3387" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C3387" s="1">
-        <x:v>41550</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D3387" s="1">
         <x:v>0</x:v>
@@ -88888,10 +88888,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3387" s="1">
-        <x:v>6500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3387" s="1">
-        <x:v>48050</x:v>
+        <x:v>15000</x:v>
       </x:c>
     </x:row>
     <x:row r="3388" spans="1:7">
@@ -88899,10 +88899,10 @@
         <x:v>3368</x:v>
       </x:c>
       <x:c r="B3388" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C3388" s="1">
-        <x:v>15000</x:v>
+        <x:v>41550</x:v>
       </x:c>
       <x:c r="D3388" s="1">
         <x:v>0</x:v>
@@ -88911,10 +88911,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3388" s="1">
-        <x:v>0</x:v>
+        <x:v>6500</x:v>
       </x:c>
       <x:c r="G3388" s="1">
-        <x:v>15000</x:v>
+        <x:v>48050</x:v>
       </x:c>
     </x:row>
     <x:row r="3389" spans="1:7">
@@ -89589,22 +89589,22 @@
         <x:v>3396</x:v>
       </x:c>
       <x:c r="B3418" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C3418" s="1">
-        <x:v>38500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3418" s="1">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E3418" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3418" s="1">
-        <x:v>26250</x:v>
+        <x:v>10700</x:v>
       </x:c>
       <x:c r="G3418" s="1">
-        <x:v>64750</x:v>
+        <x:v>10701</x:v>
       </x:c>
     </x:row>
     <x:row r="3419" spans="1:7">
@@ -89612,22 +89612,22 @@
         <x:v>3396</x:v>
       </x:c>
       <x:c r="B3419" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C3419" s="1">
-        <x:v>0</x:v>
+        <x:v>38500</x:v>
       </x:c>
       <x:c r="D3419" s="1">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3419" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3419" s="1">
-        <x:v>10700</x:v>
+        <x:v>26250</x:v>
       </x:c>
       <x:c r="G3419" s="1">
-        <x:v>10701</x:v>
+        <x:v>64750</x:v>
       </x:c>
     </x:row>
     <x:row r="3420" spans="1:7">
@@ -90624,22 +90624,22 @@
         <x:v>3436</x:v>
       </x:c>
       <x:c r="B3463" s="1" t="s">
-        <x:v>416</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C3463" s="1">
-        <x:v>437150</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D3463" s="1">
-        <x:v>468</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3463" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3463" s="1">
-        <x:v>348550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3463" s="1">
-        <x:v>786168</x:v>
+        <x:v>3000</x:v>
       </x:c>
     </x:row>
     <x:row r="3464" spans="1:7">
@@ -90670,22 +90670,22 @@
         <x:v>3436</x:v>
       </x:c>
       <x:c r="B3465" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="C3465" s="1">
-        <x:v>3000</x:v>
+        <x:v>437150</x:v>
       </x:c>
       <x:c r="D3465" s="1">
-        <x:v>0</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="E3465" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3465" s="1">
-        <x:v>0</x:v>
+        <x:v>348550</x:v>
       </x:c>
       <x:c r="G3465" s="1">
-        <x:v>3000</x:v>
+        <x:v>786168</x:v>
       </x:c>
     </x:row>
     <x:row r="3466" spans="1:7">
@@ -91383,22 +91383,22 @@
         <x:v>3466</x:v>
       </x:c>
       <x:c r="B3496" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C3496" s="1">
-        <x:v>0</x:v>
+        <x:v>265983</x:v>
       </x:c>
       <x:c r="D3496" s="1">
-        <x:v>59</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="E3496" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3496" s="1">
-        <x:v>44000</x:v>
+        <x:v>126150</x:v>
       </x:c>
       <x:c r="G3496" s="1">
-        <x:v>44059</x:v>
+        <x:v>392310</x:v>
       </x:c>
     </x:row>
     <x:row r="3497" spans="1:7">
@@ -91406,22 +91406,22 @@
         <x:v>3466</x:v>
       </x:c>
       <x:c r="B3497" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C3497" s="1">
-        <x:v>265983</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3497" s="1">
-        <x:v>177</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3497" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3497" s="1">
-        <x:v>126150</x:v>
+        <x:v>44000</x:v>
       </x:c>
       <x:c r="G3497" s="1">
-        <x:v>392310</x:v>
+        <x:v>44059</x:v>
       </x:c>
     </x:row>
     <x:row r="3498" spans="1:7">

--- a/reports/pro-oil/pro-oil-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-oil/pro-oil-candidate-lobby-lifetime-report.xlsx
@@ -19209,10 +19209,10 @@
         <x:v>412</x:v>
       </x:c>
       <x:c r="B358" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C358" s="1">
-        <x:v>163000</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D358" s="1">
         <x:v>0</x:v>
@@ -19221,10 +19221,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F358" s="1">
-        <x:v>82550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G358" s="1">
-        <x:v>245550</x:v>
+        <x:v>15000</x:v>
       </x:c>
     </x:row>
     <x:row r="359" spans="1:7">
@@ -19232,10 +19232,10 @@
         <x:v>412</x:v>
       </x:c>
       <x:c r="B359" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C359" s="1">
-        <x:v>15000</x:v>
+        <x:v>163000</x:v>
       </x:c>
       <x:c r="D359" s="1">
         <x:v>0</x:v>
@@ -19244,10 +19244,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F359" s="1">
-        <x:v>0</x:v>
+        <x:v>82550</x:v>
       </x:c>
       <x:c r="G359" s="1">
-        <x:v>15000</x:v>
+        <x:v>245550</x:v>
       </x:c>
     </x:row>
     <x:row r="360" spans="1:7">
@@ -19347,10 +19347,10 @@
         <x:v>418</x:v>
       </x:c>
       <x:c r="B364" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C364" s="1">
-        <x:v>107540</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D364" s="1">
         <x:v>0</x:v>
@@ -19359,10 +19359,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F364" s="1">
-        <x:v>59170</x:v>
+        <x:v>25150</x:v>
       </x:c>
       <x:c r="G364" s="1">
-        <x:v>166710</x:v>
+        <x:v>28150</x:v>
       </x:c>
     </x:row>
     <x:row r="365" spans="1:7">
@@ -19370,10 +19370,10 @@
         <x:v>418</x:v>
       </x:c>
       <x:c r="B365" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C365" s="1">
-        <x:v>3000</x:v>
+        <x:v>107540</x:v>
       </x:c>
       <x:c r="D365" s="1">
         <x:v>0</x:v>
@@ -19382,10 +19382,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F365" s="1">
-        <x:v>25150</x:v>
+        <x:v>59170</x:v>
       </x:c>
       <x:c r="G365" s="1">
-        <x:v>28150</x:v>
+        <x:v>166710</x:v>
       </x:c>
     </x:row>
     <x:row r="366" spans="1:7">
@@ -31353,22 +31353,22 @@
         <x:v>934</x:v>
       </x:c>
       <x:c r="B886" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="C886" s="1">
-        <x:v>91000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D886" s="1">
-        <x:v>118</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E886" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F886" s="1">
-        <x:v>26100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G886" s="1">
-        <x:v>117218</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="887" spans="1:7">
@@ -31376,22 +31376,22 @@
         <x:v>934</x:v>
       </x:c>
       <x:c r="B887" s="1" t="s">
-        <x:v>297</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C887" s="1">
-        <x:v>0</x:v>
+        <x:v>91000</x:v>
       </x:c>
       <x:c r="D887" s="1">
-        <x:v>59</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E887" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F887" s="1">
-        <x:v>0</x:v>
+        <x:v>26100</x:v>
       </x:c>
       <x:c r="G887" s="1">
-        <x:v>59</x:v>
+        <x:v>117218</x:v>
       </x:c>
     </x:row>
     <x:row r="888" spans="1:7">
@@ -38782,10 +38782,10 @@
         <x:v>1250</x:v>
       </x:c>
       <x:c r="B1209" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C1209" s="1">
-        <x:v>3000</x:v>
+        <x:v>12000</x:v>
       </x:c>
       <x:c r="D1209" s="1">
         <x:v>0</x:v>
@@ -38794,10 +38794,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1209" s="1">
-        <x:v>50751</x:v>
+        <x:v>12450</x:v>
       </x:c>
       <x:c r="G1209" s="1">
-        <x:v>53751</x:v>
+        <x:v>24450</x:v>
       </x:c>
     </x:row>
     <x:row r="1210" spans="1:7">
@@ -38805,10 +38805,10 @@
         <x:v>1250</x:v>
       </x:c>
       <x:c r="B1210" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C1210" s="1">
-        <x:v>12000</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D1210" s="1">
         <x:v>0</x:v>
@@ -38817,10 +38817,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1210" s="1">
-        <x:v>12450</x:v>
+        <x:v>50751</x:v>
       </x:c>
       <x:c r="G1210" s="1">
-        <x:v>24450</x:v>
+        <x:v>53751</x:v>
       </x:c>
     </x:row>
     <x:row r="1211" spans="1:7">
@@ -46349,10 +46349,10 @@
         <x:v>1577</x:v>
       </x:c>
       <x:c r="B1538" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="C1538" s="1">
-        <x:v>0</x:v>
+        <x:v>82250</x:v>
       </x:c>
       <x:c r="D1538" s="1">
         <x:v>0</x:v>
@@ -46361,10 +46361,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1538" s="1">
-        <x:v>1000</x:v>
+        <x:v>9000</x:v>
       </x:c>
       <x:c r="G1538" s="1">
-        <x:v>1000</x:v>
+        <x:v>91250</x:v>
       </x:c>
     </x:row>
     <x:row r="1539" spans="1:7">
@@ -46372,10 +46372,10 @@
         <x:v>1577</x:v>
       </x:c>
       <x:c r="B1539" s="1" t="s">
-        <x:v>164</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C1539" s="1">
-        <x:v>82250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1539" s="1">
         <x:v>0</x:v>
@@ -46384,10 +46384,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1539" s="1">
-        <x:v>9000</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1539" s="1">
-        <x:v>91250</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="1540" spans="1:7">
@@ -49684,10 +49684,10 @@
         <x:v>1717</x:v>
       </x:c>
       <x:c r="B1683" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C1683" s="1">
-        <x:v>27850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1683" s="1">
         <x:v>0</x:v>
@@ -49696,10 +49696,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1683" s="1">
-        <x:v>19000</x:v>
+        <x:v>102225</x:v>
       </x:c>
       <x:c r="G1683" s="1">
-        <x:v>46850</x:v>
+        <x:v>102225</x:v>
       </x:c>
     </x:row>
     <x:row r="1684" spans="1:7">
@@ -49707,10 +49707,10 @@
         <x:v>1717</x:v>
       </x:c>
       <x:c r="B1684" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C1684" s="1">
-        <x:v>0</x:v>
+        <x:v>27850</x:v>
       </x:c>
       <x:c r="D1684" s="1">
         <x:v>0</x:v>
@@ -49719,10 +49719,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1684" s="1">
-        <x:v>102225</x:v>
+        <x:v>19000</x:v>
       </x:c>
       <x:c r="G1684" s="1">
-        <x:v>102225</x:v>
+        <x:v>46850</x:v>
       </x:c>
     </x:row>
     <x:row r="1685" spans="1:7">
@@ -50650,10 +50650,10 @@
         <x:v>1758</x:v>
       </x:c>
       <x:c r="B1725" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C1725" s="1">
-        <x:v>2500</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="D1725" s="1">
         <x:v>0</x:v>
@@ -50662,10 +50662,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1725" s="1">
-        <x:v>16350</x:v>
+        <x:v>72700</x:v>
       </x:c>
       <x:c r="G1725" s="1">
-        <x:v>18850</x:v>
+        <x:v>73185</x:v>
       </x:c>
     </x:row>
     <x:row r="1726" spans="1:7">
@@ -50673,10 +50673,10 @@
         <x:v>1758</x:v>
       </x:c>
       <x:c r="B1726" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1726" s="1">
-        <x:v>485</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1726" s="1">
         <x:v>0</x:v>
@@ -50685,10 +50685,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1726" s="1">
-        <x:v>72700</x:v>
+        <x:v>16350</x:v>
       </x:c>
       <x:c r="G1726" s="1">
-        <x:v>73185</x:v>
+        <x:v>18850</x:v>
       </x:c>
     </x:row>
     <x:row r="1727" spans="1:7">
@@ -52789,10 +52789,10 @@
         <x:v>1848</x:v>
       </x:c>
       <x:c r="B1818" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C1818" s="1">
-        <x:v>147100</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="D1818" s="1">
         <x:v>0</x:v>
@@ -52801,10 +52801,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1818" s="1">
-        <x:v>34550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1818" s="1">
-        <x:v>181650</x:v>
+        <x:v>-1000</x:v>
       </x:c>
     </x:row>
     <x:row r="1819" spans="1:7">
@@ -52812,10 +52812,10 @@
         <x:v>1848</x:v>
       </x:c>
       <x:c r="B1819" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C1819" s="1">
-        <x:v>-1000</x:v>
+        <x:v>147100</x:v>
       </x:c>
       <x:c r="D1819" s="1">
         <x:v>0</x:v>
@@ -52824,10 +52824,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1819" s="1">
-        <x:v>0</x:v>
+        <x:v>34550</x:v>
       </x:c>
       <x:c r="G1819" s="1">
-        <x:v>-1000</x:v>
+        <x:v>181650</x:v>
       </x:c>
     </x:row>
     <x:row r="1820" spans="1:7">
@@ -52973,7 +52973,7 @@
         <x:v>1855</x:v>
       </x:c>
       <x:c r="B1826" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1826" s="1">
         <x:v>0</x:v>
@@ -52996,7 +52996,7 @@
         <x:v>1855</x:v>
       </x:c>
       <x:c r="B1827" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C1827" s="1">
         <x:v>0</x:v>
@@ -55618,22 +55618,22 @@
         <x:v>1968</x:v>
       </x:c>
       <x:c r="B1941" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="C1941" s="1">
-        <x:v>299950</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1941" s="1">
-        <x:v>295</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E1941" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1941" s="1">
-        <x:v>178350</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1941" s="1">
-        <x:v>478595</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="1942" spans="1:7">
@@ -55641,22 +55641,22 @@
         <x:v>1968</x:v>
       </x:c>
       <x:c r="B1942" s="1" t="s">
-        <x:v>155</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C1942" s="1">
-        <x:v>0</x:v>
+        <x:v>299950</x:v>
       </x:c>
       <x:c r="D1942" s="1">
-        <x:v>59</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E1942" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1942" s="1">
-        <x:v>0</x:v>
+        <x:v>178350</x:v>
       </x:c>
       <x:c r="G1942" s="1">
-        <x:v>59</x:v>
+        <x:v>478595</x:v>
       </x:c>
     </x:row>
     <x:row r="1943" spans="1:7">
@@ -59735,10 +59735,10 @@
         <x:v>2142</x:v>
       </x:c>
       <x:c r="B2120" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C2120" s="1">
-        <x:v>11000</x:v>
+        <x:v>960100</x:v>
       </x:c>
       <x:c r="D2120" s="1">
         <x:v>0</x:v>
@@ -59747,10 +59747,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2120" s="1">
-        <x:v>25550</x:v>
+        <x:v>882230</x:v>
       </x:c>
       <x:c r="G2120" s="1">
-        <x:v>36550</x:v>
+        <x:v>1842330</x:v>
       </x:c>
     </x:row>
     <x:row r="2121" spans="1:7">
@@ -59758,10 +59758,10 @@
         <x:v>2142</x:v>
       </x:c>
       <x:c r="B2121" s="1" t="s">
-        <x:v>190</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C2121" s="1">
-        <x:v>960100</x:v>
+        <x:v>11000</x:v>
       </x:c>
       <x:c r="D2121" s="1">
         <x:v>0</x:v>
@@ -59770,10 +59770,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2121" s="1">
-        <x:v>882230</x:v>
+        <x:v>25550</x:v>
       </x:c>
       <x:c r="G2121" s="1">
-        <x:v>1842330</x:v>
+        <x:v>36550</x:v>
       </x:c>
     </x:row>
     <x:row r="2122" spans="1:7">
@@ -59850,22 +59850,22 @@
         <x:v>2146</x:v>
       </x:c>
       <x:c r="B2125" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C2125" s="1">
+        <x:v>22450</x:v>
+      </x:c>
+      <x:c r="D2125" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E2125" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F2125" s="1">
         <x:v>250</x:v>
       </x:c>
-      <x:c r="D2125" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E2125" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F2125" s="1">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="G2125" s="1">
-        <x:v>250</x:v>
+        <x:v>22700</x:v>
       </x:c>
     </x:row>
     <x:row r="2126" spans="1:7">
@@ -59873,10 +59873,10 @@
         <x:v>2146</x:v>
       </x:c>
       <x:c r="B2126" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C2126" s="1">
-        <x:v>22450</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="D2126" s="1">
         <x:v>0</x:v>
@@ -59885,10 +59885,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2126" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G2126" s="1">
         <x:v>250</x:v>
-      </x:c>
-      <x:c r="G2126" s="1">
-        <x:v>22700</x:v>
       </x:c>
     </x:row>
     <x:row r="2127" spans="1:7">
@@ -72454,10 +72454,10 @@
         <x:v>2689</x:v>
       </x:c>
       <x:c r="B2673" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C2673" s="1">
-        <x:v>139000</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D2673" s="1">
         <x:v>0</x:v>
@@ -72466,10 +72466,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2673" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2673" s="1">
-        <x:v>139500</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="2674" spans="1:7">
@@ -72477,10 +72477,10 @@
         <x:v>2689</x:v>
       </x:c>
       <x:c r="B2674" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C2674" s="1">
-        <x:v>7000</x:v>
+        <x:v>139000</x:v>
       </x:c>
       <x:c r="D2674" s="1">
         <x:v>0</x:v>
@@ -72489,10 +72489,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2674" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G2674" s="1">
-        <x:v>7000</x:v>
+        <x:v>139500</x:v>
       </x:c>
     </x:row>
     <x:row r="2675" spans="1:7">
@@ -75260,10 +75260,10 @@
         <x:v>2809</x:v>
       </x:c>
       <x:c r="B2795" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C2795" s="1">
-        <x:v>15000</x:v>
+        <x:v>206766</x:v>
       </x:c>
       <x:c r="D2795" s="1">
         <x:v>0</x:v>
@@ -75272,10 +75272,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2795" s="1">
-        <x:v>111650</x:v>
+        <x:v>286825</x:v>
       </x:c>
       <x:c r="G2795" s="1">
-        <x:v>126650</x:v>
+        <x:v>493591</x:v>
       </x:c>
     </x:row>
     <x:row r="2796" spans="1:7">
@@ -75283,10 +75283,10 @@
         <x:v>2809</x:v>
       </x:c>
       <x:c r="B2796" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C2796" s="1">
-        <x:v>163800</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D2796" s="1">
         <x:v>0</x:v>
@@ -75295,10 +75295,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2796" s="1">
-        <x:v>277645</x:v>
+        <x:v>111650</x:v>
       </x:c>
       <x:c r="G2796" s="1">
-        <x:v>441445</x:v>
+        <x:v>126650</x:v>
       </x:c>
     </x:row>
     <x:row r="2797" spans="1:7">
@@ -75306,10 +75306,10 @@
         <x:v>2809</x:v>
       </x:c>
       <x:c r="B2797" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C2797" s="1">
-        <x:v>206766</x:v>
+        <x:v>163800</x:v>
       </x:c>
       <x:c r="D2797" s="1">
         <x:v>0</x:v>
@@ -75318,10 +75318,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2797" s="1">
-        <x:v>286825</x:v>
+        <x:v>277645</x:v>
       </x:c>
       <x:c r="G2797" s="1">
-        <x:v>493591</x:v>
+        <x:v>441445</x:v>
       </x:c>
     </x:row>
     <x:row r="2798" spans="1:7">
@@ -81608,10 +81608,10 @@
         <x:v>3075</x:v>
       </x:c>
       <x:c r="B3071" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C3071" s="1">
-        <x:v>5000</x:v>
+        <x:v>10500</x:v>
       </x:c>
       <x:c r="D3071" s="1">
         <x:v>0</x:v>
@@ -81620,10 +81620,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3071" s="1">
-        <x:v>33600</x:v>
+        <x:v>31300</x:v>
       </x:c>
       <x:c r="G3071" s="1">
-        <x:v>38600</x:v>
+        <x:v>41800</x:v>
       </x:c>
     </x:row>
     <x:row r="3072" spans="1:7">
@@ -81631,10 +81631,10 @@
         <x:v>3075</x:v>
       </x:c>
       <x:c r="B3072" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C3072" s="1">
-        <x:v>10500</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D3072" s="1">
         <x:v>0</x:v>
@@ -81643,10 +81643,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3072" s="1">
-        <x:v>31300</x:v>
+        <x:v>33600</x:v>
       </x:c>
       <x:c r="G3072" s="1">
-        <x:v>41800</x:v>
+        <x:v>38600</x:v>
       </x:c>
     </x:row>
     <x:row r="3073" spans="1:7">
@@ -83379,10 +83379,10 @@
         <x:v>3142</x:v>
       </x:c>
       <x:c r="B3148" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C3148" s="1">
-        <x:v>157500</x:v>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="D3148" s="1">
         <x:v>0</x:v>
@@ -83391,10 +83391,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3148" s="1">
-        <x:v>45517</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="G3148" s="1">
-        <x:v>203017</x:v>
+        <x:v>26000</x:v>
       </x:c>
     </x:row>
     <x:row r="3149" spans="1:7">
@@ -83402,10 +83402,10 @@
         <x:v>3142</x:v>
       </x:c>
       <x:c r="B3149" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C3149" s="1">
-        <x:v>20000</x:v>
+        <x:v>157500</x:v>
       </x:c>
       <x:c r="D3149" s="1">
         <x:v>0</x:v>
@@ -83414,10 +83414,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3149" s="1">
-        <x:v>6000</x:v>
+        <x:v>45517</x:v>
       </x:c>
       <x:c r="G3149" s="1">
-        <x:v>26000</x:v>
+        <x:v>203017</x:v>
       </x:c>
     </x:row>
     <x:row r="3150" spans="1:7">
@@ -84943,10 +84943,10 @@
         <x:v>3208</x:v>
       </x:c>
       <x:c r="B3216" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C3216" s="1">
-        <x:v>3000</x:v>
+        <x:v>2300</x:v>
       </x:c>
       <x:c r="D3216" s="1">
         <x:v>0</x:v>
@@ -84955,10 +84955,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3216" s="1">
-        <x:v>6000</x:v>
+        <x:v>8850</x:v>
       </x:c>
       <x:c r="G3216" s="1">
-        <x:v>9000</x:v>
+        <x:v>11150</x:v>
       </x:c>
     </x:row>
     <x:row r="3217" spans="1:7">
@@ -84966,10 +84966,10 @@
         <x:v>3208</x:v>
       </x:c>
       <x:c r="B3217" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C3217" s="1">
-        <x:v>2300</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D3217" s="1">
         <x:v>0</x:v>
@@ -84978,10 +84978,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3217" s="1">
-        <x:v>8850</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="G3217" s="1">
-        <x:v>11150</x:v>
+        <x:v>9000</x:v>
       </x:c>
     </x:row>
     <x:row r="3218" spans="1:7">
@@ -85472,10 +85472,10 @@
         <x:v>3228</x:v>
       </x:c>
       <x:c r="B3239" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C3239" s="1">
-        <x:v>34000</x:v>
+        <x:v>343100</x:v>
       </x:c>
       <x:c r="D3239" s="1">
         <x:v>0</x:v>
@@ -85484,10 +85484,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3239" s="1">
-        <x:v>0</x:v>
+        <x:v>244972</x:v>
       </x:c>
       <x:c r="G3239" s="1">
-        <x:v>34000</x:v>
+        <x:v>588072</x:v>
       </x:c>
     </x:row>
     <x:row r="3240" spans="1:7">
@@ -85495,10 +85495,10 @@
         <x:v>3228</x:v>
       </x:c>
       <x:c r="B3240" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C3240" s="1">
-        <x:v>343100</x:v>
+        <x:v>34000</x:v>
       </x:c>
       <x:c r="D3240" s="1">
         <x:v>0</x:v>
@@ -85507,10 +85507,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3240" s="1">
-        <x:v>244972</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3240" s="1">
-        <x:v>588072</x:v>
+        <x:v>34000</x:v>
       </x:c>
     </x:row>
     <x:row r="3241" spans="1:7">
@@ -87680,13 +87680,13 @@
         <x:v>3321</x:v>
       </x:c>
       <x:c r="B3335" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="C3335" s="1">
-        <x:v>0</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D3335" s="1">
-        <x:v>59</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E3335" s="1">
         <x:v>0</x:v>
@@ -87695,7 +87695,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G3335" s="1">
-        <x:v>59</x:v>
+        <x:v>15063</x:v>
       </x:c>
     </x:row>
     <x:row r="3336" spans="1:7">
@@ -87703,22 +87703,22 @@
         <x:v>3321</x:v>
       </x:c>
       <x:c r="B3336" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C3336" s="1">
-        <x:v>332220</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3336" s="1">
-        <x:v>0</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3336" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3336" s="1">
-        <x:v>299023</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3336" s="1">
-        <x:v>631243</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="3337" spans="1:7">
@@ -87726,22 +87726,22 @@
         <x:v>3321</x:v>
       </x:c>
       <x:c r="B3337" s="1" t="s">
-        <x:v>256</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C3337" s="1">
-        <x:v>15000</x:v>
+        <x:v>332220</x:v>
       </x:c>
       <x:c r="D3337" s="1">
-        <x:v>63</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3337" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3337" s="1">
-        <x:v>0</x:v>
+        <x:v>299023</x:v>
       </x:c>
       <x:c r="G3337" s="1">
-        <x:v>15063</x:v>
+        <x:v>631243</x:v>
       </x:c>
     </x:row>
     <x:row r="3338" spans="1:7">
@@ -88876,10 +88876,10 @@
         <x:v>3368</x:v>
       </x:c>
       <x:c r="B3387" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C3387" s="1">
-        <x:v>15000</x:v>
+        <x:v>41550</x:v>
       </x:c>
       <x:c r="D3387" s="1">
         <x:v>0</x:v>
@@ -88888,10 +88888,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3387" s="1">
-        <x:v>0</x:v>
+        <x:v>6500</x:v>
       </x:c>
       <x:c r="G3387" s="1">
-        <x:v>15000</x:v>
+        <x:v>48050</x:v>
       </x:c>
     </x:row>
     <x:row r="3388" spans="1:7">
@@ -88899,10 +88899,10 @@
         <x:v>3368</x:v>
       </x:c>
       <x:c r="B3388" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C3388" s="1">
-        <x:v>41550</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D3388" s="1">
         <x:v>0</x:v>
@@ -88911,10 +88911,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3388" s="1">
-        <x:v>6500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3388" s="1">
-        <x:v>48050</x:v>
+        <x:v>15000</x:v>
       </x:c>
     </x:row>
     <x:row r="3389" spans="1:7">
@@ -89589,22 +89589,22 @@
         <x:v>3396</x:v>
       </x:c>
       <x:c r="B3418" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C3418" s="1">
-        <x:v>0</x:v>
+        <x:v>38500</x:v>
       </x:c>
       <x:c r="D3418" s="1">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3418" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3418" s="1">
-        <x:v>10700</x:v>
+        <x:v>26250</x:v>
       </x:c>
       <x:c r="G3418" s="1">
-        <x:v>10701</x:v>
+        <x:v>64750</x:v>
       </x:c>
     </x:row>
     <x:row r="3419" spans="1:7">
@@ -89612,22 +89612,22 @@
         <x:v>3396</x:v>
       </x:c>
       <x:c r="B3419" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C3419" s="1">
-        <x:v>38500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3419" s="1">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E3419" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3419" s="1">
-        <x:v>26250</x:v>
+        <x:v>10700</x:v>
       </x:c>
       <x:c r="G3419" s="1">
-        <x:v>64750</x:v>
+        <x:v>10701</x:v>
       </x:c>
     </x:row>
     <x:row r="3420" spans="1:7">
@@ -90647,22 +90647,22 @@
         <x:v>3436</x:v>
       </x:c>
       <x:c r="B3464" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="C3464" s="1">
-        <x:v>22500</x:v>
+        <x:v>437150</x:v>
       </x:c>
       <x:c r="D3464" s="1">
-        <x:v>0</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="E3464" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3464" s="1">
-        <x:v>0</x:v>
+        <x:v>348550</x:v>
       </x:c>
       <x:c r="G3464" s="1">
-        <x:v>22500</x:v>
+        <x:v>786168</x:v>
       </x:c>
     </x:row>
     <x:row r="3465" spans="1:7">
@@ -90670,22 +90670,22 @@
         <x:v>3436</x:v>
       </x:c>
       <x:c r="B3465" s="1" t="s">
-        <x:v>416</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C3465" s="1">
-        <x:v>437150</x:v>
+        <x:v>22500</x:v>
       </x:c>
       <x:c r="D3465" s="1">
-        <x:v>468</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3465" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3465" s="1">
-        <x:v>348550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3465" s="1">
-        <x:v>786168</x:v>
+        <x:v>22500</x:v>
       </x:c>
     </x:row>
     <x:row r="3466" spans="1:7">
@@ -91820,22 +91820,22 @@
         <x:v>3483</x:v>
       </x:c>
       <x:c r="B3515" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="C3515" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D3515" s="1">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3515" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3515" s="1">
-        <x:v>0</x:v>
+        <x:v>11300</x:v>
       </x:c>
       <x:c r="G3515" s="1">
-        <x:v>3</x:v>
+        <x:v>12300</x:v>
       </x:c>
     </x:row>
     <x:row r="3516" spans="1:7">
@@ -91843,22 +91843,22 @@
         <x:v>3483</x:v>
       </x:c>
       <x:c r="B3516" s="1" t="s">
-        <x:v>258</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C3516" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3516" s="1">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E3516" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3516" s="1">
-        <x:v>11300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3516" s="1">
-        <x:v>12300</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="3517" spans="1:7">

--- a/reports/pro-oil/pro-oil-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-oil/pro-oil-candidate-lobby-lifetime-report.xlsx
@@ -16104,7 +16104,7 @@
         <x:v>277</x:v>
       </x:c>
       <x:c r="B223" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C223" s="1">
         <x:v>0</x:v>
@@ -16116,10 +16116,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F223" s="1">
-        <x:v>1000</x:v>
+        <x:v>2300</x:v>
       </x:c>
       <x:c r="G223" s="1">
-        <x:v>1000</x:v>
+        <x:v>2300</x:v>
       </x:c>
     </x:row>
     <x:row r="224" spans="1:7">
@@ -16127,7 +16127,7 @@
         <x:v>277</x:v>
       </x:c>
       <x:c r="B224" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C224" s="1">
         <x:v>0</x:v>
@@ -16139,10 +16139,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F224" s="1">
-        <x:v>2300</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G224" s="1">
-        <x:v>2300</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="225" spans="1:7">
@@ -19347,10 +19347,10 @@
         <x:v>418</x:v>
       </x:c>
       <x:c r="B364" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C364" s="1">
-        <x:v>3000</x:v>
+        <x:v>107540</x:v>
       </x:c>
       <x:c r="D364" s="1">
         <x:v>0</x:v>
@@ -19359,10 +19359,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F364" s="1">
-        <x:v>25150</x:v>
+        <x:v>59170</x:v>
       </x:c>
       <x:c r="G364" s="1">
-        <x:v>28150</x:v>
+        <x:v>166710</x:v>
       </x:c>
     </x:row>
     <x:row r="365" spans="1:7">
@@ -19370,10 +19370,10 @@
         <x:v>418</x:v>
       </x:c>
       <x:c r="B365" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C365" s="1">
-        <x:v>107540</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D365" s="1">
         <x:v>0</x:v>
@@ -19382,10 +19382,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F365" s="1">
-        <x:v>59170</x:v>
+        <x:v>25150</x:v>
       </x:c>
       <x:c r="G365" s="1">
-        <x:v>166710</x:v>
+        <x:v>28150</x:v>
       </x:c>
     </x:row>
     <x:row r="366" spans="1:7">
@@ -30755,10 +30755,10 @@
         <x:v>910</x:v>
       </x:c>
       <x:c r="B860" s="1" t="s">
-        <x:v>258</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C860" s="1">
-        <x:v>3000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D860" s="1">
         <x:v>0</x:v>
@@ -30767,10 +30767,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F860" s="1">
-        <x:v>12950</x:v>
+        <x:v>14450</x:v>
       </x:c>
       <x:c r="G860" s="1">
-        <x:v>15950</x:v>
+        <x:v>14450</x:v>
       </x:c>
     </x:row>
     <x:row r="861" spans="1:7">
@@ -30778,10 +30778,10 @@
         <x:v>910</x:v>
       </x:c>
       <x:c r="B861" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="C861" s="1">
-        <x:v>0</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D861" s="1">
         <x:v>0</x:v>
@@ -30790,10 +30790,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F861" s="1">
-        <x:v>14450</x:v>
+        <x:v>12950</x:v>
       </x:c>
       <x:c r="G861" s="1">
-        <x:v>14450</x:v>
+        <x:v>15950</x:v>
       </x:c>
     </x:row>
     <x:row r="862" spans="1:7">
@@ -31353,22 +31353,22 @@
         <x:v>934</x:v>
       </x:c>
       <x:c r="B886" s="1" t="s">
-        <x:v>297</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C886" s="1">
-        <x:v>0</x:v>
+        <x:v>91000</x:v>
       </x:c>
       <x:c r="D886" s="1">
-        <x:v>59</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E886" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F886" s="1">
-        <x:v>0</x:v>
+        <x:v>26100</x:v>
       </x:c>
       <x:c r="G886" s="1">
-        <x:v>59</x:v>
+        <x:v>117218</x:v>
       </x:c>
     </x:row>
     <x:row r="887" spans="1:7">
@@ -31376,22 +31376,22 @@
         <x:v>934</x:v>
       </x:c>
       <x:c r="B887" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="C887" s="1">
-        <x:v>91000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D887" s="1">
-        <x:v>118</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E887" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F887" s="1">
-        <x:v>26100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G887" s="1">
-        <x:v>117218</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="888" spans="1:7">
@@ -38782,10 +38782,10 @@
         <x:v>1250</x:v>
       </x:c>
       <x:c r="B1209" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C1209" s="1">
-        <x:v>12000</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D1209" s="1">
         <x:v>0</x:v>
@@ -38794,10 +38794,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1209" s="1">
-        <x:v>12450</x:v>
+        <x:v>50751</x:v>
       </x:c>
       <x:c r="G1209" s="1">
-        <x:v>24450</x:v>
+        <x:v>53751</x:v>
       </x:c>
     </x:row>
     <x:row r="1210" spans="1:7">
@@ -38805,10 +38805,10 @@
         <x:v>1250</x:v>
       </x:c>
       <x:c r="B1210" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C1210" s="1">
-        <x:v>3000</x:v>
+        <x:v>12000</x:v>
       </x:c>
       <x:c r="D1210" s="1">
         <x:v>0</x:v>
@@ -38817,10 +38817,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1210" s="1">
-        <x:v>50751</x:v>
+        <x:v>12450</x:v>
       </x:c>
       <x:c r="G1210" s="1">
-        <x:v>53751</x:v>
+        <x:v>24450</x:v>
       </x:c>
     </x:row>
     <x:row r="1211" spans="1:7">
@@ -52973,7 +52973,7 @@
         <x:v>1855</x:v>
       </x:c>
       <x:c r="B1826" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C1826" s="1">
         <x:v>0</x:v>
@@ -52996,7 +52996,7 @@
         <x:v>1855</x:v>
       </x:c>
       <x:c r="B1827" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1827" s="1">
         <x:v>0</x:v>
@@ -59735,10 +59735,10 @@
         <x:v>2142</x:v>
       </x:c>
       <x:c r="B2120" s="1" t="s">
-        <x:v>190</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C2120" s="1">
-        <x:v>960100</x:v>
+        <x:v>11000</x:v>
       </x:c>
       <x:c r="D2120" s="1">
         <x:v>0</x:v>
@@ -59747,10 +59747,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2120" s="1">
-        <x:v>882230</x:v>
+        <x:v>25550</x:v>
       </x:c>
       <x:c r="G2120" s="1">
-        <x:v>1842330</x:v>
+        <x:v>36550</x:v>
       </x:c>
     </x:row>
     <x:row r="2121" spans="1:7">
@@ -59758,10 +59758,10 @@
         <x:v>2142</x:v>
       </x:c>
       <x:c r="B2121" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C2121" s="1">
-        <x:v>11000</x:v>
+        <x:v>960100</x:v>
       </x:c>
       <x:c r="D2121" s="1">
         <x:v>0</x:v>
@@ -59770,10 +59770,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2121" s="1">
-        <x:v>25550</x:v>
+        <x:v>882230</x:v>
       </x:c>
       <x:c r="G2121" s="1">
-        <x:v>36550</x:v>
+        <x:v>1842330</x:v>
       </x:c>
     </x:row>
     <x:row r="2122" spans="1:7">
@@ -72454,10 +72454,10 @@
         <x:v>2689</x:v>
       </x:c>
       <x:c r="B2673" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C2673" s="1">
-        <x:v>7000</x:v>
+        <x:v>139000</x:v>
       </x:c>
       <x:c r="D2673" s="1">
         <x:v>0</x:v>
@@ -72466,10 +72466,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2673" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G2673" s="1">
-        <x:v>7000</x:v>
+        <x:v>139500</x:v>
       </x:c>
     </x:row>
     <x:row r="2674" spans="1:7">
@@ -72477,10 +72477,10 @@
         <x:v>2689</x:v>
       </x:c>
       <x:c r="B2674" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C2674" s="1">
-        <x:v>139000</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D2674" s="1">
         <x:v>0</x:v>
@@ -72489,10 +72489,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2674" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2674" s="1">
-        <x:v>139500</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="2675" spans="1:7">
@@ -75260,10 +75260,10 @@
         <x:v>2809</x:v>
       </x:c>
       <x:c r="B2795" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C2795" s="1">
-        <x:v>206766</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D2795" s="1">
         <x:v>0</x:v>
@@ -75272,10 +75272,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2795" s="1">
-        <x:v>286825</x:v>
+        <x:v>111650</x:v>
       </x:c>
       <x:c r="G2795" s="1">
-        <x:v>493591</x:v>
+        <x:v>126650</x:v>
       </x:c>
     </x:row>
     <x:row r="2796" spans="1:7">
@@ -75283,10 +75283,10 @@
         <x:v>2809</x:v>
       </x:c>
       <x:c r="B2796" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C2796" s="1">
-        <x:v>15000</x:v>
+        <x:v>163800</x:v>
       </x:c>
       <x:c r="D2796" s="1">
         <x:v>0</x:v>
@@ -75295,10 +75295,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2796" s="1">
-        <x:v>111650</x:v>
+        <x:v>277645</x:v>
       </x:c>
       <x:c r="G2796" s="1">
-        <x:v>126650</x:v>
+        <x:v>441445</x:v>
       </x:c>
     </x:row>
     <x:row r="2797" spans="1:7">
@@ -75306,10 +75306,10 @@
         <x:v>2809</x:v>
       </x:c>
       <x:c r="B2797" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C2797" s="1">
-        <x:v>163800</x:v>
+        <x:v>206766</x:v>
       </x:c>
       <x:c r="D2797" s="1">
         <x:v>0</x:v>
@@ -75318,10 +75318,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2797" s="1">
-        <x:v>277645</x:v>
+        <x:v>286825</x:v>
       </x:c>
       <x:c r="G2797" s="1">
-        <x:v>441445</x:v>
+        <x:v>493591</x:v>
       </x:c>
     </x:row>
     <x:row r="2798" spans="1:7">
@@ -78158,10 +78158,10 @@
         <x:v>2931</x:v>
       </x:c>
       <x:c r="B2921" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C2921" s="1">
-        <x:v>206000</x:v>
+        <x:v>37500</x:v>
       </x:c>
       <x:c r="D2921" s="1">
         <x:v>0</x:v>
@@ -78170,10 +78170,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2921" s="1">
-        <x:v>45600</x:v>
+        <x:v>8000</x:v>
       </x:c>
       <x:c r="G2921" s="1">
-        <x:v>251600</x:v>
+        <x:v>45500</x:v>
       </x:c>
     </x:row>
     <x:row r="2922" spans="1:7">
@@ -78181,10 +78181,10 @@
         <x:v>2931</x:v>
       </x:c>
       <x:c r="B2922" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C2922" s="1">
-        <x:v>37500</x:v>
+        <x:v>206000</x:v>
       </x:c>
       <x:c r="D2922" s="1">
         <x:v>0</x:v>
@@ -78193,10 +78193,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2922" s="1">
-        <x:v>8000</x:v>
+        <x:v>45600</x:v>
       </x:c>
       <x:c r="G2922" s="1">
-        <x:v>45500</x:v>
+        <x:v>251600</x:v>
       </x:c>
     </x:row>
     <x:row r="2923" spans="1:7">
@@ -78572,10 +78572,10 @@
         <x:v>2948</x:v>
       </x:c>
       <x:c r="B2939" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C2939" s="1">
-        <x:v>99950</x:v>
+        <x:v>12000</x:v>
       </x:c>
       <x:c r="D2939" s="1">
         <x:v>0</x:v>
@@ -78584,10 +78584,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2939" s="1">
-        <x:v>6650</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2939" s="1">
-        <x:v>106600</x:v>
+        <x:v>12000</x:v>
       </x:c>
     </x:row>
     <x:row r="2940" spans="1:7">
@@ -78595,10 +78595,10 @@
         <x:v>2948</x:v>
       </x:c>
       <x:c r="B2940" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C2940" s="1">
-        <x:v>12000</x:v>
+        <x:v>99950</x:v>
       </x:c>
       <x:c r="D2940" s="1">
         <x:v>0</x:v>
@@ -78607,10 +78607,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2940" s="1">
-        <x:v>0</x:v>
+        <x:v>6650</x:v>
       </x:c>
       <x:c r="G2940" s="1">
-        <x:v>12000</x:v>
+        <x:v>106600</x:v>
       </x:c>
     </x:row>
     <x:row r="2941" spans="1:7">
@@ -78618,22 +78618,22 @@
         <x:v>2949</x:v>
       </x:c>
       <x:c r="B2941" s="1" t="s">
-        <x:v>258</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C2941" s="1">
-        <x:v>10000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D2941" s="1">
-        <x:v>0</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E2941" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2941" s="1">
-        <x:v>4950</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2941" s="1">
-        <x:v>14950</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="2942" spans="1:7">
@@ -78641,22 +78641,22 @@
         <x:v>2949</x:v>
       </x:c>
       <x:c r="B2942" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="C2942" s="1">
-        <x:v>0</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="D2942" s="1">
-        <x:v>59</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E2942" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2942" s="1">
-        <x:v>0</x:v>
+        <x:v>4950</x:v>
       </x:c>
       <x:c r="G2942" s="1">
-        <x:v>59</x:v>
+        <x:v>14950</x:v>
       </x:c>
     </x:row>
     <x:row r="2943" spans="1:7">
@@ -81608,10 +81608,10 @@
         <x:v>3075</x:v>
       </x:c>
       <x:c r="B3071" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C3071" s="1">
-        <x:v>10500</x:v>
+        <x:v>44000</x:v>
       </x:c>
       <x:c r="D3071" s="1">
         <x:v>0</x:v>
@@ -81620,10 +81620,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3071" s="1">
-        <x:v>31300</x:v>
+        <x:v>2100</x:v>
       </x:c>
       <x:c r="G3071" s="1">
-        <x:v>41800</x:v>
+        <x:v>46100</x:v>
       </x:c>
     </x:row>
     <x:row r="3072" spans="1:7">
@@ -81654,10 +81654,10 @@
         <x:v>3075</x:v>
       </x:c>
       <x:c r="B3073" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C3073" s="1">
-        <x:v>44000</x:v>
+        <x:v>10500</x:v>
       </x:c>
       <x:c r="D3073" s="1">
         <x:v>0</x:v>
@@ -81666,10 +81666,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3073" s="1">
-        <x:v>2100</x:v>
+        <x:v>31300</x:v>
       </x:c>
       <x:c r="G3073" s="1">
-        <x:v>46100</x:v>
+        <x:v>41800</x:v>
       </x:c>
     </x:row>
     <x:row r="3074" spans="1:7">
@@ -83011,10 +83011,10 @@
         <x:v>3130</x:v>
       </x:c>
       <x:c r="B3132" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="C3132" s="1">
-        <x:v>5000</x:v>
+        <x:v>48000</x:v>
       </x:c>
       <x:c r="D3132" s="1">
         <x:v>0</x:v>
@@ -83023,10 +83023,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3132" s="1">
-        <x:v>250</x:v>
+        <x:v>38300</x:v>
       </x:c>
       <x:c r="G3132" s="1">
-        <x:v>5250</x:v>
+        <x:v>86300</x:v>
       </x:c>
     </x:row>
     <x:row r="3133" spans="1:7">
@@ -83034,10 +83034,10 @@
         <x:v>3130</x:v>
       </x:c>
       <x:c r="B3133" s="1" t="s">
-        <x:v>155</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C3133" s="1">
-        <x:v>48000</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D3133" s="1">
         <x:v>0</x:v>
@@ -83046,10 +83046,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3133" s="1">
-        <x:v>38300</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G3133" s="1">
-        <x:v>86300</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="3134" spans="1:7">
@@ -83379,10 +83379,10 @@
         <x:v>3142</x:v>
       </x:c>
       <x:c r="B3148" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C3148" s="1">
-        <x:v>20000</x:v>
+        <x:v>157500</x:v>
       </x:c>
       <x:c r="D3148" s="1">
         <x:v>0</x:v>
@@ -83391,10 +83391,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3148" s="1">
-        <x:v>6000</x:v>
+        <x:v>45517</x:v>
       </x:c>
       <x:c r="G3148" s="1">
-        <x:v>26000</x:v>
+        <x:v>203017</x:v>
       </x:c>
     </x:row>
     <x:row r="3149" spans="1:7">
@@ -83402,10 +83402,10 @@
         <x:v>3142</x:v>
       </x:c>
       <x:c r="B3149" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C3149" s="1">
-        <x:v>157500</x:v>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="D3149" s="1">
         <x:v>0</x:v>
@@ -83414,10 +83414,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3149" s="1">
-        <x:v>45517</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="G3149" s="1">
-        <x:v>203017</x:v>
+        <x:v>26000</x:v>
       </x:c>
     </x:row>
     <x:row r="3150" spans="1:7">
@@ -85472,10 +85472,10 @@
         <x:v>3228</x:v>
       </x:c>
       <x:c r="B3239" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C3239" s="1">
-        <x:v>343100</x:v>
+        <x:v>34000</x:v>
       </x:c>
       <x:c r="D3239" s="1">
         <x:v>0</x:v>
@@ -85484,10 +85484,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3239" s="1">
-        <x:v>244972</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3239" s="1">
-        <x:v>588072</x:v>
+        <x:v>34000</x:v>
       </x:c>
     </x:row>
     <x:row r="3240" spans="1:7">
@@ -85495,10 +85495,10 @@
         <x:v>3228</x:v>
       </x:c>
       <x:c r="B3240" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C3240" s="1">
-        <x:v>34000</x:v>
+        <x:v>343100</x:v>
       </x:c>
       <x:c r="D3240" s="1">
         <x:v>0</x:v>
@@ -85507,10 +85507,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3240" s="1">
-        <x:v>0</x:v>
+        <x:v>244972</x:v>
       </x:c>
       <x:c r="G3240" s="1">
-        <x:v>34000</x:v>
+        <x:v>588072</x:v>
       </x:c>
     </x:row>
     <x:row r="3241" spans="1:7">
@@ -85656,10 +85656,10 @@
         <x:v>3235</x:v>
       </x:c>
       <x:c r="B3247" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C3247" s="1">
-        <x:v>0</x:v>
+        <x:v>29500</x:v>
       </x:c>
       <x:c r="D3247" s="1">
         <x:v>0</x:v>
@@ -85668,10 +85668,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3247" s="1">
-        <x:v>1000</x:v>
+        <x:v>12550</x:v>
       </x:c>
       <x:c r="G3247" s="1">
-        <x:v>1000</x:v>
+        <x:v>42050</x:v>
       </x:c>
     </x:row>
     <x:row r="3248" spans="1:7">
@@ -85679,10 +85679,10 @@
         <x:v>3235</x:v>
       </x:c>
       <x:c r="B3248" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C3248" s="1">
-        <x:v>29500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3248" s="1">
         <x:v>0</x:v>
@@ -85691,10 +85691,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3248" s="1">
-        <x:v>12550</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G3248" s="1">
-        <x:v>42050</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="3249" spans="1:7">
@@ -88876,10 +88876,10 @@
         <x:v>3368</x:v>
       </x:c>
       <x:c r="B3387" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C3387" s="1">
-        <x:v>41550</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D3387" s="1">
         <x:v>0</x:v>
@@ -88888,10 +88888,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3387" s="1">
-        <x:v>6500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3387" s="1">
-        <x:v>48050</x:v>
+        <x:v>15000</x:v>
       </x:c>
     </x:row>
     <x:row r="3388" spans="1:7">
@@ -88899,10 +88899,10 @@
         <x:v>3368</x:v>
       </x:c>
       <x:c r="B3388" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C3388" s="1">
-        <x:v>15000</x:v>
+        <x:v>41550</x:v>
       </x:c>
       <x:c r="D3388" s="1">
         <x:v>0</x:v>
@@ -88911,10 +88911,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3388" s="1">
-        <x:v>0</x:v>
+        <x:v>6500</x:v>
       </x:c>
       <x:c r="G3388" s="1">
-        <x:v>15000</x:v>
+        <x:v>48050</x:v>
       </x:c>
     </x:row>
     <x:row r="3389" spans="1:7">
@@ -89589,22 +89589,22 @@
         <x:v>3396</x:v>
       </x:c>
       <x:c r="B3418" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C3418" s="1">
-        <x:v>38500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3418" s="1">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E3418" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3418" s="1">
-        <x:v>26250</x:v>
+        <x:v>10700</x:v>
       </x:c>
       <x:c r="G3418" s="1">
-        <x:v>64750</x:v>
+        <x:v>10701</x:v>
       </x:c>
     </x:row>
     <x:row r="3419" spans="1:7">
@@ -89612,22 +89612,22 @@
         <x:v>3396</x:v>
       </x:c>
       <x:c r="B3419" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C3419" s="1">
-        <x:v>0</x:v>
+        <x:v>38500</x:v>
       </x:c>
       <x:c r="D3419" s="1">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3419" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3419" s="1">
-        <x:v>10700</x:v>
+        <x:v>26250</x:v>
       </x:c>
       <x:c r="G3419" s="1">
-        <x:v>10701</x:v>
+        <x:v>64750</x:v>
       </x:c>
     </x:row>
     <x:row r="3420" spans="1:7">
@@ -90371,22 +90371,22 @@
         <x:v>3426</x:v>
       </x:c>
       <x:c r="B3452" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C3452" s="1">
-        <x:v>47850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3452" s="1">
-        <x:v>0</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3452" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3452" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3452" s="1">
-        <x:v>52850</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="3453" spans="1:7">
@@ -90394,22 +90394,22 @@
         <x:v>3426</x:v>
       </x:c>
       <x:c r="B3453" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C3453" s="1">
-        <x:v>0</x:v>
+        <x:v>47850</x:v>
       </x:c>
       <x:c r="D3453" s="1">
-        <x:v>59</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3453" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3453" s="1">
-        <x:v>0</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G3453" s="1">
-        <x:v>59</x:v>
+        <x:v>52850</x:v>
       </x:c>
     </x:row>
     <x:row r="3454" spans="1:7">
@@ -90647,22 +90647,22 @@
         <x:v>3436</x:v>
       </x:c>
       <x:c r="B3464" s="1" t="s">
-        <x:v>416</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C3464" s="1">
-        <x:v>437150</x:v>
+        <x:v>22500</x:v>
       </x:c>
       <x:c r="D3464" s="1">
-        <x:v>468</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3464" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3464" s="1">
-        <x:v>348550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3464" s="1">
-        <x:v>786168</x:v>
+        <x:v>22500</x:v>
       </x:c>
     </x:row>
     <x:row r="3465" spans="1:7">
@@ -90670,22 +90670,22 @@
         <x:v>3436</x:v>
       </x:c>
       <x:c r="B3465" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="C3465" s="1">
-        <x:v>22500</x:v>
+        <x:v>437150</x:v>
       </x:c>
       <x:c r="D3465" s="1">
-        <x:v>0</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="E3465" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3465" s="1">
-        <x:v>0</x:v>
+        <x:v>348550</x:v>
       </x:c>
       <x:c r="G3465" s="1">
-        <x:v>22500</x:v>
+        <x:v>786168</x:v>
       </x:c>
     </x:row>
     <x:row r="3466" spans="1:7">
@@ -91383,22 +91383,22 @@
         <x:v>3466</x:v>
       </x:c>
       <x:c r="B3496" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C3496" s="1">
-        <x:v>265983</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3496" s="1">
-        <x:v>177</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3496" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3496" s="1">
-        <x:v>126150</x:v>
+        <x:v>44000</x:v>
       </x:c>
       <x:c r="G3496" s="1">
-        <x:v>392310</x:v>
+        <x:v>44059</x:v>
       </x:c>
     </x:row>
     <x:row r="3497" spans="1:7">
@@ -91406,22 +91406,22 @@
         <x:v>3466</x:v>
       </x:c>
       <x:c r="B3497" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C3497" s="1">
-        <x:v>0</x:v>
+        <x:v>265983</x:v>
       </x:c>
       <x:c r="D3497" s="1">
-        <x:v>59</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="E3497" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3497" s="1">
-        <x:v>44000</x:v>
+        <x:v>126150</x:v>
       </x:c>
       <x:c r="G3497" s="1">
-        <x:v>44059</x:v>
+        <x:v>392310</x:v>
       </x:c>
     </x:row>
     <x:row r="3498" spans="1:7">
@@ -91820,22 +91820,22 @@
         <x:v>3483</x:v>
       </x:c>
       <x:c r="B3515" s="1" t="s">
-        <x:v>258</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C3515" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3515" s="1">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E3515" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3515" s="1">
-        <x:v>11300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3515" s="1">
-        <x:v>12300</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="3516" spans="1:7">
@@ -91843,22 +91843,22 @@
         <x:v>3483</x:v>
       </x:c>
       <x:c r="B3516" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="C3516" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D3516" s="1">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3516" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3516" s="1">
-        <x:v>0</x:v>
+        <x:v>11300</x:v>
       </x:c>
       <x:c r="G3516" s="1">
-        <x:v>3</x:v>
+        <x:v>12300</x:v>
       </x:c>
     </x:row>
     <x:row r="3517" spans="1:7">

--- a/reports/pro-oil/pro-oil-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-oil/pro-oil-candidate-lobby-lifetime-report.xlsx
@@ -16104,7 +16104,7 @@
         <x:v>277</x:v>
       </x:c>
       <x:c r="B223" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C223" s="1">
         <x:v>0</x:v>
@@ -16116,10 +16116,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F223" s="1">
-        <x:v>2300</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G223" s="1">
-        <x:v>2300</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="224" spans="1:7">
@@ -16127,7 +16127,7 @@
         <x:v>277</x:v>
       </x:c>
       <x:c r="B224" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C224" s="1">
         <x:v>0</x:v>
@@ -16139,10 +16139,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F224" s="1">
-        <x:v>1000</x:v>
+        <x:v>2300</x:v>
       </x:c>
       <x:c r="G224" s="1">
-        <x:v>1000</x:v>
+        <x:v>2300</x:v>
       </x:c>
     </x:row>
     <x:row r="225" spans="1:7">
@@ -19209,10 +19209,10 @@
         <x:v>412</x:v>
       </x:c>
       <x:c r="B358" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C358" s="1">
-        <x:v>15000</x:v>
+        <x:v>163000</x:v>
       </x:c>
       <x:c r="D358" s="1">
         <x:v>0</x:v>
@@ -19221,10 +19221,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F358" s="1">
-        <x:v>0</x:v>
+        <x:v>82550</x:v>
       </x:c>
       <x:c r="G358" s="1">
-        <x:v>15000</x:v>
+        <x:v>245550</x:v>
       </x:c>
     </x:row>
     <x:row r="359" spans="1:7">
@@ -19232,10 +19232,10 @@
         <x:v>412</x:v>
       </x:c>
       <x:c r="B359" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C359" s="1">
-        <x:v>163000</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D359" s="1">
         <x:v>0</x:v>
@@ -19244,10 +19244,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F359" s="1">
-        <x:v>82550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G359" s="1">
-        <x:v>245550</x:v>
+        <x:v>15000</x:v>
       </x:c>
     </x:row>
     <x:row r="360" spans="1:7">
@@ -27190,22 +27190,22 @@
         <x:v>757</x:v>
       </x:c>
       <x:c r="B705" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>747</x:v>
       </x:c>
       <x:c r="C705" s="1">
-        <x:v>25500</x:v>
+        <x:v>418533</x:v>
       </x:c>
       <x:c r="D705" s="1">
-        <x:v>0</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E705" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F705" s="1">
-        <x:v>0</x:v>
+        <x:v>51350</x:v>
       </x:c>
       <x:c r="G705" s="1">
-        <x:v>25500</x:v>
+        <x:v>470001</x:v>
       </x:c>
     </x:row>
     <x:row r="706" spans="1:7">
@@ -27213,22 +27213,22 @@
         <x:v>757</x:v>
       </x:c>
       <x:c r="B706" s="1" t="s">
-        <x:v>747</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C706" s="1">
-        <x:v>418533</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D706" s="1">
-        <x:v>118</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E706" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F706" s="1">
-        <x:v>51350</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G706" s="1">
-        <x:v>470001</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="707" spans="1:7">
@@ -30755,10 +30755,10 @@
         <x:v>910</x:v>
       </x:c>
       <x:c r="B860" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="C860" s="1">
-        <x:v>0</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D860" s="1">
         <x:v>0</x:v>
@@ -30767,10 +30767,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F860" s="1">
-        <x:v>14450</x:v>
+        <x:v>12950</x:v>
       </x:c>
       <x:c r="G860" s="1">
-        <x:v>14450</x:v>
+        <x:v>15950</x:v>
       </x:c>
     </x:row>
     <x:row r="861" spans="1:7">
@@ -30778,10 +30778,10 @@
         <x:v>910</x:v>
       </x:c>
       <x:c r="B861" s="1" t="s">
-        <x:v>258</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C861" s="1">
-        <x:v>3000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D861" s="1">
         <x:v>0</x:v>
@@ -30790,10 +30790,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F861" s="1">
-        <x:v>12950</x:v>
+        <x:v>14450</x:v>
       </x:c>
       <x:c r="G861" s="1">
-        <x:v>15950</x:v>
+        <x:v>14450</x:v>
       </x:c>
     </x:row>
     <x:row r="862" spans="1:7">
@@ -38782,10 +38782,10 @@
         <x:v>1250</x:v>
       </x:c>
       <x:c r="B1209" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C1209" s="1">
-        <x:v>3000</x:v>
+        <x:v>12000</x:v>
       </x:c>
       <x:c r="D1209" s="1">
         <x:v>0</x:v>
@@ -38794,10 +38794,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1209" s="1">
-        <x:v>50751</x:v>
+        <x:v>12450</x:v>
       </x:c>
       <x:c r="G1209" s="1">
-        <x:v>53751</x:v>
+        <x:v>24450</x:v>
       </x:c>
     </x:row>
     <x:row r="1210" spans="1:7">
@@ -38805,10 +38805,10 @@
         <x:v>1250</x:v>
       </x:c>
       <x:c r="B1210" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C1210" s="1">
-        <x:v>12000</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D1210" s="1">
         <x:v>0</x:v>
@@ -38817,10 +38817,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1210" s="1">
-        <x:v>12450</x:v>
+        <x:v>50751</x:v>
       </x:c>
       <x:c r="G1210" s="1">
-        <x:v>24450</x:v>
+        <x:v>53751</x:v>
       </x:c>
     </x:row>
     <x:row r="1211" spans="1:7">
@@ -50650,10 +50650,10 @@
         <x:v>1758</x:v>
       </x:c>
       <x:c r="B1725" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1725" s="1">
-        <x:v>485</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1725" s="1">
         <x:v>0</x:v>
@@ -50662,10 +50662,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1725" s="1">
-        <x:v>72700</x:v>
+        <x:v>16350</x:v>
       </x:c>
       <x:c r="G1725" s="1">
-        <x:v>73185</x:v>
+        <x:v>18850</x:v>
       </x:c>
     </x:row>
     <x:row r="1726" spans="1:7">
@@ -50673,10 +50673,10 @@
         <x:v>1758</x:v>
       </x:c>
       <x:c r="B1726" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C1726" s="1">
-        <x:v>2500</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="D1726" s="1">
         <x:v>0</x:v>
@@ -50685,10 +50685,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1726" s="1">
-        <x:v>16350</x:v>
+        <x:v>72700</x:v>
       </x:c>
       <x:c r="G1726" s="1">
-        <x:v>18850</x:v>
+        <x:v>73185</x:v>
       </x:c>
     </x:row>
     <x:row r="1727" spans="1:7">
@@ -51869,10 +51869,10 @@
         <x:v>1809</x:v>
       </x:c>
       <x:c r="B1778" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C1778" s="1">
-        <x:v>2000</x:v>
+        <x:v>21000</x:v>
       </x:c>
       <x:c r="D1778" s="1">
         <x:v>0</x:v>
@@ -51881,10 +51881,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1778" s="1">
-        <x:v>0</x:v>
+        <x:v>11650</x:v>
       </x:c>
       <x:c r="G1778" s="1">
-        <x:v>2000</x:v>
+        <x:v>32650</x:v>
       </x:c>
     </x:row>
     <x:row r="1779" spans="1:7">
@@ -51892,10 +51892,10 @@
         <x:v>1809</x:v>
       </x:c>
       <x:c r="B1779" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C1779" s="1">
-        <x:v>21000</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1779" s="1">
         <x:v>0</x:v>
@@ -51904,10 +51904,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1779" s="1">
-        <x:v>11650</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1779" s="1">
-        <x:v>32650</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1780" spans="1:7">
@@ -52789,10 +52789,10 @@
         <x:v>1848</x:v>
       </x:c>
       <x:c r="B1818" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C1818" s="1">
-        <x:v>-1000</x:v>
+        <x:v>147100</x:v>
       </x:c>
       <x:c r="D1818" s="1">
         <x:v>0</x:v>
@@ -52801,10 +52801,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1818" s="1">
-        <x:v>0</x:v>
+        <x:v>34550</x:v>
       </x:c>
       <x:c r="G1818" s="1">
-        <x:v>-1000</x:v>
+        <x:v>181650</x:v>
       </x:c>
     </x:row>
     <x:row r="1819" spans="1:7">
@@ -52812,10 +52812,10 @@
         <x:v>1848</x:v>
       </x:c>
       <x:c r="B1819" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C1819" s="1">
-        <x:v>147100</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="D1819" s="1">
         <x:v>0</x:v>
@@ -52824,10 +52824,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1819" s="1">
-        <x:v>34550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1819" s="1">
-        <x:v>181650</x:v>
+        <x:v>-1000</x:v>
       </x:c>
     </x:row>
     <x:row r="1820" spans="1:7">
@@ -56239,10 +56239,10 @@
         <x:v>1994</x:v>
       </x:c>
       <x:c r="B1968" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C1968" s="1">
-        <x:v>0</x:v>
+        <x:v>187150</x:v>
       </x:c>
       <x:c r="D1968" s="1">
         <x:v>31</x:v>
@@ -56251,10 +56251,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1968" s="1">
-        <x:v>0</x:v>
+        <x:v>6150</x:v>
       </x:c>
       <x:c r="G1968" s="1">
-        <x:v>31</x:v>
+        <x:v>193331</x:v>
       </x:c>
     </x:row>
     <x:row r="1969" spans="1:7">
@@ -56262,10 +56262,10 @@
         <x:v>1994</x:v>
       </x:c>
       <x:c r="B1969" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1969" s="1">
-        <x:v>187150</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1969" s="1">
         <x:v>31</x:v>
@@ -56274,10 +56274,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1969" s="1">
-        <x:v>6150</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1969" s="1">
-        <x:v>193331</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="1970" spans="1:7">
@@ -59735,10 +59735,10 @@
         <x:v>2142</x:v>
       </x:c>
       <x:c r="B2120" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C2120" s="1">
-        <x:v>11000</x:v>
+        <x:v>960100</x:v>
       </x:c>
       <x:c r="D2120" s="1">
         <x:v>0</x:v>
@@ -59747,10 +59747,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2120" s="1">
-        <x:v>25550</x:v>
+        <x:v>882230</x:v>
       </x:c>
       <x:c r="G2120" s="1">
-        <x:v>36550</x:v>
+        <x:v>1842330</x:v>
       </x:c>
     </x:row>
     <x:row r="2121" spans="1:7">
@@ -59758,10 +59758,10 @@
         <x:v>2142</x:v>
       </x:c>
       <x:c r="B2121" s="1" t="s">
-        <x:v>190</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C2121" s="1">
-        <x:v>960100</x:v>
+        <x:v>11000</x:v>
       </x:c>
       <x:c r="D2121" s="1">
         <x:v>0</x:v>
@@ -59770,10 +59770,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2121" s="1">
-        <x:v>882230</x:v>
+        <x:v>25550</x:v>
       </x:c>
       <x:c r="G2121" s="1">
-        <x:v>1842330</x:v>
+        <x:v>36550</x:v>
       </x:c>
     </x:row>
     <x:row r="2122" spans="1:7">
@@ -59850,10 +59850,10 @@
         <x:v>2146</x:v>
       </x:c>
       <x:c r="B2125" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C2125" s="1">
-        <x:v>22450</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="D2125" s="1">
         <x:v>0</x:v>
@@ -59862,10 +59862,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2125" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G2125" s="1">
         <x:v>250</x:v>
-      </x:c>
-      <x:c r="G2125" s="1">
-        <x:v>22700</x:v>
       </x:c>
     </x:row>
     <x:row r="2126" spans="1:7">
@@ -59873,22 +59873,22 @@
         <x:v>2146</x:v>
       </x:c>
       <x:c r="B2126" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C2126" s="1">
+        <x:v>22450</x:v>
+      </x:c>
+      <x:c r="D2126" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E2126" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F2126" s="1">
         <x:v>250</x:v>
       </x:c>
-      <x:c r="D2126" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E2126" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F2126" s="1">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="G2126" s="1">
-        <x:v>250</x:v>
+        <x:v>22700</x:v>
       </x:c>
     </x:row>
     <x:row r="2127" spans="1:7">
@@ -72293,10 +72293,10 @@
         <x:v>2683</x:v>
       </x:c>
       <x:c r="B2666" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C2666" s="1">
-        <x:v>409250</x:v>
+        <x:v>7061</x:v>
       </x:c>
       <x:c r="D2666" s="1">
         <x:v>0</x:v>
@@ -72305,10 +72305,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2666" s="1">
-        <x:v>159800</x:v>
+        <x:v>23500</x:v>
       </x:c>
       <x:c r="G2666" s="1">
-        <x:v>569050</x:v>
+        <x:v>30561</x:v>
       </x:c>
     </x:row>
     <x:row r="2667" spans="1:7">
@@ -72316,10 +72316,10 @@
         <x:v>2683</x:v>
       </x:c>
       <x:c r="B2667" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C2667" s="1">
-        <x:v>7061</x:v>
+        <x:v>409250</x:v>
       </x:c>
       <x:c r="D2667" s="1">
         <x:v>0</x:v>
@@ -72328,10 +72328,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2667" s="1">
-        <x:v>23500</x:v>
+        <x:v>159800</x:v>
       </x:c>
       <x:c r="G2667" s="1">
-        <x:v>30561</x:v>
+        <x:v>569050</x:v>
       </x:c>
     </x:row>
     <x:row r="2668" spans="1:7">
@@ -75260,10 +75260,10 @@
         <x:v>2809</x:v>
       </x:c>
       <x:c r="B2795" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C2795" s="1">
-        <x:v>15000</x:v>
+        <x:v>163800</x:v>
       </x:c>
       <x:c r="D2795" s="1">
         <x:v>0</x:v>
@@ -75272,10 +75272,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2795" s="1">
-        <x:v>111650</x:v>
+        <x:v>277645</x:v>
       </x:c>
       <x:c r="G2795" s="1">
-        <x:v>126650</x:v>
+        <x:v>441445</x:v>
       </x:c>
     </x:row>
     <x:row r="2796" spans="1:7">
@@ -75283,10 +75283,10 @@
         <x:v>2809</x:v>
       </x:c>
       <x:c r="B2796" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C2796" s="1">
-        <x:v>163800</x:v>
+        <x:v>206766</x:v>
       </x:c>
       <x:c r="D2796" s="1">
         <x:v>0</x:v>
@@ -75295,10 +75295,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2796" s="1">
-        <x:v>277645</x:v>
+        <x:v>286825</x:v>
       </x:c>
       <x:c r="G2796" s="1">
-        <x:v>441445</x:v>
+        <x:v>493591</x:v>
       </x:c>
     </x:row>
     <x:row r="2797" spans="1:7">
@@ -75306,10 +75306,10 @@
         <x:v>2809</x:v>
       </x:c>
       <x:c r="B2797" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C2797" s="1">
-        <x:v>206766</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D2797" s="1">
         <x:v>0</x:v>
@@ -75318,10 +75318,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2797" s="1">
-        <x:v>286825</x:v>
+        <x:v>111650</x:v>
       </x:c>
       <x:c r="G2797" s="1">
-        <x:v>493591</x:v>
+        <x:v>126650</x:v>
       </x:c>
     </x:row>
     <x:row r="2798" spans="1:7">
@@ -76801,10 +76801,10 @@
         <x:v>2873</x:v>
       </x:c>
       <x:c r="B2862" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C2862" s="1">
-        <x:v>15000</x:v>
+        <x:v>102350</x:v>
       </x:c>
       <x:c r="D2862" s="1">
         <x:v>0</x:v>
@@ -76813,10 +76813,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2862" s="1">
-        <x:v>5000</x:v>
+        <x:v>106550</x:v>
       </x:c>
       <x:c r="G2862" s="1">
-        <x:v>20000</x:v>
+        <x:v>208900</x:v>
       </x:c>
     </x:row>
     <x:row r="2863" spans="1:7">
@@ -76824,10 +76824,10 @@
         <x:v>2873</x:v>
       </x:c>
       <x:c r="B2863" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C2863" s="1">
-        <x:v>102350</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D2863" s="1">
         <x:v>0</x:v>
@@ -76836,10 +76836,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2863" s="1">
-        <x:v>106550</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G2863" s="1">
-        <x:v>208900</x:v>
+        <x:v>20000</x:v>
       </x:c>
     </x:row>
     <x:row r="2864" spans="1:7">
@@ -78618,22 +78618,22 @@
         <x:v>2949</x:v>
       </x:c>
       <x:c r="B2941" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="C2941" s="1">
-        <x:v>0</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="D2941" s="1">
-        <x:v>59</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E2941" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2941" s="1">
-        <x:v>0</x:v>
+        <x:v>4950</x:v>
       </x:c>
       <x:c r="G2941" s="1">
-        <x:v>59</x:v>
+        <x:v>14950</x:v>
       </x:c>
     </x:row>
     <x:row r="2942" spans="1:7">
@@ -78641,22 +78641,22 @@
         <x:v>2949</x:v>
       </x:c>
       <x:c r="B2942" s="1" t="s">
-        <x:v>258</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C2942" s="1">
-        <x:v>10000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D2942" s="1">
-        <x:v>0</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E2942" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2942" s="1">
-        <x:v>4950</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2942" s="1">
-        <x:v>14950</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="2943" spans="1:7">
@@ -81033,22 +81033,22 @@
         <x:v>3051</x:v>
       </x:c>
       <x:c r="B3046" s="1" t="s">
-        <x:v>256</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C3046" s="1">
-        <x:v>7000</x:v>
+        <x:v>71750</x:v>
       </x:c>
       <x:c r="D3046" s="1">
-        <x:v>0</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="E3046" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3046" s="1">
-        <x:v>0</x:v>
+        <x:v>77150</x:v>
       </x:c>
       <x:c r="G3046" s="1">
-        <x:v>7000</x:v>
+        <x:v>149077</x:v>
       </x:c>
     </x:row>
     <x:row r="3047" spans="1:7">
@@ -81056,22 +81056,22 @@
         <x:v>3051</x:v>
       </x:c>
       <x:c r="B3047" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="C3047" s="1">
-        <x:v>71750</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D3047" s="1">
-        <x:v>177</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3047" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3047" s="1">
-        <x:v>77150</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3047" s="1">
-        <x:v>149077</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="3048" spans="1:7">
@@ -81631,10 +81631,10 @@
         <x:v>3075</x:v>
       </x:c>
       <x:c r="B3072" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C3072" s="1">
-        <x:v>5000</x:v>
+        <x:v>10500</x:v>
       </x:c>
       <x:c r="D3072" s="1">
         <x:v>0</x:v>
@@ -81643,10 +81643,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3072" s="1">
-        <x:v>33600</x:v>
+        <x:v>31300</x:v>
       </x:c>
       <x:c r="G3072" s="1">
-        <x:v>38600</x:v>
+        <x:v>41800</x:v>
       </x:c>
     </x:row>
     <x:row r="3073" spans="1:7">
@@ -81654,10 +81654,10 @@
         <x:v>3075</x:v>
       </x:c>
       <x:c r="B3073" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C3073" s="1">
-        <x:v>10500</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D3073" s="1">
         <x:v>0</x:v>
@@ -81666,10 +81666,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3073" s="1">
-        <x:v>31300</x:v>
+        <x:v>33600</x:v>
       </x:c>
       <x:c r="G3073" s="1">
-        <x:v>41800</x:v>
+        <x:v>38600</x:v>
       </x:c>
     </x:row>
     <x:row r="3074" spans="1:7">
@@ -82275,22 +82275,22 @@
         <x:v>3099</x:v>
       </x:c>
       <x:c r="B3100" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C3100" s="1">
-        <x:v>0</x:v>
+        <x:v>307450</x:v>
       </x:c>
       <x:c r="D3100" s="1">
-        <x:v>59</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3100" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3100" s="1">
-        <x:v>0</x:v>
+        <x:v>40550</x:v>
       </x:c>
       <x:c r="G3100" s="1">
-        <x:v>59</x:v>
+        <x:v>348000</x:v>
       </x:c>
     </x:row>
     <x:row r="3101" spans="1:7">
@@ -82298,22 +82298,22 @@
         <x:v>3099</x:v>
       </x:c>
       <x:c r="B3101" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C3101" s="1">
-        <x:v>307450</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3101" s="1">
-        <x:v>0</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3101" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3101" s="1">
-        <x:v>40550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3101" s="1">
-        <x:v>348000</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="3102" spans="1:7">
@@ -83379,10 +83379,10 @@
         <x:v>3142</x:v>
       </x:c>
       <x:c r="B3148" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C3148" s="1">
-        <x:v>157500</x:v>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="D3148" s="1">
         <x:v>0</x:v>
@@ -83391,10 +83391,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3148" s="1">
-        <x:v>45517</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="G3148" s="1">
-        <x:v>203017</x:v>
+        <x:v>26000</x:v>
       </x:c>
     </x:row>
     <x:row r="3149" spans="1:7">
@@ -83402,10 +83402,10 @@
         <x:v>3142</x:v>
       </x:c>
       <x:c r="B3149" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C3149" s="1">
-        <x:v>20000</x:v>
+        <x:v>157500</x:v>
       </x:c>
       <x:c r="D3149" s="1">
         <x:v>0</x:v>
@@ -83414,10 +83414,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3149" s="1">
-        <x:v>6000</x:v>
+        <x:v>45517</x:v>
       </x:c>
       <x:c r="G3149" s="1">
-        <x:v>26000</x:v>
+        <x:v>203017</x:v>
       </x:c>
     </x:row>
     <x:row r="3150" spans="1:7">
@@ -85242,22 +85242,22 @@
         <x:v>3219</x:v>
       </x:c>
       <x:c r="B3229" s="1" t="s">
-        <x:v>297</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C3229" s="1">
-        <x:v>533500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3229" s="1">
-        <x:v>295</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3229" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3229" s="1">
-        <x:v>227847</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3229" s="1">
-        <x:v>761642</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="3230" spans="1:7">
@@ -85265,22 +85265,22 @@
         <x:v>3219</x:v>
       </x:c>
       <x:c r="B3230" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="C3230" s="1">
-        <x:v>0</x:v>
+        <x:v>533500</x:v>
       </x:c>
       <x:c r="D3230" s="1">
-        <x:v>59</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E3230" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3230" s="1">
-        <x:v>0</x:v>
+        <x:v>227847</x:v>
       </x:c>
       <x:c r="G3230" s="1">
-        <x:v>59</x:v>
+        <x:v>761642</x:v>
       </x:c>
     </x:row>
     <x:row r="3231" spans="1:7">
@@ -87680,13 +87680,13 @@
         <x:v>3321</x:v>
       </x:c>
       <x:c r="B3335" s="1" t="s">
-        <x:v>256</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C3335" s="1">
-        <x:v>15000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3335" s="1">
-        <x:v>63</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3335" s="1">
         <x:v>0</x:v>
@@ -87695,7 +87695,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G3335" s="1">
-        <x:v>15063</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="3336" spans="1:7">
@@ -87703,22 +87703,22 @@
         <x:v>3321</x:v>
       </x:c>
       <x:c r="B3336" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C3336" s="1">
-        <x:v>0</x:v>
+        <x:v>332220</x:v>
       </x:c>
       <x:c r="D3336" s="1">
-        <x:v>59</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3336" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3336" s="1">
-        <x:v>0</x:v>
+        <x:v>299023</x:v>
       </x:c>
       <x:c r="G3336" s="1">
-        <x:v>59</x:v>
+        <x:v>631243</x:v>
       </x:c>
     </x:row>
     <x:row r="3337" spans="1:7">
@@ -87726,22 +87726,22 @@
         <x:v>3321</x:v>
       </x:c>
       <x:c r="B3337" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="C3337" s="1">
-        <x:v>332220</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D3337" s="1">
-        <x:v>0</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E3337" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3337" s="1">
-        <x:v>299023</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3337" s="1">
-        <x:v>631243</x:v>
+        <x:v>15063</x:v>
       </x:c>
     </x:row>
     <x:row r="3338" spans="1:7">
@@ -88876,10 +88876,10 @@
         <x:v>3368</x:v>
       </x:c>
       <x:c r="B3387" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C3387" s="1">
-        <x:v>15000</x:v>
+        <x:v>41550</x:v>
       </x:c>
       <x:c r="D3387" s="1">
         <x:v>0</x:v>
@@ -88888,10 +88888,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3387" s="1">
-        <x:v>0</x:v>
+        <x:v>6500</x:v>
       </x:c>
       <x:c r="G3387" s="1">
-        <x:v>15000</x:v>
+        <x:v>48050</x:v>
       </x:c>
     </x:row>
     <x:row r="3388" spans="1:7">
@@ -88899,10 +88899,10 @@
         <x:v>3368</x:v>
       </x:c>
       <x:c r="B3388" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C3388" s="1">
-        <x:v>41550</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D3388" s="1">
         <x:v>0</x:v>
@@ -88911,10 +88911,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3388" s="1">
-        <x:v>6500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3388" s="1">
-        <x:v>48050</x:v>
+        <x:v>15000</x:v>
       </x:c>
     </x:row>
     <x:row r="3389" spans="1:7">
@@ -89589,22 +89589,22 @@
         <x:v>3396</x:v>
       </x:c>
       <x:c r="B3418" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C3418" s="1">
-        <x:v>0</x:v>
+        <x:v>38500</x:v>
       </x:c>
       <x:c r="D3418" s="1">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3418" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3418" s="1">
-        <x:v>10700</x:v>
+        <x:v>26250</x:v>
       </x:c>
       <x:c r="G3418" s="1">
-        <x:v>10701</x:v>
+        <x:v>64750</x:v>
       </x:c>
     </x:row>
     <x:row r="3419" spans="1:7">
@@ -89612,22 +89612,22 @@
         <x:v>3396</x:v>
       </x:c>
       <x:c r="B3419" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C3419" s="1">
-        <x:v>38500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3419" s="1">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E3419" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3419" s="1">
-        <x:v>26250</x:v>
+        <x:v>10700</x:v>
       </x:c>
       <x:c r="G3419" s="1">
-        <x:v>64750</x:v>
+        <x:v>10701</x:v>
       </x:c>
     </x:row>
     <x:row r="3420" spans="1:7">
@@ -90371,22 +90371,22 @@
         <x:v>3426</x:v>
       </x:c>
       <x:c r="B3452" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C3452" s="1">
-        <x:v>0</x:v>
+        <x:v>47850</x:v>
       </x:c>
       <x:c r="D3452" s="1">
-        <x:v>59</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3452" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3452" s="1">
-        <x:v>0</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G3452" s="1">
-        <x:v>59</x:v>
+        <x:v>52850</x:v>
       </x:c>
     </x:row>
     <x:row r="3453" spans="1:7">
@@ -90394,22 +90394,22 @@
         <x:v>3426</x:v>
       </x:c>
       <x:c r="B3453" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C3453" s="1">
-        <x:v>47850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3453" s="1">
-        <x:v>0</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3453" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3453" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3453" s="1">
-        <x:v>52850</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="3454" spans="1:7">
@@ -90624,22 +90624,22 @@
         <x:v>3436</x:v>
       </x:c>
       <x:c r="B3463" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="C3463" s="1">
-        <x:v>3000</x:v>
+        <x:v>437150</x:v>
       </x:c>
       <x:c r="D3463" s="1">
-        <x:v>0</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="E3463" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3463" s="1">
-        <x:v>0</x:v>
+        <x:v>348550</x:v>
       </x:c>
       <x:c r="G3463" s="1">
-        <x:v>3000</x:v>
+        <x:v>786168</x:v>
       </x:c>
     </x:row>
     <x:row r="3464" spans="1:7">
@@ -90647,10 +90647,10 @@
         <x:v>3436</x:v>
       </x:c>
       <x:c r="B3464" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C3464" s="1">
-        <x:v>22500</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D3464" s="1">
         <x:v>0</x:v>
@@ -90662,7 +90662,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G3464" s="1">
-        <x:v>22500</x:v>
+        <x:v>3000</x:v>
       </x:c>
     </x:row>
     <x:row r="3465" spans="1:7">
@@ -90670,22 +90670,22 @@
         <x:v>3436</x:v>
       </x:c>
       <x:c r="B3465" s="1" t="s">
-        <x:v>416</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C3465" s="1">
-        <x:v>437150</x:v>
+        <x:v>22500</x:v>
       </x:c>
       <x:c r="D3465" s="1">
-        <x:v>468</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3465" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3465" s="1">
-        <x:v>348550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3465" s="1">
-        <x:v>786168</x:v>
+        <x:v>22500</x:v>
       </x:c>
     </x:row>
     <x:row r="3466" spans="1:7">
@@ -91383,22 +91383,22 @@
         <x:v>3466</x:v>
       </x:c>
       <x:c r="B3496" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C3496" s="1">
-        <x:v>0</x:v>
+        <x:v>265983</x:v>
       </x:c>
       <x:c r="D3496" s="1">
-        <x:v>59</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="E3496" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3496" s="1">
-        <x:v>44000</x:v>
+        <x:v>126150</x:v>
       </x:c>
       <x:c r="G3496" s="1">
-        <x:v>44059</x:v>
+        <x:v>392310</x:v>
       </x:c>
     </x:row>
     <x:row r="3497" spans="1:7">
@@ -91406,22 +91406,22 @@
         <x:v>3466</x:v>
       </x:c>
       <x:c r="B3497" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C3497" s="1">
-        <x:v>265983</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3497" s="1">
-        <x:v>177</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3497" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3497" s="1">
-        <x:v>126150</x:v>
+        <x:v>44000</x:v>
       </x:c>
       <x:c r="G3497" s="1">
-        <x:v>392310</x:v>
+        <x:v>44059</x:v>
       </x:c>
     </x:row>
     <x:row r="3498" spans="1:7">
@@ -92395,10 +92395,10 @@
         <x:v>3507</x:v>
       </x:c>
       <x:c r="B3540" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C3540" s="1">
-        <x:v>0</x:v>
+        <x:v>130750</x:v>
       </x:c>
       <x:c r="D3540" s="1">
         <x:v>7</x:v>
@@ -92407,10 +92407,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3540" s="1">
-        <x:v>0</x:v>
+        <x:v>83750</x:v>
       </x:c>
       <x:c r="G3540" s="1">
-        <x:v>7</x:v>
+        <x:v>214507</x:v>
       </x:c>
     </x:row>
     <x:row r="3541" spans="1:7">
@@ -92418,10 +92418,10 @@
         <x:v>3507</x:v>
       </x:c>
       <x:c r="B3541" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C3541" s="1">
-        <x:v>130750</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3541" s="1">
         <x:v>7</x:v>
@@ -92430,10 +92430,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3541" s="1">
-        <x:v>83750</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3541" s="1">
-        <x:v>214507</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="3542" spans="1:7">

--- a/reports/pro-oil/pro-oil-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-oil/pro-oil-candidate-lobby-lifetime-report.xlsx
@@ -19215,10 +19215,10 @@
         <x:v>412</x:v>
       </x:c>
       <x:c r="B358" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C358" s="1">
-        <x:v>15000</x:v>
+        <x:v>163000</x:v>
       </x:c>
       <x:c r="D358" s="1">
         <x:v>0</x:v>
@@ -19227,10 +19227,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F358" s="1">
-        <x:v>0</x:v>
+        <x:v>82550</x:v>
       </x:c>
       <x:c r="G358" s="1">
-        <x:v>15000</x:v>
+        <x:v>245550</x:v>
       </x:c>
     </x:row>
     <x:row r="359" spans="1:7">
@@ -19238,10 +19238,10 @@
         <x:v>412</x:v>
       </x:c>
       <x:c r="B359" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C359" s="1">
-        <x:v>163000</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D359" s="1">
         <x:v>0</x:v>
@@ -19250,10 +19250,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F359" s="1">
-        <x:v>82550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G359" s="1">
-        <x:v>245550</x:v>
+        <x:v>15000</x:v>
       </x:c>
     </x:row>
     <x:row r="360" spans="1:7">
@@ -21009,11 +21009,11 @@
         <x:v>488</x:v>
       </x:c>
       <x:c r="B436" s="1" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C436" s="1">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="C436" s="1">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="D436" s="1">
         <x:v>0</x:v>
       </x:c>
@@ -21021,10 +21021,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F436" s="1">
-        <x:v>40350</x:v>
+        <x:v>13450</x:v>
       </x:c>
       <x:c r="G436" s="1">
-        <x:v>40350</x:v>
+        <x:v>13500</x:v>
       </x:c>
     </x:row>
     <x:row r="437" spans="1:7">
@@ -21032,10 +21032,10 @@
         <x:v>488</x:v>
       </x:c>
       <x:c r="B437" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C437" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D437" s="1">
         <x:v>0</x:v>
@@ -21044,10 +21044,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F437" s="1">
-        <x:v>13450</x:v>
+        <x:v>40350</x:v>
       </x:c>
       <x:c r="G437" s="1">
-        <x:v>13500</x:v>
+        <x:v>40350</x:v>
       </x:c>
     </x:row>
     <x:row r="438" spans="1:7">
@@ -27196,22 +27196,22 @@
         <x:v>757</x:v>
       </x:c>
       <x:c r="B705" s="1" t="s">
-        <x:v>747</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C705" s="1">
-        <x:v>418533</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D705" s="1">
-        <x:v>118</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E705" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F705" s="1">
-        <x:v>51350</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G705" s="1">
-        <x:v>470001</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="706" spans="1:7">
@@ -27219,22 +27219,22 @@
         <x:v>757</x:v>
       </x:c>
       <x:c r="B706" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>747</x:v>
       </x:c>
       <x:c r="C706" s="1">
-        <x:v>25500</x:v>
+        <x:v>418533</x:v>
       </x:c>
       <x:c r="D706" s="1">
-        <x:v>0</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E706" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F706" s="1">
-        <x:v>0</x:v>
+        <x:v>51350</x:v>
       </x:c>
       <x:c r="G706" s="1">
-        <x:v>25500</x:v>
+        <x:v>470001</x:v>
       </x:c>
     </x:row>
     <x:row r="707" spans="1:7">
@@ -31382,22 +31382,22 @@
         <x:v>935</x:v>
       </x:c>
       <x:c r="B887" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="C887" s="1">
-        <x:v>91000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D887" s="1">
-        <x:v>118</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E887" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F887" s="1">
-        <x:v>26100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G887" s="1">
-        <x:v>117218</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="888" spans="1:7">
@@ -31405,22 +31405,22 @@
         <x:v>935</x:v>
       </x:c>
       <x:c r="B888" s="1" t="s">
-        <x:v>297</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C888" s="1">
-        <x:v>0</x:v>
+        <x:v>91000</x:v>
       </x:c>
       <x:c r="D888" s="1">
-        <x:v>59</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E888" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F888" s="1">
-        <x:v>0</x:v>
+        <x:v>26100</x:v>
       </x:c>
       <x:c r="G888" s="1">
-        <x:v>59</x:v>
+        <x:v>117218</x:v>
       </x:c>
     </x:row>
     <x:row r="889" spans="1:7">
@@ -38811,10 +38811,10 @@
         <x:v>1251</x:v>
       </x:c>
       <x:c r="B1210" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C1210" s="1">
-        <x:v>3000</x:v>
+        <x:v>12000</x:v>
       </x:c>
       <x:c r="D1210" s="1">
         <x:v>0</x:v>
@@ -38823,10 +38823,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1210" s="1">
-        <x:v>50751</x:v>
+        <x:v>12450</x:v>
       </x:c>
       <x:c r="G1210" s="1">
-        <x:v>53751</x:v>
+        <x:v>24450</x:v>
       </x:c>
     </x:row>
     <x:row r="1211" spans="1:7">
@@ -38834,10 +38834,10 @@
         <x:v>1251</x:v>
       </x:c>
       <x:c r="B1211" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C1211" s="1">
-        <x:v>12000</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D1211" s="1">
         <x:v>0</x:v>
@@ -38846,10 +38846,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1211" s="1">
-        <x:v>12450</x:v>
+        <x:v>50751</x:v>
       </x:c>
       <x:c r="G1211" s="1">
-        <x:v>24450</x:v>
+        <x:v>53751</x:v>
       </x:c>
     </x:row>
     <x:row r="1212" spans="1:7">
@@ -46401,10 +46401,10 @@
         <x:v>1579</x:v>
       </x:c>
       <x:c r="B1540" s="1" t="s">
-        <x:v>164</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C1540" s="1">
-        <x:v>82250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1540" s="1">
         <x:v>0</x:v>
@@ -46413,10 +46413,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1540" s="1">
-        <x:v>9000</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1540" s="1">
-        <x:v>91250</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="1541" spans="1:7">
@@ -46424,10 +46424,10 @@
         <x:v>1579</x:v>
       </x:c>
       <x:c r="B1541" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="C1541" s="1">
-        <x:v>0</x:v>
+        <x:v>82250</x:v>
       </x:c>
       <x:c r="D1541" s="1">
         <x:v>0</x:v>
@@ -46436,10 +46436,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1541" s="1">
-        <x:v>1000</x:v>
+        <x:v>9000</x:v>
       </x:c>
       <x:c r="G1541" s="1">
-        <x:v>1000</x:v>
+        <x:v>91250</x:v>
       </x:c>
     </x:row>
     <x:row r="1542" spans="1:7">
@@ -47091,10 +47091,10 @@
         <x:v>1606</x:v>
       </x:c>
       <x:c r="B1570" s="1" t="s">
-        <x:v>416</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C1570" s="1">
-        <x:v>181700</x:v>
+        <x:v>8000</x:v>
       </x:c>
       <x:c r="D1570" s="1">
         <x:v>0</x:v>
@@ -47103,10 +47103,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1570" s="1">
-        <x:v>168050</x:v>
+        <x:v>66000</x:v>
       </x:c>
       <x:c r="G1570" s="1">
-        <x:v>349750</x:v>
+        <x:v>74000</x:v>
       </x:c>
     </x:row>
     <x:row r="1571" spans="1:7">
@@ -47114,10 +47114,10 @@
         <x:v>1606</x:v>
       </x:c>
       <x:c r="B1571" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="C1571" s="1">
-        <x:v>8000</x:v>
+        <x:v>181700</x:v>
       </x:c>
       <x:c r="D1571" s="1">
         <x:v>0</x:v>
@@ -47126,10 +47126,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1571" s="1">
-        <x:v>66000</x:v>
+        <x:v>168050</x:v>
       </x:c>
       <x:c r="G1571" s="1">
-        <x:v>74000</x:v>
+        <x:v>349750</x:v>
       </x:c>
     </x:row>
     <x:row r="1572" spans="1:7">
@@ -49736,10 +49736,10 @@
         <x:v>1719</x:v>
       </x:c>
       <x:c r="B1685" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C1685" s="1">
-        <x:v>0</x:v>
+        <x:v>27850</x:v>
       </x:c>
       <x:c r="D1685" s="1">
         <x:v>0</x:v>
@@ -49748,10 +49748,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1685" s="1">
-        <x:v>102225</x:v>
+        <x:v>19000</x:v>
       </x:c>
       <x:c r="G1685" s="1">
-        <x:v>102225</x:v>
+        <x:v>46850</x:v>
       </x:c>
     </x:row>
     <x:row r="1686" spans="1:7">
@@ -49759,10 +49759,10 @@
         <x:v>1719</x:v>
       </x:c>
       <x:c r="B1686" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C1686" s="1">
-        <x:v>27850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1686" s="1">
         <x:v>0</x:v>
@@ -49771,10 +49771,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1686" s="1">
-        <x:v>19000</x:v>
+        <x:v>102225</x:v>
       </x:c>
       <x:c r="G1686" s="1">
-        <x:v>46850</x:v>
+        <x:v>102225</x:v>
       </x:c>
     </x:row>
     <x:row r="1687" spans="1:7">
@@ -50702,10 +50702,10 @@
         <x:v>1760</x:v>
       </x:c>
       <x:c r="B1727" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1727" s="1">
-        <x:v>485</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1727" s="1">
         <x:v>0</x:v>
@@ -50714,10 +50714,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1727" s="1">
-        <x:v>72700</x:v>
+        <x:v>16350</x:v>
       </x:c>
       <x:c r="G1727" s="1">
-        <x:v>73185</x:v>
+        <x:v>18850</x:v>
       </x:c>
     </x:row>
     <x:row r="1728" spans="1:7">
@@ -50725,10 +50725,10 @@
         <x:v>1760</x:v>
       </x:c>
       <x:c r="B1728" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C1728" s="1">
-        <x:v>2500</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="D1728" s="1">
         <x:v>0</x:v>
@@ -50737,10 +50737,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1728" s="1">
-        <x:v>16350</x:v>
+        <x:v>72700</x:v>
       </x:c>
       <x:c r="G1728" s="1">
-        <x:v>18850</x:v>
+        <x:v>73185</x:v>
       </x:c>
     </x:row>
     <x:row r="1729" spans="1:7">
@@ -52841,10 +52841,10 @@
         <x:v>1850</x:v>
       </x:c>
       <x:c r="B1820" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C1820" s="1">
-        <x:v>-1000</x:v>
+        <x:v>147100</x:v>
       </x:c>
       <x:c r="D1820" s="1">
         <x:v>0</x:v>
@@ -52853,10 +52853,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1820" s="1">
-        <x:v>0</x:v>
+        <x:v>34550</x:v>
       </x:c>
       <x:c r="G1820" s="1">
-        <x:v>-1000</x:v>
+        <x:v>181650</x:v>
       </x:c>
     </x:row>
     <x:row r="1821" spans="1:7">
@@ -52864,10 +52864,10 @@
         <x:v>1850</x:v>
       </x:c>
       <x:c r="B1821" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C1821" s="1">
-        <x:v>147100</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="D1821" s="1">
         <x:v>0</x:v>
@@ -52876,10 +52876,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1821" s="1">
-        <x:v>34550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1821" s="1">
-        <x:v>181650</x:v>
+        <x:v>-1000</x:v>
       </x:c>
     </x:row>
     <x:row r="1822" spans="1:7">
@@ -55670,22 +55670,22 @@
         <x:v>1970</x:v>
       </x:c>
       <x:c r="B1943" s="1" t="s">
-        <x:v>155</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C1943" s="1">
-        <x:v>0</x:v>
+        <x:v>299950</x:v>
       </x:c>
       <x:c r="D1943" s="1">
-        <x:v>59</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E1943" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1943" s="1">
-        <x:v>0</x:v>
+        <x:v>178350</x:v>
       </x:c>
       <x:c r="G1943" s="1">
-        <x:v>59</x:v>
+        <x:v>478595</x:v>
       </x:c>
     </x:row>
     <x:row r="1944" spans="1:7">
@@ -55693,22 +55693,22 @@
         <x:v>1970</x:v>
       </x:c>
       <x:c r="B1944" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="C1944" s="1">
-        <x:v>299950</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1944" s="1">
-        <x:v>295</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E1944" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1944" s="1">
-        <x:v>178350</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1944" s="1">
-        <x:v>478595</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="1945" spans="1:7">
@@ -72345,10 +72345,10 @@
         <x:v>2685</x:v>
       </x:c>
       <x:c r="B2668" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C2668" s="1">
-        <x:v>7061</x:v>
+        <x:v>409250</x:v>
       </x:c>
       <x:c r="D2668" s="1">
         <x:v>0</x:v>
@@ -72357,10 +72357,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2668" s="1">
-        <x:v>23500</x:v>
+        <x:v>159800</x:v>
       </x:c>
       <x:c r="G2668" s="1">
-        <x:v>30561</x:v>
+        <x:v>569050</x:v>
       </x:c>
     </x:row>
     <x:row r="2669" spans="1:7">
@@ -72368,10 +72368,10 @@
         <x:v>2685</x:v>
       </x:c>
       <x:c r="B2669" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C2669" s="1">
-        <x:v>409250</x:v>
+        <x:v>7061</x:v>
       </x:c>
       <x:c r="D2669" s="1">
         <x:v>0</x:v>
@@ -72380,10 +72380,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2669" s="1">
-        <x:v>159800</x:v>
+        <x:v>23500</x:v>
       </x:c>
       <x:c r="G2669" s="1">
-        <x:v>569050</x:v>
+        <x:v>30561</x:v>
       </x:c>
     </x:row>
     <x:row r="2670" spans="1:7">
@@ -72506,10 +72506,10 @@
         <x:v>2691</x:v>
       </x:c>
       <x:c r="B2675" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C2675" s="1">
-        <x:v>139000</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D2675" s="1">
         <x:v>0</x:v>
@@ -72518,10 +72518,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2675" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2675" s="1">
-        <x:v>139500</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="2676" spans="1:7">
@@ -72529,10 +72529,10 @@
         <x:v>2691</x:v>
       </x:c>
       <x:c r="B2676" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C2676" s="1">
-        <x:v>7000</x:v>
+        <x:v>139000</x:v>
       </x:c>
       <x:c r="D2676" s="1">
         <x:v>0</x:v>
@@ -72541,10 +72541,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2676" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G2676" s="1">
-        <x:v>7000</x:v>
+        <x:v>139500</x:v>
       </x:c>
     </x:row>
     <x:row r="2677" spans="1:7">
@@ -75312,10 +75312,10 @@
         <x:v>2811</x:v>
       </x:c>
       <x:c r="B2797" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C2797" s="1">
-        <x:v>163800</x:v>
+        <x:v>206766</x:v>
       </x:c>
       <x:c r="D2797" s="1">
         <x:v>0</x:v>
@@ -75324,10 +75324,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2797" s="1">
-        <x:v>277645</x:v>
+        <x:v>286825</x:v>
       </x:c>
       <x:c r="G2797" s="1">
-        <x:v>441445</x:v>
+        <x:v>493591</x:v>
       </x:c>
     </x:row>
     <x:row r="2798" spans="1:7">
@@ -75358,10 +75358,10 @@
         <x:v>2811</x:v>
       </x:c>
       <x:c r="B2799" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C2799" s="1">
-        <x:v>206766</x:v>
+        <x:v>163800</x:v>
       </x:c>
       <x:c r="D2799" s="1">
         <x:v>0</x:v>
@@ -75370,10 +75370,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2799" s="1">
-        <x:v>286825</x:v>
+        <x:v>277645</x:v>
       </x:c>
       <x:c r="G2799" s="1">
-        <x:v>493591</x:v>
+        <x:v>441445</x:v>
       </x:c>
     </x:row>
     <x:row r="2800" spans="1:7">
@@ -76853,10 +76853,10 @@
         <x:v>2875</x:v>
       </x:c>
       <x:c r="B2864" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C2864" s="1">
-        <x:v>15000</x:v>
+        <x:v>102350</x:v>
       </x:c>
       <x:c r="D2864" s="1">
         <x:v>0</x:v>
@@ -76865,10 +76865,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2864" s="1">
-        <x:v>5000</x:v>
+        <x:v>106550</x:v>
       </x:c>
       <x:c r="G2864" s="1">
-        <x:v>20000</x:v>
+        <x:v>208900</x:v>
       </x:c>
     </x:row>
     <x:row r="2865" spans="1:7">
@@ -76876,10 +76876,10 @@
         <x:v>2875</x:v>
       </x:c>
       <x:c r="B2865" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C2865" s="1">
-        <x:v>102350</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D2865" s="1">
         <x:v>0</x:v>
@@ -76888,10 +76888,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2865" s="1">
-        <x:v>106550</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G2865" s="1">
-        <x:v>208900</x:v>
+        <x:v>20000</x:v>
       </x:c>
     </x:row>
     <x:row r="2866" spans="1:7">
@@ -78624,10 +78624,10 @@
         <x:v>2950</x:v>
       </x:c>
       <x:c r="B2941" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C2941" s="1">
-        <x:v>99950</x:v>
+        <x:v>12000</x:v>
       </x:c>
       <x:c r="D2941" s="1">
         <x:v>0</x:v>
@@ -78636,10 +78636,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2941" s="1">
-        <x:v>6650</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2941" s="1">
-        <x:v>106600</x:v>
+        <x:v>12000</x:v>
       </x:c>
     </x:row>
     <x:row r="2942" spans="1:7">
@@ -78647,10 +78647,10 @@
         <x:v>2950</x:v>
       </x:c>
       <x:c r="B2942" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C2942" s="1">
-        <x:v>12000</x:v>
+        <x:v>99950</x:v>
       </x:c>
       <x:c r="D2942" s="1">
         <x:v>0</x:v>
@@ -78659,10 +78659,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2942" s="1">
-        <x:v>0</x:v>
+        <x:v>6650</x:v>
       </x:c>
       <x:c r="G2942" s="1">
-        <x:v>12000</x:v>
+        <x:v>106600</x:v>
       </x:c>
     </x:row>
     <x:row r="2943" spans="1:7">
@@ -79314,10 +79314,10 @@
         <x:v>2978</x:v>
       </x:c>
       <x:c r="B2971" s="1" t="s">
-        <x:v>747</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C2971" s="1">
-        <x:v>286800</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D2971" s="1">
         <x:v>0</x:v>
@@ -79326,10 +79326,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2971" s="1">
-        <x:v>75150</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2971" s="1">
-        <x:v>361950</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="2972" spans="1:7">
@@ -79337,10 +79337,10 @@
         <x:v>2978</x:v>
       </x:c>
       <x:c r="B2972" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>747</x:v>
       </x:c>
       <x:c r="C2972" s="1">
-        <x:v>5000</x:v>
+        <x:v>286800</x:v>
       </x:c>
       <x:c r="D2972" s="1">
         <x:v>0</x:v>
@@ -79349,10 +79349,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2972" s="1">
-        <x:v>0</x:v>
+        <x:v>75150</x:v>
       </x:c>
       <x:c r="G2972" s="1">
-        <x:v>5000</x:v>
+        <x:v>361950</x:v>
       </x:c>
     </x:row>
     <x:row r="2973" spans="1:7">
@@ -81085,22 +81085,22 @@
         <x:v>3053</x:v>
       </x:c>
       <x:c r="B3048" s="1" t="s">
-        <x:v>256</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C3048" s="1">
-        <x:v>7000</x:v>
+        <x:v>71750</x:v>
       </x:c>
       <x:c r="D3048" s="1">
-        <x:v>0</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="E3048" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3048" s="1">
-        <x:v>0</x:v>
+        <x:v>77150</x:v>
       </x:c>
       <x:c r="G3048" s="1">
-        <x:v>7000</x:v>
+        <x:v>149077</x:v>
       </x:c>
     </x:row>
     <x:row r="3049" spans="1:7">
@@ -81108,22 +81108,22 @@
         <x:v>3053</x:v>
       </x:c>
       <x:c r="B3049" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="C3049" s="1">
-        <x:v>71750</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D3049" s="1">
-        <x:v>177</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3049" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3049" s="1">
-        <x:v>77150</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3049" s="1">
-        <x:v>149077</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="3050" spans="1:7">
@@ -84995,10 +84995,10 @@
         <x:v>3210</x:v>
       </x:c>
       <x:c r="B3218" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C3218" s="1">
-        <x:v>2300</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D3218" s="1">
         <x:v>0</x:v>
@@ -85007,10 +85007,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3218" s="1">
-        <x:v>8850</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="G3218" s="1">
-        <x:v>11150</x:v>
+        <x:v>9000</x:v>
       </x:c>
     </x:row>
     <x:row r="3219" spans="1:7">
@@ -85018,10 +85018,10 @@
         <x:v>3210</x:v>
       </x:c>
       <x:c r="B3219" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C3219" s="1">
-        <x:v>3000</x:v>
+        <x:v>2300</x:v>
       </x:c>
       <x:c r="D3219" s="1">
         <x:v>0</x:v>
@@ -85030,10 +85030,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3219" s="1">
-        <x:v>6000</x:v>
+        <x:v>8850</x:v>
       </x:c>
       <x:c r="G3219" s="1">
-        <x:v>9000</x:v>
+        <x:v>11150</x:v>
       </x:c>
     </x:row>
     <x:row r="3220" spans="1:7">
@@ -85524,10 +85524,10 @@
         <x:v>3230</x:v>
       </x:c>
       <x:c r="B3241" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C3241" s="1">
-        <x:v>343100</x:v>
+        <x:v>34000</x:v>
       </x:c>
       <x:c r="D3241" s="1">
         <x:v>0</x:v>
@@ -85536,10 +85536,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3241" s="1">
-        <x:v>244972</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3241" s="1">
-        <x:v>588072</x:v>
+        <x:v>34000</x:v>
       </x:c>
     </x:row>
     <x:row r="3242" spans="1:7">
@@ -85547,10 +85547,10 @@
         <x:v>3230</x:v>
       </x:c>
       <x:c r="B3242" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C3242" s="1">
-        <x:v>34000</x:v>
+        <x:v>343100</x:v>
       </x:c>
       <x:c r="D3242" s="1">
         <x:v>0</x:v>
@@ -85559,10 +85559,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3242" s="1">
-        <x:v>0</x:v>
+        <x:v>244972</x:v>
       </x:c>
       <x:c r="G3242" s="1">
-        <x:v>34000</x:v>
+        <x:v>588072</x:v>
       </x:c>
     </x:row>
     <x:row r="3243" spans="1:7">
@@ -87755,13 +87755,13 @@
         <x:v>3323</x:v>
       </x:c>
       <x:c r="B3338" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="C3338" s="1">
-        <x:v>0</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D3338" s="1">
-        <x:v>59</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E3338" s="1">
         <x:v>0</x:v>
@@ -87770,7 +87770,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G3338" s="1">
-        <x:v>59</x:v>
+        <x:v>15063</x:v>
       </x:c>
     </x:row>
     <x:row r="3339" spans="1:7">
@@ -87778,13 +87778,13 @@
         <x:v>3323</x:v>
       </x:c>
       <x:c r="B3339" s="1" t="s">
-        <x:v>256</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C3339" s="1">
-        <x:v>15000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3339" s="1">
-        <x:v>63</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3339" s="1">
         <x:v>0</x:v>
@@ -87793,7 +87793,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G3339" s="1">
-        <x:v>15063</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="3340" spans="1:7">
@@ -87847,22 +87847,22 @@
         <x:v>3325</x:v>
       </x:c>
       <x:c r="B3342" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C3342" s="1">
-        <x:v>7000</x:v>
+        <x:v>116050</x:v>
       </x:c>
       <x:c r="D3342" s="1">
-        <x:v>63</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="E3342" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3342" s="1">
-        <x:v>7000</x:v>
+        <x:v>47699</x:v>
       </x:c>
       <x:c r="G3342" s="1">
-        <x:v>14063</x:v>
+        <x:v>163985</x:v>
       </x:c>
     </x:row>
     <x:row r="3343" spans="1:7">
@@ -87870,22 +87870,22 @@
         <x:v>3325</x:v>
       </x:c>
       <x:c r="B3343" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C3343" s="1">
-        <x:v>116050</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D3343" s="1">
-        <x:v>236</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E3343" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3343" s="1">
-        <x:v>47699</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="G3343" s="1">
-        <x:v>163985</x:v>
+        <x:v>14063</x:v>
       </x:c>
     </x:row>
     <x:row r="3344" spans="1:7">
@@ -88928,10 +88928,10 @@
         <x:v>3370</x:v>
       </x:c>
       <x:c r="B3389" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C3389" s="1">
-        <x:v>15000</x:v>
+        <x:v>41550</x:v>
       </x:c>
       <x:c r="D3389" s="1">
         <x:v>0</x:v>
@@ -88940,10 +88940,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3389" s="1">
-        <x:v>0</x:v>
+        <x:v>6500</x:v>
       </x:c>
       <x:c r="G3389" s="1">
-        <x:v>15000</x:v>
+        <x:v>48050</x:v>
       </x:c>
     </x:row>
     <x:row r="3390" spans="1:7">
@@ -88951,10 +88951,10 @@
         <x:v>3370</x:v>
       </x:c>
       <x:c r="B3390" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C3390" s="1">
-        <x:v>41550</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D3390" s="1">
         <x:v>0</x:v>
@@ -88963,10 +88963,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3390" s="1">
-        <x:v>6500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3390" s="1">
-        <x:v>48050</x:v>
+        <x:v>15000</x:v>
       </x:c>
     </x:row>
     <x:row r="3391" spans="1:7">
@@ -90193,22 +90193,22 @@
         <x:v>3420</x:v>
       </x:c>
       <x:c r="B3444" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C3444" s="1">
-        <x:v>72750</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3444" s="1">
-        <x:v>295</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3444" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3444" s="1">
-        <x:v>25450</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3444" s="1">
-        <x:v>98495</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="3445" spans="1:7">
@@ -90216,22 +90216,22 @@
         <x:v>3420</x:v>
       </x:c>
       <x:c r="B3445" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C3445" s="1">
-        <x:v>0</x:v>
+        <x:v>72750</x:v>
       </x:c>
       <x:c r="D3445" s="1">
-        <x:v>59</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E3445" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3445" s="1">
-        <x:v>0</x:v>
+        <x:v>25450</x:v>
       </x:c>
       <x:c r="G3445" s="1">
-        <x:v>59</x:v>
+        <x:v>98495</x:v>
       </x:c>
     </x:row>
     <x:row r="3446" spans="1:7">
@@ -90423,22 +90423,22 @@
         <x:v>3428</x:v>
       </x:c>
       <x:c r="B3454" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C3454" s="1">
-        <x:v>0</x:v>
+        <x:v>47850</x:v>
       </x:c>
       <x:c r="D3454" s="1">
-        <x:v>59</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3454" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3454" s="1">
-        <x:v>0</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G3454" s="1">
-        <x:v>59</x:v>
+        <x:v>52850</x:v>
       </x:c>
     </x:row>
     <x:row r="3455" spans="1:7">
@@ -90446,22 +90446,22 @@
         <x:v>3428</x:v>
       </x:c>
       <x:c r="B3455" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C3455" s="1">
-        <x:v>47850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3455" s="1">
-        <x:v>0</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3455" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3455" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3455" s="1">
-        <x:v>52850</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="3456" spans="1:7">
@@ -90699,10 +90699,10 @@
         <x:v>3438</x:v>
       </x:c>
       <x:c r="B3466" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C3466" s="1">
-        <x:v>3000</x:v>
+        <x:v>22500</x:v>
       </x:c>
       <x:c r="D3466" s="1">
         <x:v>0</x:v>
@@ -90714,7 +90714,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G3466" s="1">
-        <x:v>3000</x:v>
+        <x:v>22500</x:v>
       </x:c>
     </x:row>
     <x:row r="3467" spans="1:7">
@@ -90722,10 +90722,10 @@
         <x:v>3438</x:v>
       </x:c>
       <x:c r="B3467" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C3467" s="1">
-        <x:v>22500</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D3467" s="1">
         <x:v>0</x:v>
@@ -90737,7 +90737,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G3467" s="1">
-        <x:v>22500</x:v>
+        <x:v>3000</x:v>
       </x:c>
     </x:row>
     <x:row r="3468" spans="1:7">
@@ -91435,22 +91435,22 @@
         <x:v>3468</x:v>
       </x:c>
       <x:c r="B3498" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C3498" s="1">
-        <x:v>265983</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3498" s="1">
-        <x:v>177</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3498" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3498" s="1">
-        <x:v>126150</x:v>
+        <x:v>44000</x:v>
       </x:c>
       <x:c r="G3498" s="1">
-        <x:v>392310</x:v>
+        <x:v>44059</x:v>
       </x:c>
     </x:row>
     <x:row r="3499" spans="1:7">
@@ -91458,22 +91458,22 @@
         <x:v>3468</x:v>
       </x:c>
       <x:c r="B3499" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C3499" s="1">
-        <x:v>0</x:v>
+        <x:v>265983</x:v>
       </x:c>
       <x:c r="D3499" s="1">
-        <x:v>59</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="E3499" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3499" s="1">
-        <x:v>44000</x:v>
+        <x:v>126150</x:v>
       </x:c>
       <x:c r="G3499" s="1">
-        <x:v>44059</x:v>
+        <x:v>392310</x:v>
       </x:c>
     </x:row>
     <x:row r="3500" spans="1:7">

--- a/reports/pro-oil/pro-oil-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-oil/pro-oil-candidate-lobby-lifetime-report.xlsx
@@ -19353,10 +19353,10 @@
         <x:v>418</x:v>
       </x:c>
       <x:c r="B364" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C364" s="1">
-        <x:v>3000</x:v>
+        <x:v>107540</x:v>
       </x:c>
       <x:c r="D364" s="1">
         <x:v>0</x:v>
@@ -19365,10 +19365,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F364" s="1">
-        <x:v>25150</x:v>
+        <x:v>59170</x:v>
       </x:c>
       <x:c r="G364" s="1">
-        <x:v>28150</x:v>
+        <x:v>166710</x:v>
       </x:c>
     </x:row>
     <x:row r="365" spans="1:7">
@@ -19376,10 +19376,10 @@
         <x:v>418</x:v>
       </x:c>
       <x:c r="B365" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C365" s="1">
-        <x:v>107540</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D365" s="1">
         <x:v>0</x:v>
@@ -19388,10 +19388,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F365" s="1">
-        <x:v>59170</x:v>
+        <x:v>25150</x:v>
       </x:c>
       <x:c r="G365" s="1">
-        <x:v>166710</x:v>
+        <x:v>28150</x:v>
       </x:c>
     </x:row>
     <x:row r="366" spans="1:7">
@@ -30784,10 +30784,10 @@
         <x:v>911</x:v>
       </x:c>
       <x:c r="B861" s="1" t="s">
-        <x:v>258</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C861" s="1">
-        <x:v>3000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D861" s="1">
         <x:v>0</x:v>
@@ -30796,10 +30796,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F861" s="1">
-        <x:v>12950</x:v>
+        <x:v>14450</x:v>
       </x:c>
       <x:c r="G861" s="1">
-        <x:v>15950</x:v>
+        <x:v>14450</x:v>
       </x:c>
     </x:row>
     <x:row r="862" spans="1:7">
@@ -30807,10 +30807,10 @@
         <x:v>911</x:v>
       </x:c>
       <x:c r="B862" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="C862" s="1">
-        <x:v>0</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D862" s="1">
         <x:v>0</x:v>
@@ -30819,10 +30819,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F862" s="1">
-        <x:v>14450</x:v>
+        <x:v>12950</x:v>
       </x:c>
       <x:c r="G862" s="1">
-        <x:v>14450</x:v>
+        <x:v>15950</x:v>
       </x:c>
     </x:row>
     <x:row r="863" spans="1:7">
@@ -31382,22 +31382,22 @@
         <x:v>935</x:v>
       </x:c>
       <x:c r="B887" s="1" t="s">
-        <x:v>297</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C887" s="1">
-        <x:v>0</x:v>
+        <x:v>91000</x:v>
       </x:c>
       <x:c r="D887" s="1">
-        <x:v>59</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E887" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F887" s="1">
-        <x:v>0</x:v>
+        <x:v>26100</x:v>
       </x:c>
       <x:c r="G887" s="1">
-        <x:v>59</x:v>
+        <x:v>117218</x:v>
       </x:c>
     </x:row>
     <x:row r="888" spans="1:7">
@@ -31405,22 +31405,22 @@
         <x:v>935</x:v>
       </x:c>
       <x:c r="B888" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="C888" s="1">
-        <x:v>91000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D888" s="1">
-        <x:v>118</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E888" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F888" s="1">
-        <x:v>26100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G888" s="1">
-        <x:v>117218</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="889" spans="1:7">
@@ -46401,10 +46401,10 @@
         <x:v>1579</x:v>
       </x:c>
       <x:c r="B1540" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="C1540" s="1">
-        <x:v>0</x:v>
+        <x:v>82250</x:v>
       </x:c>
       <x:c r="D1540" s="1">
         <x:v>0</x:v>
@@ -46413,10 +46413,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1540" s="1">
-        <x:v>1000</x:v>
+        <x:v>9000</x:v>
       </x:c>
       <x:c r="G1540" s="1">
-        <x:v>1000</x:v>
+        <x:v>91250</x:v>
       </x:c>
     </x:row>
     <x:row r="1541" spans="1:7">
@@ -46424,10 +46424,10 @@
         <x:v>1579</x:v>
       </x:c>
       <x:c r="B1541" s="1" t="s">
-        <x:v>164</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C1541" s="1">
-        <x:v>82250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1541" s="1">
         <x:v>0</x:v>
@@ -46436,10 +46436,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1541" s="1">
-        <x:v>9000</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1541" s="1">
-        <x:v>91250</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="1542" spans="1:7">
@@ -50702,10 +50702,10 @@
         <x:v>1760</x:v>
       </x:c>
       <x:c r="B1727" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C1727" s="1">
-        <x:v>2500</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="D1727" s="1">
         <x:v>0</x:v>
@@ -50714,10 +50714,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1727" s="1">
-        <x:v>16350</x:v>
+        <x:v>72700</x:v>
       </x:c>
       <x:c r="G1727" s="1">
-        <x:v>18850</x:v>
+        <x:v>73185</x:v>
       </x:c>
     </x:row>
     <x:row r="1728" spans="1:7">
@@ -50725,10 +50725,10 @@
         <x:v>1760</x:v>
       </x:c>
       <x:c r="B1728" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1728" s="1">
-        <x:v>485</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1728" s="1">
         <x:v>0</x:v>
@@ -50737,10 +50737,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1728" s="1">
-        <x:v>72700</x:v>
+        <x:v>16350</x:v>
       </x:c>
       <x:c r="G1728" s="1">
-        <x:v>73185</x:v>
+        <x:v>18850</x:v>
       </x:c>
     </x:row>
     <x:row r="1729" spans="1:7">
@@ -55670,22 +55670,22 @@
         <x:v>1970</x:v>
       </x:c>
       <x:c r="B1943" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="C1943" s="1">
-        <x:v>299950</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1943" s="1">
-        <x:v>295</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E1943" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1943" s="1">
-        <x:v>178350</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1943" s="1">
-        <x:v>478595</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="1944" spans="1:7">
@@ -55693,22 +55693,22 @@
         <x:v>1970</x:v>
       </x:c>
       <x:c r="B1944" s="1" t="s">
-        <x:v>155</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C1944" s="1">
-        <x:v>0</x:v>
+        <x:v>299950</x:v>
       </x:c>
       <x:c r="D1944" s="1">
-        <x:v>59</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E1944" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1944" s="1">
-        <x:v>0</x:v>
+        <x:v>178350</x:v>
       </x:c>
       <x:c r="G1944" s="1">
-        <x:v>59</x:v>
+        <x:v>478595</x:v>
       </x:c>
     </x:row>
     <x:row r="1945" spans="1:7">
@@ -56291,10 +56291,10 @@
         <x:v>1996</x:v>
       </x:c>
       <x:c r="B1970" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C1970" s="1">
-        <x:v>0</x:v>
+        <x:v>187150</x:v>
       </x:c>
       <x:c r="D1970" s="1">
         <x:v>31</x:v>
@@ -56303,10 +56303,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1970" s="1">
-        <x:v>0</x:v>
+        <x:v>6150</x:v>
       </x:c>
       <x:c r="G1970" s="1">
-        <x:v>31</x:v>
+        <x:v>193331</x:v>
       </x:c>
     </x:row>
     <x:row r="1971" spans="1:7">
@@ -56314,10 +56314,10 @@
         <x:v>1996</x:v>
       </x:c>
       <x:c r="B1971" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1971" s="1">
-        <x:v>187150</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1971" s="1">
         <x:v>31</x:v>
@@ -56326,10 +56326,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1971" s="1">
-        <x:v>6150</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1971" s="1">
-        <x:v>193331</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="1972" spans="1:7">
@@ -59787,10 +59787,10 @@
         <x:v>2144</x:v>
       </x:c>
       <x:c r="B2122" s="1" t="s">
-        <x:v>190</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C2122" s="1">
-        <x:v>960100</x:v>
+        <x:v>11000</x:v>
       </x:c>
       <x:c r="D2122" s="1">
         <x:v>0</x:v>
@@ -59799,10 +59799,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2122" s="1">
-        <x:v>882230</x:v>
+        <x:v>25550</x:v>
       </x:c>
       <x:c r="G2122" s="1">
-        <x:v>1842330</x:v>
+        <x:v>36550</x:v>
       </x:c>
     </x:row>
     <x:row r="2123" spans="1:7">
@@ -59810,10 +59810,10 @@
         <x:v>2144</x:v>
       </x:c>
       <x:c r="B2123" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C2123" s="1">
-        <x:v>11000</x:v>
+        <x:v>960100</x:v>
       </x:c>
       <x:c r="D2123" s="1">
         <x:v>0</x:v>
@@ -59822,10 +59822,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2123" s="1">
-        <x:v>25550</x:v>
+        <x:v>882230</x:v>
       </x:c>
       <x:c r="G2123" s="1">
-        <x:v>36550</x:v>
+        <x:v>1842330</x:v>
       </x:c>
     </x:row>
     <x:row r="2124" spans="1:7">
@@ -59902,10 +59902,10 @@
         <x:v>2148</x:v>
       </x:c>
       <x:c r="B2127" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C2127" s="1">
-        <x:v>22450</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="D2127" s="1">
         <x:v>0</x:v>
@@ -59914,10 +59914,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2127" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G2127" s="1">
         <x:v>250</x:v>
-      </x:c>
-      <x:c r="G2127" s="1">
-        <x:v>22700</x:v>
       </x:c>
     </x:row>
     <x:row r="2128" spans="1:7">
@@ -59925,22 +59925,22 @@
         <x:v>2148</x:v>
       </x:c>
       <x:c r="B2128" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C2128" s="1">
+        <x:v>22450</x:v>
+      </x:c>
+      <x:c r="D2128" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E2128" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F2128" s="1">
         <x:v>250</x:v>
       </x:c>
-      <x:c r="D2128" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E2128" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F2128" s="1">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="G2128" s="1">
-        <x:v>250</x:v>
+        <x:v>22700</x:v>
       </x:c>
     </x:row>
     <x:row r="2129" spans="1:7">
@@ -76853,10 +76853,10 @@
         <x:v>2875</x:v>
       </x:c>
       <x:c r="B2864" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C2864" s="1">
-        <x:v>102350</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D2864" s="1">
         <x:v>0</x:v>
@@ -76865,10 +76865,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2864" s="1">
-        <x:v>106550</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G2864" s="1">
-        <x:v>208900</x:v>
+        <x:v>20000</x:v>
       </x:c>
     </x:row>
     <x:row r="2865" spans="1:7">
@@ -76876,10 +76876,10 @@
         <x:v>2875</x:v>
       </x:c>
       <x:c r="B2865" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C2865" s="1">
-        <x:v>15000</x:v>
+        <x:v>102350</x:v>
       </x:c>
       <x:c r="D2865" s="1">
         <x:v>0</x:v>
@@ -76888,10 +76888,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2865" s="1">
-        <x:v>5000</x:v>
+        <x:v>106550</x:v>
       </x:c>
       <x:c r="G2865" s="1">
-        <x:v>20000</x:v>
+        <x:v>208900</x:v>
       </x:c>
     </x:row>
     <x:row r="2866" spans="1:7">
@@ -78210,10 +78210,10 @@
         <x:v>2933</x:v>
       </x:c>
       <x:c r="B2923" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C2923" s="1">
-        <x:v>206000</x:v>
+        <x:v>37500</x:v>
       </x:c>
       <x:c r="D2923" s="1">
         <x:v>0</x:v>
@@ -78222,10 +78222,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2923" s="1">
-        <x:v>45600</x:v>
+        <x:v>8000</x:v>
       </x:c>
       <x:c r="G2923" s="1">
-        <x:v>251600</x:v>
+        <x:v>45500</x:v>
       </x:c>
     </x:row>
     <x:row r="2924" spans="1:7">
@@ -78233,10 +78233,10 @@
         <x:v>2933</x:v>
       </x:c>
       <x:c r="B2924" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C2924" s="1">
-        <x:v>37500</x:v>
+        <x:v>206000</x:v>
       </x:c>
       <x:c r="D2924" s="1">
         <x:v>0</x:v>
@@ -78245,10 +78245,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2924" s="1">
-        <x:v>8000</x:v>
+        <x:v>45600</x:v>
       </x:c>
       <x:c r="G2924" s="1">
-        <x:v>45500</x:v>
+        <x:v>251600</x:v>
       </x:c>
     </x:row>
     <x:row r="2925" spans="1:7">
@@ -78670,22 +78670,22 @@
         <x:v>2951</x:v>
       </x:c>
       <x:c r="B2943" s="1" t="s">
-        <x:v>258</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C2943" s="1">
-        <x:v>10000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D2943" s="1">
-        <x:v>0</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E2943" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2943" s="1">
-        <x:v>4950</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2943" s="1">
-        <x:v>14950</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="2944" spans="1:7">
@@ -78693,22 +78693,22 @@
         <x:v>2951</x:v>
       </x:c>
       <x:c r="B2944" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="C2944" s="1">
-        <x:v>0</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="D2944" s="1">
-        <x:v>59</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E2944" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2944" s="1">
-        <x:v>0</x:v>
+        <x:v>4950</x:v>
       </x:c>
       <x:c r="G2944" s="1">
-        <x:v>59</x:v>
+        <x:v>14950</x:v>
       </x:c>
     </x:row>
     <x:row r="2945" spans="1:7">
@@ -79314,10 +79314,10 @@
         <x:v>2978</x:v>
       </x:c>
       <x:c r="B2971" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>747</x:v>
       </x:c>
       <x:c r="C2971" s="1">
-        <x:v>5000</x:v>
+        <x:v>286800</x:v>
       </x:c>
       <x:c r="D2971" s="1">
         <x:v>0</x:v>
@@ -79326,10 +79326,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2971" s="1">
-        <x:v>0</x:v>
+        <x:v>75150</x:v>
       </x:c>
       <x:c r="G2971" s="1">
-        <x:v>5000</x:v>
+        <x:v>361950</x:v>
       </x:c>
     </x:row>
     <x:row r="2972" spans="1:7">
@@ -79337,10 +79337,10 @@
         <x:v>2978</x:v>
       </x:c>
       <x:c r="B2972" s="1" t="s">
-        <x:v>747</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C2972" s="1">
-        <x:v>286800</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D2972" s="1">
         <x:v>0</x:v>
@@ -79349,10 +79349,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2972" s="1">
-        <x:v>75150</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2972" s="1">
-        <x:v>361950</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="2973" spans="1:7">
@@ -81085,22 +81085,22 @@
         <x:v>3053</x:v>
       </x:c>
       <x:c r="B3048" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="C3048" s="1">
-        <x:v>71750</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D3048" s="1">
-        <x:v>177</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3048" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3048" s="1">
-        <x:v>77150</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3048" s="1">
-        <x:v>149077</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="3049" spans="1:7">
@@ -81108,22 +81108,22 @@
         <x:v>3053</x:v>
       </x:c>
       <x:c r="B3049" s="1" t="s">
-        <x:v>256</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C3049" s="1">
-        <x:v>7000</x:v>
+        <x:v>71750</x:v>
       </x:c>
       <x:c r="D3049" s="1">
-        <x:v>0</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="E3049" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3049" s="1">
-        <x:v>0</x:v>
+        <x:v>77150</x:v>
       </x:c>
       <x:c r="G3049" s="1">
-        <x:v>7000</x:v>
+        <x:v>149077</x:v>
       </x:c>
     </x:row>
     <x:row r="3050" spans="1:7">
@@ -83063,10 +83063,10 @@
         <x:v>3132</x:v>
       </x:c>
       <x:c r="B3134" s="1" t="s">
-        <x:v>155</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C3134" s="1">
-        <x:v>48000</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D3134" s="1">
         <x:v>0</x:v>
@@ -83075,10 +83075,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3134" s="1">
-        <x:v>38300</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G3134" s="1">
-        <x:v>86300</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="3135" spans="1:7">
@@ -83086,10 +83086,10 @@
         <x:v>3132</x:v>
       </x:c>
       <x:c r="B3135" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="C3135" s="1">
-        <x:v>5000</x:v>
+        <x:v>48000</x:v>
       </x:c>
       <x:c r="D3135" s="1">
         <x:v>0</x:v>
@@ -83098,10 +83098,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3135" s="1">
-        <x:v>250</x:v>
+        <x:v>38300</x:v>
       </x:c>
       <x:c r="G3135" s="1">
-        <x:v>5250</x:v>
+        <x:v>86300</x:v>
       </x:c>
     </x:row>
     <x:row r="3136" spans="1:7">
@@ -84995,10 +84995,10 @@
         <x:v>3210</x:v>
       </x:c>
       <x:c r="B3218" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C3218" s="1">
-        <x:v>3000</x:v>
+        <x:v>2300</x:v>
       </x:c>
       <x:c r="D3218" s="1">
         <x:v>0</x:v>
@@ -85007,10 +85007,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3218" s="1">
-        <x:v>6000</x:v>
+        <x:v>8850</x:v>
       </x:c>
       <x:c r="G3218" s="1">
-        <x:v>9000</x:v>
+        <x:v>11150</x:v>
       </x:c>
     </x:row>
     <x:row r="3219" spans="1:7">
@@ -85018,10 +85018,10 @@
         <x:v>3210</x:v>
       </x:c>
       <x:c r="B3219" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C3219" s="1">
-        <x:v>2300</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D3219" s="1">
         <x:v>0</x:v>
@@ -85030,10 +85030,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3219" s="1">
-        <x:v>8850</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="G3219" s="1">
-        <x:v>11150</x:v>
+        <x:v>9000</x:v>
       </x:c>
     </x:row>
     <x:row r="3220" spans="1:7">
@@ -85915,22 +85915,22 @@
         <x:v>3245</x:v>
       </x:c>
       <x:c r="B3258" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C3258" s="1">
-        <x:v>25500</x:v>
+        <x:v>420650</x:v>
       </x:c>
       <x:c r="D3258" s="1">
-        <x:v>0</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="E3258" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3258" s="1">
-        <x:v>0</x:v>
+        <x:v>448881</x:v>
       </x:c>
       <x:c r="G3258" s="1">
-        <x:v>25500</x:v>
+        <x:v>869712</x:v>
       </x:c>
     </x:row>
     <x:row r="3259" spans="1:7">
@@ -85938,22 +85938,22 @@
         <x:v>3245</x:v>
       </x:c>
       <x:c r="B3259" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C3259" s="1">
-        <x:v>420650</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D3259" s="1">
-        <x:v>181</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3259" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3259" s="1">
-        <x:v>448881</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3259" s="1">
-        <x:v>869712</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="3260" spans="1:7">
@@ -87732,22 +87732,22 @@
         <x:v>3323</x:v>
       </x:c>
       <x:c r="B3337" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="C3337" s="1">
-        <x:v>332220</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D3337" s="1">
-        <x:v>0</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E3337" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3337" s="1">
-        <x:v>299023</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3337" s="1">
-        <x:v>631243</x:v>
+        <x:v>15063</x:v>
       </x:c>
     </x:row>
     <x:row r="3338" spans="1:7">
@@ -87755,22 +87755,22 @@
         <x:v>3323</x:v>
       </x:c>
       <x:c r="B3338" s="1" t="s">
-        <x:v>256</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C3338" s="1">
-        <x:v>15000</x:v>
+        <x:v>332220</x:v>
       </x:c>
       <x:c r="D3338" s="1">
-        <x:v>63</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3338" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3338" s="1">
-        <x:v>0</x:v>
+        <x:v>299023</x:v>
       </x:c>
       <x:c r="G3338" s="1">
-        <x:v>15063</x:v>
+        <x:v>631243</x:v>
       </x:c>
     </x:row>
     <x:row r="3339" spans="1:7">
@@ -87847,22 +87847,22 @@
         <x:v>3325</x:v>
       </x:c>
       <x:c r="B3342" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C3342" s="1">
-        <x:v>116050</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D3342" s="1">
-        <x:v>236</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E3342" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3342" s="1">
-        <x:v>47699</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="G3342" s="1">
-        <x:v>163985</x:v>
+        <x:v>14063</x:v>
       </x:c>
     </x:row>
     <x:row r="3343" spans="1:7">
@@ -87870,22 +87870,22 @@
         <x:v>3325</x:v>
       </x:c>
       <x:c r="B3343" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C3343" s="1">
-        <x:v>7000</x:v>
+        <x:v>116050</x:v>
       </x:c>
       <x:c r="D3343" s="1">
-        <x:v>63</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="E3343" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3343" s="1">
-        <x:v>7000</x:v>
+        <x:v>47699</x:v>
       </x:c>
       <x:c r="G3343" s="1">
-        <x:v>14063</x:v>
+        <x:v>163985</x:v>
       </x:c>
     </x:row>
     <x:row r="3344" spans="1:7">
@@ -89641,22 +89641,22 @@
         <x:v>3398</x:v>
       </x:c>
       <x:c r="B3420" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C3420" s="1">
-        <x:v>38500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3420" s="1">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E3420" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3420" s="1">
-        <x:v>26250</x:v>
+        <x:v>10700</x:v>
       </x:c>
       <x:c r="G3420" s="1">
-        <x:v>64750</x:v>
+        <x:v>10701</x:v>
       </x:c>
     </x:row>
     <x:row r="3421" spans="1:7">
@@ -89664,22 +89664,22 @@
         <x:v>3398</x:v>
       </x:c>
       <x:c r="B3421" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C3421" s="1">
-        <x:v>0</x:v>
+        <x:v>38500</x:v>
       </x:c>
       <x:c r="D3421" s="1">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3421" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3421" s="1">
-        <x:v>10700</x:v>
+        <x:v>26250</x:v>
       </x:c>
       <x:c r="G3421" s="1">
-        <x:v>10701</x:v>
+        <x:v>64750</x:v>
       </x:c>
     </x:row>
     <x:row r="3422" spans="1:7">
@@ -90193,22 +90193,22 @@
         <x:v>3420</x:v>
       </x:c>
       <x:c r="B3444" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C3444" s="1">
-        <x:v>0</x:v>
+        <x:v>72750</x:v>
       </x:c>
       <x:c r="D3444" s="1">
-        <x:v>59</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E3444" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3444" s="1">
-        <x:v>0</x:v>
+        <x:v>25450</x:v>
       </x:c>
       <x:c r="G3444" s="1">
-        <x:v>59</x:v>
+        <x:v>98495</x:v>
       </x:c>
     </x:row>
     <x:row r="3445" spans="1:7">
@@ -90216,22 +90216,22 @@
         <x:v>3420</x:v>
       </x:c>
       <x:c r="B3445" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C3445" s="1">
-        <x:v>72750</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3445" s="1">
-        <x:v>295</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3445" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3445" s="1">
-        <x:v>25450</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3445" s="1">
-        <x:v>98495</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="3446" spans="1:7">
@@ -90285,10 +90285,10 @@
         <x:v>3423</x:v>
       </x:c>
       <x:c r="B3448" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C3448" s="1">
-        <x:v>500</x:v>
+        <x:v>19500</x:v>
       </x:c>
       <x:c r="D3448" s="1">
         <x:v>0</x:v>
@@ -90297,10 +90297,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3448" s="1">
-        <x:v>0</x:v>
+        <x:v>8650</x:v>
       </x:c>
       <x:c r="G3448" s="1">
-        <x:v>500</x:v>
+        <x:v>28150</x:v>
       </x:c>
     </x:row>
     <x:row r="3449" spans="1:7">
@@ -90308,10 +90308,10 @@
         <x:v>3423</x:v>
       </x:c>
       <x:c r="B3449" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C3449" s="1">
-        <x:v>19500</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="D3449" s="1">
         <x:v>0</x:v>
@@ -90320,10 +90320,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3449" s="1">
-        <x:v>8650</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3449" s="1">
-        <x:v>28150</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="3450" spans="1:7">
@@ -90676,22 +90676,22 @@
         <x:v>3438</x:v>
       </x:c>
       <x:c r="B3465" s="1" t="s">
-        <x:v>416</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C3465" s="1">
-        <x:v>437150</x:v>
+        <x:v>22500</x:v>
       </x:c>
       <x:c r="D3465" s="1">
-        <x:v>468</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3465" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3465" s="1">
-        <x:v>348550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3465" s="1">
-        <x:v>786168</x:v>
+        <x:v>22500</x:v>
       </x:c>
     </x:row>
     <x:row r="3466" spans="1:7">
@@ -90699,10 +90699,10 @@
         <x:v>3438</x:v>
       </x:c>
       <x:c r="B3466" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C3466" s="1">
-        <x:v>22500</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D3466" s="1">
         <x:v>0</x:v>
@@ -90714,7 +90714,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G3466" s="1">
-        <x:v>22500</x:v>
+        <x:v>3000</x:v>
       </x:c>
     </x:row>
     <x:row r="3467" spans="1:7">
@@ -90722,22 +90722,22 @@
         <x:v>3438</x:v>
       </x:c>
       <x:c r="B3467" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="C3467" s="1">
-        <x:v>3000</x:v>
+        <x:v>437150</x:v>
       </x:c>
       <x:c r="D3467" s="1">
-        <x:v>0</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="E3467" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3467" s="1">
-        <x:v>0</x:v>
+        <x:v>348550</x:v>
       </x:c>
       <x:c r="G3467" s="1">
-        <x:v>3000</x:v>
+        <x:v>786168</x:v>
       </x:c>
     </x:row>
     <x:row r="3468" spans="1:7">
@@ -91872,22 +91872,22 @@
         <x:v>3485</x:v>
       </x:c>
       <x:c r="B3517" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="C3517" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D3517" s="1">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3517" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3517" s="1">
-        <x:v>0</x:v>
+        <x:v>11300</x:v>
       </x:c>
       <x:c r="G3517" s="1">
-        <x:v>3</x:v>
+        <x:v>12300</x:v>
       </x:c>
     </x:row>
     <x:row r="3518" spans="1:7">
@@ -91895,22 +91895,22 @@
         <x:v>3485</x:v>
       </x:c>
       <x:c r="B3518" s="1" t="s">
-        <x:v>258</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C3518" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3518" s="1">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E3518" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3518" s="1">
-        <x:v>11300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3518" s="1">
-        <x:v>12300</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="3519" spans="1:7">
@@ -92447,10 +92447,10 @@
         <x:v>3509</x:v>
       </x:c>
       <x:c r="B3542" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C3542" s="1">
-        <x:v>130750</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3542" s="1">
         <x:v>7</x:v>
@@ -92459,10 +92459,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3542" s="1">
-        <x:v>83750</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3542" s="1">
-        <x:v>214507</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="3543" spans="1:7">
@@ -92470,10 +92470,10 @@
         <x:v>3509</x:v>
       </x:c>
       <x:c r="B3543" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C3543" s="1">
-        <x:v>0</x:v>
+        <x:v>130750</x:v>
       </x:c>
       <x:c r="D3543" s="1">
         <x:v>7</x:v>
@@ -92482,10 +92482,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3543" s="1">
-        <x:v>0</x:v>
+        <x:v>83750</x:v>
       </x:c>
       <x:c r="G3543" s="1">
-        <x:v>7</x:v>
+        <x:v>214507</x:v>
       </x:c>
     </x:row>
     <x:row r="3544" spans="1:7">

--- a/reports/pro-oil/pro-oil-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-oil/pro-oil-candidate-lobby-lifetime-report.xlsx
@@ -16110,7 +16110,7 @@
         <x:v>277</x:v>
       </x:c>
       <x:c r="B223" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C223" s="1">
         <x:v>0</x:v>
@@ -16122,10 +16122,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F223" s="1">
-        <x:v>1000</x:v>
+        <x:v>2300</x:v>
       </x:c>
       <x:c r="G223" s="1">
-        <x:v>1000</x:v>
+        <x:v>2300</x:v>
       </x:c>
     </x:row>
     <x:row r="224" spans="1:7">
@@ -16133,7 +16133,7 @@
         <x:v>277</x:v>
       </x:c>
       <x:c r="B224" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C224" s="1">
         <x:v>0</x:v>
@@ -16145,10 +16145,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F224" s="1">
-        <x:v>2300</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G224" s="1">
-        <x:v>2300</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="225" spans="1:7">
@@ -30784,10 +30784,10 @@
         <x:v>911</x:v>
       </x:c>
       <x:c r="B861" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="C861" s="1">
-        <x:v>0</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D861" s="1">
         <x:v>0</x:v>
@@ -30796,10 +30796,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F861" s="1">
-        <x:v>14450</x:v>
+        <x:v>12950</x:v>
       </x:c>
       <x:c r="G861" s="1">
-        <x:v>14450</x:v>
+        <x:v>15950</x:v>
       </x:c>
     </x:row>
     <x:row r="862" spans="1:7">
@@ -30807,10 +30807,10 @@
         <x:v>911</x:v>
       </x:c>
       <x:c r="B862" s="1" t="s">
-        <x:v>258</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C862" s="1">
-        <x:v>3000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D862" s="1">
         <x:v>0</x:v>
@@ -30819,10 +30819,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F862" s="1">
-        <x:v>12950</x:v>
+        <x:v>14450</x:v>
       </x:c>
       <x:c r="G862" s="1">
-        <x:v>15950</x:v>
+        <x:v>14450</x:v>
       </x:c>
     </x:row>
     <x:row r="863" spans="1:7">
@@ -37592,10 +37592,10 @@
         <x:v>1201</x:v>
       </x:c>
       <x:c r="B1157" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C1157" s="1">
-        <x:v>752389</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1157" s="1">
         <x:v>0</x:v>
@@ -37604,10 +37604,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1157" s="1">
-        <x:v>418794</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="G1157" s="1">
-        <x:v>1171183</x:v>
+        <x:v>10000</x:v>
       </x:c>
     </x:row>
     <x:row r="1158" spans="1:7">
@@ -37615,10 +37615,10 @@
         <x:v>1201</x:v>
       </x:c>
       <x:c r="B1158" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1158" s="1">
-        <x:v>0</x:v>
+        <x:v>752389</x:v>
       </x:c>
       <x:c r="D1158" s="1">
         <x:v>0</x:v>
@@ -37627,10 +37627,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1158" s="1">
-        <x:v>10000</x:v>
+        <x:v>418794</x:v>
       </x:c>
       <x:c r="G1158" s="1">
-        <x:v>10000</x:v>
+        <x:v>1171183</x:v>
       </x:c>
     </x:row>
     <x:row r="1159" spans="1:7">
@@ -47091,10 +47091,10 @@
         <x:v>1606</x:v>
       </x:c>
       <x:c r="B1570" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="C1570" s="1">
-        <x:v>8000</x:v>
+        <x:v>181700</x:v>
       </x:c>
       <x:c r="D1570" s="1">
         <x:v>0</x:v>
@@ -47103,10 +47103,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1570" s="1">
-        <x:v>66000</x:v>
+        <x:v>168050</x:v>
       </x:c>
       <x:c r="G1570" s="1">
-        <x:v>74000</x:v>
+        <x:v>349750</x:v>
       </x:c>
     </x:row>
     <x:row r="1571" spans="1:7">
@@ -47114,10 +47114,10 @@
         <x:v>1606</x:v>
       </x:c>
       <x:c r="B1571" s="1" t="s">
-        <x:v>416</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C1571" s="1">
-        <x:v>181700</x:v>
+        <x:v>8000</x:v>
       </x:c>
       <x:c r="D1571" s="1">
         <x:v>0</x:v>
@@ -47126,10 +47126,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1571" s="1">
-        <x:v>168050</x:v>
+        <x:v>66000</x:v>
       </x:c>
       <x:c r="G1571" s="1">
-        <x:v>349750</x:v>
+        <x:v>74000</x:v>
       </x:c>
     </x:row>
     <x:row r="1572" spans="1:7">
@@ -49736,10 +49736,10 @@
         <x:v>1719</x:v>
       </x:c>
       <x:c r="B1685" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C1685" s="1">
-        <x:v>27850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1685" s="1">
         <x:v>0</x:v>
@@ -49748,10 +49748,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1685" s="1">
-        <x:v>19000</x:v>
+        <x:v>102225</x:v>
       </x:c>
       <x:c r="G1685" s="1">
-        <x:v>46850</x:v>
+        <x:v>102225</x:v>
       </x:c>
     </x:row>
     <x:row r="1686" spans="1:7">
@@ -49759,10 +49759,10 @@
         <x:v>1719</x:v>
       </x:c>
       <x:c r="B1686" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C1686" s="1">
-        <x:v>0</x:v>
+        <x:v>27850</x:v>
       </x:c>
       <x:c r="D1686" s="1">
         <x:v>0</x:v>
@@ -49771,10 +49771,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1686" s="1">
-        <x:v>102225</x:v>
+        <x:v>19000</x:v>
       </x:c>
       <x:c r="G1686" s="1">
-        <x:v>102225</x:v>
+        <x:v>46850</x:v>
       </x:c>
     </x:row>
     <x:row r="1687" spans="1:7">
@@ -56291,10 +56291,10 @@
         <x:v>1996</x:v>
       </x:c>
       <x:c r="B1970" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1970" s="1">
-        <x:v>187150</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1970" s="1">
         <x:v>31</x:v>
@@ -56303,10 +56303,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1970" s="1">
-        <x:v>6150</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1970" s="1">
-        <x:v>193331</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="1971" spans="1:7">
@@ -56314,10 +56314,10 @@
         <x:v>1996</x:v>
       </x:c>
       <x:c r="B1971" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C1971" s="1">
-        <x:v>0</x:v>
+        <x:v>187150</x:v>
       </x:c>
       <x:c r="D1971" s="1">
         <x:v>31</x:v>
@@ -56326,10 +56326,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1971" s="1">
-        <x:v>0</x:v>
+        <x:v>6150</x:v>
       </x:c>
       <x:c r="G1971" s="1">
-        <x:v>31</x:v>
+        <x:v>193331</x:v>
       </x:c>
     </x:row>
     <x:row r="1972" spans="1:7">
@@ -59787,10 +59787,10 @@
         <x:v>2144</x:v>
       </x:c>
       <x:c r="B2122" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C2122" s="1">
-        <x:v>11000</x:v>
+        <x:v>960100</x:v>
       </x:c>
       <x:c r="D2122" s="1">
         <x:v>0</x:v>
@@ -59799,10 +59799,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2122" s="1">
-        <x:v>25550</x:v>
+        <x:v>882230</x:v>
       </x:c>
       <x:c r="G2122" s="1">
-        <x:v>36550</x:v>
+        <x:v>1842330</x:v>
       </x:c>
     </x:row>
     <x:row r="2123" spans="1:7">
@@ -59810,10 +59810,10 @@
         <x:v>2144</x:v>
       </x:c>
       <x:c r="B2123" s="1" t="s">
-        <x:v>190</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C2123" s="1">
-        <x:v>960100</x:v>
+        <x:v>11000</x:v>
       </x:c>
       <x:c r="D2123" s="1">
         <x:v>0</x:v>
@@ -59822,10 +59822,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2123" s="1">
-        <x:v>882230</x:v>
+        <x:v>25550</x:v>
       </x:c>
       <x:c r="G2123" s="1">
-        <x:v>1842330</x:v>
+        <x:v>36550</x:v>
       </x:c>
     </x:row>
     <x:row r="2124" spans="1:7">
@@ -59902,22 +59902,22 @@
         <x:v>2148</x:v>
       </x:c>
       <x:c r="B2127" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C2127" s="1">
+        <x:v>22450</x:v>
+      </x:c>
+      <x:c r="D2127" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E2127" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F2127" s="1">
         <x:v>250</x:v>
       </x:c>
-      <x:c r="D2127" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E2127" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F2127" s="1">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="G2127" s="1">
-        <x:v>250</x:v>
+        <x:v>22700</x:v>
       </x:c>
     </x:row>
     <x:row r="2128" spans="1:7">
@@ -59925,10 +59925,10 @@
         <x:v>2148</x:v>
       </x:c>
       <x:c r="B2128" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C2128" s="1">
-        <x:v>22450</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="D2128" s="1">
         <x:v>0</x:v>
@@ -59937,10 +59937,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2128" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G2128" s="1">
         <x:v>250</x:v>
-      </x:c>
-      <x:c r="G2128" s="1">
-        <x:v>22700</x:v>
       </x:c>
     </x:row>
     <x:row r="2129" spans="1:7">
@@ -72345,10 +72345,10 @@
         <x:v>2685</x:v>
       </x:c>
       <x:c r="B2668" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C2668" s="1">
-        <x:v>409250</x:v>
+        <x:v>7061</x:v>
       </x:c>
       <x:c r="D2668" s="1">
         <x:v>0</x:v>
@@ -72357,10 +72357,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2668" s="1">
-        <x:v>159800</x:v>
+        <x:v>23500</x:v>
       </x:c>
       <x:c r="G2668" s="1">
-        <x:v>569050</x:v>
+        <x:v>30561</x:v>
       </x:c>
     </x:row>
     <x:row r="2669" spans="1:7">
@@ -72368,10 +72368,10 @@
         <x:v>2685</x:v>
       </x:c>
       <x:c r="B2669" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C2669" s="1">
-        <x:v>7061</x:v>
+        <x:v>409250</x:v>
       </x:c>
       <x:c r="D2669" s="1">
         <x:v>0</x:v>
@@ -72380,10 +72380,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2669" s="1">
-        <x:v>23500</x:v>
+        <x:v>159800</x:v>
       </x:c>
       <x:c r="G2669" s="1">
-        <x:v>30561</x:v>
+        <x:v>569050</x:v>
       </x:c>
     </x:row>
     <x:row r="2670" spans="1:7">
@@ -72506,10 +72506,10 @@
         <x:v>2691</x:v>
       </x:c>
       <x:c r="B2675" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C2675" s="1">
-        <x:v>7000</x:v>
+        <x:v>139000</x:v>
       </x:c>
       <x:c r="D2675" s="1">
         <x:v>0</x:v>
@@ -72518,10 +72518,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2675" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G2675" s="1">
-        <x:v>7000</x:v>
+        <x:v>139500</x:v>
       </x:c>
     </x:row>
     <x:row r="2676" spans="1:7">
@@ -72529,10 +72529,10 @@
         <x:v>2691</x:v>
       </x:c>
       <x:c r="B2676" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C2676" s="1">
-        <x:v>139000</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D2676" s="1">
         <x:v>0</x:v>
@@ -72541,10 +72541,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2676" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2676" s="1">
-        <x:v>139500</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="2677" spans="1:7">
@@ -75312,10 +75312,10 @@
         <x:v>2811</x:v>
       </x:c>
       <x:c r="B2797" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C2797" s="1">
-        <x:v>206766</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D2797" s="1">
         <x:v>0</x:v>
@@ -75324,10 +75324,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2797" s="1">
-        <x:v>286825</x:v>
+        <x:v>111650</x:v>
       </x:c>
       <x:c r="G2797" s="1">
-        <x:v>493591</x:v>
+        <x:v>126650</x:v>
       </x:c>
     </x:row>
     <x:row r="2798" spans="1:7">
@@ -75335,10 +75335,10 @@
         <x:v>2811</x:v>
       </x:c>
       <x:c r="B2798" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C2798" s="1">
-        <x:v>15000</x:v>
+        <x:v>163800</x:v>
       </x:c>
       <x:c r="D2798" s="1">
         <x:v>0</x:v>
@@ -75347,10 +75347,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2798" s="1">
-        <x:v>111650</x:v>
+        <x:v>277645</x:v>
       </x:c>
       <x:c r="G2798" s="1">
-        <x:v>126650</x:v>
+        <x:v>441445</x:v>
       </x:c>
     </x:row>
     <x:row r="2799" spans="1:7">
@@ -75358,10 +75358,10 @@
         <x:v>2811</x:v>
       </x:c>
       <x:c r="B2799" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C2799" s="1">
-        <x:v>163800</x:v>
+        <x:v>206766</x:v>
       </x:c>
       <x:c r="D2799" s="1">
         <x:v>0</x:v>
@@ -75370,10 +75370,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2799" s="1">
-        <x:v>277645</x:v>
+        <x:v>286825</x:v>
       </x:c>
       <x:c r="G2799" s="1">
-        <x:v>441445</x:v>
+        <x:v>493591</x:v>
       </x:c>
     </x:row>
     <x:row r="2800" spans="1:7">
@@ -76853,10 +76853,10 @@
         <x:v>2875</x:v>
       </x:c>
       <x:c r="B2864" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C2864" s="1">
-        <x:v>15000</x:v>
+        <x:v>102350</x:v>
       </x:c>
       <x:c r="D2864" s="1">
         <x:v>0</x:v>
@@ -76865,10 +76865,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2864" s="1">
-        <x:v>5000</x:v>
+        <x:v>106550</x:v>
       </x:c>
       <x:c r="G2864" s="1">
-        <x:v>20000</x:v>
+        <x:v>208900</x:v>
       </x:c>
     </x:row>
     <x:row r="2865" spans="1:7">
@@ -76876,10 +76876,10 @@
         <x:v>2875</x:v>
       </x:c>
       <x:c r="B2865" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C2865" s="1">
-        <x:v>102350</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D2865" s="1">
         <x:v>0</x:v>
@@ -76888,10 +76888,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2865" s="1">
-        <x:v>106550</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G2865" s="1">
-        <x:v>208900</x:v>
+        <x:v>20000</x:v>
       </x:c>
     </x:row>
     <x:row r="2866" spans="1:7">
@@ -78670,22 +78670,22 @@
         <x:v>2951</x:v>
       </x:c>
       <x:c r="B2943" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="C2943" s="1">
-        <x:v>0</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="D2943" s="1">
-        <x:v>59</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E2943" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2943" s="1">
-        <x:v>0</x:v>
+        <x:v>4950</x:v>
       </x:c>
       <x:c r="G2943" s="1">
-        <x:v>59</x:v>
+        <x:v>14950</x:v>
       </x:c>
     </x:row>
     <x:row r="2944" spans="1:7">
@@ -78693,22 +78693,22 @@
         <x:v>2951</x:v>
       </x:c>
       <x:c r="B2944" s="1" t="s">
-        <x:v>258</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C2944" s="1">
-        <x:v>10000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D2944" s="1">
-        <x:v>0</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E2944" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2944" s="1">
-        <x:v>4950</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2944" s="1">
-        <x:v>14950</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="2945" spans="1:7">
@@ -81660,10 +81660,10 @@
         <x:v>3077</x:v>
       </x:c>
       <x:c r="B3073" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C3073" s="1">
-        <x:v>10500</x:v>
+        <x:v>44000</x:v>
       </x:c>
       <x:c r="D3073" s="1">
         <x:v>0</x:v>
@@ -81672,10 +81672,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3073" s="1">
-        <x:v>31300</x:v>
+        <x:v>2100</x:v>
       </x:c>
       <x:c r="G3073" s="1">
-        <x:v>41800</x:v>
+        <x:v>46100</x:v>
       </x:c>
     </x:row>
     <x:row r="3074" spans="1:7">
@@ -81706,10 +81706,10 @@
         <x:v>3077</x:v>
       </x:c>
       <x:c r="B3075" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C3075" s="1">
-        <x:v>44000</x:v>
+        <x:v>10500</x:v>
       </x:c>
       <x:c r="D3075" s="1">
         <x:v>0</x:v>
@@ -81718,10 +81718,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3075" s="1">
-        <x:v>2100</x:v>
+        <x:v>31300</x:v>
       </x:c>
       <x:c r="G3075" s="1">
-        <x:v>46100</x:v>
+        <x:v>41800</x:v>
       </x:c>
     </x:row>
     <x:row r="3076" spans="1:7">
@@ -83063,10 +83063,10 @@
         <x:v>3132</x:v>
       </x:c>
       <x:c r="B3134" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="C3134" s="1">
-        <x:v>5000</x:v>
+        <x:v>48000</x:v>
       </x:c>
       <x:c r="D3134" s="1">
         <x:v>0</x:v>
@@ -83075,10 +83075,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3134" s="1">
-        <x:v>250</x:v>
+        <x:v>38300</x:v>
       </x:c>
       <x:c r="G3134" s="1">
-        <x:v>5250</x:v>
+        <x:v>86300</x:v>
       </x:c>
     </x:row>
     <x:row r="3135" spans="1:7">
@@ -83086,10 +83086,10 @@
         <x:v>3132</x:v>
       </x:c>
       <x:c r="B3135" s="1" t="s">
-        <x:v>155</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C3135" s="1">
-        <x:v>48000</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D3135" s="1">
         <x:v>0</x:v>
@@ -83098,10 +83098,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3135" s="1">
-        <x:v>38300</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G3135" s="1">
-        <x:v>86300</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="3136" spans="1:7">
@@ -83431,10 +83431,10 @@
         <x:v>3144</x:v>
       </x:c>
       <x:c r="B3150" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C3150" s="1">
-        <x:v>157500</x:v>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="D3150" s="1">
         <x:v>0</x:v>
@@ -83443,10 +83443,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3150" s="1">
-        <x:v>45517</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="G3150" s="1">
-        <x:v>203017</x:v>
+        <x:v>26000</x:v>
       </x:c>
     </x:row>
     <x:row r="3151" spans="1:7">
@@ -83454,10 +83454,10 @@
         <x:v>3144</x:v>
       </x:c>
       <x:c r="B3151" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C3151" s="1">
-        <x:v>20000</x:v>
+        <x:v>157500</x:v>
       </x:c>
       <x:c r="D3151" s="1">
         <x:v>0</x:v>
@@ -83466,10 +83466,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3151" s="1">
-        <x:v>6000</x:v>
+        <x:v>45517</x:v>
       </x:c>
       <x:c r="G3151" s="1">
-        <x:v>26000</x:v>
+        <x:v>203017</x:v>
       </x:c>
     </x:row>
     <x:row r="3152" spans="1:7">
@@ -84995,10 +84995,10 @@
         <x:v>3210</x:v>
       </x:c>
       <x:c r="B3218" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C3218" s="1">
-        <x:v>2300</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D3218" s="1">
         <x:v>0</x:v>
@@ -85007,10 +85007,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3218" s="1">
-        <x:v>8850</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="G3218" s="1">
-        <x:v>11150</x:v>
+        <x:v>9000</x:v>
       </x:c>
     </x:row>
     <x:row r="3219" spans="1:7">
@@ -85018,10 +85018,10 @@
         <x:v>3210</x:v>
       </x:c>
       <x:c r="B3219" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C3219" s="1">
-        <x:v>3000</x:v>
+        <x:v>2300</x:v>
       </x:c>
       <x:c r="D3219" s="1">
         <x:v>0</x:v>
@@ -85030,10 +85030,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3219" s="1">
-        <x:v>6000</x:v>
+        <x:v>8850</x:v>
       </x:c>
       <x:c r="G3219" s="1">
-        <x:v>9000</x:v>
+        <x:v>11150</x:v>
       </x:c>
     </x:row>
     <x:row r="3220" spans="1:7">
@@ -85294,22 +85294,22 @@
         <x:v>3221</x:v>
       </x:c>
       <x:c r="B3231" s="1" t="s">
-        <x:v>297</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C3231" s="1">
-        <x:v>536500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3231" s="1">
-        <x:v>295</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3231" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3231" s="1">
-        <x:v>227847</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3231" s="1">
-        <x:v>764642</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="3232" spans="1:7">
@@ -85317,22 +85317,22 @@
         <x:v>3221</x:v>
       </x:c>
       <x:c r="B3232" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="C3232" s="1">
-        <x:v>0</x:v>
+        <x:v>536500</x:v>
       </x:c>
       <x:c r="D3232" s="1">
-        <x:v>59</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E3232" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3232" s="1">
-        <x:v>0</x:v>
+        <x:v>227847</x:v>
       </x:c>
       <x:c r="G3232" s="1">
-        <x:v>59</x:v>
+        <x:v>764642</x:v>
       </x:c>
     </x:row>
     <x:row r="3233" spans="1:7">
@@ -85524,10 +85524,10 @@
         <x:v>3230</x:v>
       </x:c>
       <x:c r="B3241" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C3241" s="1">
-        <x:v>34000</x:v>
+        <x:v>343100</x:v>
       </x:c>
       <x:c r="D3241" s="1">
         <x:v>0</x:v>
@@ -85536,10 +85536,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3241" s="1">
-        <x:v>0</x:v>
+        <x:v>244972</x:v>
       </x:c>
       <x:c r="G3241" s="1">
-        <x:v>34000</x:v>
+        <x:v>588072</x:v>
       </x:c>
     </x:row>
     <x:row r="3242" spans="1:7">
@@ -85547,10 +85547,10 @@
         <x:v>3230</x:v>
       </x:c>
       <x:c r="B3242" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C3242" s="1">
-        <x:v>343100</x:v>
+        <x:v>34000</x:v>
       </x:c>
       <x:c r="D3242" s="1">
         <x:v>0</x:v>
@@ -85559,10 +85559,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3242" s="1">
-        <x:v>244972</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3242" s="1">
-        <x:v>588072</x:v>
+        <x:v>34000</x:v>
       </x:c>
     </x:row>
     <x:row r="3243" spans="1:7">
@@ -87755,22 +87755,22 @@
         <x:v>3323</x:v>
       </x:c>
       <x:c r="B3338" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C3338" s="1">
-        <x:v>332220</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3338" s="1">
-        <x:v>0</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3338" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3338" s="1">
-        <x:v>299023</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3338" s="1">
-        <x:v>631243</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="3339" spans="1:7">
@@ -87778,22 +87778,22 @@
         <x:v>3323</x:v>
       </x:c>
       <x:c r="B3339" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C3339" s="1">
-        <x:v>0</x:v>
+        <x:v>332220</x:v>
       </x:c>
       <x:c r="D3339" s="1">
-        <x:v>59</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3339" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3339" s="1">
-        <x:v>0</x:v>
+        <x:v>299023</x:v>
       </x:c>
       <x:c r="G3339" s="1">
-        <x:v>59</x:v>
+        <x:v>631243</x:v>
       </x:c>
     </x:row>
     <x:row r="3340" spans="1:7">
@@ -88928,10 +88928,10 @@
         <x:v>3370</x:v>
       </x:c>
       <x:c r="B3389" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C3389" s="1">
-        <x:v>41550</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D3389" s="1">
         <x:v>0</x:v>
@@ -88940,10 +88940,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3389" s="1">
-        <x:v>6500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3389" s="1">
-        <x:v>48050</x:v>
+        <x:v>15000</x:v>
       </x:c>
     </x:row>
     <x:row r="3390" spans="1:7">
@@ -88951,10 +88951,10 @@
         <x:v>3370</x:v>
       </x:c>
       <x:c r="B3390" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C3390" s="1">
-        <x:v>15000</x:v>
+        <x:v>41550</x:v>
       </x:c>
       <x:c r="D3390" s="1">
         <x:v>0</x:v>
@@ -88963,10 +88963,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3390" s="1">
-        <x:v>0</x:v>
+        <x:v>6500</x:v>
       </x:c>
       <x:c r="G3390" s="1">
-        <x:v>15000</x:v>
+        <x:v>48050</x:v>
       </x:c>
     </x:row>
     <x:row r="3391" spans="1:7">
@@ -89641,22 +89641,22 @@
         <x:v>3398</x:v>
       </x:c>
       <x:c r="B3420" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C3420" s="1">
-        <x:v>0</x:v>
+        <x:v>38500</x:v>
       </x:c>
       <x:c r="D3420" s="1">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3420" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3420" s="1">
-        <x:v>10700</x:v>
+        <x:v>26250</x:v>
       </x:c>
       <x:c r="G3420" s="1">
-        <x:v>10701</x:v>
+        <x:v>64750</x:v>
       </x:c>
     </x:row>
     <x:row r="3421" spans="1:7">
@@ -89664,22 +89664,22 @@
         <x:v>3398</x:v>
       </x:c>
       <x:c r="B3421" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C3421" s="1">
-        <x:v>38500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3421" s="1">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E3421" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3421" s="1">
-        <x:v>26250</x:v>
+        <x:v>10700</x:v>
       </x:c>
       <x:c r="G3421" s="1">
-        <x:v>64750</x:v>
+        <x:v>10701</x:v>
       </x:c>
     </x:row>
     <x:row r="3422" spans="1:7">
@@ -90285,10 +90285,10 @@
         <x:v>3423</x:v>
       </x:c>
       <x:c r="B3448" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C3448" s="1">
-        <x:v>19500</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="D3448" s="1">
         <x:v>0</x:v>
@@ -90297,10 +90297,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3448" s="1">
-        <x:v>8650</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3448" s="1">
-        <x:v>28150</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="3449" spans="1:7">
@@ -90308,10 +90308,10 @@
         <x:v>3423</x:v>
       </x:c>
       <x:c r="B3449" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C3449" s="1">
-        <x:v>500</x:v>
+        <x:v>19500</x:v>
       </x:c>
       <x:c r="D3449" s="1">
         <x:v>0</x:v>
@@ -90320,10 +90320,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3449" s="1">
-        <x:v>0</x:v>
+        <x:v>8650</x:v>
       </x:c>
       <x:c r="G3449" s="1">
-        <x:v>500</x:v>
+        <x:v>28150</x:v>
       </x:c>
     </x:row>
     <x:row r="3450" spans="1:7">
@@ -90423,22 +90423,22 @@
         <x:v>3428</x:v>
       </x:c>
       <x:c r="B3454" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C3454" s="1">
-        <x:v>47850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3454" s="1">
-        <x:v>0</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3454" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3454" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3454" s="1">
-        <x:v>52850</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="3455" spans="1:7">
@@ -90446,22 +90446,22 @@
         <x:v>3428</x:v>
       </x:c>
       <x:c r="B3455" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C3455" s="1">
-        <x:v>0</x:v>
+        <x:v>47850</x:v>
       </x:c>
       <x:c r="D3455" s="1">
-        <x:v>59</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3455" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3455" s="1">
-        <x:v>0</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G3455" s="1">
-        <x:v>59</x:v>
+        <x:v>52850</x:v>
       </x:c>
     </x:row>
     <x:row r="3456" spans="1:7">
@@ -91872,22 +91872,22 @@
         <x:v>3485</x:v>
       </x:c>
       <x:c r="B3517" s="1" t="s">
-        <x:v>258</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C3517" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3517" s="1">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E3517" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3517" s="1">
-        <x:v>11300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3517" s="1">
-        <x:v>12300</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="3518" spans="1:7">
@@ -91895,22 +91895,22 @@
         <x:v>3485</x:v>
       </x:c>
       <x:c r="B3518" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="C3518" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D3518" s="1">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3518" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3518" s="1">
-        <x:v>0</x:v>
+        <x:v>11300</x:v>
       </x:c>
       <x:c r="G3518" s="1">
-        <x:v>3</x:v>
+        <x:v>12300</x:v>
       </x:c>
     </x:row>
     <x:row r="3519" spans="1:7">
@@ -92447,10 +92447,10 @@
         <x:v>3509</x:v>
       </x:c>
       <x:c r="B3542" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C3542" s="1">
-        <x:v>0</x:v>
+        <x:v>130750</x:v>
       </x:c>
       <x:c r="D3542" s="1">
         <x:v>7</x:v>
@@ -92459,10 +92459,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3542" s="1">
-        <x:v>0</x:v>
+        <x:v>83750</x:v>
       </x:c>
       <x:c r="G3542" s="1">
-        <x:v>7</x:v>
+        <x:v>214507</x:v>
       </x:c>
     </x:row>
     <x:row r="3543" spans="1:7">
@@ -92470,10 +92470,10 @@
         <x:v>3509</x:v>
       </x:c>
       <x:c r="B3543" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C3543" s="1">
-        <x:v>130750</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3543" s="1">
         <x:v>7</x:v>
@@ -92482,10 +92482,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3543" s="1">
-        <x:v>83750</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3543" s="1">
-        <x:v>214507</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="3544" spans="1:7">

--- a/reports/pro-oil/pro-oil-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-oil/pro-oil-candidate-lobby-lifetime-report.xlsx
@@ -21009,10 +21009,10 @@
         <x:v>488</x:v>
       </x:c>
       <x:c r="B436" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C436" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D436" s="1">
         <x:v>0</x:v>
@@ -21021,10 +21021,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F436" s="1">
-        <x:v>13450</x:v>
+        <x:v>40350</x:v>
       </x:c>
       <x:c r="G436" s="1">
-        <x:v>13500</x:v>
+        <x:v>40350</x:v>
       </x:c>
     </x:row>
     <x:row r="437" spans="1:7">
@@ -21032,11 +21032,11 @@
         <x:v>488</x:v>
       </x:c>
       <x:c r="B437" s="1" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C437" s="1">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="C437" s="1">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="D437" s="1">
         <x:v>0</x:v>
       </x:c>
@@ -21044,10 +21044,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F437" s="1">
-        <x:v>40350</x:v>
+        <x:v>13450</x:v>
       </x:c>
       <x:c r="G437" s="1">
-        <x:v>40350</x:v>
+        <x:v>13500</x:v>
       </x:c>
     </x:row>
     <x:row r="438" spans="1:7">
@@ -30784,10 +30784,10 @@
         <x:v>911</x:v>
       </x:c>
       <x:c r="B861" s="1" t="s">
-        <x:v>258</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C861" s="1">
-        <x:v>3000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D861" s="1">
         <x:v>0</x:v>
@@ -30796,10 +30796,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F861" s="1">
-        <x:v>12950</x:v>
+        <x:v>14450</x:v>
       </x:c>
       <x:c r="G861" s="1">
-        <x:v>15950</x:v>
+        <x:v>14450</x:v>
       </x:c>
     </x:row>
     <x:row r="862" spans="1:7">
@@ -30807,10 +30807,10 @@
         <x:v>911</x:v>
       </x:c>
       <x:c r="B862" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="C862" s="1">
-        <x:v>0</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D862" s="1">
         <x:v>0</x:v>
@@ -30819,10 +30819,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F862" s="1">
-        <x:v>14450</x:v>
+        <x:v>12950</x:v>
       </x:c>
       <x:c r="G862" s="1">
-        <x:v>14450</x:v>
+        <x:v>15950</x:v>
       </x:c>
     </x:row>
     <x:row r="863" spans="1:7">
@@ -37592,10 +37592,10 @@
         <x:v>1201</x:v>
       </x:c>
       <x:c r="B1157" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1157" s="1">
-        <x:v>0</x:v>
+        <x:v>752389</x:v>
       </x:c>
       <x:c r="D1157" s="1">
         <x:v>0</x:v>
@@ -37604,10 +37604,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1157" s="1">
-        <x:v>10000</x:v>
+        <x:v>418794</x:v>
       </x:c>
       <x:c r="G1157" s="1">
-        <x:v>10000</x:v>
+        <x:v>1171183</x:v>
       </x:c>
     </x:row>
     <x:row r="1158" spans="1:7">
@@ -37615,10 +37615,10 @@
         <x:v>1201</x:v>
       </x:c>
       <x:c r="B1158" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C1158" s="1">
-        <x:v>752389</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1158" s="1">
         <x:v>0</x:v>
@@ -37627,10 +37627,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1158" s="1">
-        <x:v>418794</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="G1158" s="1">
-        <x:v>1171183</x:v>
+        <x:v>10000</x:v>
       </x:c>
     </x:row>
     <x:row r="1159" spans="1:7">
@@ -38811,10 +38811,10 @@
         <x:v>1251</x:v>
       </x:c>
       <x:c r="B1210" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C1210" s="1">
-        <x:v>12000</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D1210" s="1">
         <x:v>0</x:v>
@@ -38823,10 +38823,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1210" s="1">
-        <x:v>12450</x:v>
+        <x:v>50751</x:v>
       </x:c>
       <x:c r="G1210" s="1">
-        <x:v>24450</x:v>
+        <x:v>53751</x:v>
       </x:c>
     </x:row>
     <x:row r="1211" spans="1:7">
@@ -38834,10 +38834,10 @@
         <x:v>1251</x:v>
       </x:c>
       <x:c r="B1211" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C1211" s="1">
-        <x:v>3000</x:v>
+        <x:v>12000</x:v>
       </x:c>
       <x:c r="D1211" s="1">
         <x:v>0</x:v>
@@ -38846,10 +38846,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1211" s="1">
-        <x:v>50751</x:v>
+        <x:v>12450</x:v>
       </x:c>
       <x:c r="G1211" s="1">
-        <x:v>53751</x:v>
+        <x:v>24450</x:v>
       </x:c>
     </x:row>
     <x:row r="1212" spans="1:7">
@@ -46401,10 +46401,10 @@
         <x:v>1579</x:v>
       </x:c>
       <x:c r="B1540" s="1" t="s">
-        <x:v>164</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C1540" s="1">
-        <x:v>82250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1540" s="1">
         <x:v>0</x:v>
@@ -46413,10 +46413,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1540" s="1">
-        <x:v>9000</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1540" s="1">
-        <x:v>91250</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="1541" spans="1:7">
@@ -46424,10 +46424,10 @@
         <x:v>1579</x:v>
       </x:c>
       <x:c r="B1541" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="C1541" s="1">
-        <x:v>0</x:v>
+        <x:v>82250</x:v>
       </x:c>
       <x:c r="D1541" s="1">
         <x:v>0</x:v>
@@ -46436,10 +46436,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1541" s="1">
-        <x:v>1000</x:v>
+        <x:v>9000</x:v>
       </x:c>
       <x:c r="G1541" s="1">
-        <x:v>1000</x:v>
+        <x:v>91250</x:v>
       </x:c>
     </x:row>
     <x:row r="1542" spans="1:7">
@@ -47091,10 +47091,10 @@
         <x:v>1606</x:v>
       </x:c>
       <x:c r="B1570" s="1" t="s">
-        <x:v>416</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C1570" s="1">
-        <x:v>181700</x:v>
+        <x:v>8000</x:v>
       </x:c>
       <x:c r="D1570" s="1">
         <x:v>0</x:v>
@@ -47103,10 +47103,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1570" s="1">
-        <x:v>168050</x:v>
+        <x:v>66000</x:v>
       </x:c>
       <x:c r="G1570" s="1">
-        <x:v>349750</x:v>
+        <x:v>74000</x:v>
       </x:c>
     </x:row>
     <x:row r="1571" spans="1:7">
@@ -47114,10 +47114,10 @@
         <x:v>1606</x:v>
       </x:c>
       <x:c r="B1571" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="C1571" s="1">
-        <x:v>8000</x:v>
+        <x:v>181700</x:v>
       </x:c>
       <x:c r="D1571" s="1">
         <x:v>0</x:v>
@@ -47126,10 +47126,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1571" s="1">
-        <x:v>66000</x:v>
+        <x:v>168050</x:v>
       </x:c>
       <x:c r="G1571" s="1">
-        <x:v>74000</x:v>
+        <x:v>349750</x:v>
       </x:c>
     </x:row>
     <x:row r="1572" spans="1:7">
@@ -52841,10 +52841,10 @@
         <x:v>1850</x:v>
       </x:c>
       <x:c r="B1820" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C1820" s="1">
-        <x:v>147100</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="D1820" s="1">
         <x:v>0</x:v>
@@ -52853,10 +52853,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1820" s="1">
-        <x:v>34550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1820" s="1">
-        <x:v>181650</x:v>
+        <x:v>-1000</x:v>
       </x:c>
     </x:row>
     <x:row r="1821" spans="1:7">
@@ -52864,10 +52864,10 @@
         <x:v>1850</x:v>
       </x:c>
       <x:c r="B1821" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C1821" s="1">
-        <x:v>-1000</x:v>
+        <x:v>147100</x:v>
       </x:c>
       <x:c r="D1821" s="1">
         <x:v>0</x:v>
@@ -52876,10 +52876,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1821" s="1">
-        <x:v>0</x:v>
+        <x:v>34550</x:v>
       </x:c>
       <x:c r="G1821" s="1">
-        <x:v>-1000</x:v>
+        <x:v>181650</x:v>
       </x:c>
     </x:row>
     <x:row r="1822" spans="1:7">
@@ -53025,7 +53025,7 @@
         <x:v>1857</x:v>
       </x:c>
       <x:c r="B1828" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1828" s="1">
         <x:v>0</x:v>
@@ -53048,7 +53048,7 @@
         <x:v>1857</x:v>
       </x:c>
       <x:c r="B1829" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C1829" s="1">
         <x:v>0</x:v>
@@ -56291,10 +56291,10 @@
         <x:v>1996</x:v>
       </x:c>
       <x:c r="B1970" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C1970" s="1">
-        <x:v>0</x:v>
+        <x:v>187150</x:v>
       </x:c>
       <x:c r="D1970" s="1">
         <x:v>31</x:v>
@@ -56303,10 +56303,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1970" s="1">
-        <x:v>0</x:v>
+        <x:v>6150</x:v>
       </x:c>
       <x:c r="G1970" s="1">
-        <x:v>31</x:v>
+        <x:v>193331</x:v>
       </x:c>
     </x:row>
     <x:row r="1971" spans="1:7">
@@ -56314,10 +56314,10 @@
         <x:v>1996</x:v>
       </x:c>
       <x:c r="B1971" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1971" s="1">
-        <x:v>187150</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1971" s="1">
         <x:v>31</x:v>
@@ -56326,10 +56326,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1971" s="1">
-        <x:v>6150</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1971" s="1">
-        <x:v>193331</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="1972" spans="1:7">
@@ -59787,10 +59787,10 @@
         <x:v>2144</x:v>
       </x:c>
       <x:c r="B2122" s="1" t="s">
-        <x:v>190</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C2122" s="1">
-        <x:v>960100</x:v>
+        <x:v>11000</x:v>
       </x:c>
       <x:c r="D2122" s="1">
         <x:v>0</x:v>
@@ -59799,10 +59799,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2122" s="1">
-        <x:v>882230</x:v>
+        <x:v>25550</x:v>
       </x:c>
       <x:c r="G2122" s="1">
-        <x:v>1842330</x:v>
+        <x:v>36550</x:v>
       </x:c>
     </x:row>
     <x:row r="2123" spans="1:7">
@@ -59810,10 +59810,10 @@
         <x:v>2144</x:v>
       </x:c>
       <x:c r="B2123" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C2123" s="1">
-        <x:v>11000</x:v>
+        <x:v>960100</x:v>
       </x:c>
       <x:c r="D2123" s="1">
         <x:v>0</x:v>
@@ -59822,10 +59822,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2123" s="1">
-        <x:v>25550</x:v>
+        <x:v>882230</x:v>
       </x:c>
       <x:c r="G2123" s="1">
-        <x:v>36550</x:v>
+        <x:v>1842330</x:v>
       </x:c>
     </x:row>
     <x:row r="2124" spans="1:7">
@@ -59902,10 +59902,10 @@
         <x:v>2148</x:v>
       </x:c>
       <x:c r="B2127" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C2127" s="1">
-        <x:v>22450</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="D2127" s="1">
         <x:v>0</x:v>
@@ -59914,10 +59914,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2127" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G2127" s="1">
         <x:v>250</x:v>
-      </x:c>
-      <x:c r="G2127" s="1">
-        <x:v>22700</x:v>
       </x:c>
     </x:row>
     <x:row r="2128" spans="1:7">
@@ -59925,22 +59925,22 @@
         <x:v>2148</x:v>
       </x:c>
       <x:c r="B2128" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C2128" s="1">
+        <x:v>22450</x:v>
+      </x:c>
+      <x:c r="D2128" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E2128" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F2128" s="1">
         <x:v>250</x:v>
       </x:c>
-      <x:c r="D2128" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E2128" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F2128" s="1">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="G2128" s="1">
-        <x:v>250</x:v>
+        <x:v>22700</x:v>
       </x:c>
     </x:row>
     <x:row r="2129" spans="1:7">
@@ -72345,10 +72345,10 @@
         <x:v>2685</x:v>
       </x:c>
       <x:c r="B2668" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C2668" s="1">
-        <x:v>7061</x:v>
+        <x:v>409250</x:v>
       </x:c>
       <x:c r="D2668" s="1">
         <x:v>0</x:v>
@@ -72357,10 +72357,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2668" s="1">
-        <x:v>23500</x:v>
+        <x:v>159800</x:v>
       </x:c>
       <x:c r="G2668" s="1">
-        <x:v>30561</x:v>
+        <x:v>569050</x:v>
       </x:c>
     </x:row>
     <x:row r="2669" spans="1:7">
@@ -72368,10 +72368,10 @@
         <x:v>2685</x:v>
       </x:c>
       <x:c r="B2669" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C2669" s="1">
-        <x:v>409250</x:v>
+        <x:v>7061</x:v>
       </x:c>
       <x:c r="D2669" s="1">
         <x:v>0</x:v>
@@ -72380,10 +72380,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2669" s="1">
-        <x:v>159800</x:v>
+        <x:v>23500</x:v>
       </x:c>
       <x:c r="G2669" s="1">
-        <x:v>569050</x:v>
+        <x:v>30561</x:v>
       </x:c>
     </x:row>
     <x:row r="2670" spans="1:7">
@@ -75312,10 +75312,10 @@
         <x:v>2811</x:v>
       </x:c>
       <x:c r="B2797" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C2797" s="1">
-        <x:v>15000</x:v>
+        <x:v>163800</x:v>
       </x:c>
       <x:c r="D2797" s="1">
         <x:v>0</x:v>
@@ -75324,10 +75324,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2797" s="1">
-        <x:v>111650</x:v>
+        <x:v>277645</x:v>
       </x:c>
       <x:c r="G2797" s="1">
-        <x:v>126650</x:v>
+        <x:v>441445</x:v>
       </x:c>
     </x:row>
     <x:row r="2798" spans="1:7">
@@ -75335,10 +75335,10 @@
         <x:v>2811</x:v>
       </x:c>
       <x:c r="B2798" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C2798" s="1">
-        <x:v>163800</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D2798" s="1">
         <x:v>0</x:v>
@@ -75347,10 +75347,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2798" s="1">
-        <x:v>277645</x:v>
+        <x:v>111650</x:v>
       </x:c>
       <x:c r="G2798" s="1">
-        <x:v>441445</x:v>
+        <x:v>126650</x:v>
       </x:c>
     </x:row>
     <x:row r="2799" spans="1:7">
@@ -82005,7 +82005,7 @@
         <x:v>3088</x:v>
       </x:c>
       <x:c r="B3088" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C3088" s="1">
         <x:v>1000</x:v>
@@ -82017,10 +82017,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3088" s="1">
-        <x:v>0</x:v>
+        <x:v>4750</x:v>
       </x:c>
       <x:c r="G3088" s="1">
-        <x:v>1000</x:v>
+        <x:v>5750</x:v>
       </x:c>
     </x:row>
     <x:row r="3089" spans="1:7">
@@ -82028,7 +82028,7 @@
         <x:v>3088</x:v>
       </x:c>
       <x:c r="B3089" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C3089" s="1">
         <x:v>1000</x:v>
@@ -82040,10 +82040,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3089" s="1">
-        <x:v>4750</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3089" s="1">
-        <x:v>5750</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="3090" spans="1:7">
@@ -82327,22 +82327,22 @@
         <x:v>3101</x:v>
       </x:c>
       <x:c r="B3102" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C3102" s="1">
-        <x:v>307450</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3102" s="1">
-        <x:v>0</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3102" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3102" s="1">
-        <x:v>40550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3102" s="1">
-        <x:v>348000</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="3103" spans="1:7">
@@ -82350,22 +82350,22 @@
         <x:v>3101</x:v>
       </x:c>
       <x:c r="B3103" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C3103" s="1">
-        <x:v>0</x:v>
+        <x:v>307450</x:v>
       </x:c>
       <x:c r="D3103" s="1">
-        <x:v>59</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3103" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3103" s="1">
-        <x:v>0</x:v>
+        <x:v>40550</x:v>
       </x:c>
       <x:c r="G3103" s="1">
-        <x:v>59</x:v>
+        <x:v>348000</x:v>
       </x:c>
     </x:row>
     <x:row r="3104" spans="1:7">
@@ -83063,10 +83063,10 @@
         <x:v>3132</x:v>
       </x:c>
       <x:c r="B3134" s="1" t="s">
-        <x:v>155</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C3134" s="1">
-        <x:v>48000</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D3134" s="1">
         <x:v>0</x:v>
@@ -83075,10 +83075,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3134" s="1">
-        <x:v>38300</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G3134" s="1">
-        <x:v>86300</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="3135" spans="1:7">
@@ -83086,10 +83086,10 @@
         <x:v>3132</x:v>
       </x:c>
       <x:c r="B3135" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="C3135" s="1">
-        <x:v>5000</x:v>
+        <x:v>48000</x:v>
       </x:c>
       <x:c r="D3135" s="1">
         <x:v>0</x:v>
@@ -83098,10 +83098,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3135" s="1">
-        <x:v>250</x:v>
+        <x:v>38300</x:v>
       </x:c>
       <x:c r="G3135" s="1">
-        <x:v>5250</x:v>
+        <x:v>86300</x:v>
       </x:c>
     </x:row>
     <x:row r="3136" spans="1:7">
@@ -83201,7 +83201,7 @@
         <x:v>3135</x:v>
       </x:c>
       <x:c r="B3140" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C3140" s="1">
         <x:v>0</x:v>
@@ -83213,10 +83213,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3140" s="1">
-        <x:v>4300</x:v>
+        <x:v>1100</x:v>
       </x:c>
       <x:c r="G3140" s="1">
-        <x:v>4300</x:v>
+        <x:v>1100</x:v>
       </x:c>
     </x:row>
     <x:row r="3141" spans="1:7">
@@ -83224,7 +83224,7 @@
         <x:v>3135</x:v>
       </x:c>
       <x:c r="B3141" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C3141" s="1">
         <x:v>0</x:v>
@@ -83236,10 +83236,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3141" s="1">
-        <x:v>1100</x:v>
+        <x:v>4300</x:v>
       </x:c>
       <x:c r="G3141" s="1">
-        <x:v>1100</x:v>
+        <x:v>4300</x:v>
       </x:c>
     </x:row>
     <x:row r="3142" spans="1:7">
@@ -83431,10 +83431,10 @@
         <x:v>3144</x:v>
       </x:c>
       <x:c r="B3150" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C3150" s="1">
-        <x:v>20000</x:v>
+        <x:v>157500</x:v>
       </x:c>
       <x:c r="D3150" s="1">
         <x:v>0</x:v>
@@ -83443,10 +83443,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3150" s="1">
-        <x:v>6000</x:v>
+        <x:v>45517</x:v>
       </x:c>
       <x:c r="G3150" s="1">
-        <x:v>26000</x:v>
+        <x:v>203017</x:v>
       </x:c>
     </x:row>
     <x:row r="3151" spans="1:7">
@@ -83454,10 +83454,10 @@
         <x:v>3144</x:v>
       </x:c>
       <x:c r="B3151" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C3151" s="1">
-        <x:v>157500</x:v>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="D3151" s="1">
         <x:v>0</x:v>
@@ -83466,10 +83466,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3151" s="1">
-        <x:v>45517</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="G3151" s="1">
-        <x:v>203017</x:v>
+        <x:v>26000</x:v>
       </x:c>
     </x:row>
     <x:row r="3152" spans="1:7">
@@ -84995,10 +84995,10 @@
         <x:v>3210</x:v>
       </x:c>
       <x:c r="B3218" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C3218" s="1">
-        <x:v>3000</x:v>
+        <x:v>2300</x:v>
       </x:c>
       <x:c r="D3218" s="1">
         <x:v>0</x:v>
@@ -85007,10 +85007,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3218" s="1">
-        <x:v>6000</x:v>
+        <x:v>8850</x:v>
       </x:c>
       <x:c r="G3218" s="1">
-        <x:v>9000</x:v>
+        <x:v>11150</x:v>
       </x:c>
     </x:row>
     <x:row r="3219" spans="1:7">
@@ -85018,10 +85018,10 @@
         <x:v>3210</x:v>
       </x:c>
       <x:c r="B3219" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C3219" s="1">
-        <x:v>2300</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D3219" s="1">
         <x:v>0</x:v>
@@ -85030,10 +85030,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3219" s="1">
-        <x:v>8850</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="G3219" s="1">
-        <x:v>11150</x:v>
+        <x:v>9000</x:v>
       </x:c>
     </x:row>
     <x:row r="3220" spans="1:7">
@@ -85294,22 +85294,22 @@
         <x:v>3221</x:v>
       </x:c>
       <x:c r="B3231" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="C3231" s="1">
-        <x:v>0</x:v>
+        <x:v>536500</x:v>
       </x:c>
       <x:c r="D3231" s="1">
-        <x:v>59</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E3231" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3231" s="1">
-        <x:v>0</x:v>
+        <x:v>227847</x:v>
       </x:c>
       <x:c r="G3231" s="1">
-        <x:v>59</x:v>
+        <x:v>764642</x:v>
       </x:c>
     </x:row>
     <x:row r="3232" spans="1:7">
@@ -85317,22 +85317,22 @@
         <x:v>3221</x:v>
       </x:c>
       <x:c r="B3232" s="1" t="s">
-        <x:v>297</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C3232" s="1">
-        <x:v>536500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3232" s="1">
-        <x:v>295</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3232" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3232" s="1">
-        <x:v>227847</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3232" s="1">
-        <x:v>764642</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="3233" spans="1:7">
@@ -85524,10 +85524,10 @@
         <x:v>3230</x:v>
       </x:c>
       <x:c r="B3241" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C3241" s="1">
-        <x:v>343100</x:v>
+        <x:v>34000</x:v>
       </x:c>
       <x:c r="D3241" s="1">
         <x:v>0</x:v>
@@ -85536,10 +85536,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3241" s="1">
-        <x:v>244972</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3241" s="1">
-        <x:v>588072</x:v>
+        <x:v>34000</x:v>
       </x:c>
     </x:row>
     <x:row r="3242" spans="1:7">
@@ -85547,10 +85547,10 @@
         <x:v>3230</x:v>
       </x:c>
       <x:c r="B3242" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C3242" s="1">
-        <x:v>34000</x:v>
+        <x:v>343100</x:v>
       </x:c>
       <x:c r="D3242" s="1">
         <x:v>0</x:v>
@@ -85559,10 +85559,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3242" s="1">
-        <x:v>0</x:v>
+        <x:v>244972</x:v>
       </x:c>
       <x:c r="G3242" s="1">
-        <x:v>34000</x:v>
+        <x:v>588072</x:v>
       </x:c>
     </x:row>
     <x:row r="3243" spans="1:7">
@@ -85708,10 +85708,10 @@
         <x:v>3237</x:v>
       </x:c>
       <x:c r="B3249" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C3249" s="1">
-        <x:v>29500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3249" s="1">
         <x:v>0</x:v>
@@ -85720,10 +85720,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3249" s="1">
-        <x:v>12550</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G3249" s="1">
-        <x:v>42050</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="3250" spans="1:7">
@@ -85731,10 +85731,10 @@
         <x:v>3237</x:v>
       </x:c>
       <x:c r="B3250" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C3250" s="1">
-        <x:v>0</x:v>
+        <x:v>29500</x:v>
       </x:c>
       <x:c r="D3250" s="1">
         <x:v>0</x:v>
@@ -85743,10 +85743,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3250" s="1">
-        <x:v>1000</x:v>
+        <x:v>12550</x:v>
       </x:c>
       <x:c r="G3250" s="1">
-        <x:v>1000</x:v>
+        <x:v>42050</x:v>
       </x:c>
     </x:row>
     <x:row r="3251" spans="1:7">
@@ -85915,22 +85915,22 @@
         <x:v>3245</x:v>
       </x:c>
       <x:c r="B3258" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C3258" s="1">
-        <x:v>420650</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D3258" s="1">
-        <x:v>181</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3258" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3258" s="1">
-        <x:v>448881</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3258" s="1">
-        <x:v>869712</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="3259" spans="1:7">
@@ -85938,22 +85938,22 @@
         <x:v>3245</x:v>
       </x:c>
       <x:c r="B3259" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C3259" s="1">
-        <x:v>25500</x:v>
+        <x:v>420650</x:v>
       </x:c>
       <x:c r="D3259" s="1">
-        <x:v>0</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="E3259" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3259" s="1">
-        <x:v>0</x:v>
+        <x:v>448881</x:v>
       </x:c>
       <x:c r="G3259" s="1">
-        <x:v>25500</x:v>
+        <x:v>869712</x:v>
       </x:c>
     </x:row>
     <x:row r="3260" spans="1:7">
@@ -87732,13 +87732,13 @@
         <x:v>3323</x:v>
       </x:c>
       <x:c r="B3337" s="1" t="s">
-        <x:v>256</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C3337" s="1">
-        <x:v>15000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3337" s="1">
-        <x:v>63</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3337" s="1">
         <x:v>0</x:v>
@@ -87747,7 +87747,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G3337" s="1">
-        <x:v>15063</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="3338" spans="1:7">
@@ -87755,22 +87755,22 @@
         <x:v>3323</x:v>
       </x:c>
       <x:c r="B3338" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C3338" s="1">
-        <x:v>0</x:v>
+        <x:v>332220</x:v>
       </x:c>
       <x:c r="D3338" s="1">
-        <x:v>59</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3338" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3338" s="1">
-        <x:v>0</x:v>
+        <x:v>299023</x:v>
       </x:c>
       <x:c r="G3338" s="1">
-        <x:v>59</x:v>
+        <x:v>631243</x:v>
       </x:c>
     </x:row>
     <x:row r="3339" spans="1:7">
@@ -87778,22 +87778,22 @@
         <x:v>3323</x:v>
       </x:c>
       <x:c r="B3339" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="C3339" s="1">
-        <x:v>332220</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D3339" s="1">
-        <x:v>0</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E3339" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3339" s="1">
-        <x:v>299023</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3339" s="1">
-        <x:v>631243</x:v>
+        <x:v>15063</x:v>
       </x:c>
     </x:row>
     <x:row r="3340" spans="1:7">
@@ -89641,22 +89641,22 @@
         <x:v>3398</x:v>
       </x:c>
       <x:c r="B3420" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C3420" s="1">
-        <x:v>38500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3420" s="1">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E3420" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3420" s="1">
-        <x:v>26250</x:v>
+        <x:v>10700</x:v>
       </x:c>
       <x:c r="G3420" s="1">
-        <x:v>64750</x:v>
+        <x:v>10701</x:v>
       </x:c>
     </x:row>
     <x:row r="3421" spans="1:7">
@@ -89664,22 +89664,22 @@
         <x:v>3398</x:v>
       </x:c>
       <x:c r="B3421" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C3421" s="1">
-        <x:v>0</x:v>
+        <x:v>38500</x:v>
       </x:c>
       <x:c r="D3421" s="1">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3421" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3421" s="1">
-        <x:v>10700</x:v>
+        <x:v>26250</x:v>
       </x:c>
       <x:c r="G3421" s="1">
-        <x:v>10701</x:v>
+        <x:v>64750</x:v>
       </x:c>
     </x:row>
     <x:row r="3422" spans="1:7">
@@ -90193,22 +90193,22 @@
         <x:v>3420</x:v>
       </x:c>
       <x:c r="B3444" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C3444" s="1">
-        <x:v>72750</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3444" s="1">
-        <x:v>295</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3444" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3444" s="1">
-        <x:v>25450</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3444" s="1">
-        <x:v>98495</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="3445" spans="1:7">
@@ -90216,22 +90216,22 @@
         <x:v>3420</x:v>
       </x:c>
       <x:c r="B3445" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C3445" s="1">
-        <x:v>0</x:v>
+        <x:v>72750</x:v>
       </x:c>
       <x:c r="D3445" s="1">
-        <x:v>59</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E3445" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3445" s="1">
-        <x:v>0</x:v>
+        <x:v>25450</x:v>
       </x:c>
       <x:c r="G3445" s="1">
-        <x:v>59</x:v>
+        <x:v>98495</x:v>
       </x:c>
     </x:row>
     <x:row r="3446" spans="1:7">
@@ -92447,10 +92447,10 @@
         <x:v>3509</x:v>
       </x:c>
       <x:c r="B3542" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C3542" s="1">
-        <x:v>130750</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3542" s="1">
         <x:v>7</x:v>
@@ -92459,10 +92459,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3542" s="1">
-        <x:v>83750</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3542" s="1">
-        <x:v>214507</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="3543" spans="1:7">
@@ -92470,10 +92470,10 @@
         <x:v>3509</x:v>
       </x:c>
       <x:c r="B3543" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C3543" s="1">
-        <x:v>0</x:v>
+        <x:v>130750</x:v>
       </x:c>
       <x:c r="D3543" s="1">
         <x:v>7</x:v>
@@ -92482,10 +92482,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3543" s="1">
-        <x:v>0</x:v>
+        <x:v>83750</x:v>
       </x:c>
       <x:c r="G3543" s="1">
-        <x:v>7</x:v>
+        <x:v>214507</x:v>
       </x:c>
     </x:row>
     <x:row r="3544" spans="1:7">

--- a/reports/pro-oil/pro-oil-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-oil/pro-oil-candidate-lobby-lifetime-report.xlsx
@@ -19215,10 +19215,10 @@
         <x:v>412</x:v>
       </x:c>
       <x:c r="B358" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C358" s="1">
-        <x:v>163000</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D358" s="1">
         <x:v>0</x:v>
@@ -19227,10 +19227,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F358" s="1">
-        <x:v>82550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G358" s="1">
-        <x:v>245550</x:v>
+        <x:v>15000</x:v>
       </x:c>
     </x:row>
     <x:row r="359" spans="1:7">
@@ -19238,10 +19238,10 @@
         <x:v>412</x:v>
       </x:c>
       <x:c r="B359" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C359" s="1">
-        <x:v>15000</x:v>
+        <x:v>163000</x:v>
       </x:c>
       <x:c r="D359" s="1">
         <x:v>0</x:v>
@@ -19250,10 +19250,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F359" s="1">
-        <x:v>0</x:v>
+        <x:v>82550</x:v>
       </x:c>
       <x:c r="G359" s="1">
-        <x:v>15000</x:v>
+        <x:v>245550</x:v>
       </x:c>
     </x:row>
     <x:row r="360" spans="1:7">
@@ -30784,10 +30784,10 @@
         <x:v>911</x:v>
       </x:c>
       <x:c r="B861" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="C861" s="1">
-        <x:v>0</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D861" s="1">
         <x:v>0</x:v>
@@ -30796,10 +30796,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F861" s="1">
-        <x:v>14450</x:v>
+        <x:v>12950</x:v>
       </x:c>
       <x:c r="G861" s="1">
-        <x:v>14450</x:v>
+        <x:v>15950</x:v>
       </x:c>
     </x:row>
     <x:row r="862" spans="1:7">
@@ -30807,10 +30807,10 @@
         <x:v>911</x:v>
       </x:c>
       <x:c r="B862" s="1" t="s">
-        <x:v>258</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C862" s="1">
-        <x:v>3000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D862" s="1">
         <x:v>0</x:v>
@@ -30819,10 +30819,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F862" s="1">
-        <x:v>12950</x:v>
+        <x:v>14450</x:v>
       </x:c>
       <x:c r="G862" s="1">
-        <x:v>15950</x:v>
+        <x:v>14450</x:v>
       </x:c>
     </x:row>
     <x:row r="863" spans="1:7">
@@ -31382,22 +31382,22 @@
         <x:v>935</x:v>
       </x:c>
       <x:c r="B887" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="C887" s="1">
-        <x:v>91000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D887" s="1">
-        <x:v>118</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E887" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F887" s="1">
-        <x:v>26100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G887" s="1">
-        <x:v>117218</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="888" spans="1:7">
@@ -31405,22 +31405,22 @@
         <x:v>935</x:v>
       </x:c>
       <x:c r="B888" s="1" t="s">
-        <x:v>297</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C888" s="1">
-        <x:v>0</x:v>
+        <x:v>91000</x:v>
       </x:c>
       <x:c r="D888" s="1">
-        <x:v>59</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E888" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F888" s="1">
-        <x:v>0</x:v>
+        <x:v>26100</x:v>
       </x:c>
       <x:c r="G888" s="1">
-        <x:v>59</x:v>
+        <x:v>117218</x:v>
       </x:c>
     </x:row>
     <x:row r="889" spans="1:7">
@@ -37592,10 +37592,10 @@
         <x:v>1201</x:v>
       </x:c>
       <x:c r="B1157" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C1157" s="1">
-        <x:v>752389</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1157" s="1">
         <x:v>0</x:v>
@@ -37604,10 +37604,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1157" s="1">
-        <x:v>418794</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="G1157" s="1">
-        <x:v>1171183</x:v>
+        <x:v>10000</x:v>
       </x:c>
     </x:row>
     <x:row r="1158" spans="1:7">
@@ -37615,10 +37615,10 @@
         <x:v>1201</x:v>
       </x:c>
       <x:c r="B1158" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1158" s="1">
-        <x:v>0</x:v>
+        <x:v>752389</x:v>
       </x:c>
       <x:c r="D1158" s="1">
         <x:v>0</x:v>
@@ -37627,10 +37627,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1158" s="1">
-        <x:v>10000</x:v>
+        <x:v>418794</x:v>
       </x:c>
       <x:c r="G1158" s="1">
-        <x:v>10000</x:v>
+        <x:v>1171183</x:v>
       </x:c>
     </x:row>
     <x:row r="1159" spans="1:7">
@@ -38811,10 +38811,10 @@
         <x:v>1251</x:v>
       </x:c>
       <x:c r="B1210" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C1210" s="1">
-        <x:v>3000</x:v>
+        <x:v>12000</x:v>
       </x:c>
       <x:c r="D1210" s="1">
         <x:v>0</x:v>
@@ -38823,10 +38823,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1210" s="1">
-        <x:v>50751</x:v>
+        <x:v>12450</x:v>
       </x:c>
       <x:c r="G1210" s="1">
-        <x:v>53751</x:v>
+        <x:v>24450</x:v>
       </x:c>
     </x:row>
     <x:row r="1211" spans="1:7">
@@ -38834,10 +38834,10 @@
         <x:v>1251</x:v>
       </x:c>
       <x:c r="B1211" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C1211" s="1">
-        <x:v>12000</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D1211" s="1">
         <x:v>0</x:v>
@@ -38846,10 +38846,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1211" s="1">
-        <x:v>12450</x:v>
+        <x:v>50751</x:v>
       </x:c>
       <x:c r="G1211" s="1">
-        <x:v>24450</x:v>
+        <x:v>53751</x:v>
       </x:c>
     </x:row>
     <x:row r="1212" spans="1:7">
@@ -46401,10 +46401,10 @@
         <x:v>1579</x:v>
       </x:c>
       <x:c r="B1540" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="C1540" s="1">
-        <x:v>0</x:v>
+        <x:v>82250</x:v>
       </x:c>
       <x:c r="D1540" s="1">
         <x:v>0</x:v>
@@ -46413,10 +46413,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1540" s="1">
-        <x:v>1000</x:v>
+        <x:v>9000</x:v>
       </x:c>
       <x:c r="G1540" s="1">
-        <x:v>1000</x:v>
+        <x:v>91250</x:v>
       </x:c>
     </x:row>
     <x:row r="1541" spans="1:7">
@@ -46424,10 +46424,10 @@
         <x:v>1579</x:v>
       </x:c>
       <x:c r="B1541" s="1" t="s">
-        <x:v>164</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C1541" s="1">
-        <x:v>82250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1541" s="1">
         <x:v>0</x:v>
@@ -46436,10 +46436,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1541" s="1">
-        <x:v>9000</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1541" s="1">
-        <x:v>91250</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="1542" spans="1:7">
@@ -47091,10 +47091,10 @@
         <x:v>1606</x:v>
       </x:c>
       <x:c r="B1570" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="C1570" s="1">
-        <x:v>8000</x:v>
+        <x:v>181700</x:v>
       </x:c>
       <x:c r="D1570" s="1">
         <x:v>0</x:v>
@@ -47103,10 +47103,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1570" s="1">
-        <x:v>66000</x:v>
+        <x:v>168050</x:v>
       </x:c>
       <x:c r="G1570" s="1">
-        <x:v>74000</x:v>
+        <x:v>349750</x:v>
       </x:c>
     </x:row>
     <x:row r="1571" spans="1:7">
@@ -47114,10 +47114,10 @@
         <x:v>1606</x:v>
       </x:c>
       <x:c r="B1571" s="1" t="s">
-        <x:v>416</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C1571" s="1">
-        <x:v>181700</x:v>
+        <x:v>8000</x:v>
       </x:c>
       <x:c r="D1571" s="1">
         <x:v>0</x:v>
@@ -47126,10 +47126,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1571" s="1">
-        <x:v>168050</x:v>
+        <x:v>66000</x:v>
       </x:c>
       <x:c r="G1571" s="1">
-        <x:v>349750</x:v>
+        <x:v>74000</x:v>
       </x:c>
     </x:row>
     <x:row r="1572" spans="1:7">
@@ -49736,10 +49736,10 @@
         <x:v>1719</x:v>
       </x:c>
       <x:c r="B1685" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C1685" s="1">
-        <x:v>0</x:v>
+        <x:v>27850</x:v>
       </x:c>
       <x:c r="D1685" s="1">
         <x:v>0</x:v>
@@ -49748,10 +49748,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1685" s="1">
-        <x:v>102225</x:v>
+        <x:v>19000</x:v>
       </x:c>
       <x:c r="G1685" s="1">
-        <x:v>102225</x:v>
+        <x:v>46850</x:v>
       </x:c>
     </x:row>
     <x:row r="1686" spans="1:7">
@@ -49759,10 +49759,10 @@
         <x:v>1719</x:v>
       </x:c>
       <x:c r="B1686" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C1686" s="1">
-        <x:v>27850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1686" s="1">
         <x:v>0</x:v>
@@ -49771,10 +49771,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1686" s="1">
-        <x:v>19000</x:v>
+        <x:v>102225</x:v>
       </x:c>
       <x:c r="G1686" s="1">
-        <x:v>46850</x:v>
+        <x:v>102225</x:v>
       </x:c>
     </x:row>
     <x:row r="1687" spans="1:7">
@@ -50702,10 +50702,10 @@
         <x:v>1760</x:v>
       </x:c>
       <x:c r="B1727" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1727" s="1">
-        <x:v>485</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1727" s="1">
         <x:v>0</x:v>
@@ -50714,10 +50714,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1727" s="1">
-        <x:v>72700</x:v>
+        <x:v>16350</x:v>
       </x:c>
       <x:c r="G1727" s="1">
-        <x:v>73185</x:v>
+        <x:v>18850</x:v>
       </x:c>
     </x:row>
     <x:row r="1728" spans="1:7">
@@ -50725,10 +50725,10 @@
         <x:v>1760</x:v>
       </x:c>
       <x:c r="B1728" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C1728" s="1">
-        <x:v>2500</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="D1728" s="1">
         <x:v>0</x:v>
@@ -50737,10 +50737,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1728" s="1">
-        <x:v>16350</x:v>
+        <x:v>72700</x:v>
       </x:c>
       <x:c r="G1728" s="1">
-        <x:v>18850</x:v>
+        <x:v>73185</x:v>
       </x:c>
     </x:row>
     <x:row r="1729" spans="1:7">
@@ -52841,10 +52841,10 @@
         <x:v>1850</x:v>
       </x:c>
       <x:c r="B1820" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C1820" s="1">
-        <x:v>-1000</x:v>
+        <x:v>147100</x:v>
       </x:c>
       <x:c r="D1820" s="1">
         <x:v>0</x:v>
@@ -52853,10 +52853,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1820" s="1">
-        <x:v>0</x:v>
+        <x:v>34550</x:v>
       </x:c>
       <x:c r="G1820" s="1">
-        <x:v>-1000</x:v>
+        <x:v>181650</x:v>
       </x:c>
     </x:row>
     <x:row r="1821" spans="1:7">
@@ -52864,10 +52864,10 @@
         <x:v>1850</x:v>
       </x:c>
       <x:c r="B1821" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C1821" s="1">
-        <x:v>147100</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="D1821" s="1">
         <x:v>0</x:v>
@@ -52876,10 +52876,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1821" s="1">
-        <x:v>34550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1821" s="1">
-        <x:v>181650</x:v>
+        <x:v>-1000</x:v>
       </x:c>
     </x:row>
     <x:row r="1822" spans="1:7">
@@ -53025,7 +53025,7 @@
         <x:v>1857</x:v>
       </x:c>
       <x:c r="B1828" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C1828" s="1">
         <x:v>0</x:v>
@@ -53048,7 +53048,7 @@
         <x:v>1857</x:v>
       </x:c>
       <x:c r="B1829" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1829" s="1">
         <x:v>0</x:v>
@@ -56291,10 +56291,10 @@
         <x:v>1996</x:v>
       </x:c>
       <x:c r="B1970" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1970" s="1">
-        <x:v>187150</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1970" s="1">
         <x:v>31</x:v>
@@ -56303,10 +56303,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1970" s="1">
-        <x:v>6150</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1970" s="1">
-        <x:v>193331</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="1971" spans="1:7">
@@ -56314,10 +56314,10 @@
         <x:v>1996</x:v>
       </x:c>
       <x:c r="B1971" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C1971" s="1">
-        <x:v>0</x:v>
+        <x:v>187150</x:v>
       </x:c>
       <x:c r="D1971" s="1">
         <x:v>31</x:v>
@@ -56326,10 +56326,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1971" s="1">
-        <x:v>0</x:v>
+        <x:v>6150</x:v>
       </x:c>
       <x:c r="G1971" s="1">
-        <x:v>31</x:v>
+        <x:v>193331</x:v>
       </x:c>
     </x:row>
     <x:row r="1972" spans="1:7">
@@ -72345,10 +72345,10 @@
         <x:v>2685</x:v>
       </x:c>
       <x:c r="B2668" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C2668" s="1">
-        <x:v>409250</x:v>
+        <x:v>7061</x:v>
       </x:c>
       <x:c r="D2668" s="1">
         <x:v>0</x:v>
@@ -72357,10 +72357,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2668" s="1">
-        <x:v>159800</x:v>
+        <x:v>23500</x:v>
       </x:c>
       <x:c r="G2668" s="1">
-        <x:v>569050</x:v>
+        <x:v>30561</x:v>
       </x:c>
     </x:row>
     <x:row r="2669" spans="1:7">
@@ -72368,10 +72368,10 @@
         <x:v>2685</x:v>
       </x:c>
       <x:c r="B2669" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C2669" s="1">
-        <x:v>7061</x:v>
+        <x:v>409250</x:v>
       </x:c>
       <x:c r="D2669" s="1">
         <x:v>0</x:v>
@@ -72380,10 +72380,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2669" s="1">
-        <x:v>23500</x:v>
+        <x:v>159800</x:v>
       </x:c>
       <x:c r="G2669" s="1">
-        <x:v>30561</x:v>
+        <x:v>569050</x:v>
       </x:c>
     </x:row>
     <x:row r="2670" spans="1:7">
@@ -75312,10 +75312,10 @@
         <x:v>2811</x:v>
       </x:c>
       <x:c r="B2797" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C2797" s="1">
-        <x:v>163800</x:v>
+        <x:v>206766</x:v>
       </x:c>
       <x:c r="D2797" s="1">
         <x:v>0</x:v>
@@ -75324,10 +75324,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2797" s="1">
-        <x:v>277645</x:v>
+        <x:v>286825</x:v>
       </x:c>
       <x:c r="G2797" s="1">
-        <x:v>441445</x:v>
+        <x:v>493591</x:v>
       </x:c>
     </x:row>
     <x:row r="2798" spans="1:7">
@@ -75335,10 +75335,10 @@
         <x:v>2811</x:v>
       </x:c>
       <x:c r="B2798" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C2798" s="1">
-        <x:v>15000</x:v>
+        <x:v>163800</x:v>
       </x:c>
       <x:c r="D2798" s="1">
         <x:v>0</x:v>
@@ -75347,10 +75347,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2798" s="1">
-        <x:v>111650</x:v>
+        <x:v>277645</x:v>
       </x:c>
       <x:c r="G2798" s="1">
-        <x:v>126650</x:v>
+        <x:v>441445</x:v>
       </x:c>
     </x:row>
     <x:row r="2799" spans="1:7">
@@ -75358,10 +75358,10 @@
         <x:v>2811</x:v>
       </x:c>
       <x:c r="B2799" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C2799" s="1">
-        <x:v>206766</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D2799" s="1">
         <x:v>0</x:v>
@@ -75370,10 +75370,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2799" s="1">
-        <x:v>286825</x:v>
+        <x:v>111650</x:v>
       </x:c>
       <x:c r="G2799" s="1">
-        <x:v>493591</x:v>
+        <x:v>126650</x:v>
       </x:c>
     </x:row>
     <x:row r="2800" spans="1:7">
@@ -78624,10 +78624,10 @@
         <x:v>2950</x:v>
       </x:c>
       <x:c r="B2941" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C2941" s="1">
-        <x:v>12000</x:v>
+        <x:v>99950</x:v>
       </x:c>
       <x:c r="D2941" s="1">
         <x:v>0</x:v>
@@ -78636,10 +78636,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2941" s="1">
-        <x:v>0</x:v>
+        <x:v>6650</x:v>
       </x:c>
       <x:c r="G2941" s="1">
-        <x:v>12000</x:v>
+        <x:v>106600</x:v>
       </x:c>
     </x:row>
     <x:row r="2942" spans="1:7">
@@ -78647,10 +78647,10 @@
         <x:v>2950</x:v>
       </x:c>
       <x:c r="B2942" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C2942" s="1">
-        <x:v>99950</x:v>
+        <x:v>12000</x:v>
       </x:c>
       <x:c r="D2942" s="1">
         <x:v>0</x:v>
@@ -78659,10 +78659,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2942" s="1">
-        <x:v>6650</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2942" s="1">
-        <x:v>106600</x:v>
+        <x:v>12000</x:v>
       </x:c>
     </x:row>
     <x:row r="2943" spans="1:7">
@@ -79314,10 +79314,10 @@
         <x:v>2978</x:v>
       </x:c>
       <x:c r="B2971" s="1" t="s">
-        <x:v>747</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C2971" s="1">
-        <x:v>286800</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D2971" s="1">
         <x:v>0</x:v>
@@ -79326,10 +79326,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2971" s="1">
-        <x:v>75150</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2971" s="1">
-        <x:v>361950</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="2972" spans="1:7">
@@ -79337,10 +79337,10 @@
         <x:v>2978</x:v>
       </x:c>
       <x:c r="B2972" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>747</x:v>
       </x:c>
       <x:c r="C2972" s="1">
-        <x:v>5000</x:v>
+        <x:v>286800</x:v>
       </x:c>
       <x:c r="D2972" s="1">
         <x:v>0</x:v>
@@ -79349,10 +79349,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2972" s="1">
-        <x:v>0</x:v>
+        <x:v>75150</x:v>
       </x:c>
       <x:c r="G2972" s="1">
-        <x:v>5000</x:v>
+        <x:v>361950</x:v>
       </x:c>
     </x:row>
     <x:row r="2973" spans="1:7">
@@ -83201,7 +83201,7 @@
         <x:v>3135</x:v>
       </x:c>
       <x:c r="B3140" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C3140" s="1">
         <x:v>0</x:v>
@@ -83213,10 +83213,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3140" s="1">
-        <x:v>1100</x:v>
+        <x:v>4300</x:v>
       </x:c>
       <x:c r="G3140" s="1">
-        <x:v>1100</x:v>
+        <x:v>4300</x:v>
       </x:c>
     </x:row>
     <x:row r="3141" spans="1:7">
@@ -83224,7 +83224,7 @@
         <x:v>3135</x:v>
       </x:c>
       <x:c r="B3141" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C3141" s="1">
         <x:v>0</x:v>
@@ -83236,10 +83236,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3141" s="1">
-        <x:v>4300</x:v>
+        <x:v>1100</x:v>
       </x:c>
       <x:c r="G3141" s="1">
-        <x:v>4300</x:v>
+        <x:v>1100</x:v>
       </x:c>
     </x:row>
     <x:row r="3142" spans="1:7">
@@ -83431,10 +83431,10 @@
         <x:v>3144</x:v>
       </x:c>
       <x:c r="B3150" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C3150" s="1">
-        <x:v>157500</x:v>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="D3150" s="1">
         <x:v>0</x:v>
@@ -83443,10 +83443,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3150" s="1">
-        <x:v>45517</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="G3150" s="1">
-        <x:v>203017</x:v>
+        <x:v>26000</x:v>
       </x:c>
     </x:row>
     <x:row r="3151" spans="1:7">
@@ -83454,10 +83454,10 @@
         <x:v>3144</x:v>
       </x:c>
       <x:c r="B3151" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C3151" s="1">
-        <x:v>20000</x:v>
+        <x:v>157500</x:v>
       </x:c>
       <x:c r="D3151" s="1">
         <x:v>0</x:v>
@@ -83466,10 +83466,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3151" s="1">
-        <x:v>6000</x:v>
+        <x:v>45517</x:v>
       </x:c>
       <x:c r="G3151" s="1">
-        <x:v>26000</x:v>
+        <x:v>203017</x:v>
       </x:c>
     </x:row>
     <x:row r="3152" spans="1:7">
@@ -87732,13 +87732,13 @@
         <x:v>3323</x:v>
       </x:c>
       <x:c r="B3337" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="C3337" s="1">
-        <x:v>0</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D3337" s="1">
-        <x:v>59</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E3337" s="1">
         <x:v>0</x:v>
@@ -87747,7 +87747,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G3337" s="1">
-        <x:v>59</x:v>
+        <x:v>15063</x:v>
       </x:c>
     </x:row>
     <x:row r="3338" spans="1:7">
@@ -87778,13 +87778,13 @@
         <x:v>3323</x:v>
       </x:c>
       <x:c r="B3339" s="1" t="s">
-        <x:v>256</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C3339" s="1">
-        <x:v>15000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3339" s="1">
-        <x:v>63</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3339" s="1">
         <x:v>0</x:v>
@@ -87793,7 +87793,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G3339" s="1">
-        <x:v>15063</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="3340" spans="1:7">
@@ -88928,10 +88928,10 @@
         <x:v>3370</x:v>
       </x:c>
       <x:c r="B3389" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C3389" s="1">
-        <x:v>15000</x:v>
+        <x:v>41550</x:v>
       </x:c>
       <x:c r="D3389" s="1">
         <x:v>0</x:v>
@@ -88940,10 +88940,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3389" s="1">
-        <x:v>0</x:v>
+        <x:v>6500</x:v>
       </x:c>
       <x:c r="G3389" s="1">
-        <x:v>15000</x:v>
+        <x:v>48050</x:v>
       </x:c>
     </x:row>
     <x:row r="3390" spans="1:7">
@@ -88951,10 +88951,10 @@
         <x:v>3370</x:v>
       </x:c>
       <x:c r="B3390" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C3390" s="1">
-        <x:v>41550</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D3390" s="1">
         <x:v>0</x:v>
@@ -88963,10 +88963,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3390" s="1">
-        <x:v>6500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3390" s="1">
-        <x:v>48050</x:v>
+        <x:v>15000</x:v>
       </x:c>
     </x:row>
     <x:row r="3391" spans="1:7">
@@ -89641,22 +89641,22 @@
         <x:v>3398</x:v>
       </x:c>
       <x:c r="B3420" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C3420" s="1">
-        <x:v>0</x:v>
+        <x:v>38500</x:v>
       </x:c>
       <x:c r="D3420" s="1">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3420" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3420" s="1">
-        <x:v>10700</x:v>
+        <x:v>26250</x:v>
       </x:c>
       <x:c r="G3420" s="1">
-        <x:v>10701</x:v>
+        <x:v>64750</x:v>
       </x:c>
     </x:row>
     <x:row r="3421" spans="1:7">
@@ -89664,22 +89664,22 @@
         <x:v>3398</x:v>
       </x:c>
       <x:c r="B3421" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C3421" s="1">
-        <x:v>38500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3421" s="1">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E3421" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3421" s="1">
-        <x:v>26250</x:v>
+        <x:v>10700</x:v>
       </x:c>
       <x:c r="G3421" s="1">
-        <x:v>64750</x:v>
+        <x:v>10701</x:v>
       </x:c>
     </x:row>
     <x:row r="3422" spans="1:7">
@@ -90423,22 +90423,22 @@
         <x:v>3428</x:v>
       </x:c>
       <x:c r="B3454" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C3454" s="1">
-        <x:v>0</x:v>
+        <x:v>47850</x:v>
       </x:c>
       <x:c r="D3454" s="1">
-        <x:v>59</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3454" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3454" s="1">
-        <x:v>0</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G3454" s="1">
-        <x:v>59</x:v>
+        <x:v>52850</x:v>
       </x:c>
     </x:row>
     <x:row r="3455" spans="1:7">
@@ -90446,22 +90446,22 @@
         <x:v>3428</x:v>
       </x:c>
       <x:c r="B3455" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C3455" s="1">
-        <x:v>47850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3455" s="1">
-        <x:v>0</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3455" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3455" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3455" s="1">
-        <x:v>52850</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="3456" spans="1:7">
@@ -90676,10 +90676,10 @@
         <x:v>3438</x:v>
       </x:c>
       <x:c r="B3465" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C3465" s="1">
-        <x:v>22500</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D3465" s="1">
         <x:v>0</x:v>
@@ -90691,7 +90691,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G3465" s="1">
-        <x:v>22500</x:v>
+        <x:v>3000</x:v>
       </x:c>
     </x:row>
     <x:row r="3466" spans="1:7">
@@ -90699,22 +90699,22 @@
         <x:v>3438</x:v>
       </x:c>
       <x:c r="B3466" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="C3466" s="1">
-        <x:v>3000</x:v>
+        <x:v>437150</x:v>
       </x:c>
       <x:c r="D3466" s="1">
-        <x:v>0</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="E3466" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3466" s="1">
-        <x:v>0</x:v>
+        <x:v>348550</x:v>
       </x:c>
       <x:c r="G3466" s="1">
-        <x:v>3000</x:v>
+        <x:v>786168</x:v>
       </x:c>
     </x:row>
     <x:row r="3467" spans="1:7">
@@ -90722,22 +90722,22 @@
         <x:v>3438</x:v>
       </x:c>
       <x:c r="B3467" s="1" t="s">
-        <x:v>416</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C3467" s="1">
-        <x:v>437150</x:v>
+        <x:v>22500</x:v>
       </x:c>
       <x:c r="D3467" s="1">
-        <x:v>468</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3467" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3467" s="1">
-        <x:v>348550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3467" s="1">
-        <x:v>786168</x:v>
+        <x:v>22500</x:v>
       </x:c>
     </x:row>
     <x:row r="3468" spans="1:7">
@@ -91435,22 +91435,22 @@
         <x:v>3468</x:v>
       </x:c>
       <x:c r="B3498" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C3498" s="1">
-        <x:v>0</x:v>
+        <x:v>265983</x:v>
       </x:c>
       <x:c r="D3498" s="1">
-        <x:v>59</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="E3498" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3498" s="1">
-        <x:v>44000</x:v>
+        <x:v>126150</x:v>
       </x:c>
       <x:c r="G3498" s="1">
-        <x:v>44059</x:v>
+        <x:v>392310</x:v>
       </x:c>
     </x:row>
     <x:row r="3499" spans="1:7">
@@ -91458,22 +91458,22 @@
         <x:v>3468</x:v>
       </x:c>
       <x:c r="B3499" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C3499" s="1">
-        <x:v>265983</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3499" s="1">
-        <x:v>177</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3499" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3499" s="1">
-        <x:v>126150</x:v>
+        <x:v>44000</x:v>
       </x:c>
       <x:c r="G3499" s="1">
-        <x:v>392310</x:v>
+        <x:v>44059</x:v>
       </x:c>
     </x:row>
     <x:row r="3500" spans="1:7">

--- a/reports/pro-oil/pro-oil-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-oil/pro-oil-candidate-lobby-lifetime-report.xlsx
@@ -19215,10 +19215,10 @@
         <x:v>412</x:v>
       </x:c>
       <x:c r="B358" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C358" s="1">
-        <x:v>15000</x:v>
+        <x:v>163000</x:v>
       </x:c>
       <x:c r="D358" s="1">
         <x:v>0</x:v>
@@ -19227,10 +19227,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F358" s="1">
-        <x:v>0</x:v>
+        <x:v>82550</x:v>
       </x:c>
       <x:c r="G358" s="1">
-        <x:v>15000</x:v>
+        <x:v>245550</x:v>
       </x:c>
     </x:row>
     <x:row r="359" spans="1:7">
@@ -19238,10 +19238,10 @@
         <x:v>412</x:v>
       </x:c>
       <x:c r="B359" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C359" s="1">
-        <x:v>163000</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D359" s="1">
         <x:v>0</x:v>
@@ -19250,10 +19250,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F359" s="1">
-        <x:v>82550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G359" s="1">
-        <x:v>245550</x:v>
+        <x:v>15000</x:v>
       </x:c>
     </x:row>
     <x:row r="360" spans="1:7">
@@ -27196,22 +27196,22 @@
         <x:v>757</x:v>
       </x:c>
       <x:c r="B705" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>747</x:v>
       </x:c>
       <x:c r="C705" s="1">
-        <x:v>25500</x:v>
+        <x:v>418533</x:v>
       </x:c>
       <x:c r="D705" s="1">
-        <x:v>0</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E705" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F705" s="1">
-        <x:v>0</x:v>
+        <x:v>51350</x:v>
       </x:c>
       <x:c r="G705" s="1">
-        <x:v>25500</x:v>
+        <x:v>470001</x:v>
       </x:c>
     </x:row>
     <x:row r="706" spans="1:7">
@@ -27219,22 +27219,22 @@
         <x:v>757</x:v>
       </x:c>
       <x:c r="B706" s="1" t="s">
-        <x:v>747</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C706" s="1">
-        <x:v>418533</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D706" s="1">
-        <x:v>118</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E706" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F706" s="1">
-        <x:v>51350</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G706" s="1">
-        <x:v>470001</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="707" spans="1:7">
@@ -30784,10 +30784,10 @@
         <x:v>911</x:v>
       </x:c>
       <x:c r="B861" s="1" t="s">
-        <x:v>258</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C861" s="1">
-        <x:v>3000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D861" s="1">
         <x:v>0</x:v>
@@ -30796,10 +30796,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F861" s="1">
-        <x:v>12950</x:v>
+        <x:v>14450</x:v>
       </x:c>
       <x:c r="G861" s="1">
-        <x:v>15950</x:v>
+        <x:v>14450</x:v>
       </x:c>
     </x:row>
     <x:row r="862" spans="1:7">
@@ -30807,10 +30807,10 @@
         <x:v>911</x:v>
       </x:c>
       <x:c r="B862" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="C862" s="1">
-        <x:v>0</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D862" s="1">
         <x:v>0</x:v>
@@ -30819,10 +30819,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F862" s="1">
-        <x:v>14450</x:v>
+        <x:v>12950</x:v>
       </x:c>
       <x:c r="G862" s="1">
-        <x:v>14450</x:v>
+        <x:v>15950</x:v>
       </x:c>
     </x:row>
     <x:row r="863" spans="1:7">
@@ -49736,10 +49736,10 @@
         <x:v>1719</x:v>
       </x:c>
       <x:c r="B1685" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C1685" s="1">
-        <x:v>27850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1685" s="1">
         <x:v>0</x:v>
@@ -49748,10 +49748,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1685" s="1">
-        <x:v>19000</x:v>
+        <x:v>102225</x:v>
       </x:c>
       <x:c r="G1685" s="1">
-        <x:v>46850</x:v>
+        <x:v>102225</x:v>
       </x:c>
     </x:row>
     <x:row r="1686" spans="1:7">
@@ -49759,10 +49759,10 @@
         <x:v>1719</x:v>
       </x:c>
       <x:c r="B1686" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C1686" s="1">
-        <x:v>0</x:v>
+        <x:v>27850</x:v>
       </x:c>
       <x:c r="D1686" s="1">
         <x:v>0</x:v>
@@ -49771,10 +49771,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1686" s="1">
-        <x:v>102225</x:v>
+        <x:v>19000</x:v>
       </x:c>
       <x:c r="G1686" s="1">
-        <x:v>102225</x:v>
+        <x:v>46850</x:v>
       </x:c>
     </x:row>
     <x:row r="1687" spans="1:7">
@@ -52841,10 +52841,10 @@
         <x:v>1850</x:v>
       </x:c>
       <x:c r="B1820" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C1820" s="1">
-        <x:v>147100</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="D1820" s="1">
         <x:v>0</x:v>
@@ -52853,10 +52853,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1820" s="1">
-        <x:v>34550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1820" s="1">
-        <x:v>181650</x:v>
+        <x:v>-1000</x:v>
       </x:c>
     </x:row>
     <x:row r="1821" spans="1:7">
@@ -52864,10 +52864,10 @@
         <x:v>1850</x:v>
       </x:c>
       <x:c r="B1821" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C1821" s="1">
-        <x:v>-1000</x:v>
+        <x:v>147100</x:v>
       </x:c>
       <x:c r="D1821" s="1">
         <x:v>0</x:v>
@@ -52876,10 +52876,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1821" s="1">
-        <x:v>0</x:v>
+        <x:v>34550</x:v>
       </x:c>
       <x:c r="G1821" s="1">
-        <x:v>-1000</x:v>
+        <x:v>181650</x:v>
       </x:c>
     </x:row>
     <x:row r="1822" spans="1:7">
@@ -59787,10 +59787,10 @@
         <x:v>2144</x:v>
       </x:c>
       <x:c r="B2122" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C2122" s="1">
-        <x:v>11000</x:v>
+        <x:v>960100</x:v>
       </x:c>
       <x:c r="D2122" s="1">
         <x:v>0</x:v>
@@ -59799,10 +59799,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2122" s="1">
-        <x:v>25550</x:v>
+        <x:v>882230</x:v>
       </x:c>
       <x:c r="G2122" s="1">
-        <x:v>36550</x:v>
+        <x:v>1842330</x:v>
       </x:c>
     </x:row>
     <x:row r="2123" spans="1:7">
@@ -59810,10 +59810,10 @@
         <x:v>2144</x:v>
       </x:c>
       <x:c r="B2123" s="1" t="s">
-        <x:v>190</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C2123" s="1">
-        <x:v>960100</x:v>
+        <x:v>11000</x:v>
       </x:c>
       <x:c r="D2123" s="1">
         <x:v>0</x:v>
@@ -59822,10 +59822,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2123" s="1">
-        <x:v>882230</x:v>
+        <x:v>25550</x:v>
       </x:c>
       <x:c r="G2123" s="1">
-        <x:v>1842330</x:v>
+        <x:v>36550</x:v>
       </x:c>
     </x:row>
     <x:row r="2124" spans="1:7">
@@ -59902,22 +59902,22 @@
         <x:v>2148</x:v>
       </x:c>
       <x:c r="B2127" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C2127" s="1">
+        <x:v>22450</x:v>
+      </x:c>
+      <x:c r="D2127" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E2127" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F2127" s="1">
         <x:v>250</x:v>
       </x:c>
-      <x:c r="D2127" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E2127" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F2127" s="1">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="G2127" s="1">
-        <x:v>250</x:v>
+        <x:v>22700</x:v>
       </x:c>
     </x:row>
     <x:row r="2128" spans="1:7">
@@ -59925,10 +59925,10 @@
         <x:v>2148</x:v>
       </x:c>
       <x:c r="B2128" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C2128" s="1">
-        <x:v>22450</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="D2128" s="1">
         <x:v>0</x:v>
@@ -59937,10 +59937,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2128" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G2128" s="1">
         <x:v>250</x:v>
-      </x:c>
-      <x:c r="G2128" s="1">
-        <x:v>22700</x:v>
       </x:c>
     </x:row>
     <x:row r="2129" spans="1:7">
@@ -72345,10 +72345,10 @@
         <x:v>2685</x:v>
       </x:c>
       <x:c r="B2668" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C2668" s="1">
-        <x:v>7061</x:v>
+        <x:v>409250</x:v>
       </x:c>
       <x:c r="D2668" s="1">
         <x:v>0</x:v>
@@ -72357,10 +72357,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2668" s="1">
-        <x:v>23500</x:v>
+        <x:v>159800</x:v>
       </x:c>
       <x:c r="G2668" s="1">
-        <x:v>30561</x:v>
+        <x:v>569050</x:v>
       </x:c>
     </x:row>
     <x:row r="2669" spans="1:7">
@@ -72368,10 +72368,10 @@
         <x:v>2685</x:v>
       </x:c>
       <x:c r="B2669" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C2669" s="1">
-        <x:v>409250</x:v>
+        <x:v>7061</x:v>
       </x:c>
       <x:c r="D2669" s="1">
         <x:v>0</x:v>
@@ -72380,10 +72380,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2669" s="1">
-        <x:v>159800</x:v>
+        <x:v>23500</x:v>
       </x:c>
       <x:c r="G2669" s="1">
-        <x:v>569050</x:v>
+        <x:v>30561</x:v>
       </x:c>
     </x:row>
     <x:row r="2670" spans="1:7">
@@ -72506,10 +72506,10 @@
         <x:v>2691</x:v>
       </x:c>
       <x:c r="B2675" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C2675" s="1">
-        <x:v>139000</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D2675" s="1">
         <x:v>0</x:v>
@@ -72518,10 +72518,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2675" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2675" s="1">
-        <x:v>139500</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="2676" spans="1:7">
@@ -72529,10 +72529,10 @@
         <x:v>2691</x:v>
       </x:c>
       <x:c r="B2676" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C2676" s="1">
-        <x:v>7000</x:v>
+        <x:v>139000</x:v>
       </x:c>
       <x:c r="D2676" s="1">
         <x:v>0</x:v>
@@ -72541,10 +72541,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2676" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G2676" s="1">
-        <x:v>7000</x:v>
+        <x:v>139500</x:v>
       </x:c>
     </x:row>
     <x:row r="2677" spans="1:7">
@@ -75312,10 +75312,10 @@
         <x:v>2811</x:v>
       </x:c>
       <x:c r="B2797" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C2797" s="1">
-        <x:v>206766</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D2797" s="1">
         <x:v>0</x:v>
@@ -75324,10 +75324,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2797" s="1">
-        <x:v>286825</x:v>
+        <x:v>111650</x:v>
       </x:c>
       <x:c r="G2797" s="1">
-        <x:v>493591</x:v>
+        <x:v>126650</x:v>
       </x:c>
     </x:row>
     <x:row r="2798" spans="1:7">
@@ -75335,10 +75335,10 @@
         <x:v>2811</x:v>
       </x:c>
       <x:c r="B2798" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C2798" s="1">
-        <x:v>163800</x:v>
+        <x:v>206766</x:v>
       </x:c>
       <x:c r="D2798" s="1">
         <x:v>0</x:v>
@@ -75347,10 +75347,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2798" s="1">
-        <x:v>277645</x:v>
+        <x:v>286825</x:v>
       </x:c>
       <x:c r="G2798" s="1">
-        <x:v>441445</x:v>
+        <x:v>493591</x:v>
       </x:c>
     </x:row>
     <x:row r="2799" spans="1:7">
@@ -75358,10 +75358,10 @@
         <x:v>2811</x:v>
       </x:c>
       <x:c r="B2799" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C2799" s="1">
-        <x:v>15000</x:v>
+        <x:v>163800</x:v>
       </x:c>
       <x:c r="D2799" s="1">
         <x:v>0</x:v>
@@ -75370,10 +75370,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2799" s="1">
-        <x:v>111650</x:v>
+        <x:v>277645</x:v>
       </x:c>
       <x:c r="G2799" s="1">
-        <x:v>126650</x:v>
+        <x:v>441445</x:v>
       </x:c>
     </x:row>
     <x:row r="2800" spans="1:7">
@@ -76853,10 +76853,10 @@
         <x:v>2875</x:v>
       </x:c>
       <x:c r="B2864" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C2864" s="1">
-        <x:v>102350</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D2864" s="1">
         <x:v>0</x:v>
@@ -76865,10 +76865,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2864" s="1">
-        <x:v>106550</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G2864" s="1">
-        <x:v>208900</x:v>
+        <x:v>20000</x:v>
       </x:c>
     </x:row>
     <x:row r="2865" spans="1:7">
@@ -76876,10 +76876,10 @@
         <x:v>2875</x:v>
       </x:c>
       <x:c r="B2865" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C2865" s="1">
-        <x:v>15000</x:v>
+        <x:v>102350</x:v>
       </x:c>
       <x:c r="D2865" s="1">
         <x:v>0</x:v>
@@ -76888,10 +76888,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2865" s="1">
-        <x:v>5000</x:v>
+        <x:v>106550</x:v>
       </x:c>
       <x:c r="G2865" s="1">
-        <x:v>20000</x:v>
+        <x:v>208900</x:v>
       </x:c>
     </x:row>
     <x:row r="2866" spans="1:7">
@@ -78210,10 +78210,10 @@
         <x:v>2933</x:v>
       </x:c>
       <x:c r="B2923" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C2923" s="1">
-        <x:v>37500</x:v>
+        <x:v>206000</x:v>
       </x:c>
       <x:c r="D2923" s="1">
         <x:v>0</x:v>
@@ -78222,10 +78222,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2923" s="1">
-        <x:v>8000</x:v>
+        <x:v>45600</x:v>
       </x:c>
       <x:c r="G2923" s="1">
-        <x:v>45500</x:v>
+        <x:v>251600</x:v>
       </x:c>
     </x:row>
     <x:row r="2924" spans="1:7">
@@ -78233,10 +78233,10 @@
         <x:v>2933</x:v>
       </x:c>
       <x:c r="B2924" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C2924" s="1">
-        <x:v>206000</x:v>
+        <x:v>37500</x:v>
       </x:c>
       <x:c r="D2924" s="1">
         <x:v>0</x:v>
@@ -78245,10 +78245,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2924" s="1">
-        <x:v>45600</x:v>
+        <x:v>8000</x:v>
       </x:c>
       <x:c r="G2924" s="1">
-        <x:v>251600</x:v>
+        <x:v>45500</x:v>
       </x:c>
     </x:row>
     <x:row r="2925" spans="1:7">
@@ -78624,10 +78624,10 @@
         <x:v>2950</x:v>
       </x:c>
       <x:c r="B2941" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C2941" s="1">
-        <x:v>99950</x:v>
+        <x:v>12000</x:v>
       </x:c>
       <x:c r="D2941" s="1">
         <x:v>0</x:v>
@@ -78636,10 +78636,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2941" s="1">
-        <x:v>6650</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2941" s="1">
-        <x:v>106600</x:v>
+        <x:v>12000</x:v>
       </x:c>
     </x:row>
     <x:row r="2942" spans="1:7">
@@ -78647,10 +78647,10 @@
         <x:v>2950</x:v>
       </x:c>
       <x:c r="B2942" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C2942" s="1">
-        <x:v>12000</x:v>
+        <x:v>99950</x:v>
       </x:c>
       <x:c r="D2942" s="1">
         <x:v>0</x:v>
@@ -78659,10 +78659,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2942" s="1">
-        <x:v>0</x:v>
+        <x:v>6650</x:v>
       </x:c>
       <x:c r="G2942" s="1">
-        <x:v>12000</x:v>
+        <x:v>106600</x:v>
       </x:c>
     </x:row>
     <x:row r="2943" spans="1:7">
@@ -81660,10 +81660,10 @@
         <x:v>3077</x:v>
       </x:c>
       <x:c r="B3073" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C3073" s="1">
-        <x:v>44000</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D3073" s="1">
         <x:v>0</x:v>
@@ -81672,10 +81672,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3073" s="1">
-        <x:v>2100</x:v>
+        <x:v>33600</x:v>
       </x:c>
       <x:c r="G3073" s="1">
-        <x:v>46100</x:v>
+        <x:v>38600</x:v>
       </x:c>
     </x:row>
     <x:row r="3074" spans="1:7">
@@ -81683,10 +81683,10 @@
         <x:v>3077</x:v>
       </x:c>
       <x:c r="B3074" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C3074" s="1">
-        <x:v>5000</x:v>
+        <x:v>10500</x:v>
       </x:c>
       <x:c r="D3074" s="1">
         <x:v>0</x:v>
@@ -81695,10 +81695,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3074" s="1">
-        <x:v>33600</x:v>
+        <x:v>31300</x:v>
       </x:c>
       <x:c r="G3074" s="1">
-        <x:v>38600</x:v>
+        <x:v>41800</x:v>
       </x:c>
     </x:row>
     <x:row r="3075" spans="1:7">
@@ -81706,10 +81706,10 @@
         <x:v>3077</x:v>
       </x:c>
       <x:c r="B3075" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C3075" s="1">
-        <x:v>10500</x:v>
+        <x:v>44000</x:v>
       </x:c>
       <x:c r="D3075" s="1">
         <x:v>0</x:v>
@@ -81718,10 +81718,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3075" s="1">
-        <x:v>31300</x:v>
+        <x:v>2100</x:v>
       </x:c>
       <x:c r="G3075" s="1">
-        <x:v>41800</x:v>
+        <x:v>46100</x:v>
       </x:c>
     </x:row>
     <x:row r="3076" spans="1:7">
@@ -82005,7 +82005,7 @@
         <x:v>3088</x:v>
       </x:c>
       <x:c r="B3088" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C3088" s="1">
         <x:v>1000</x:v>
@@ -82017,10 +82017,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3088" s="1">
-        <x:v>4750</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3088" s="1">
-        <x:v>5750</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="3089" spans="1:7">
@@ -82028,7 +82028,7 @@
         <x:v>3088</x:v>
       </x:c>
       <x:c r="B3089" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C3089" s="1">
         <x:v>1000</x:v>
@@ -82040,10 +82040,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3089" s="1">
-        <x:v>0</x:v>
+        <x:v>4750</x:v>
       </x:c>
       <x:c r="G3089" s="1">
-        <x:v>1000</x:v>
+        <x:v>5750</x:v>
       </x:c>
     </x:row>
     <x:row r="3090" spans="1:7">
@@ -82327,22 +82327,22 @@
         <x:v>3101</x:v>
       </x:c>
       <x:c r="B3102" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C3102" s="1">
-        <x:v>0</x:v>
+        <x:v>307450</x:v>
       </x:c>
       <x:c r="D3102" s="1">
-        <x:v>59</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3102" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3102" s="1">
-        <x:v>0</x:v>
+        <x:v>40550</x:v>
       </x:c>
       <x:c r="G3102" s="1">
-        <x:v>59</x:v>
+        <x:v>348000</x:v>
       </x:c>
     </x:row>
     <x:row r="3103" spans="1:7">
@@ -82350,22 +82350,22 @@
         <x:v>3101</x:v>
       </x:c>
       <x:c r="B3103" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C3103" s="1">
-        <x:v>307450</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3103" s="1">
-        <x:v>0</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3103" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3103" s="1">
-        <x:v>40550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3103" s="1">
-        <x:v>348000</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="3104" spans="1:7">
@@ -83431,10 +83431,10 @@
         <x:v>3144</x:v>
       </x:c>
       <x:c r="B3150" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C3150" s="1">
-        <x:v>20000</x:v>
+        <x:v>157500</x:v>
       </x:c>
       <x:c r="D3150" s="1">
         <x:v>0</x:v>
@@ -83443,10 +83443,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3150" s="1">
-        <x:v>6000</x:v>
+        <x:v>45517</x:v>
       </x:c>
       <x:c r="G3150" s="1">
-        <x:v>26000</x:v>
+        <x:v>203017</x:v>
       </x:c>
     </x:row>
     <x:row r="3151" spans="1:7">
@@ -83454,10 +83454,10 @@
         <x:v>3144</x:v>
       </x:c>
       <x:c r="B3151" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C3151" s="1">
-        <x:v>157500</x:v>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="D3151" s="1">
         <x:v>0</x:v>
@@ -83466,10 +83466,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3151" s="1">
-        <x:v>45517</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="G3151" s="1">
-        <x:v>203017</x:v>
+        <x:v>26000</x:v>
       </x:c>
     </x:row>
     <x:row r="3152" spans="1:7">
@@ -85524,10 +85524,10 @@
         <x:v>3230</x:v>
       </x:c>
       <x:c r="B3241" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C3241" s="1">
-        <x:v>34000</x:v>
+        <x:v>343100</x:v>
       </x:c>
       <x:c r="D3241" s="1">
         <x:v>0</x:v>
@@ -85536,10 +85536,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3241" s="1">
-        <x:v>0</x:v>
+        <x:v>244972</x:v>
       </x:c>
       <x:c r="G3241" s="1">
-        <x:v>34000</x:v>
+        <x:v>588072</x:v>
       </x:c>
     </x:row>
     <x:row r="3242" spans="1:7">
@@ -85547,10 +85547,10 @@
         <x:v>3230</x:v>
       </x:c>
       <x:c r="B3242" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C3242" s="1">
-        <x:v>343100</x:v>
+        <x:v>34000</x:v>
       </x:c>
       <x:c r="D3242" s="1">
         <x:v>0</x:v>
@@ -85559,10 +85559,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3242" s="1">
-        <x:v>244972</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3242" s="1">
-        <x:v>588072</x:v>
+        <x:v>34000</x:v>
       </x:c>
     </x:row>
     <x:row r="3243" spans="1:7">
@@ -85915,22 +85915,22 @@
         <x:v>3245</x:v>
       </x:c>
       <x:c r="B3258" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C3258" s="1">
-        <x:v>25500</x:v>
+        <x:v>420650</x:v>
       </x:c>
       <x:c r="D3258" s="1">
-        <x:v>0</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="E3258" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3258" s="1">
-        <x:v>0</x:v>
+        <x:v>448881</x:v>
       </x:c>
       <x:c r="G3258" s="1">
-        <x:v>25500</x:v>
+        <x:v>869712</x:v>
       </x:c>
     </x:row>
     <x:row r="3259" spans="1:7">
@@ -85938,22 +85938,22 @@
         <x:v>3245</x:v>
       </x:c>
       <x:c r="B3259" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C3259" s="1">
-        <x:v>420650</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D3259" s="1">
-        <x:v>181</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3259" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3259" s="1">
-        <x:v>448881</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3259" s="1">
-        <x:v>869712</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="3260" spans="1:7">
@@ -87732,13 +87732,13 @@
         <x:v>3323</x:v>
       </x:c>
       <x:c r="B3337" s="1" t="s">
-        <x:v>256</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C3337" s="1">
-        <x:v>15000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3337" s="1">
-        <x:v>63</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3337" s="1">
         <x:v>0</x:v>
@@ -87747,7 +87747,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G3337" s="1">
-        <x:v>15063</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="3338" spans="1:7">
@@ -87755,22 +87755,22 @@
         <x:v>3323</x:v>
       </x:c>
       <x:c r="B3338" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="C3338" s="1">
-        <x:v>332220</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D3338" s="1">
-        <x:v>0</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E3338" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3338" s="1">
-        <x:v>299023</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3338" s="1">
-        <x:v>631243</x:v>
+        <x:v>15063</x:v>
       </x:c>
     </x:row>
     <x:row r="3339" spans="1:7">
@@ -87778,22 +87778,22 @@
         <x:v>3323</x:v>
       </x:c>
       <x:c r="B3339" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C3339" s="1">
-        <x:v>0</x:v>
+        <x:v>332220</x:v>
       </x:c>
       <x:c r="D3339" s="1">
-        <x:v>59</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3339" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3339" s="1">
-        <x:v>0</x:v>
+        <x:v>299023</x:v>
       </x:c>
       <x:c r="G3339" s="1">
-        <x:v>59</x:v>
+        <x:v>631243</x:v>
       </x:c>
     </x:row>
     <x:row r="3340" spans="1:7">
@@ -88928,10 +88928,10 @@
         <x:v>3370</x:v>
       </x:c>
       <x:c r="B3389" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C3389" s="1">
-        <x:v>41550</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D3389" s="1">
         <x:v>0</x:v>
@@ -88940,10 +88940,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3389" s="1">
-        <x:v>6500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3389" s="1">
-        <x:v>48050</x:v>
+        <x:v>15000</x:v>
       </x:c>
     </x:row>
     <x:row r="3390" spans="1:7">
@@ -88951,10 +88951,10 @@
         <x:v>3370</x:v>
       </x:c>
       <x:c r="B3390" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C3390" s="1">
-        <x:v>15000</x:v>
+        <x:v>41550</x:v>
       </x:c>
       <x:c r="D3390" s="1">
         <x:v>0</x:v>
@@ -88963,10 +88963,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3390" s="1">
-        <x:v>0</x:v>
+        <x:v>6500</x:v>
       </x:c>
       <x:c r="G3390" s="1">
-        <x:v>15000</x:v>
+        <x:v>48050</x:v>
       </x:c>
     </x:row>
     <x:row r="3391" spans="1:7">
@@ -90699,22 +90699,22 @@
         <x:v>3438</x:v>
       </x:c>
       <x:c r="B3466" s="1" t="s">
-        <x:v>416</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C3466" s="1">
-        <x:v>437150</x:v>
+        <x:v>22500</x:v>
       </x:c>
       <x:c r="D3466" s="1">
-        <x:v>468</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3466" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3466" s="1">
-        <x:v>348550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3466" s="1">
-        <x:v>786168</x:v>
+        <x:v>22500</x:v>
       </x:c>
     </x:row>
     <x:row r="3467" spans="1:7">
@@ -90722,22 +90722,22 @@
         <x:v>3438</x:v>
       </x:c>
       <x:c r="B3467" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="C3467" s="1">
-        <x:v>22500</x:v>
+        <x:v>437150</x:v>
       </x:c>
       <x:c r="D3467" s="1">
-        <x:v>0</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="E3467" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3467" s="1">
-        <x:v>0</x:v>
+        <x:v>348550</x:v>
       </x:c>
       <x:c r="G3467" s="1">
-        <x:v>22500</x:v>
+        <x:v>786168</x:v>
       </x:c>
     </x:row>
     <x:row r="3468" spans="1:7">
@@ -91872,22 +91872,22 @@
         <x:v>3485</x:v>
       </x:c>
       <x:c r="B3517" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="C3517" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D3517" s="1">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3517" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3517" s="1">
-        <x:v>0</x:v>
+        <x:v>11300</x:v>
       </x:c>
       <x:c r="G3517" s="1">
-        <x:v>3</x:v>
+        <x:v>12300</x:v>
       </x:c>
     </x:row>
     <x:row r="3518" spans="1:7">
@@ -91895,22 +91895,22 @@
         <x:v>3485</x:v>
       </x:c>
       <x:c r="B3518" s="1" t="s">
-        <x:v>258</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C3518" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3518" s="1">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E3518" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3518" s="1">
-        <x:v>11300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3518" s="1">
-        <x:v>12300</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="3519" spans="1:7">

--- a/reports/pro-oil/pro-oil-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-oil/pro-oil-candidate-lobby-lifetime-report.xlsx
@@ -15674,7 +15674,7 @@
         <x:v>275</x:v>
       </x:c>
       <x:c r="B221" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C221" s="1">
         <x:v>0</x:v>
@@ -15686,10 +15686,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F221" s="1">
-        <x:v>2300</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G221" s="1">
-        <x:v>2300</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="222" spans="1:7">
@@ -15697,7 +15697,7 @@
         <x:v>275</x:v>
       </x:c>
       <x:c r="B222" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C222" s="1">
         <x:v>0</x:v>
@@ -15709,10 +15709,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F222" s="1">
-        <x:v>1000</x:v>
+        <x:v>2300</x:v>
       </x:c>
       <x:c r="G222" s="1">
-        <x:v>1000</x:v>
+        <x:v>2300</x:v>
       </x:c>
     </x:row>
     <x:row r="223" spans="1:7">
@@ -18825,10 +18825,10 @@
         <x:v>412</x:v>
       </x:c>
       <x:c r="B358" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C358" s="1">
-        <x:v>3000</x:v>
+        <x:v>107540</x:v>
       </x:c>
       <x:c r="D358" s="1">
         <x:v>0</x:v>
@@ -18837,10 +18837,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F358" s="1">
-        <x:v>25150</x:v>
+        <x:v>59170</x:v>
       </x:c>
       <x:c r="G358" s="1">
-        <x:v>28150</x:v>
+        <x:v>166710</x:v>
       </x:c>
     </x:row>
     <x:row r="359" spans="1:7">
@@ -18848,10 +18848,10 @@
         <x:v>412</x:v>
       </x:c>
       <x:c r="B359" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C359" s="1">
-        <x:v>107540</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D359" s="1">
         <x:v>0</x:v>
@@ -18860,10 +18860,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F359" s="1">
-        <x:v>59170</x:v>
+        <x:v>25150</x:v>
       </x:c>
       <x:c r="G359" s="1">
-        <x:v>166710</x:v>
+        <x:v>28150</x:v>
       </x:c>
     </x:row>
     <x:row r="360" spans="1:7">
@@ -26346,10 +26346,10 @@
         <x:v>737</x:v>
       </x:c>
       <x:c r="B685" s="1" t="s">
-        <x:v>727</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C685" s="1">
-        <x:v>370033</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D685" s="1">
         <x:v>0</x:v>
@@ -26358,10 +26358,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F685" s="1">
-        <x:v>45850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G685" s="1">
-        <x:v>415883</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="686" spans="1:7">
@@ -26369,10 +26369,10 @@
         <x:v>737</x:v>
       </x:c>
       <x:c r="B686" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>727</x:v>
       </x:c>
       <x:c r="C686" s="1">
-        <x:v>25500</x:v>
+        <x:v>370033</x:v>
       </x:c>
       <x:c r="D686" s="1">
         <x:v>0</x:v>
@@ -26381,10 +26381,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F686" s="1">
-        <x:v>0</x:v>
+        <x:v>45850</x:v>
       </x:c>
       <x:c r="G686" s="1">
-        <x:v>25500</x:v>
+        <x:v>415883</x:v>
       </x:c>
     </x:row>
     <x:row r="687" spans="1:7">
@@ -29796,10 +29796,10 @@
         <x:v>885</x:v>
       </x:c>
       <x:c r="B835" s="1" t="s">
-        <x:v>256</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C835" s="1">
-        <x:v>3000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D835" s="1">
         <x:v>0</x:v>
@@ -29808,10 +29808,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F835" s="1">
-        <x:v>5950</x:v>
+        <x:v>14450</x:v>
       </x:c>
       <x:c r="G835" s="1">
-        <x:v>8950</x:v>
+        <x:v>14450</x:v>
       </x:c>
     </x:row>
     <x:row r="836" spans="1:7">
@@ -29819,10 +29819,10 @@
         <x:v>885</x:v>
       </x:c>
       <x:c r="B836" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="C836" s="1">
-        <x:v>0</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D836" s="1">
         <x:v>0</x:v>
@@ -29831,10 +29831,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F836" s="1">
-        <x:v>14450</x:v>
+        <x:v>5950</x:v>
       </x:c>
       <x:c r="G836" s="1">
-        <x:v>14450</x:v>
+        <x:v>8950</x:v>
       </x:c>
     </x:row>
     <x:row r="837" spans="1:7">
@@ -36190,10 +36190,10 @@
         <x:v>1158</x:v>
       </x:c>
       <x:c r="B1113" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C1113" s="1">
-        <x:v>752389</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1113" s="1">
         <x:v>0</x:v>
@@ -36202,10 +36202,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1113" s="1">
-        <x:v>418794</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="G1113" s="1">
-        <x:v>1171183</x:v>
+        <x:v>10000</x:v>
       </x:c>
     </x:row>
     <x:row r="1114" spans="1:7">
@@ -36213,10 +36213,10 @@
         <x:v>1158</x:v>
       </x:c>
       <x:c r="B1114" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1114" s="1">
-        <x:v>0</x:v>
+        <x:v>752389</x:v>
       </x:c>
       <x:c r="D1114" s="1">
         <x:v>0</x:v>
@@ -36225,10 +36225,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1114" s="1">
-        <x:v>10000</x:v>
+        <x:v>418794</x:v>
       </x:c>
       <x:c r="G1114" s="1">
-        <x:v>10000</x:v>
+        <x:v>1171183</x:v>
       </x:c>
     </x:row>
     <x:row r="1115" spans="1:7">
@@ -50910,10 +50910,10 @@
         <x:v>1784</x:v>
       </x:c>
       <x:c r="B1753" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C1753" s="1">
-        <x:v>147100</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="D1753" s="1">
         <x:v>0</x:v>
@@ -50922,10 +50922,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1753" s="1">
-        <x:v>34550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1753" s="1">
-        <x:v>181650</x:v>
+        <x:v>-1000</x:v>
       </x:c>
     </x:row>
     <x:row r="1754" spans="1:7">
@@ -50933,10 +50933,10 @@
         <x:v>1784</x:v>
       </x:c>
       <x:c r="B1754" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C1754" s="1">
-        <x:v>-1000</x:v>
+        <x:v>147100</x:v>
       </x:c>
       <x:c r="D1754" s="1">
         <x:v>0</x:v>
@@ -50945,10 +50945,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1754" s="1">
-        <x:v>0</x:v>
+        <x:v>34550</x:v>
       </x:c>
       <x:c r="G1754" s="1">
-        <x:v>-1000</x:v>
+        <x:v>181650</x:v>
       </x:c>
     </x:row>
     <x:row r="1755" spans="1:7">
@@ -51094,7 +51094,7 @@
         <x:v>1791</x:v>
       </x:c>
       <x:c r="B1761" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C1761" s="1">
         <x:v>0</x:v>
@@ -51117,7 +51117,7 @@
         <x:v>1791</x:v>
       </x:c>
       <x:c r="B1762" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1762" s="1">
         <x:v>0</x:v>
@@ -57649,10 +57649,10 @@
         <x:v>2070</x:v>
       </x:c>
       <x:c r="B2046" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C2046" s="1">
-        <x:v>22450</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="D2046" s="1">
         <x:v>0</x:v>
@@ -57661,10 +57661,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2046" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G2046" s="1">
         <x:v>250</x:v>
-      </x:c>
-      <x:c r="G2046" s="1">
-        <x:v>22700</x:v>
       </x:c>
     </x:row>
     <x:row r="2047" spans="1:7">
@@ -57672,22 +57672,22 @@
         <x:v>2070</x:v>
       </x:c>
       <x:c r="B2047" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C2047" s="1">
+        <x:v>22450</x:v>
+      </x:c>
+      <x:c r="D2047" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E2047" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F2047" s="1">
         <x:v>250</x:v>
       </x:c>
-      <x:c r="D2047" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E2047" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F2047" s="1">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="G2047" s="1">
-        <x:v>250</x:v>
+        <x:v>22700</x:v>
       </x:c>
     </x:row>
     <x:row r="2048" spans="1:7">
@@ -69494,10 +69494,10 @@
         <x:v>2581</x:v>
       </x:c>
       <x:c r="B2561" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C2561" s="1">
-        <x:v>409250</x:v>
+        <x:v>7061</x:v>
       </x:c>
       <x:c r="D2561" s="1">
         <x:v>0</x:v>
@@ -69506,10 +69506,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2561" s="1">
-        <x:v>159800</x:v>
+        <x:v>23500</x:v>
       </x:c>
       <x:c r="G2561" s="1">
-        <x:v>569050</x:v>
+        <x:v>30561</x:v>
       </x:c>
     </x:row>
     <x:row r="2562" spans="1:7">
@@ -69517,10 +69517,10 @@
         <x:v>2581</x:v>
       </x:c>
       <x:c r="B2562" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C2562" s="1">
-        <x:v>7061</x:v>
+        <x:v>409250</x:v>
       </x:c>
       <x:c r="D2562" s="1">
         <x:v>0</x:v>
@@ -69529,10 +69529,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2562" s="1">
-        <x:v>23500</x:v>
+        <x:v>159800</x:v>
       </x:c>
       <x:c r="G2562" s="1">
-        <x:v>30561</x:v>
+        <x:v>569050</x:v>
       </x:c>
     </x:row>
     <x:row r="2563" spans="1:7">
@@ -69655,10 +69655,10 @@
         <x:v>2587</x:v>
       </x:c>
       <x:c r="B2568" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="C2568" s="1">
-        <x:v>139000</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D2568" s="1">
         <x:v>0</x:v>
@@ -69667,10 +69667,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2568" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2568" s="1">
-        <x:v>139500</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="2569" spans="1:7">
@@ -69678,10 +69678,10 @@
         <x:v>2587</x:v>
       </x:c>
       <x:c r="B2569" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C2569" s="1">
-        <x:v>7000</x:v>
+        <x:v>139000</x:v>
       </x:c>
       <x:c r="D2569" s="1">
         <x:v>0</x:v>
@@ -69690,10 +69690,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2569" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G2569" s="1">
-        <x:v>7000</x:v>
+        <x:v>139500</x:v>
       </x:c>
     </x:row>
     <x:row r="2570" spans="1:7">
@@ -72438,10 +72438,10 @@
         <x:v>2706</x:v>
       </x:c>
       <x:c r="B2689" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="C2689" s="1">
-        <x:v>206766</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D2689" s="1">
         <x:v>0</x:v>
@@ -72450,10 +72450,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2689" s="1">
-        <x:v>286825</x:v>
+        <x:v>111650</x:v>
       </x:c>
       <x:c r="G2689" s="1">
-        <x:v>493591</x:v>
+        <x:v>126650</x:v>
       </x:c>
     </x:row>
     <x:row r="2690" spans="1:7">
@@ -72461,10 +72461,10 @@
         <x:v>2706</x:v>
       </x:c>
       <x:c r="B2690" s="1" t="s">
-        <x:v>156</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C2690" s="1">
-        <x:v>15000</x:v>
+        <x:v>206766</x:v>
       </x:c>
       <x:c r="D2690" s="1">
         <x:v>0</x:v>
@@ -72473,10 +72473,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2690" s="1">
-        <x:v>111650</x:v>
+        <x:v>286825</x:v>
       </x:c>
       <x:c r="G2690" s="1">
-        <x:v>126650</x:v>
+        <x:v>493591</x:v>
       </x:c>
     </x:row>
     <x:row r="2691" spans="1:7">
@@ -75704,10 +75704,10 @@
         <x:v>2843</x:v>
       </x:c>
       <x:c r="B2831" s="1" t="s">
-        <x:v>165</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C2831" s="1">
-        <x:v>12000</x:v>
+        <x:v>99950</x:v>
       </x:c>
       <x:c r="D2831" s="1">
         <x:v>0</x:v>
@@ -75716,10 +75716,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2831" s="1">
-        <x:v>0</x:v>
+        <x:v>6650</x:v>
       </x:c>
       <x:c r="G2831" s="1">
-        <x:v>12000</x:v>
+        <x:v>106600</x:v>
       </x:c>
     </x:row>
     <x:row r="2832" spans="1:7">
@@ -75727,10 +75727,10 @@
         <x:v>2843</x:v>
       </x:c>
       <x:c r="B2832" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C2832" s="1">
-        <x:v>99950</x:v>
+        <x:v>12000</x:v>
       </x:c>
       <x:c r="D2832" s="1">
         <x:v>0</x:v>
@@ -75739,10 +75739,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2832" s="1">
-        <x:v>6650</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2832" s="1">
-        <x:v>106600</x:v>
+        <x:v>12000</x:v>
       </x:c>
     </x:row>
     <x:row r="2833" spans="1:7">
@@ -76371,10 +76371,10 @@
         <x:v>2871</x:v>
       </x:c>
       <x:c r="B2860" s="1" t="s">
-        <x:v>727</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C2860" s="1">
-        <x:v>284300</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D2860" s="1">
         <x:v>0</x:v>
@@ -76383,10 +76383,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2860" s="1">
-        <x:v>71650</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2860" s="1">
-        <x:v>355950</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="2861" spans="1:7">
@@ -76394,10 +76394,10 @@
         <x:v>2871</x:v>
       </x:c>
       <x:c r="B2861" s="1" t="s">
-        <x:v>165</x:v>
+        <x:v>727</x:v>
       </x:c>
       <x:c r="C2861" s="1">
-        <x:v>5000</x:v>
+        <x:v>284300</x:v>
       </x:c>
       <x:c r="D2861" s="1">
         <x:v>0</x:v>
@@ -76406,10 +76406,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2861" s="1">
-        <x:v>0</x:v>
+        <x:v>71650</x:v>
       </x:c>
       <x:c r="G2861" s="1">
-        <x:v>5000</x:v>
+        <x:v>355950</x:v>
       </x:c>
     </x:row>
     <x:row r="2862" spans="1:7">
@@ -78119,10 +78119,10 @@
         <x:v>2946</x:v>
       </x:c>
       <x:c r="B2936" s="1" t="s">
-        <x:v>254</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C2936" s="1">
-        <x:v>7000</x:v>
+        <x:v>71750</x:v>
       </x:c>
       <x:c r="D2936" s="1">
         <x:v>0</x:v>
@@ -78131,10 +78131,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2936" s="1">
-        <x:v>0</x:v>
+        <x:v>77150</x:v>
       </x:c>
       <x:c r="G2936" s="1">
-        <x:v>7000</x:v>
+        <x:v>148900</x:v>
       </x:c>
     </x:row>
     <x:row r="2937" spans="1:7">
@@ -78142,10 +78142,10 @@
         <x:v>2946</x:v>
       </x:c>
       <x:c r="B2937" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="C2937" s="1">
-        <x:v>71750</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D2937" s="1">
         <x:v>0</x:v>
@@ -78154,10 +78154,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2937" s="1">
-        <x:v>77150</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2937" s="1">
-        <x:v>148900</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="2938" spans="1:7">
@@ -78671,10 +78671,10 @@
         <x:v>2969</x:v>
       </x:c>
       <x:c r="B2960" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C2960" s="1">
-        <x:v>44000</x:v>
+        <x:v>10500</x:v>
       </x:c>
       <x:c r="D2960" s="1">
         <x:v>0</x:v>
@@ -78683,10 +78683,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2960" s="1">
-        <x:v>2100</x:v>
+        <x:v>31300</x:v>
       </x:c>
       <x:c r="G2960" s="1">
-        <x:v>46100</x:v>
+        <x:v>41800</x:v>
       </x:c>
     </x:row>
     <x:row r="2961" spans="1:7">
@@ -78717,10 +78717,10 @@
         <x:v>2969</x:v>
       </x:c>
       <x:c r="B2962" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C2962" s="1">
-        <x:v>10500</x:v>
+        <x:v>44000</x:v>
       </x:c>
       <x:c r="D2962" s="1">
         <x:v>0</x:v>
@@ -78729,10 +78729,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2962" s="1">
-        <x:v>31300</x:v>
+        <x:v>2100</x:v>
       </x:c>
       <x:c r="G2962" s="1">
-        <x:v>41800</x:v>
+        <x:v>46100</x:v>
       </x:c>
     </x:row>
     <x:row r="2963" spans="1:7">
@@ -80327,10 +80327,10 @@
         <x:v>3032</x:v>
       </x:c>
       <x:c r="B3032" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C3032" s="1">
-        <x:v>20000</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="D3032" s="1">
         <x:v>0</x:v>
@@ -80339,10 +80339,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3032" s="1">
-        <x:v>6000</x:v>
+        <x:v>45517</x:v>
       </x:c>
       <x:c r="G3032" s="1">
-        <x:v>26000</x:v>
+        <x:v>195517</x:v>
       </x:c>
     </x:row>
     <x:row r="3033" spans="1:7">
@@ -80350,10 +80350,10 @@
         <x:v>3032</x:v>
       </x:c>
       <x:c r="B3033" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C3033" s="1">
-        <x:v>150000</x:v>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="D3033" s="1">
         <x:v>0</x:v>
@@ -80362,10 +80362,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3033" s="1">
-        <x:v>45517</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="G3033" s="1">
-        <x:v>195517</x:v>
+        <x:v>26000</x:v>
       </x:c>
     </x:row>
     <x:row r="3034" spans="1:7">
@@ -81845,10 +81845,10 @@
         <x:v>3096</x:v>
       </x:c>
       <x:c r="B3098" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C3098" s="1">
-        <x:v>3000</x:v>
+        <x:v>2300</x:v>
       </x:c>
       <x:c r="D3098" s="1">
         <x:v>0</x:v>
@@ -81857,10 +81857,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3098" s="1">
-        <x:v>6000</x:v>
+        <x:v>8850</x:v>
       </x:c>
       <x:c r="G3098" s="1">
-        <x:v>9000</x:v>
+        <x:v>11150</x:v>
       </x:c>
     </x:row>
     <x:row r="3099" spans="1:7">
@@ -81868,10 +81868,10 @@
         <x:v>3096</x:v>
       </x:c>
       <x:c r="B3099" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C3099" s="1">
-        <x:v>2300</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D3099" s="1">
         <x:v>0</x:v>
@@ -81880,10 +81880,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3099" s="1">
-        <x:v>8850</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="G3099" s="1">
-        <x:v>11150</x:v>
+        <x:v>9000</x:v>
       </x:c>
     </x:row>
     <x:row r="3100" spans="1:7">
@@ -82328,10 +82328,10 @@
         <x:v>3115</x:v>
       </x:c>
       <x:c r="B3119" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C3119" s="1">
-        <x:v>34000</x:v>
+        <x:v>292600</x:v>
       </x:c>
       <x:c r="D3119" s="1">
         <x:v>0</x:v>
@@ -82340,10 +82340,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3119" s="1">
-        <x:v>0</x:v>
+        <x:v>222972</x:v>
       </x:c>
       <x:c r="G3119" s="1">
-        <x:v>34000</x:v>
+        <x:v>515572</x:v>
       </x:c>
     </x:row>
     <x:row r="3120" spans="1:7">
@@ -82351,10 +82351,10 @@
         <x:v>3115</x:v>
       </x:c>
       <x:c r="B3120" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="C3120" s="1">
-        <x:v>292600</x:v>
+        <x:v>34000</x:v>
       </x:c>
       <x:c r="D3120" s="1">
         <x:v>0</x:v>
@@ -82363,10 +82363,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3120" s="1">
-        <x:v>222972</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3120" s="1">
-        <x:v>515572</x:v>
+        <x:v>34000</x:v>
       </x:c>
     </x:row>
     <x:row r="3121" spans="1:7">
@@ -82512,10 +82512,10 @@
         <x:v>3122</x:v>
       </x:c>
       <x:c r="B3127" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C3127" s="1">
-        <x:v>29500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3127" s="1">
         <x:v>0</x:v>
@@ -82524,10 +82524,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3127" s="1">
-        <x:v>12550</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G3127" s="1">
-        <x:v>42050</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="3128" spans="1:7">
@@ -82535,10 +82535,10 @@
         <x:v>3122</x:v>
       </x:c>
       <x:c r="B3128" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C3128" s="1">
-        <x:v>0</x:v>
+        <x:v>29500</x:v>
       </x:c>
       <x:c r="D3128" s="1">
         <x:v>0</x:v>
@@ -82547,10 +82547,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3128" s="1">
-        <x:v>1000</x:v>
+        <x:v>12550</x:v>
       </x:c>
       <x:c r="G3128" s="1">
-        <x:v>1000</x:v>
+        <x:v>42050</x:v>
       </x:c>
     </x:row>
     <x:row r="3129" spans="1:7">
@@ -87273,10 +87273,10 @@
         <x:v>3316</x:v>
       </x:c>
       <x:c r="B3334" s="1" t="s">
-        <x:v>410</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C3334" s="1">
-        <x:v>429650</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D3334" s="1">
         <x:v>0</x:v>
@@ -87285,10 +87285,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3334" s="1">
-        <x:v>347550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3334" s="1">
-        <x:v>777200</x:v>
+        <x:v>3000</x:v>
       </x:c>
     </x:row>
     <x:row r="3335" spans="1:7">
@@ -87296,10 +87296,10 @@
         <x:v>3316</x:v>
       </x:c>
       <x:c r="B3335" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="C3335" s="1">
-        <x:v>3000</x:v>
+        <x:v>429650</x:v>
       </x:c>
       <x:c r="D3335" s="1">
         <x:v>0</x:v>
@@ -87308,10 +87308,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3335" s="1">
-        <x:v>0</x:v>
+        <x:v>347550</x:v>
       </x:c>
       <x:c r="G3335" s="1">
-        <x:v>3000</x:v>
+        <x:v>777200</x:v>
       </x:c>
     </x:row>
     <x:row r="3336" spans="1:7">
@@ -87917,10 +87917,10 @@
         <x:v>3343</x:v>
       </x:c>
       <x:c r="B3362" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C3362" s="1">
-        <x:v>0</x:v>
+        <x:v>119000</x:v>
       </x:c>
       <x:c r="D3362" s="1">
         <x:v>0</x:v>
@@ -87929,10 +87929,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3362" s="1">
-        <x:v>35750</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3362" s="1">
-        <x:v>35750</x:v>
+        <x:v>119000</x:v>
       </x:c>
     </x:row>
     <x:row r="3363" spans="1:7">
@@ -87940,10 +87940,10 @@
         <x:v>3343</x:v>
       </x:c>
       <x:c r="B3363" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C3363" s="1">
-        <x:v>119000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3363" s="1">
         <x:v>0</x:v>
@@ -87952,10 +87952,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3363" s="1">
-        <x:v>0</x:v>
+        <x:v>35750</x:v>
       </x:c>
       <x:c r="G3363" s="1">
-        <x:v>119000</x:v>
+        <x:v>35750</x:v>
       </x:c>
     </x:row>
     <x:row r="3364" spans="1:7">

--- a/reports/pro-oil/pro-oil-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-oil/pro-oil-candidate-lobby-lifetime-report.xlsx
@@ -18710,10 +18710,10 @@
         <x:v>407</x:v>
       </x:c>
       <x:c r="B353" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C353" s="1">
-        <x:v>15000</x:v>
+        <x:v>163000</x:v>
       </x:c>
       <x:c r="D353" s="1">
         <x:v>0</x:v>
@@ -18722,10 +18722,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F353" s="1">
-        <x:v>0</x:v>
+        <x:v>82550</x:v>
       </x:c>
       <x:c r="G353" s="1">
-        <x:v>15000</x:v>
+        <x:v>245550</x:v>
       </x:c>
     </x:row>
     <x:row r="354" spans="1:7">
@@ -18733,10 +18733,10 @@
         <x:v>407</x:v>
       </x:c>
       <x:c r="B354" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="C354" s="1">
-        <x:v>163000</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D354" s="1">
         <x:v>0</x:v>
@@ -18745,10 +18745,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F354" s="1">
-        <x:v>82550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G354" s="1">
-        <x:v>245550</x:v>
+        <x:v>15000</x:v>
       </x:c>
     </x:row>
     <x:row r="355" spans="1:7">
@@ -26346,10 +26346,10 @@
         <x:v>737</x:v>
       </x:c>
       <x:c r="B685" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>727</x:v>
       </x:c>
       <x:c r="C685" s="1">
-        <x:v>25500</x:v>
+        <x:v>370033</x:v>
       </x:c>
       <x:c r="D685" s="1">
         <x:v>0</x:v>
@@ -26358,10 +26358,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F685" s="1">
-        <x:v>0</x:v>
+        <x:v>45850</x:v>
       </x:c>
       <x:c r="G685" s="1">
-        <x:v>25500</x:v>
+        <x:v>415883</x:v>
       </x:c>
     </x:row>
     <x:row r="686" spans="1:7">
@@ -26369,10 +26369,10 @@
         <x:v>737</x:v>
       </x:c>
       <x:c r="B686" s="1" t="s">
-        <x:v>727</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C686" s="1">
-        <x:v>370033</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D686" s="1">
         <x:v>0</x:v>
@@ -26381,10 +26381,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F686" s="1">
-        <x:v>45850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G686" s="1">
-        <x:v>415883</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="687" spans="1:7">
@@ -37386,10 +37386,10 @@
         <x:v>1207</x:v>
       </x:c>
       <x:c r="B1165" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C1165" s="1">
-        <x:v>3000</x:v>
+        <x:v>12000</x:v>
       </x:c>
       <x:c r="D1165" s="1">
         <x:v>0</x:v>
@@ -37398,10 +37398,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1165" s="1">
-        <x:v>50751</x:v>
+        <x:v>12450</x:v>
       </x:c>
       <x:c r="G1165" s="1">
-        <x:v>53751</x:v>
+        <x:v>24450</x:v>
       </x:c>
     </x:row>
     <x:row r="1166" spans="1:7">
@@ -37409,10 +37409,10 @@
         <x:v>1207</x:v>
       </x:c>
       <x:c r="B1166" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C1166" s="1">
-        <x:v>12000</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D1166" s="1">
         <x:v>0</x:v>
@@ -37421,10 +37421,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1166" s="1">
-        <x:v>12450</x:v>
+        <x:v>50751</x:v>
       </x:c>
       <x:c r="G1166" s="1">
-        <x:v>24450</x:v>
+        <x:v>53751</x:v>
       </x:c>
     </x:row>
     <x:row r="1167" spans="1:7">
@@ -45252,10 +45252,10 @@
         <x:v>1544</x:v>
       </x:c>
       <x:c r="B1507" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="C1507" s="1">
-        <x:v>8000</x:v>
+        <x:v>146700</x:v>
       </x:c>
       <x:c r="D1507" s="1">
         <x:v>0</x:v>
@@ -45264,10 +45264,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1507" s="1">
-        <x:v>66000</x:v>
+        <x:v>157050</x:v>
       </x:c>
       <x:c r="G1507" s="1">
-        <x:v>74000</x:v>
+        <x:v>303750</x:v>
       </x:c>
     </x:row>
     <x:row r="1508" spans="1:7">
@@ -45275,10 +45275,10 @@
         <x:v>1544</x:v>
       </x:c>
       <x:c r="B1508" s="1" t="s">
-        <x:v>410</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C1508" s="1">
-        <x:v>146700</x:v>
+        <x:v>8000</x:v>
       </x:c>
       <x:c r="D1508" s="1">
         <x:v>0</x:v>
@@ -45287,10 +45287,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1508" s="1">
-        <x:v>157050</x:v>
+        <x:v>66000</x:v>
       </x:c>
       <x:c r="G1508" s="1">
-        <x:v>303750</x:v>
+        <x:v>74000</x:v>
       </x:c>
     </x:row>
     <x:row r="1509" spans="1:7">
@@ -48840,10 +48840,10 @@
         <x:v>1697</x:v>
       </x:c>
       <x:c r="B1663" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C1663" s="1">
-        <x:v>2500</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="D1663" s="1">
         <x:v>0</x:v>
@@ -48852,10 +48852,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1663" s="1">
-        <x:v>16350</x:v>
+        <x:v>72700</x:v>
       </x:c>
       <x:c r="G1663" s="1">
-        <x:v>18850</x:v>
+        <x:v>73185</x:v>
       </x:c>
     </x:row>
     <x:row r="1664" spans="1:7">
@@ -48863,10 +48863,10 @@
         <x:v>1697</x:v>
       </x:c>
       <x:c r="B1664" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1664" s="1">
-        <x:v>485</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1664" s="1">
         <x:v>0</x:v>
@@ -48875,10 +48875,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1664" s="1">
-        <x:v>72700</x:v>
+        <x:v>16350</x:v>
       </x:c>
       <x:c r="G1664" s="1">
-        <x:v>73185</x:v>
+        <x:v>18850</x:v>
       </x:c>
     </x:row>
     <x:row r="1665" spans="1:7">
@@ -57534,10 +57534,10 @@
         <x:v>2066</x:v>
       </x:c>
       <x:c r="B2041" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C2041" s="1">
-        <x:v>11000</x:v>
+        <x:v>960100</x:v>
       </x:c>
       <x:c r="D2041" s="1">
         <x:v>0</x:v>
@@ -57546,10 +57546,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2041" s="1">
-        <x:v>25550</x:v>
+        <x:v>882230</x:v>
       </x:c>
       <x:c r="G2041" s="1">
-        <x:v>36550</x:v>
+        <x:v>1842330</x:v>
       </x:c>
     </x:row>
     <x:row r="2042" spans="1:7">
@@ -57557,10 +57557,10 @@
         <x:v>2066</x:v>
       </x:c>
       <x:c r="B2042" s="1" t="s">
-        <x:v>188</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C2042" s="1">
-        <x:v>960100</x:v>
+        <x:v>11000</x:v>
       </x:c>
       <x:c r="D2042" s="1">
         <x:v>0</x:v>
@@ -57569,10 +57569,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2042" s="1">
-        <x:v>882230</x:v>
+        <x:v>25550</x:v>
       </x:c>
       <x:c r="G2042" s="1">
-        <x:v>1842330</x:v>
+        <x:v>36550</x:v>
       </x:c>
     </x:row>
     <x:row r="2043" spans="1:7">
@@ -57649,22 +57649,22 @@
         <x:v>2070</x:v>
       </x:c>
       <x:c r="B2046" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C2046" s="1">
+        <x:v>22450</x:v>
+      </x:c>
+      <x:c r="D2046" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E2046" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F2046" s="1">
         <x:v>250</x:v>
       </x:c>
-      <x:c r="D2046" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E2046" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F2046" s="1">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="G2046" s="1">
-        <x:v>250</x:v>
+        <x:v>22700</x:v>
       </x:c>
     </x:row>
     <x:row r="2047" spans="1:7">
@@ -57672,10 +57672,10 @@
         <x:v>2070</x:v>
       </x:c>
       <x:c r="B2047" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C2047" s="1">
-        <x:v>22450</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="D2047" s="1">
         <x:v>0</x:v>
@@ -57684,10 +57684,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2047" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G2047" s="1">
         <x:v>250</x:v>
-      </x:c>
-      <x:c r="G2047" s="1">
-        <x:v>22700</x:v>
       </x:c>
     </x:row>
     <x:row r="2048" spans="1:7">
@@ -69494,10 +69494,10 @@
         <x:v>2581</x:v>
       </x:c>
       <x:c r="B2561" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C2561" s="1">
-        <x:v>7061</x:v>
+        <x:v>409250</x:v>
       </x:c>
       <x:c r="D2561" s="1">
         <x:v>0</x:v>
@@ -69506,10 +69506,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2561" s="1">
-        <x:v>23500</x:v>
+        <x:v>159800</x:v>
       </x:c>
       <x:c r="G2561" s="1">
-        <x:v>30561</x:v>
+        <x:v>569050</x:v>
       </x:c>
     </x:row>
     <x:row r="2562" spans="1:7">
@@ -69517,10 +69517,10 @@
         <x:v>2581</x:v>
       </x:c>
       <x:c r="B2562" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C2562" s="1">
-        <x:v>409250</x:v>
+        <x:v>7061</x:v>
       </x:c>
       <x:c r="D2562" s="1">
         <x:v>0</x:v>
@@ -69529,10 +69529,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2562" s="1">
-        <x:v>159800</x:v>
+        <x:v>23500</x:v>
       </x:c>
       <x:c r="G2562" s="1">
-        <x:v>569050</x:v>
+        <x:v>30561</x:v>
       </x:c>
     </x:row>
     <x:row r="2563" spans="1:7">
@@ -69655,10 +69655,10 @@
         <x:v>2587</x:v>
       </x:c>
       <x:c r="B2568" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C2568" s="1">
-        <x:v>7000</x:v>
+        <x:v>139000</x:v>
       </x:c>
       <x:c r="D2568" s="1">
         <x:v>0</x:v>
@@ -69667,10 +69667,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2568" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G2568" s="1">
-        <x:v>7000</x:v>
+        <x:v>139500</x:v>
       </x:c>
     </x:row>
     <x:row r="2569" spans="1:7">
@@ -69678,10 +69678,10 @@
         <x:v>2587</x:v>
       </x:c>
       <x:c r="B2569" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="C2569" s="1">
-        <x:v>139000</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D2569" s="1">
         <x:v>0</x:v>
@@ -69690,10 +69690,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2569" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2569" s="1">
-        <x:v>139500</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="2570" spans="1:7">
@@ -73979,10 +73979,10 @@
         <x:v>2770</x:v>
       </x:c>
       <x:c r="B2756" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C2756" s="1">
-        <x:v>102350</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D2756" s="1">
         <x:v>0</x:v>
@@ -73991,10 +73991,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2756" s="1">
-        <x:v>106550</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G2756" s="1">
-        <x:v>208900</x:v>
+        <x:v>20000</x:v>
       </x:c>
     </x:row>
     <x:row r="2757" spans="1:7">
@@ -74002,10 +74002,10 @@
         <x:v>2770</x:v>
       </x:c>
       <x:c r="B2757" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C2757" s="1">
-        <x:v>15000</x:v>
+        <x:v>102350</x:v>
       </x:c>
       <x:c r="D2757" s="1">
         <x:v>0</x:v>
@@ -74014,10 +74014,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2757" s="1">
-        <x:v>5000</x:v>
+        <x:v>106550</x:v>
       </x:c>
       <x:c r="G2757" s="1">
-        <x:v>20000</x:v>
+        <x:v>208900</x:v>
       </x:c>
     </x:row>
     <x:row r="2758" spans="1:7">
@@ -75290,10 +75290,10 @@
         <x:v>2826</x:v>
       </x:c>
       <x:c r="B2813" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="C2813" s="1">
-        <x:v>206000</x:v>
+        <x:v>37500</x:v>
       </x:c>
       <x:c r="D2813" s="1">
         <x:v>0</x:v>
@@ -75302,10 +75302,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2813" s="1">
-        <x:v>45600</x:v>
+        <x:v>8000</x:v>
       </x:c>
       <x:c r="G2813" s="1">
-        <x:v>251600</x:v>
+        <x:v>45500</x:v>
       </x:c>
     </x:row>
     <x:row r="2814" spans="1:7">
@@ -75313,10 +75313,10 @@
         <x:v>2826</x:v>
       </x:c>
       <x:c r="B2814" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C2814" s="1">
-        <x:v>37500</x:v>
+        <x:v>206000</x:v>
       </x:c>
       <x:c r="D2814" s="1">
         <x:v>0</x:v>
@@ -75325,10 +75325,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2814" s="1">
-        <x:v>8000</x:v>
+        <x:v>45600</x:v>
       </x:c>
       <x:c r="G2814" s="1">
-        <x:v>45500</x:v>
+        <x:v>251600</x:v>
       </x:c>
     </x:row>
     <x:row r="2815" spans="1:7">
@@ -75704,10 +75704,10 @@
         <x:v>2843</x:v>
       </x:c>
       <x:c r="B2831" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C2831" s="1">
-        <x:v>99950</x:v>
+        <x:v>12000</x:v>
       </x:c>
       <x:c r="D2831" s="1">
         <x:v>0</x:v>
@@ -75716,10 +75716,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2831" s="1">
-        <x:v>6650</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2831" s="1">
-        <x:v>106600</x:v>
+        <x:v>12000</x:v>
       </x:c>
     </x:row>
     <x:row r="2832" spans="1:7">
@@ -75727,10 +75727,10 @@
         <x:v>2843</x:v>
       </x:c>
       <x:c r="B2832" s="1" t="s">
-        <x:v>165</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C2832" s="1">
-        <x:v>12000</x:v>
+        <x:v>99950</x:v>
       </x:c>
       <x:c r="D2832" s="1">
         <x:v>0</x:v>
@@ -75739,10 +75739,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2832" s="1">
-        <x:v>0</x:v>
+        <x:v>6650</x:v>
       </x:c>
       <x:c r="G2832" s="1">
-        <x:v>12000</x:v>
+        <x:v>106600</x:v>
       </x:c>
     </x:row>
     <x:row r="2833" spans="1:7">
@@ -76371,10 +76371,10 @@
         <x:v>2871</x:v>
       </x:c>
       <x:c r="B2860" s="1" t="s">
-        <x:v>165</x:v>
+        <x:v>727</x:v>
       </x:c>
       <x:c r="C2860" s="1">
-        <x:v>5000</x:v>
+        <x:v>284300</x:v>
       </x:c>
       <x:c r="D2860" s="1">
         <x:v>0</x:v>
@@ -76383,10 +76383,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2860" s="1">
-        <x:v>0</x:v>
+        <x:v>71650</x:v>
       </x:c>
       <x:c r="G2860" s="1">
-        <x:v>5000</x:v>
+        <x:v>355950</x:v>
       </x:c>
     </x:row>
     <x:row r="2861" spans="1:7">
@@ -76394,10 +76394,10 @@
         <x:v>2871</x:v>
       </x:c>
       <x:c r="B2861" s="1" t="s">
-        <x:v>727</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C2861" s="1">
-        <x:v>284300</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D2861" s="1">
         <x:v>0</x:v>
@@ -76406,10 +76406,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2861" s="1">
-        <x:v>71650</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2861" s="1">
-        <x:v>355950</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="2862" spans="1:7">
@@ -78119,10 +78119,10 @@
         <x:v>2946</x:v>
       </x:c>
       <x:c r="B2936" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="C2936" s="1">
-        <x:v>71750</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D2936" s="1">
         <x:v>0</x:v>
@@ -78131,10 +78131,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2936" s="1">
-        <x:v>77150</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2936" s="1">
-        <x:v>148900</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="2937" spans="1:7">
@@ -78142,10 +78142,10 @@
         <x:v>2946</x:v>
       </x:c>
       <x:c r="B2937" s="1" t="s">
-        <x:v>254</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C2937" s="1">
-        <x:v>7000</x:v>
+        <x:v>71750</x:v>
       </x:c>
       <x:c r="D2937" s="1">
         <x:v>0</x:v>
@@ -78154,10 +78154,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2937" s="1">
-        <x:v>0</x:v>
+        <x:v>77150</x:v>
       </x:c>
       <x:c r="G2937" s="1">
-        <x:v>7000</x:v>
+        <x:v>148900</x:v>
       </x:c>
     </x:row>
     <x:row r="2938" spans="1:7">
@@ -78671,10 +78671,10 @@
         <x:v>2969</x:v>
       </x:c>
       <x:c r="B2960" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="C2960" s="1">
-        <x:v>10500</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D2960" s="1">
         <x:v>0</x:v>
@@ -78683,10 +78683,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2960" s="1">
-        <x:v>31300</x:v>
+        <x:v>33600</x:v>
       </x:c>
       <x:c r="G2960" s="1">
-        <x:v>41800</x:v>
+        <x:v>38600</x:v>
       </x:c>
     </x:row>
     <x:row r="2961" spans="1:7">
@@ -78694,10 +78694,10 @@
         <x:v>2969</x:v>
       </x:c>
       <x:c r="B2961" s="1" t="s">
-        <x:v>156</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C2961" s="1">
-        <x:v>5000</x:v>
+        <x:v>10500</x:v>
       </x:c>
       <x:c r="D2961" s="1">
         <x:v>0</x:v>
@@ -78706,10 +78706,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2961" s="1">
-        <x:v>33600</x:v>
+        <x:v>31300</x:v>
       </x:c>
       <x:c r="G2961" s="1">
-        <x:v>38600</x:v>
+        <x:v>41800</x:v>
       </x:c>
     </x:row>
     <x:row r="2962" spans="1:7">
@@ -78947,7 +78947,7 @@
         <x:v>2977</x:v>
       </x:c>
       <x:c r="B2972" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C2972" s="1">
         <x:v>1000</x:v>
@@ -78959,10 +78959,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2972" s="1">
-        <x:v>0</x:v>
+        <x:v>4750</x:v>
       </x:c>
       <x:c r="G2972" s="1">
-        <x:v>1000</x:v>
+        <x:v>5750</x:v>
       </x:c>
     </x:row>
     <x:row r="2973" spans="1:7">
@@ -78970,7 +78970,7 @@
         <x:v>2977</x:v>
       </x:c>
       <x:c r="B2973" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C2973" s="1">
         <x:v>1000</x:v>
@@ -78982,10 +78982,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2973" s="1">
-        <x:v>4750</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2973" s="1">
-        <x:v>5750</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="2974" spans="1:7">
@@ -82719,10 +82719,10 @@
         <x:v>3130</x:v>
       </x:c>
       <x:c r="B3136" s="1" t="s">
-        <x:v>165</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C3136" s="1">
-        <x:v>25500</x:v>
+        <x:v>420650</x:v>
       </x:c>
       <x:c r="D3136" s="1">
         <x:v>0</x:v>
@@ -82731,10 +82731,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3136" s="1">
-        <x:v>0</x:v>
+        <x:v>448381</x:v>
       </x:c>
       <x:c r="G3136" s="1">
-        <x:v>25500</x:v>
+        <x:v>869031</x:v>
       </x:c>
     </x:row>
     <x:row r="3137" spans="1:7">
@@ -82742,10 +82742,10 @@
         <x:v>3130</x:v>
       </x:c>
       <x:c r="B3137" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C3137" s="1">
-        <x:v>420650</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D3137" s="1">
         <x:v>0</x:v>
@@ -82754,10 +82754,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3137" s="1">
-        <x:v>448381</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3137" s="1">
-        <x:v>869031</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="3138" spans="1:7">
@@ -84444,10 +84444,10 @@
         <x:v>3204</x:v>
       </x:c>
       <x:c r="B3211" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="C3211" s="1">
-        <x:v>332220</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D3211" s="1">
         <x:v>0</x:v>
@@ -84456,10 +84456,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3211" s="1">
-        <x:v>299023</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3211" s="1">
-        <x:v>631243</x:v>
+        <x:v>15000</x:v>
       </x:c>
     </x:row>
     <x:row r="3212" spans="1:7">
@@ -84467,10 +84467,10 @@
         <x:v>3204</x:v>
       </x:c>
       <x:c r="B3212" s="1" t="s">
-        <x:v>254</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C3212" s="1">
-        <x:v>15000</x:v>
+        <x:v>332220</x:v>
       </x:c>
       <x:c r="D3212" s="1">
         <x:v>0</x:v>
@@ -84479,10 +84479,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3212" s="1">
-        <x:v>0</x:v>
+        <x:v>299023</x:v>
       </x:c>
       <x:c r="G3212" s="1">
-        <x:v>15000</x:v>
+        <x:v>631243</x:v>
       </x:c>
     </x:row>
     <x:row r="3213" spans="1:7">
@@ -85594,10 +85594,10 @@
         <x:v>3250</x:v>
       </x:c>
       <x:c r="B3261" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C3261" s="1">
-        <x:v>15000</x:v>
+        <x:v>41550</x:v>
       </x:c>
       <x:c r="D3261" s="1">
         <x:v>0</x:v>
@@ -85606,10 +85606,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3261" s="1">
-        <x:v>0</x:v>
+        <x:v>6500</x:v>
       </x:c>
       <x:c r="G3261" s="1">
-        <x:v>15000</x:v>
+        <x:v>48050</x:v>
       </x:c>
     </x:row>
     <x:row r="3262" spans="1:7">
@@ -85617,10 +85617,10 @@
         <x:v>3250</x:v>
       </x:c>
       <x:c r="B3262" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="C3262" s="1">
-        <x:v>41550</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D3262" s="1">
         <x:v>0</x:v>
@@ -85629,10 +85629,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3262" s="1">
-        <x:v>6500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3262" s="1">
-        <x:v>48050</x:v>
+        <x:v>15000</x:v>
       </x:c>
     </x:row>
     <x:row r="3263" spans="1:7">
@@ -87250,10 +87250,10 @@
         <x:v>3316</x:v>
       </x:c>
       <x:c r="B3333" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C3333" s="1">
-        <x:v>22500</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D3333" s="1">
         <x:v>0</x:v>
@@ -87265,7 +87265,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G3333" s="1">
-        <x:v>22500</x:v>
+        <x:v>3000</x:v>
       </x:c>
     </x:row>
     <x:row r="3334" spans="1:7">
@@ -87273,10 +87273,10 @@
         <x:v>3316</x:v>
       </x:c>
       <x:c r="B3334" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="C3334" s="1">
-        <x:v>3000</x:v>
+        <x:v>429650</x:v>
       </x:c>
       <x:c r="D3334" s="1">
         <x:v>0</x:v>
@@ -87285,10 +87285,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3334" s="1">
-        <x:v>0</x:v>
+        <x:v>347550</x:v>
       </x:c>
       <x:c r="G3334" s="1">
-        <x:v>3000</x:v>
+        <x:v>777200</x:v>
       </x:c>
     </x:row>
     <x:row r="3335" spans="1:7">
@@ -87296,10 +87296,10 @@
         <x:v>3316</x:v>
       </x:c>
       <x:c r="B3335" s="1" t="s">
-        <x:v>410</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="C3335" s="1">
-        <x:v>429650</x:v>
+        <x:v>22500</x:v>
       </x:c>
       <x:c r="D3335" s="1">
         <x:v>0</x:v>
@@ -87308,10 +87308,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3335" s="1">
-        <x:v>347550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3335" s="1">
-        <x:v>777200</x:v>
+        <x:v>22500</x:v>
       </x:c>
     </x:row>
     <x:row r="3336" spans="1:7">
@@ -87917,10 +87917,10 @@
         <x:v>3343</x:v>
       </x:c>
       <x:c r="B3362" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C3362" s="1">
-        <x:v>119000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3362" s="1">
         <x:v>0</x:v>
@@ -87929,10 +87929,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3362" s="1">
-        <x:v>0</x:v>
+        <x:v>35750</x:v>
       </x:c>
       <x:c r="G3362" s="1">
-        <x:v>119000</x:v>
+        <x:v>35750</x:v>
       </x:c>
     </x:row>
     <x:row r="3363" spans="1:7">
@@ -87940,10 +87940,10 @@
         <x:v>3343</x:v>
       </x:c>
       <x:c r="B3363" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C3363" s="1">
-        <x:v>0</x:v>
+        <x:v>119000</x:v>
       </x:c>
       <x:c r="D3363" s="1">
         <x:v>0</x:v>
@@ -87952,10 +87952,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3363" s="1">
-        <x:v>35750</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3363" s="1">
-        <x:v>35750</x:v>
+        <x:v>119000</x:v>
       </x:c>
     </x:row>
     <x:row r="3364" spans="1:7">

--- a/reports/pro-oil/pro-oil-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-oil/pro-oil-candidate-lobby-lifetime-report.xlsx
@@ -15674,7 +15674,7 @@
         <x:v>275</x:v>
       </x:c>
       <x:c r="B221" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C221" s="1">
         <x:v>0</x:v>
@@ -15686,10 +15686,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F221" s="1">
-        <x:v>1000</x:v>
+        <x:v>2300</x:v>
       </x:c>
       <x:c r="G221" s="1">
-        <x:v>1000</x:v>
+        <x:v>2300</x:v>
       </x:c>
     </x:row>
     <x:row r="222" spans="1:7">
@@ -15697,7 +15697,7 @@
         <x:v>275</x:v>
       </x:c>
       <x:c r="B222" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C222" s="1">
         <x:v>0</x:v>
@@ -15709,10 +15709,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F222" s="1">
-        <x:v>2300</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G222" s="1">
-        <x:v>2300</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="223" spans="1:7">
@@ -26346,10 +26346,10 @@
         <x:v>737</x:v>
       </x:c>
       <x:c r="B685" s="1" t="s">
-        <x:v>727</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C685" s="1">
-        <x:v>370033</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D685" s="1">
         <x:v>0</x:v>
@@ -26358,10 +26358,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F685" s="1">
-        <x:v>45850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G685" s="1">
-        <x:v>415883</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="686" spans="1:7">
@@ -26369,10 +26369,10 @@
         <x:v>737</x:v>
       </x:c>
       <x:c r="B686" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>727</x:v>
       </x:c>
       <x:c r="C686" s="1">
-        <x:v>25500</x:v>
+        <x:v>370033</x:v>
       </x:c>
       <x:c r="D686" s="1">
         <x:v>0</x:v>
@@ -26381,10 +26381,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F686" s="1">
-        <x:v>0</x:v>
+        <x:v>45850</x:v>
       </x:c>
       <x:c r="G686" s="1">
-        <x:v>25500</x:v>
+        <x:v>415883</x:v>
       </x:c>
     </x:row>
     <x:row r="687" spans="1:7">
@@ -29796,10 +29796,10 @@
         <x:v>885</x:v>
       </x:c>
       <x:c r="B835" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="C835" s="1">
-        <x:v>0</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D835" s="1">
         <x:v>0</x:v>
@@ -29808,10 +29808,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F835" s="1">
-        <x:v>14450</x:v>
+        <x:v>5950</x:v>
       </x:c>
       <x:c r="G835" s="1">
-        <x:v>14450</x:v>
+        <x:v>8950</x:v>
       </x:c>
     </x:row>
     <x:row r="836" spans="1:7">
@@ -29819,10 +29819,10 @@
         <x:v>885</x:v>
       </x:c>
       <x:c r="B836" s="1" t="s">
-        <x:v>256</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C836" s="1">
-        <x:v>3000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D836" s="1">
         <x:v>0</x:v>
@@ -29831,10 +29831,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F836" s="1">
-        <x:v>5950</x:v>
+        <x:v>14450</x:v>
       </x:c>
       <x:c r="G836" s="1">
-        <x:v>8950</x:v>
+        <x:v>14450</x:v>
       </x:c>
     </x:row>
     <x:row r="837" spans="1:7">
@@ -36190,10 +36190,10 @@
         <x:v>1158</x:v>
       </x:c>
       <x:c r="B1113" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1113" s="1">
-        <x:v>0</x:v>
+        <x:v>752389</x:v>
       </x:c>
       <x:c r="D1113" s="1">
         <x:v>0</x:v>
@@ -36202,10 +36202,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1113" s="1">
-        <x:v>10000</x:v>
+        <x:v>418794</x:v>
       </x:c>
       <x:c r="G1113" s="1">
-        <x:v>10000</x:v>
+        <x:v>1171183</x:v>
       </x:c>
     </x:row>
     <x:row r="1114" spans="1:7">
@@ -36213,10 +36213,10 @@
         <x:v>1158</x:v>
       </x:c>
       <x:c r="B1114" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C1114" s="1">
-        <x:v>752389</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1114" s="1">
         <x:v>0</x:v>
@@ -36225,10 +36225,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1114" s="1">
-        <x:v>418794</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="G1114" s="1">
-        <x:v>1171183</x:v>
+        <x:v>10000</x:v>
       </x:c>
     </x:row>
     <x:row r="1115" spans="1:7">
@@ -37386,10 +37386,10 @@
         <x:v>1207</x:v>
       </x:c>
       <x:c r="B1165" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C1165" s="1">
-        <x:v>12000</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D1165" s="1">
         <x:v>0</x:v>
@@ -37398,10 +37398,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1165" s="1">
-        <x:v>12450</x:v>
+        <x:v>50751</x:v>
       </x:c>
       <x:c r="G1165" s="1">
-        <x:v>24450</x:v>
+        <x:v>53751</x:v>
       </x:c>
     </x:row>
     <x:row r="1166" spans="1:7">
@@ -37409,10 +37409,10 @@
         <x:v>1207</x:v>
       </x:c>
       <x:c r="B1166" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C1166" s="1">
-        <x:v>3000</x:v>
+        <x:v>12000</x:v>
       </x:c>
       <x:c r="D1166" s="1">
         <x:v>0</x:v>
@@ -37421,10 +37421,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1166" s="1">
-        <x:v>50751</x:v>
+        <x:v>12450</x:v>
       </x:c>
       <x:c r="G1166" s="1">
-        <x:v>53751</x:v>
+        <x:v>24450</x:v>
       </x:c>
     </x:row>
     <x:row r="1167" spans="1:7">
@@ -45252,10 +45252,10 @@
         <x:v>1544</x:v>
       </x:c>
       <x:c r="B1507" s="1" t="s">
-        <x:v>410</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C1507" s="1">
-        <x:v>146700</x:v>
+        <x:v>8000</x:v>
       </x:c>
       <x:c r="D1507" s="1">
         <x:v>0</x:v>
@@ -45264,10 +45264,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1507" s="1">
-        <x:v>157050</x:v>
+        <x:v>66000</x:v>
       </x:c>
       <x:c r="G1507" s="1">
-        <x:v>303750</x:v>
+        <x:v>74000</x:v>
       </x:c>
     </x:row>
     <x:row r="1508" spans="1:7">
@@ -45275,10 +45275,10 @@
         <x:v>1544</x:v>
       </x:c>
       <x:c r="B1508" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="C1508" s="1">
-        <x:v>8000</x:v>
+        <x:v>146700</x:v>
       </x:c>
       <x:c r="D1508" s="1">
         <x:v>0</x:v>
@@ -45287,10 +45287,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1508" s="1">
-        <x:v>66000</x:v>
+        <x:v>157050</x:v>
       </x:c>
       <x:c r="G1508" s="1">
-        <x:v>74000</x:v>
+        <x:v>303750</x:v>
       </x:c>
     </x:row>
     <x:row r="1509" spans="1:7">
@@ -47897,10 +47897,10 @@
         <x:v>1657</x:v>
       </x:c>
       <x:c r="B1622" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C1622" s="1">
-        <x:v>0</x:v>
+        <x:v>27850</x:v>
       </x:c>
       <x:c r="D1622" s="1">
         <x:v>0</x:v>
@@ -47909,10 +47909,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1622" s="1">
-        <x:v>102225</x:v>
+        <x:v>19000</x:v>
       </x:c>
       <x:c r="G1622" s="1">
-        <x:v>102225</x:v>
+        <x:v>46850</x:v>
       </x:c>
     </x:row>
     <x:row r="1623" spans="1:7">
@@ -47920,10 +47920,10 @@
         <x:v>1657</x:v>
       </x:c>
       <x:c r="B1623" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C1623" s="1">
-        <x:v>27850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1623" s="1">
         <x:v>0</x:v>
@@ -47932,10 +47932,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1623" s="1">
-        <x:v>19000</x:v>
+        <x:v>102225</x:v>
       </x:c>
       <x:c r="G1623" s="1">
-        <x:v>46850</x:v>
+        <x:v>102225</x:v>
       </x:c>
     </x:row>
     <x:row r="1624" spans="1:7">
@@ -50910,10 +50910,10 @@
         <x:v>1784</x:v>
       </x:c>
       <x:c r="B1753" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C1753" s="1">
-        <x:v>-1000</x:v>
+        <x:v>147100</x:v>
       </x:c>
       <x:c r="D1753" s="1">
         <x:v>0</x:v>
@@ -50922,10 +50922,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1753" s="1">
-        <x:v>0</x:v>
+        <x:v>34550</x:v>
       </x:c>
       <x:c r="G1753" s="1">
-        <x:v>-1000</x:v>
+        <x:v>181650</x:v>
       </x:c>
     </x:row>
     <x:row r="1754" spans="1:7">
@@ -50933,10 +50933,10 @@
         <x:v>1784</x:v>
       </x:c>
       <x:c r="B1754" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C1754" s="1">
-        <x:v>147100</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="D1754" s="1">
         <x:v>0</x:v>
@@ -50945,10 +50945,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1754" s="1">
-        <x:v>34550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1754" s="1">
-        <x:v>181650</x:v>
+        <x:v>-1000</x:v>
       </x:c>
     </x:row>
     <x:row r="1755" spans="1:7">
@@ -51094,7 +51094,7 @@
         <x:v>1791</x:v>
       </x:c>
       <x:c r="B1761" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1761" s="1">
         <x:v>0</x:v>
@@ -51117,7 +51117,7 @@
         <x:v>1791</x:v>
       </x:c>
       <x:c r="B1762" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C1762" s="1">
         <x:v>0</x:v>
@@ -57534,10 +57534,10 @@
         <x:v>2066</x:v>
       </x:c>
       <x:c r="B2041" s="1" t="s">
-        <x:v>188</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C2041" s="1">
-        <x:v>960100</x:v>
+        <x:v>11000</x:v>
       </x:c>
       <x:c r="D2041" s="1">
         <x:v>0</x:v>
@@ -57546,10 +57546,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2041" s="1">
-        <x:v>882230</x:v>
+        <x:v>25550</x:v>
       </x:c>
       <x:c r="G2041" s="1">
-        <x:v>1842330</x:v>
+        <x:v>36550</x:v>
       </x:c>
     </x:row>
     <x:row r="2042" spans="1:7">
@@ -57557,10 +57557,10 @@
         <x:v>2066</x:v>
       </x:c>
       <x:c r="B2042" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C2042" s="1">
-        <x:v>11000</x:v>
+        <x:v>960100</x:v>
       </x:c>
       <x:c r="D2042" s="1">
         <x:v>0</x:v>
@@ -57569,10 +57569,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2042" s="1">
-        <x:v>25550</x:v>
+        <x:v>882230</x:v>
       </x:c>
       <x:c r="G2042" s="1">
-        <x:v>36550</x:v>
+        <x:v>1842330</x:v>
       </x:c>
     </x:row>
     <x:row r="2043" spans="1:7">
@@ -57649,10 +57649,10 @@
         <x:v>2070</x:v>
       </x:c>
       <x:c r="B2046" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C2046" s="1">
-        <x:v>22450</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="D2046" s="1">
         <x:v>0</x:v>
@@ -57661,10 +57661,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2046" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G2046" s="1">
         <x:v>250</x:v>
-      </x:c>
-      <x:c r="G2046" s="1">
-        <x:v>22700</x:v>
       </x:c>
     </x:row>
     <x:row r="2047" spans="1:7">
@@ -57672,22 +57672,22 @@
         <x:v>2070</x:v>
       </x:c>
       <x:c r="B2047" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C2047" s="1">
+        <x:v>22450</x:v>
+      </x:c>
+      <x:c r="D2047" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E2047" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F2047" s="1">
         <x:v>250</x:v>
       </x:c>
-      <x:c r="D2047" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E2047" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F2047" s="1">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="G2047" s="1">
-        <x:v>250</x:v>
+        <x:v>22700</x:v>
       </x:c>
     </x:row>
     <x:row r="2048" spans="1:7">
@@ -69494,10 +69494,10 @@
         <x:v>2581</x:v>
       </x:c>
       <x:c r="B2561" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C2561" s="1">
-        <x:v>409250</x:v>
+        <x:v>7061</x:v>
       </x:c>
       <x:c r="D2561" s="1">
         <x:v>0</x:v>
@@ -69506,10 +69506,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2561" s="1">
-        <x:v>159800</x:v>
+        <x:v>23500</x:v>
       </x:c>
       <x:c r="G2561" s="1">
-        <x:v>569050</x:v>
+        <x:v>30561</x:v>
       </x:c>
     </x:row>
     <x:row r="2562" spans="1:7">
@@ -69517,10 +69517,10 @@
         <x:v>2581</x:v>
       </x:c>
       <x:c r="B2562" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C2562" s="1">
-        <x:v>7061</x:v>
+        <x:v>409250</x:v>
       </x:c>
       <x:c r="D2562" s="1">
         <x:v>0</x:v>
@@ -69529,10 +69529,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2562" s="1">
-        <x:v>23500</x:v>
+        <x:v>159800</x:v>
       </x:c>
       <x:c r="G2562" s="1">
-        <x:v>30561</x:v>
+        <x:v>569050</x:v>
       </x:c>
     </x:row>
     <x:row r="2563" spans="1:7">
@@ -72461,10 +72461,10 @@
         <x:v>2706</x:v>
       </x:c>
       <x:c r="B2690" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C2690" s="1">
-        <x:v>206766</x:v>
+        <x:v>163800</x:v>
       </x:c>
       <x:c r="D2690" s="1">
         <x:v>0</x:v>
@@ -72473,10 +72473,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2690" s="1">
-        <x:v>286825</x:v>
+        <x:v>276645</x:v>
       </x:c>
       <x:c r="G2690" s="1">
-        <x:v>493591</x:v>
+        <x:v>440445</x:v>
       </x:c>
     </x:row>
     <x:row r="2691" spans="1:7">
@@ -72484,10 +72484,10 @@
         <x:v>2706</x:v>
       </x:c>
       <x:c r="B2691" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C2691" s="1">
-        <x:v>163800</x:v>
+        <x:v>206766</x:v>
       </x:c>
       <x:c r="D2691" s="1">
         <x:v>0</x:v>
@@ -72496,10 +72496,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2691" s="1">
-        <x:v>276645</x:v>
+        <x:v>286825</x:v>
       </x:c>
       <x:c r="G2691" s="1">
-        <x:v>440445</x:v>
+        <x:v>493591</x:v>
       </x:c>
     </x:row>
     <x:row r="2692" spans="1:7">
@@ -73979,10 +73979,10 @@
         <x:v>2770</x:v>
       </x:c>
       <x:c r="B2756" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C2756" s="1">
-        <x:v>15000</x:v>
+        <x:v>102350</x:v>
       </x:c>
       <x:c r="D2756" s="1">
         <x:v>0</x:v>
@@ -73991,10 +73991,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2756" s="1">
-        <x:v>5000</x:v>
+        <x:v>106550</x:v>
       </x:c>
       <x:c r="G2756" s="1">
-        <x:v>20000</x:v>
+        <x:v>208900</x:v>
       </x:c>
     </x:row>
     <x:row r="2757" spans="1:7">
@@ -74002,10 +74002,10 @@
         <x:v>2770</x:v>
       </x:c>
       <x:c r="B2757" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C2757" s="1">
-        <x:v>102350</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D2757" s="1">
         <x:v>0</x:v>
@@ -74014,10 +74014,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2757" s="1">
-        <x:v>106550</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G2757" s="1">
-        <x:v>208900</x:v>
+        <x:v>20000</x:v>
       </x:c>
     </x:row>
     <x:row r="2758" spans="1:7">
@@ -78119,10 +78119,10 @@
         <x:v>2946</x:v>
       </x:c>
       <x:c r="B2936" s="1" t="s">
-        <x:v>254</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C2936" s="1">
-        <x:v>7000</x:v>
+        <x:v>71750</x:v>
       </x:c>
       <x:c r="D2936" s="1">
         <x:v>0</x:v>
@@ -78131,10 +78131,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2936" s="1">
-        <x:v>0</x:v>
+        <x:v>77150</x:v>
       </x:c>
       <x:c r="G2936" s="1">
-        <x:v>7000</x:v>
+        <x:v>148900</x:v>
       </x:c>
     </x:row>
     <x:row r="2937" spans="1:7">
@@ -78142,10 +78142,10 @@
         <x:v>2946</x:v>
       </x:c>
       <x:c r="B2937" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="C2937" s="1">
-        <x:v>71750</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D2937" s="1">
         <x:v>0</x:v>
@@ -78154,10 +78154,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2937" s="1">
-        <x:v>77150</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2937" s="1">
-        <x:v>148900</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="2938" spans="1:7">
@@ -78671,10 +78671,10 @@
         <x:v>2969</x:v>
       </x:c>
       <x:c r="B2960" s="1" t="s">
-        <x:v>156</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C2960" s="1">
-        <x:v>5000</x:v>
+        <x:v>10500</x:v>
       </x:c>
       <x:c r="D2960" s="1">
         <x:v>0</x:v>
@@ -78683,10 +78683,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2960" s="1">
-        <x:v>33600</x:v>
+        <x:v>31300</x:v>
       </x:c>
       <x:c r="G2960" s="1">
-        <x:v>38600</x:v>
+        <x:v>41800</x:v>
       </x:c>
     </x:row>
     <x:row r="2961" spans="1:7">
@@ -78694,10 +78694,10 @@
         <x:v>2969</x:v>
       </x:c>
       <x:c r="B2961" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C2961" s="1">
-        <x:v>10500</x:v>
+        <x:v>44000</x:v>
       </x:c>
       <x:c r="D2961" s="1">
         <x:v>0</x:v>
@@ -78706,10 +78706,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2961" s="1">
-        <x:v>31300</x:v>
+        <x:v>2100</x:v>
       </x:c>
       <x:c r="G2961" s="1">
-        <x:v>41800</x:v>
+        <x:v>46100</x:v>
       </x:c>
     </x:row>
     <x:row r="2962" spans="1:7">
@@ -78717,10 +78717,10 @@
         <x:v>2969</x:v>
       </x:c>
       <x:c r="B2962" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="C2962" s="1">
-        <x:v>44000</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D2962" s="1">
         <x:v>0</x:v>
@@ -78729,10 +78729,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2962" s="1">
-        <x:v>2100</x:v>
+        <x:v>33600</x:v>
       </x:c>
       <x:c r="G2962" s="1">
-        <x:v>46100</x:v>
+        <x:v>38600</x:v>
       </x:c>
     </x:row>
     <x:row r="2963" spans="1:7">
@@ -79959,10 +79959,10 @@
         <x:v>3020</x:v>
       </x:c>
       <x:c r="B3016" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C3016" s="1">
-        <x:v>5000</x:v>
+        <x:v>48000</x:v>
       </x:c>
       <x:c r="D3016" s="1">
         <x:v>0</x:v>
@@ -79971,10 +79971,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3016" s="1">
-        <x:v>250</x:v>
+        <x:v>38300</x:v>
       </x:c>
       <x:c r="G3016" s="1">
-        <x:v>5250</x:v>
+        <x:v>86300</x:v>
       </x:c>
     </x:row>
     <x:row r="3017" spans="1:7">
@@ -79982,10 +79982,10 @@
         <x:v>3020</x:v>
       </x:c>
       <x:c r="B3017" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C3017" s="1">
-        <x:v>48000</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D3017" s="1">
         <x:v>0</x:v>
@@ -79994,10 +79994,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3017" s="1">
-        <x:v>38300</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G3017" s="1">
-        <x:v>86300</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="3018" spans="1:7">
@@ -82328,10 +82328,10 @@
         <x:v>3115</x:v>
       </x:c>
       <x:c r="B3119" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="C3119" s="1">
-        <x:v>292600</x:v>
+        <x:v>34000</x:v>
       </x:c>
       <x:c r="D3119" s="1">
         <x:v>0</x:v>
@@ -82340,10 +82340,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3119" s="1">
-        <x:v>222972</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3119" s="1">
-        <x:v>515572</x:v>
+        <x:v>34000</x:v>
       </x:c>
     </x:row>
     <x:row r="3120" spans="1:7">
@@ -82351,10 +82351,10 @@
         <x:v>3115</x:v>
       </x:c>
       <x:c r="B3120" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C3120" s="1">
-        <x:v>34000</x:v>
+        <x:v>292600</x:v>
       </x:c>
       <x:c r="D3120" s="1">
         <x:v>0</x:v>
@@ -82363,10 +82363,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3120" s="1">
-        <x:v>0</x:v>
+        <x:v>222972</x:v>
       </x:c>
       <x:c r="G3120" s="1">
-        <x:v>34000</x:v>
+        <x:v>515572</x:v>
       </x:c>
     </x:row>
     <x:row r="3121" spans="1:7">
@@ -82719,10 +82719,10 @@
         <x:v>3130</x:v>
       </x:c>
       <x:c r="B3136" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C3136" s="1">
-        <x:v>420650</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D3136" s="1">
         <x:v>0</x:v>
@@ -82731,10 +82731,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3136" s="1">
-        <x:v>448381</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3136" s="1">
-        <x:v>869031</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="3137" spans="1:7">
@@ -82742,10 +82742,10 @@
         <x:v>3130</x:v>
       </x:c>
       <x:c r="B3137" s="1" t="s">
-        <x:v>165</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C3137" s="1">
-        <x:v>25500</x:v>
+        <x:v>420650</x:v>
       </x:c>
       <x:c r="D3137" s="1">
         <x:v>0</x:v>
@@ -82754,10 +82754,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3137" s="1">
-        <x:v>0</x:v>
+        <x:v>448381</x:v>
       </x:c>
       <x:c r="G3137" s="1">
-        <x:v>25500</x:v>
+        <x:v>869031</x:v>
       </x:c>
     </x:row>
     <x:row r="3138" spans="1:7">
@@ -84444,10 +84444,10 @@
         <x:v>3204</x:v>
       </x:c>
       <x:c r="B3211" s="1" t="s">
-        <x:v>254</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C3211" s="1">
-        <x:v>15000</x:v>
+        <x:v>332220</x:v>
       </x:c>
       <x:c r="D3211" s="1">
         <x:v>0</x:v>
@@ -84456,10 +84456,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3211" s="1">
-        <x:v>0</x:v>
+        <x:v>299023</x:v>
       </x:c>
       <x:c r="G3211" s="1">
-        <x:v>15000</x:v>
+        <x:v>631243</x:v>
       </x:c>
     </x:row>
     <x:row r="3212" spans="1:7">
@@ -84467,10 +84467,10 @@
         <x:v>3204</x:v>
       </x:c>
       <x:c r="B3212" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="C3212" s="1">
-        <x:v>332220</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D3212" s="1">
         <x:v>0</x:v>
@@ -84479,10 +84479,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3212" s="1">
-        <x:v>299023</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3212" s="1">
-        <x:v>631243</x:v>
+        <x:v>15000</x:v>
       </x:c>
     </x:row>
     <x:row r="3213" spans="1:7">
@@ -85594,10 +85594,10 @@
         <x:v>3250</x:v>
       </x:c>
       <x:c r="B3261" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="C3261" s="1">
-        <x:v>41550</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D3261" s="1">
         <x:v>0</x:v>
@@ -85606,10 +85606,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3261" s="1">
-        <x:v>6500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3261" s="1">
-        <x:v>48050</x:v>
+        <x:v>15000</x:v>
       </x:c>
     </x:row>
     <x:row r="3262" spans="1:7">
@@ -85617,10 +85617,10 @@
         <x:v>3250</x:v>
       </x:c>
       <x:c r="B3262" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C3262" s="1">
-        <x:v>15000</x:v>
+        <x:v>41550</x:v>
       </x:c>
       <x:c r="D3262" s="1">
         <x:v>0</x:v>
@@ -85629,10 +85629,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3262" s="1">
-        <x:v>0</x:v>
+        <x:v>6500</x:v>
       </x:c>
       <x:c r="G3262" s="1">
-        <x:v>15000</x:v>
+        <x:v>48050</x:v>
       </x:c>
     </x:row>
     <x:row r="3263" spans="1:7">
@@ -85709,7 +85709,7 @@
         <x:v>3253</x:v>
       </x:c>
       <x:c r="B3266" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C3266" s="1">
         <x:v>0</x:v>
@@ -85721,10 +85721,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3266" s="1">
-        <x:v>1600</x:v>
+        <x:v>913</x:v>
       </x:c>
       <x:c r="G3266" s="1">
-        <x:v>1600</x:v>
+        <x:v>913</x:v>
       </x:c>
     </x:row>
     <x:row r="3267" spans="1:7">
@@ -85732,7 +85732,7 @@
         <x:v>3253</x:v>
       </x:c>
       <x:c r="B3267" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C3267" s="1">
         <x:v>0</x:v>
@@ -85744,10 +85744,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3267" s="1">
-        <x:v>913</x:v>
+        <x:v>1600</x:v>
       </x:c>
       <x:c r="G3267" s="1">
-        <x:v>913</x:v>
+        <x:v>1600</x:v>
       </x:c>
     </x:row>
     <x:row r="3268" spans="1:7">
@@ -86905,10 +86905,10 @@
         <x:v>3302</x:v>
       </x:c>
       <x:c r="B3318" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C3318" s="1">
-        <x:v>500</x:v>
+        <x:v>19500</x:v>
       </x:c>
       <x:c r="D3318" s="1">
         <x:v>0</x:v>
@@ -86917,10 +86917,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3318" s="1">
-        <x:v>0</x:v>
+        <x:v>8650</x:v>
       </x:c>
       <x:c r="G3318" s="1">
-        <x:v>500</x:v>
+        <x:v>28150</x:v>
       </x:c>
     </x:row>
     <x:row r="3319" spans="1:7">
@@ -86928,10 +86928,10 @@
         <x:v>3302</x:v>
       </x:c>
       <x:c r="B3319" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C3319" s="1">
-        <x:v>19500</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="D3319" s="1">
         <x:v>0</x:v>
@@ -86940,10 +86940,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3319" s="1">
-        <x:v>8650</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3319" s="1">
-        <x:v>28150</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="3320" spans="1:7">
@@ -87250,10 +87250,10 @@
         <x:v>3316</x:v>
       </x:c>
       <x:c r="B3333" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="C3333" s="1">
-        <x:v>3000</x:v>
+        <x:v>429650</x:v>
       </x:c>
       <x:c r="D3333" s="1">
         <x:v>0</x:v>
@@ -87262,10 +87262,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3333" s="1">
-        <x:v>0</x:v>
+        <x:v>347550</x:v>
       </x:c>
       <x:c r="G3333" s="1">
-        <x:v>3000</x:v>
+        <x:v>777200</x:v>
       </x:c>
     </x:row>
     <x:row r="3334" spans="1:7">
@@ -87273,10 +87273,10 @@
         <x:v>3316</x:v>
       </x:c>
       <x:c r="B3334" s="1" t="s">
-        <x:v>410</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C3334" s="1">
-        <x:v>429650</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D3334" s="1">
         <x:v>0</x:v>
@@ -87285,10 +87285,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3334" s="1">
-        <x:v>347550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3334" s="1">
-        <x:v>777200</x:v>
+        <x:v>3000</x:v>
       </x:c>
     </x:row>
     <x:row r="3335" spans="1:7">

--- a/reports/pro-oil/pro-oil-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-oil/pro-oil-candidate-lobby-lifetime-report.xlsx
@@ -18825,10 +18825,10 @@
         <x:v>412</x:v>
       </x:c>
       <x:c r="B358" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C358" s="1">
-        <x:v>107540</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D358" s="1">
         <x:v>0</x:v>
@@ -18837,10 +18837,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F358" s="1">
-        <x:v>59170</x:v>
+        <x:v>25150</x:v>
       </x:c>
       <x:c r="G358" s="1">
-        <x:v>166710</x:v>
+        <x:v>28150</x:v>
       </x:c>
     </x:row>
     <x:row r="359" spans="1:7">
@@ -18848,10 +18848,10 @@
         <x:v>412</x:v>
       </x:c>
       <x:c r="B359" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C359" s="1">
-        <x:v>3000</x:v>
+        <x:v>107540</x:v>
       </x:c>
       <x:c r="D359" s="1">
         <x:v>0</x:v>
@@ -18860,10 +18860,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F359" s="1">
-        <x:v>25150</x:v>
+        <x:v>59170</x:v>
       </x:c>
       <x:c r="G359" s="1">
-        <x:v>28150</x:v>
+        <x:v>166710</x:v>
       </x:c>
     </x:row>
     <x:row r="360" spans="1:7">
@@ -26346,10 +26346,10 @@
         <x:v>737</x:v>
       </x:c>
       <x:c r="B685" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>727</x:v>
       </x:c>
       <x:c r="C685" s="1">
-        <x:v>25500</x:v>
+        <x:v>370033</x:v>
       </x:c>
       <x:c r="D685" s="1">
         <x:v>0</x:v>
@@ -26358,10 +26358,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F685" s="1">
-        <x:v>0</x:v>
+        <x:v>45850</x:v>
       </x:c>
       <x:c r="G685" s="1">
-        <x:v>25500</x:v>
+        <x:v>415883</x:v>
       </x:c>
     </x:row>
     <x:row r="686" spans="1:7">
@@ -26369,10 +26369,10 @@
         <x:v>737</x:v>
       </x:c>
       <x:c r="B686" s="1" t="s">
-        <x:v>727</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C686" s="1">
-        <x:v>370033</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D686" s="1">
         <x:v>0</x:v>
@@ -26381,10 +26381,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F686" s="1">
-        <x:v>45850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G686" s="1">
-        <x:v>415883</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="687" spans="1:7">
@@ -29796,10 +29796,10 @@
         <x:v>885</x:v>
       </x:c>
       <x:c r="B835" s="1" t="s">
-        <x:v>256</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C835" s="1">
-        <x:v>3000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D835" s="1">
         <x:v>0</x:v>
@@ -29808,10 +29808,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F835" s="1">
-        <x:v>5950</x:v>
+        <x:v>14450</x:v>
       </x:c>
       <x:c r="G835" s="1">
-        <x:v>8950</x:v>
+        <x:v>14450</x:v>
       </x:c>
     </x:row>
     <x:row r="836" spans="1:7">
@@ -29819,10 +29819,10 @@
         <x:v>885</x:v>
       </x:c>
       <x:c r="B836" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="C836" s="1">
-        <x:v>0</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D836" s="1">
         <x:v>0</x:v>
@@ -29831,10 +29831,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F836" s="1">
-        <x:v>14450</x:v>
+        <x:v>5950</x:v>
       </x:c>
       <x:c r="G836" s="1">
-        <x:v>14450</x:v>
+        <x:v>8950</x:v>
       </x:c>
     </x:row>
     <x:row r="837" spans="1:7">
@@ -36190,10 +36190,10 @@
         <x:v>1158</x:v>
       </x:c>
       <x:c r="B1113" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C1113" s="1">
-        <x:v>752389</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1113" s="1">
         <x:v>0</x:v>
@@ -36202,10 +36202,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1113" s="1">
-        <x:v>418794</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="G1113" s="1">
-        <x:v>1171183</x:v>
+        <x:v>10000</x:v>
       </x:c>
     </x:row>
     <x:row r="1114" spans="1:7">
@@ -36213,10 +36213,10 @@
         <x:v>1158</x:v>
       </x:c>
       <x:c r="B1114" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1114" s="1">
-        <x:v>0</x:v>
+        <x:v>752389</x:v>
       </x:c>
       <x:c r="D1114" s="1">
         <x:v>0</x:v>
@@ -36225,10 +36225,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1114" s="1">
-        <x:v>10000</x:v>
+        <x:v>418794</x:v>
       </x:c>
       <x:c r="G1114" s="1">
-        <x:v>10000</x:v>
+        <x:v>1171183</x:v>
       </x:c>
     </x:row>
     <x:row r="1115" spans="1:7">
@@ -44608,10 +44608,10 @@
         <x:v>1519</x:v>
       </x:c>
       <x:c r="B1479" s="1" t="s">
-        <x:v>161</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C1479" s="1">
-        <x:v>82250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1479" s="1">
         <x:v>0</x:v>
@@ -44620,10 +44620,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1479" s="1">
-        <x:v>9000</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1479" s="1">
-        <x:v>91250</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="1480" spans="1:7">
@@ -44631,10 +44631,10 @@
         <x:v>1519</x:v>
       </x:c>
       <x:c r="B1480" s="1" t="s">
-        <x:v>165</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C1480" s="1">
-        <x:v>0</x:v>
+        <x:v>82250</x:v>
       </x:c>
       <x:c r="D1480" s="1">
         <x:v>0</x:v>
@@ -44643,10 +44643,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1480" s="1">
-        <x:v>1000</x:v>
+        <x:v>9000</x:v>
       </x:c>
       <x:c r="G1480" s="1">
-        <x:v>1000</x:v>
+        <x:v>91250</x:v>
       </x:c>
     </x:row>
     <x:row r="1481" spans="1:7">
@@ -45252,10 +45252,10 @@
         <x:v>1544</x:v>
       </x:c>
       <x:c r="B1507" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="C1507" s="1">
-        <x:v>8000</x:v>
+        <x:v>146700</x:v>
       </x:c>
       <x:c r="D1507" s="1">
         <x:v>0</x:v>
@@ -45264,10 +45264,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1507" s="1">
-        <x:v>66000</x:v>
+        <x:v>157050</x:v>
       </x:c>
       <x:c r="G1507" s="1">
-        <x:v>74000</x:v>
+        <x:v>303750</x:v>
       </x:c>
     </x:row>
     <x:row r="1508" spans="1:7">
@@ -45275,10 +45275,10 @@
         <x:v>1544</x:v>
       </x:c>
       <x:c r="B1508" s="1" t="s">
-        <x:v>410</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C1508" s="1">
-        <x:v>146700</x:v>
+        <x:v>8000</x:v>
       </x:c>
       <x:c r="D1508" s="1">
         <x:v>0</x:v>
@@ -45287,10 +45287,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1508" s="1">
-        <x:v>157050</x:v>
+        <x:v>66000</x:v>
       </x:c>
       <x:c r="G1508" s="1">
-        <x:v>303750</x:v>
+        <x:v>74000</x:v>
       </x:c>
     </x:row>
     <x:row r="1509" spans="1:7">
@@ -48840,10 +48840,10 @@
         <x:v>1697</x:v>
       </x:c>
       <x:c r="B1663" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1663" s="1">
-        <x:v>485</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1663" s="1">
         <x:v>0</x:v>
@@ -48852,10 +48852,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1663" s="1">
-        <x:v>72700</x:v>
+        <x:v>16350</x:v>
       </x:c>
       <x:c r="G1663" s="1">
-        <x:v>73185</x:v>
+        <x:v>18850</x:v>
       </x:c>
     </x:row>
     <x:row r="1664" spans="1:7">
@@ -48863,10 +48863,10 @@
         <x:v>1697</x:v>
       </x:c>
       <x:c r="B1664" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C1664" s="1">
-        <x:v>2500</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="D1664" s="1">
         <x:v>0</x:v>
@@ -48875,10 +48875,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1664" s="1">
-        <x:v>16350</x:v>
+        <x:v>72700</x:v>
       </x:c>
       <x:c r="G1664" s="1">
-        <x:v>18850</x:v>
+        <x:v>73185</x:v>
       </x:c>
     </x:row>
     <x:row r="1665" spans="1:7">
@@ -51094,7 +51094,7 @@
         <x:v>1791</x:v>
       </x:c>
       <x:c r="B1761" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C1761" s="1">
         <x:v>0</x:v>
@@ -51117,7 +51117,7 @@
         <x:v>1791</x:v>
       </x:c>
       <x:c r="B1762" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1762" s="1">
         <x:v>0</x:v>
@@ -69494,10 +69494,10 @@
         <x:v>2581</x:v>
       </x:c>
       <x:c r="B2561" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C2561" s="1">
-        <x:v>7061</x:v>
+        <x:v>409250</x:v>
       </x:c>
       <x:c r="D2561" s="1">
         <x:v>0</x:v>
@@ -69506,10 +69506,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2561" s="1">
-        <x:v>23500</x:v>
+        <x:v>159800</x:v>
       </x:c>
       <x:c r="G2561" s="1">
-        <x:v>30561</x:v>
+        <x:v>569050</x:v>
       </x:c>
     </x:row>
     <x:row r="2562" spans="1:7">
@@ -69517,10 +69517,10 @@
         <x:v>2581</x:v>
       </x:c>
       <x:c r="B2562" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C2562" s="1">
-        <x:v>409250</x:v>
+        <x:v>7061</x:v>
       </x:c>
       <x:c r="D2562" s="1">
         <x:v>0</x:v>
@@ -69529,10 +69529,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2562" s="1">
-        <x:v>159800</x:v>
+        <x:v>23500</x:v>
       </x:c>
       <x:c r="G2562" s="1">
-        <x:v>569050</x:v>
+        <x:v>30561</x:v>
       </x:c>
     </x:row>
     <x:row r="2563" spans="1:7">
@@ -72438,10 +72438,10 @@
         <x:v>2706</x:v>
       </x:c>
       <x:c r="B2689" s="1" t="s">
-        <x:v>156</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C2689" s="1">
-        <x:v>15000</x:v>
+        <x:v>163800</x:v>
       </x:c>
       <x:c r="D2689" s="1">
         <x:v>0</x:v>
@@ -72450,10 +72450,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2689" s="1">
-        <x:v>111650</x:v>
+        <x:v>276645</x:v>
       </x:c>
       <x:c r="G2689" s="1">
-        <x:v>126650</x:v>
+        <x:v>440445</x:v>
       </x:c>
     </x:row>
     <x:row r="2690" spans="1:7">
@@ -72461,10 +72461,10 @@
         <x:v>2706</x:v>
       </x:c>
       <x:c r="B2690" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="C2690" s="1">
-        <x:v>163800</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D2690" s="1">
         <x:v>0</x:v>
@@ -72473,10 +72473,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2690" s="1">
-        <x:v>276645</x:v>
+        <x:v>111650</x:v>
       </x:c>
       <x:c r="G2690" s="1">
-        <x:v>440445</x:v>
+        <x:v>126650</x:v>
       </x:c>
     </x:row>
     <x:row r="2691" spans="1:7">
@@ -73979,10 +73979,10 @@
         <x:v>2770</x:v>
       </x:c>
       <x:c r="B2756" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C2756" s="1">
-        <x:v>102350</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D2756" s="1">
         <x:v>0</x:v>
@@ -73991,10 +73991,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2756" s="1">
-        <x:v>106550</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G2756" s="1">
-        <x:v>208900</x:v>
+        <x:v>20000</x:v>
       </x:c>
     </x:row>
     <x:row r="2757" spans="1:7">
@@ -74002,10 +74002,10 @@
         <x:v>2770</x:v>
       </x:c>
       <x:c r="B2757" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C2757" s="1">
-        <x:v>15000</x:v>
+        <x:v>102350</x:v>
       </x:c>
       <x:c r="D2757" s="1">
         <x:v>0</x:v>
@@ -74014,10 +74014,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2757" s="1">
-        <x:v>5000</x:v>
+        <x:v>106550</x:v>
       </x:c>
       <x:c r="G2757" s="1">
-        <x:v>20000</x:v>
+        <x:v>208900</x:v>
       </x:c>
     </x:row>
     <x:row r="2758" spans="1:7">
@@ -76371,10 +76371,10 @@
         <x:v>2871</x:v>
       </x:c>
       <x:c r="B2860" s="1" t="s">
-        <x:v>727</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C2860" s="1">
-        <x:v>284300</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D2860" s="1">
         <x:v>0</x:v>
@@ -76383,10 +76383,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2860" s="1">
-        <x:v>71650</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2860" s="1">
-        <x:v>355950</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="2861" spans="1:7">
@@ -76394,10 +76394,10 @@
         <x:v>2871</x:v>
       </x:c>
       <x:c r="B2861" s="1" t="s">
-        <x:v>165</x:v>
+        <x:v>727</x:v>
       </x:c>
       <x:c r="C2861" s="1">
-        <x:v>5000</x:v>
+        <x:v>284300</x:v>
       </x:c>
       <x:c r="D2861" s="1">
         <x:v>0</x:v>
@@ -76406,10 +76406,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2861" s="1">
-        <x:v>0</x:v>
+        <x:v>71650</x:v>
       </x:c>
       <x:c r="G2861" s="1">
-        <x:v>5000</x:v>
+        <x:v>355950</x:v>
       </x:c>
     </x:row>
     <x:row r="2862" spans="1:7">
@@ -78671,10 +78671,10 @@
         <x:v>2969</x:v>
       </x:c>
       <x:c r="B2960" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C2960" s="1">
-        <x:v>10500</x:v>
+        <x:v>44000</x:v>
       </x:c>
       <x:c r="D2960" s="1">
         <x:v>0</x:v>
@@ -78683,10 +78683,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2960" s="1">
-        <x:v>31300</x:v>
+        <x:v>2100</x:v>
       </x:c>
       <x:c r="G2960" s="1">
-        <x:v>41800</x:v>
+        <x:v>46100</x:v>
       </x:c>
     </x:row>
     <x:row r="2961" spans="1:7">
@@ -78694,10 +78694,10 @@
         <x:v>2969</x:v>
       </x:c>
       <x:c r="B2961" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C2961" s="1">
-        <x:v>44000</x:v>
+        <x:v>10500</x:v>
       </x:c>
       <x:c r="D2961" s="1">
         <x:v>0</x:v>
@@ -78706,10 +78706,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2961" s="1">
-        <x:v>2100</x:v>
+        <x:v>31300</x:v>
       </x:c>
       <x:c r="G2961" s="1">
-        <x:v>46100</x:v>
+        <x:v>41800</x:v>
       </x:c>
     </x:row>
     <x:row r="2962" spans="1:7">
@@ -82719,10 +82719,10 @@
         <x:v>3130</x:v>
       </x:c>
       <x:c r="B3136" s="1" t="s">
-        <x:v>165</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C3136" s="1">
-        <x:v>25500</x:v>
+        <x:v>420650</x:v>
       </x:c>
       <x:c r="D3136" s="1">
         <x:v>0</x:v>
@@ -82731,10 +82731,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3136" s="1">
-        <x:v>0</x:v>
+        <x:v>448381</x:v>
       </x:c>
       <x:c r="G3136" s="1">
-        <x:v>25500</x:v>
+        <x:v>869031</x:v>
       </x:c>
     </x:row>
     <x:row r="3137" spans="1:7">
@@ -82742,10 +82742,10 @@
         <x:v>3130</x:v>
       </x:c>
       <x:c r="B3137" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C3137" s="1">
-        <x:v>420650</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D3137" s="1">
         <x:v>0</x:v>
@@ -82754,10 +82754,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3137" s="1">
-        <x:v>448381</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3137" s="1">
-        <x:v>869031</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="3138" spans="1:7">
@@ -84444,10 +84444,10 @@
         <x:v>3204</x:v>
       </x:c>
       <x:c r="B3211" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="C3211" s="1">
-        <x:v>332220</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D3211" s="1">
         <x:v>0</x:v>
@@ -84456,10 +84456,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3211" s="1">
-        <x:v>299023</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3211" s="1">
-        <x:v>631243</x:v>
+        <x:v>15000</x:v>
       </x:c>
     </x:row>
     <x:row r="3212" spans="1:7">
@@ -84467,10 +84467,10 @@
         <x:v>3204</x:v>
       </x:c>
       <x:c r="B3212" s="1" t="s">
-        <x:v>254</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C3212" s="1">
-        <x:v>15000</x:v>
+        <x:v>332220</x:v>
       </x:c>
       <x:c r="D3212" s="1">
         <x:v>0</x:v>
@@ -84479,10 +84479,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3212" s="1">
-        <x:v>0</x:v>
+        <x:v>299023</x:v>
       </x:c>
       <x:c r="G3212" s="1">
-        <x:v>15000</x:v>
+        <x:v>631243</x:v>
       </x:c>
     </x:row>
     <x:row r="3213" spans="1:7">
@@ -84536,10 +84536,10 @@
         <x:v>3206</x:v>
       </x:c>
       <x:c r="B3215" s="1" t="s">
-        <x:v>156</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C3215" s="1">
-        <x:v>7000</x:v>
+        <x:v>116050</x:v>
       </x:c>
       <x:c r="D3215" s="1">
         <x:v>0</x:v>
@@ -84548,10 +84548,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3215" s="1">
-        <x:v>7000</x:v>
+        <x:v>47699</x:v>
       </x:c>
       <x:c r="G3215" s="1">
-        <x:v>14000</x:v>
+        <x:v>163749</x:v>
       </x:c>
     </x:row>
     <x:row r="3216" spans="1:7">
@@ -84559,10 +84559,10 @@
         <x:v>3206</x:v>
       </x:c>
       <x:c r="B3216" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="C3216" s="1">
-        <x:v>116050</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D3216" s="1">
         <x:v>0</x:v>
@@ -84571,10 +84571,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3216" s="1">
-        <x:v>47699</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="G3216" s="1">
-        <x:v>163749</x:v>
+        <x:v>14000</x:v>
       </x:c>
     </x:row>
     <x:row r="3217" spans="1:7">
@@ -87273,10 +87273,10 @@
         <x:v>3316</x:v>
       </x:c>
       <x:c r="B3334" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="C3334" s="1">
-        <x:v>3000</x:v>
+        <x:v>22500</x:v>
       </x:c>
       <x:c r="D3334" s="1">
         <x:v>0</x:v>
@@ -87288,7 +87288,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G3334" s="1">
-        <x:v>3000</x:v>
+        <x:v>22500</x:v>
       </x:c>
     </x:row>
     <x:row r="3335" spans="1:7">
@@ -87296,10 +87296,10 @@
         <x:v>3316</x:v>
       </x:c>
       <x:c r="B3335" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C3335" s="1">
-        <x:v>22500</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D3335" s="1">
         <x:v>0</x:v>
@@ -87311,7 +87311,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G3335" s="1">
-        <x:v>22500</x:v>
+        <x:v>3000</x:v>
       </x:c>
     </x:row>
     <x:row r="3336" spans="1:7">

--- a/reports/pro-oil/pro-oil-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-oil/pro-oil-candidate-lobby-lifetime-report.xlsx
@@ -15674,7 +15674,7 @@
         <x:v>275</x:v>
       </x:c>
       <x:c r="B221" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C221" s="1">
         <x:v>0</x:v>
@@ -15686,10 +15686,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F221" s="1">
-        <x:v>2300</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G221" s="1">
-        <x:v>2300</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="222" spans="1:7">
@@ -15697,7 +15697,7 @@
         <x:v>275</x:v>
       </x:c>
       <x:c r="B222" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C222" s="1">
         <x:v>0</x:v>
@@ -15709,10 +15709,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F222" s="1">
-        <x:v>1000</x:v>
+        <x:v>2300</x:v>
       </x:c>
       <x:c r="G222" s="1">
-        <x:v>1000</x:v>
+        <x:v>2300</x:v>
       </x:c>
     </x:row>
     <x:row r="223" spans="1:7">
@@ -18825,10 +18825,10 @@
         <x:v>412</x:v>
       </x:c>
       <x:c r="B358" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C358" s="1">
-        <x:v>3000</x:v>
+        <x:v>107540</x:v>
       </x:c>
       <x:c r="D358" s="1">
         <x:v>0</x:v>
@@ -18837,10 +18837,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F358" s="1">
-        <x:v>25150</x:v>
+        <x:v>59170</x:v>
       </x:c>
       <x:c r="G358" s="1">
-        <x:v>28150</x:v>
+        <x:v>166710</x:v>
       </x:c>
     </x:row>
     <x:row r="359" spans="1:7">
@@ -18848,10 +18848,10 @@
         <x:v>412</x:v>
       </x:c>
       <x:c r="B359" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C359" s="1">
-        <x:v>107540</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D359" s="1">
         <x:v>0</x:v>
@@ -18860,10 +18860,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F359" s="1">
-        <x:v>59170</x:v>
+        <x:v>25150</x:v>
       </x:c>
       <x:c r="G359" s="1">
-        <x:v>166710</x:v>
+        <x:v>28150</x:v>
       </x:c>
     </x:row>
     <x:row r="360" spans="1:7">
@@ -29796,10 +29796,10 @@
         <x:v>885</x:v>
       </x:c>
       <x:c r="B835" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="C835" s="1">
-        <x:v>0</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D835" s="1">
         <x:v>0</x:v>
@@ -29808,10 +29808,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F835" s="1">
-        <x:v>14450</x:v>
+        <x:v>5950</x:v>
       </x:c>
       <x:c r="G835" s="1">
-        <x:v>14450</x:v>
+        <x:v>8950</x:v>
       </x:c>
     </x:row>
     <x:row r="836" spans="1:7">
@@ -29819,10 +29819,10 @@
         <x:v>885</x:v>
       </x:c>
       <x:c r="B836" s="1" t="s">
-        <x:v>256</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C836" s="1">
-        <x:v>3000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D836" s="1">
         <x:v>0</x:v>
@@ -29831,10 +29831,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F836" s="1">
-        <x:v>5950</x:v>
+        <x:v>14450</x:v>
       </x:c>
       <x:c r="G836" s="1">
-        <x:v>8950</x:v>
+        <x:v>14450</x:v>
       </x:c>
     </x:row>
     <x:row r="837" spans="1:7">
@@ -36190,10 +36190,10 @@
         <x:v>1158</x:v>
       </x:c>
       <x:c r="B1113" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1113" s="1">
-        <x:v>0</x:v>
+        <x:v>752389</x:v>
       </x:c>
       <x:c r="D1113" s="1">
         <x:v>0</x:v>
@@ -36202,10 +36202,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1113" s="1">
-        <x:v>10000</x:v>
+        <x:v>418794</x:v>
       </x:c>
       <x:c r="G1113" s="1">
-        <x:v>10000</x:v>
+        <x:v>1171183</x:v>
       </x:c>
     </x:row>
     <x:row r="1114" spans="1:7">
@@ -36213,10 +36213,10 @@
         <x:v>1158</x:v>
       </x:c>
       <x:c r="B1114" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C1114" s="1">
-        <x:v>752389</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1114" s="1">
         <x:v>0</x:v>
@@ -36225,10 +36225,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1114" s="1">
-        <x:v>418794</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="G1114" s="1">
-        <x:v>1171183</x:v>
+        <x:v>10000</x:v>
       </x:c>
     </x:row>
     <x:row r="1115" spans="1:7">
@@ -44608,10 +44608,10 @@
         <x:v>1519</x:v>
       </x:c>
       <x:c r="B1479" s="1" t="s">
-        <x:v>165</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C1479" s="1">
-        <x:v>0</x:v>
+        <x:v>82250</x:v>
       </x:c>
       <x:c r="D1479" s="1">
         <x:v>0</x:v>
@@ -44620,10 +44620,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1479" s="1">
-        <x:v>1000</x:v>
+        <x:v>9000</x:v>
       </x:c>
       <x:c r="G1479" s="1">
-        <x:v>1000</x:v>
+        <x:v>91250</x:v>
       </x:c>
     </x:row>
     <x:row r="1480" spans="1:7">
@@ -44631,10 +44631,10 @@
         <x:v>1519</x:v>
       </x:c>
       <x:c r="B1480" s="1" t="s">
-        <x:v>161</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C1480" s="1">
-        <x:v>82250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1480" s="1">
         <x:v>0</x:v>
@@ -44643,10 +44643,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1480" s="1">
-        <x:v>9000</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1480" s="1">
-        <x:v>91250</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="1481" spans="1:7">
@@ -47897,10 +47897,10 @@
         <x:v>1657</x:v>
       </x:c>
       <x:c r="B1622" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C1622" s="1">
-        <x:v>27850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1622" s="1">
         <x:v>0</x:v>
@@ -47909,10 +47909,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1622" s="1">
-        <x:v>19000</x:v>
+        <x:v>102225</x:v>
       </x:c>
       <x:c r="G1622" s="1">
-        <x:v>46850</x:v>
+        <x:v>102225</x:v>
       </x:c>
     </x:row>
     <x:row r="1623" spans="1:7">
@@ -47920,10 +47920,10 @@
         <x:v>1657</x:v>
       </x:c>
       <x:c r="B1623" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C1623" s="1">
-        <x:v>0</x:v>
+        <x:v>27850</x:v>
       </x:c>
       <x:c r="D1623" s="1">
         <x:v>0</x:v>
@@ -47932,10 +47932,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1623" s="1">
-        <x:v>102225</x:v>
+        <x:v>19000</x:v>
       </x:c>
       <x:c r="G1623" s="1">
-        <x:v>102225</x:v>
+        <x:v>46850</x:v>
       </x:c>
     </x:row>
     <x:row r="1624" spans="1:7">
@@ -48840,10 +48840,10 @@
         <x:v>1697</x:v>
       </x:c>
       <x:c r="B1663" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C1663" s="1">
-        <x:v>2500</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="D1663" s="1">
         <x:v>0</x:v>
@@ -48852,10 +48852,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1663" s="1">
-        <x:v>16350</x:v>
+        <x:v>72700</x:v>
       </x:c>
       <x:c r="G1663" s="1">
-        <x:v>18850</x:v>
+        <x:v>73185</x:v>
       </x:c>
     </x:row>
     <x:row r="1664" spans="1:7">
@@ -48863,10 +48863,10 @@
         <x:v>1697</x:v>
       </x:c>
       <x:c r="B1664" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1664" s="1">
-        <x:v>485</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1664" s="1">
         <x:v>0</x:v>
@@ -48875,10 +48875,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1664" s="1">
-        <x:v>72700</x:v>
+        <x:v>16350</x:v>
       </x:c>
       <x:c r="G1664" s="1">
-        <x:v>73185</x:v>
+        <x:v>18850</x:v>
       </x:c>
     </x:row>
     <x:row r="1665" spans="1:7">
@@ -48909,7 +48909,7 @@
         <x:v>1699</x:v>
       </x:c>
       <x:c r="B1666" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C1666" s="1">
         <x:v>0</x:v>
@@ -48921,10 +48921,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1666" s="1">
-        <x:v>3000</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1666" s="1">
-        <x:v>3000</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="1667" spans="1:7">
@@ -48932,7 +48932,7 @@
         <x:v>1699</x:v>
       </x:c>
       <x:c r="B1667" s="1" t="s">
-        <x:v>161</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C1667" s="1">
         <x:v>0</x:v>
@@ -48944,10 +48944,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1667" s="1">
-        <x:v>1000</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="G1667" s="1">
-        <x:v>1000</x:v>
+        <x:v>3000</x:v>
       </x:c>
     </x:row>
     <x:row r="1668" spans="1:7">
@@ -51094,7 +51094,7 @@
         <x:v>1791</x:v>
       </x:c>
       <x:c r="B1761" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1761" s="1">
         <x:v>0</x:v>
@@ -51117,7 +51117,7 @@
         <x:v>1791</x:v>
       </x:c>
       <x:c r="B1762" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C1762" s="1">
         <x:v>0</x:v>
@@ -66044,10 +66044,10 @@
         <x:v>2434</x:v>
       </x:c>
       <x:c r="B2411" s="1" t="s">
-        <x:v>188</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C2411" s="1">
-        <x:v>102350</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D2411" s="1">
         <x:v>0</x:v>
@@ -66056,10 +66056,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2411" s="1">
-        <x:v>41792</x:v>
+        <x:v>7072</x:v>
       </x:c>
       <x:c r="G2411" s="1">
-        <x:v>144142</x:v>
+        <x:v>7072</x:v>
       </x:c>
     </x:row>
     <x:row r="2412" spans="1:7">
@@ -66067,10 +66067,10 @@
         <x:v>2434</x:v>
       </x:c>
       <x:c r="B2412" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C2412" s="1">
-        <x:v>0</x:v>
+        <x:v>102350</x:v>
       </x:c>
       <x:c r="D2412" s="1">
         <x:v>0</x:v>
@@ -66079,10 +66079,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2412" s="1">
-        <x:v>7072</x:v>
+        <x:v>41792</x:v>
       </x:c>
       <x:c r="G2412" s="1">
-        <x:v>7072</x:v>
+        <x:v>144142</x:v>
       </x:c>
     </x:row>
     <x:row r="2413" spans="1:7">
@@ -69655,10 +69655,10 @@
         <x:v>2587</x:v>
       </x:c>
       <x:c r="B2568" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="C2568" s="1">
-        <x:v>139000</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D2568" s="1">
         <x:v>0</x:v>
@@ -69667,10 +69667,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2568" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2568" s="1">
-        <x:v>139500</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="2569" spans="1:7">
@@ -69678,10 +69678,10 @@
         <x:v>2587</x:v>
       </x:c>
       <x:c r="B2569" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C2569" s="1">
-        <x:v>7000</x:v>
+        <x:v>139000</x:v>
       </x:c>
       <x:c r="D2569" s="1">
         <x:v>0</x:v>
@@ -69690,10 +69690,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2569" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G2569" s="1">
-        <x:v>7000</x:v>
+        <x:v>139500</x:v>
       </x:c>
     </x:row>
     <x:row r="2570" spans="1:7">
@@ -72438,10 +72438,10 @@
         <x:v>2706</x:v>
       </x:c>
       <x:c r="B2689" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="C2689" s="1">
-        <x:v>163800</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D2689" s="1">
         <x:v>0</x:v>
@@ -72450,10 +72450,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2689" s="1">
-        <x:v>276645</x:v>
+        <x:v>111650</x:v>
       </x:c>
       <x:c r="G2689" s="1">
-        <x:v>440445</x:v>
+        <x:v>126650</x:v>
       </x:c>
     </x:row>
     <x:row r="2690" spans="1:7">
@@ -72461,10 +72461,10 @@
         <x:v>2706</x:v>
       </x:c>
       <x:c r="B2690" s="1" t="s">
-        <x:v>156</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C2690" s="1">
-        <x:v>15000</x:v>
+        <x:v>163800</x:v>
       </x:c>
       <x:c r="D2690" s="1">
         <x:v>0</x:v>
@@ -72473,10 +72473,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2690" s="1">
-        <x:v>111650</x:v>
+        <x:v>276645</x:v>
       </x:c>
       <x:c r="G2690" s="1">
-        <x:v>126650</x:v>
+        <x:v>440445</x:v>
       </x:c>
     </x:row>
     <x:row r="2691" spans="1:7">
@@ -76371,10 +76371,10 @@
         <x:v>2871</x:v>
       </x:c>
       <x:c r="B2860" s="1" t="s">
-        <x:v>165</x:v>
+        <x:v>727</x:v>
       </x:c>
       <x:c r="C2860" s="1">
-        <x:v>5000</x:v>
+        <x:v>284300</x:v>
       </x:c>
       <x:c r="D2860" s="1">
         <x:v>0</x:v>
@@ -76383,10 +76383,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2860" s="1">
-        <x:v>0</x:v>
+        <x:v>71650</x:v>
       </x:c>
       <x:c r="G2860" s="1">
-        <x:v>5000</x:v>
+        <x:v>355950</x:v>
       </x:c>
     </x:row>
     <x:row r="2861" spans="1:7">
@@ -76394,10 +76394,10 @@
         <x:v>2871</x:v>
       </x:c>
       <x:c r="B2861" s="1" t="s">
-        <x:v>727</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C2861" s="1">
-        <x:v>284300</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D2861" s="1">
         <x:v>0</x:v>
@@ -76406,10 +76406,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2861" s="1">
-        <x:v>71650</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2861" s="1">
-        <x:v>355950</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="2862" spans="1:7">
@@ -78694,10 +78694,10 @@
         <x:v>2969</x:v>
       </x:c>
       <x:c r="B2961" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="C2961" s="1">
-        <x:v>10500</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D2961" s="1">
         <x:v>0</x:v>
@@ -78706,10 +78706,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2961" s="1">
-        <x:v>31300</x:v>
+        <x:v>33600</x:v>
       </x:c>
       <x:c r="G2961" s="1">
-        <x:v>41800</x:v>
+        <x:v>38600</x:v>
       </x:c>
     </x:row>
     <x:row r="2962" spans="1:7">
@@ -78717,10 +78717,10 @@
         <x:v>2969</x:v>
       </x:c>
       <x:c r="B2962" s="1" t="s">
-        <x:v>156</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C2962" s="1">
-        <x:v>5000</x:v>
+        <x:v>10500</x:v>
       </x:c>
       <x:c r="D2962" s="1">
         <x:v>0</x:v>
@@ -78729,10 +78729,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2962" s="1">
-        <x:v>33600</x:v>
+        <x:v>31300</x:v>
       </x:c>
       <x:c r="G2962" s="1">
-        <x:v>38600</x:v>
+        <x:v>41800</x:v>
       </x:c>
     </x:row>
     <x:row r="2963" spans="1:7">
@@ -78947,7 +78947,7 @@
         <x:v>2977</x:v>
       </x:c>
       <x:c r="B2972" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C2972" s="1">
         <x:v>1000</x:v>
@@ -78959,10 +78959,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2972" s="1">
-        <x:v>4750</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2972" s="1">
-        <x:v>5750</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="2973" spans="1:7">
@@ -78970,7 +78970,7 @@
         <x:v>2977</x:v>
       </x:c>
       <x:c r="B2973" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C2973" s="1">
         <x:v>1000</x:v>
@@ -78982,10 +78982,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2973" s="1">
-        <x:v>0</x:v>
+        <x:v>4750</x:v>
       </x:c>
       <x:c r="G2973" s="1">
-        <x:v>1000</x:v>
+        <x:v>5750</x:v>
       </x:c>
     </x:row>
     <x:row r="2974" spans="1:7">
@@ -79959,10 +79959,10 @@
         <x:v>3020</x:v>
       </x:c>
       <x:c r="B3016" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C3016" s="1">
-        <x:v>48000</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D3016" s="1">
         <x:v>0</x:v>
@@ -79971,10 +79971,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3016" s="1">
-        <x:v>38300</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G3016" s="1">
-        <x:v>86300</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="3017" spans="1:7">
@@ -79982,10 +79982,10 @@
         <x:v>3020</x:v>
       </x:c>
       <x:c r="B3017" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C3017" s="1">
-        <x:v>5000</x:v>
+        <x:v>48000</x:v>
       </x:c>
       <x:c r="D3017" s="1">
         <x:v>0</x:v>
@@ -79994,10 +79994,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3017" s="1">
-        <x:v>250</x:v>
+        <x:v>38300</x:v>
       </x:c>
       <x:c r="G3017" s="1">
-        <x:v>5250</x:v>
+        <x:v>86300</x:v>
       </x:c>
     </x:row>
     <x:row r="3018" spans="1:7">
@@ -80327,10 +80327,10 @@
         <x:v>3032</x:v>
       </x:c>
       <x:c r="B3032" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C3032" s="1">
-        <x:v>150000</x:v>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="D3032" s="1">
         <x:v>0</x:v>
@@ -80339,10 +80339,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3032" s="1">
-        <x:v>45517</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="G3032" s="1">
-        <x:v>195517</x:v>
+        <x:v>26000</x:v>
       </x:c>
     </x:row>
     <x:row r="3033" spans="1:7">
@@ -80350,10 +80350,10 @@
         <x:v>3032</x:v>
       </x:c>
       <x:c r="B3033" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C3033" s="1">
-        <x:v>20000</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="D3033" s="1">
         <x:v>0</x:v>
@@ -80362,10 +80362,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3033" s="1">
-        <x:v>6000</x:v>
+        <x:v>45517</x:v>
       </x:c>
       <x:c r="G3033" s="1">
-        <x:v>26000</x:v>
+        <x:v>195517</x:v>
       </x:c>
     </x:row>
     <x:row r="3034" spans="1:7">
@@ -82719,10 +82719,10 @@
         <x:v>3130</x:v>
       </x:c>
       <x:c r="B3136" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C3136" s="1">
-        <x:v>420650</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D3136" s="1">
         <x:v>0</x:v>
@@ -82731,10 +82731,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3136" s="1">
-        <x:v>448381</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3136" s="1">
-        <x:v>869031</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="3137" spans="1:7">
@@ -82742,10 +82742,10 @@
         <x:v>3130</x:v>
       </x:c>
       <x:c r="B3137" s="1" t="s">
-        <x:v>165</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C3137" s="1">
-        <x:v>25500</x:v>
+        <x:v>420650</x:v>
       </x:c>
       <x:c r="D3137" s="1">
         <x:v>0</x:v>
@@ -82754,10 +82754,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3137" s="1">
-        <x:v>0</x:v>
+        <x:v>448381</x:v>
       </x:c>
       <x:c r="G3137" s="1">
-        <x:v>25500</x:v>
+        <x:v>869031</x:v>
       </x:c>
     </x:row>
     <x:row r="3138" spans="1:7">
@@ -84536,10 +84536,10 @@
         <x:v>3206</x:v>
       </x:c>
       <x:c r="B3215" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="C3215" s="1">
-        <x:v>116050</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D3215" s="1">
         <x:v>0</x:v>
@@ -84548,10 +84548,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3215" s="1">
-        <x:v>47699</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="G3215" s="1">
-        <x:v>163749</x:v>
+        <x:v>14000</x:v>
       </x:c>
     </x:row>
     <x:row r="3216" spans="1:7">
@@ -84559,10 +84559,10 @@
         <x:v>3206</x:v>
       </x:c>
       <x:c r="B3216" s="1" t="s">
-        <x:v>156</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C3216" s="1">
-        <x:v>7000</x:v>
+        <x:v>116050</x:v>
       </x:c>
       <x:c r="D3216" s="1">
         <x:v>0</x:v>
@@ -84571,10 +84571,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3216" s="1">
-        <x:v>7000</x:v>
+        <x:v>47699</x:v>
       </x:c>
       <x:c r="G3216" s="1">
-        <x:v>14000</x:v>
+        <x:v>163749</x:v>
       </x:c>
     </x:row>
     <x:row r="3217" spans="1:7">
@@ -85594,10 +85594,10 @@
         <x:v>3250</x:v>
       </x:c>
       <x:c r="B3261" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C3261" s="1">
-        <x:v>15000</x:v>
+        <x:v>41550</x:v>
       </x:c>
       <x:c r="D3261" s="1">
         <x:v>0</x:v>
@@ -85606,10 +85606,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3261" s="1">
-        <x:v>0</x:v>
+        <x:v>6500</x:v>
       </x:c>
       <x:c r="G3261" s="1">
-        <x:v>15000</x:v>
+        <x:v>48050</x:v>
       </x:c>
     </x:row>
     <x:row r="3262" spans="1:7">
@@ -85617,10 +85617,10 @@
         <x:v>3250</x:v>
       </x:c>
       <x:c r="B3262" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="C3262" s="1">
-        <x:v>41550</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D3262" s="1">
         <x:v>0</x:v>
@@ -85629,10 +85629,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3262" s="1">
-        <x:v>6500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3262" s="1">
-        <x:v>48050</x:v>
+        <x:v>15000</x:v>
       </x:c>
     </x:row>
     <x:row r="3263" spans="1:7">
@@ -86790,10 +86790,10 @@
         <x:v>3298</x:v>
       </x:c>
       <x:c r="B3313" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C3313" s="1">
-        <x:v>0</x:v>
+        <x:v>478900</x:v>
       </x:c>
       <x:c r="D3313" s="1">
         <x:v>0</x:v>
@@ -86802,10 +86802,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3313" s="1">
-        <x:v>18200</x:v>
+        <x:v>94250</x:v>
       </x:c>
       <x:c r="G3313" s="1">
-        <x:v>18200</x:v>
+        <x:v>573150</x:v>
       </x:c>
     </x:row>
     <x:row r="3314" spans="1:7">
@@ -86813,10 +86813,10 @@
         <x:v>3298</x:v>
       </x:c>
       <x:c r="B3314" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C3314" s="1">
-        <x:v>478900</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3314" s="1">
         <x:v>0</x:v>
@@ -86825,10 +86825,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3314" s="1">
-        <x:v>94250</x:v>
+        <x:v>18200</x:v>
       </x:c>
       <x:c r="G3314" s="1">
-        <x:v>573150</x:v>
+        <x:v>18200</x:v>
       </x:c>
     </x:row>
     <x:row r="3315" spans="1:7">
@@ -86905,10 +86905,10 @@
         <x:v>3302</x:v>
       </x:c>
       <x:c r="B3318" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C3318" s="1">
-        <x:v>19500</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="D3318" s="1">
         <x:v>0</x:v>
@@ -86917,10 +86917,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3318" s="1">
-        <x:v>8650</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3318" s="1">
-        <x:v>28150</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="3319" spans="1:7">
@@ -86928,10 +86928,10 @@
         <x:v>3302</x:v>
       </x:c>
       <x:c r="B3319" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C3319" s="1">
-        <x:v>500</x:v>
+        <x:v>19500</x:v>
       </x:c>
       <x:c r="D3319" s="1">
         <x:v>0</x:v>
@@ -86940,10 +86940,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3319" s="1">
-        <x:v>0</x:v>
+        <x:v>8650</x:v>
       </x:c>
       <x:c r="G3319" s="1">
-        <x:v>500</x:v>
+        <x:v>28150</x:v>
       </x:c>
     </x:row>
     <x:row r="3320" spans="1:7">
@@ -87250,10 +87250,10 @@
         <x:v>3316</x:v>
       </x:c>
       <x:c r="B3333" s="1" t="s">
-        <x:v>410</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C3333" s="1">
-        <x:v>429650</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D3333" s="1">
         <x:v>0</x:v>
@@ -87262,10 +87262,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3333" s="1">
-        <x:v>347550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3333" s="1">
-        <x:v>777200</x:v>
+        <x:v>3000</x:v>
       </x:c>
     </x:row>
     <x:row r="3334" spans="1:7">
@@ -87273,10 +87273,10 @@
         <x:v>3316</x:v>
       </x:c>
       <x:c r="B3334" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="C3334" s="1">
-        <x:v>22500</x:v>
+        <x:v>429650</x:v>
       </x:c>
       <x:c r="D3334" s="1">
         <x:v>0</x:v>
@@ -87285,10 +87285,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3334" s="1">
-        <x:v>0</x:v>
+        <x:v>347550</x:v>
       </x:c>
       <x:c r="G3334" s="1">
-        <x:v>22500</x:v>
+        <x:v>777200</x:v>
       </x:c>
     </x:row>
     <x:row r="3335" spans="1:7">
@@ -87296,10 +87296,10 @@
         <x:v>3316</x:v>
       </x:c>
       <x:c r="B3335" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="C3335" s="1">
-        <x:v>3000</x:v>
+        <x:v>22500</x:v>
       </x:c>
       <x:c r="D3335" s="1">
         <x:v>0</x:v>
@@ -87311,7 +87311,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G3335" s="1">
-        <x:v>3000</x:v>
+        <x:v>22500</x:v>
       </x:c>
     </x:row>
     <x:row r="3336" spans="1:7">

--- a/reports/pro-oil/pro-oil-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-oil/pro-oil-candidate-lobby-lifetime-report.xlsx
@@ -15674,7 +15674,7 @@
         <x:v>275</x:v>
       </x:c>
       <x:c r="B221" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C221" s="1">
         <x:v>0</x:v>
@@ -15686,10 +15686,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F221" s="1">
-        <x:v>1000</x:v>
+        <x:v>2300</x:v>
       </x:c>
       <x:c r="G221" s="1">
-        <x:v>1000</x:v>
+        <x:v>2300</x:v>
       </x:c>
     </x:row>
     <x:row r="222" spans="1:7">
@@ -15697,7 +15697,7 @@
         <x:v>275</x:v>
       </x:c>
       <x:c r="B222" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C222" s="1">
         <x:v>0</x:v>
@@ -15709,10 +15709,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F222" s="1">
-        <x:v>2300</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G222" s="1">
-        <x:v>2300</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="223" spans="1:7">
@@ -18710,10 +18710,10 @@
         <x:v>407</x:v>
       </x:c>
       <x:c r="B353" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="C353" s="1">
-        <x:v>163000</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D353" s="1">
         <x:v>0</x:v>
@@ -18722,10 +18722,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F353" s="1">
-        <x:v>82550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G353" s="1">
-        <x:v>245550</x:v>
+        <x:v>15000</x:v>
       </x:c>
     </x:row>
     <x:row r="354" spans="1:7">
@@ -18733,10 +18733,10 @@
         <x:v>407</x:v>
       </x:c>
       <x:c r="B354" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C354" s="1">
-        <x:v>15000</x:v>
+        <x:v>163000</x:v>
       </x:c>
       <x:c r="D354" s="1">
         <x:v>0</x:v>
@@ -18745,10 +18745,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F354" s="1">
-        <x:v>0</x:v>
+        <x:v>82550</x:v>
       </x:c>
       <x:c r="G354" s="1">
-        <x:v>15000</x:v>
+        <x:v>245550</x:v>
       </x:c>
     </x:row>
     <x:row r="355" spans="1:7">
@@ -18825,10 +18825,10 @@
         <x:v>412</x:v>
       </x:c>
       <x:c r="B358" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C358" s="1">
-        <x:v>107540</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D358" s="1">
         <x:v>0</x:v>
@@ -18837,10 +18837,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F358" s="1">
-        <x:v>59170</x:v>
+        <x:v>25150</x:v>
       </x:c>
       <x:c r="G358" s="1">
-        <x:v>166710</x:v>
+        <x:v>28150</x:v>
       </x:c>
     </x:row>
     <x:row r="359" spans="1:7">
@@ -18848,10 +18848,10 @@
         <x:v>412</x:v>
       </x:c>
       <x:c r="B359" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C359" s="1">
-        <x:v>3000</x:v>
+        <x:v>107540</x:v>
       </x:c>
       <x:c r="D359" s="1">
         <x:v>0</x:v>
@@ -18860,10 +18860,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F359" s="1">
-        <x:v>25150</x:v>
+        <x:v>59170</x:v>
       </x:c>
       <x:c r="G359" s="1">
-        <x:v>28150</x:v>
+        <x:v>166710</x:v>
       </x:c>
     </x:row>
     <x:row r="360" spans="1:7">
@@ -26346,10 +26346,10 @@
         <x:v>737</x:v>
       </x:c>
       <x:c r="B685" s="1" t="s">
-        <x:v>727</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C685" s="1">
-        <x:v>370033</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D685" s="1">
         <x:v>0</x:v>
@@ -26358,10 +26358,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F685" s="1">
-        <x:v>45850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G685" s="1">
-        <x:v>415883</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="686" spans="1:7">
@@ -26369,10 +26369,10 @@
         <x:v>737</x:v>
       </x:c>
       <x:c r="B686" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>727</x:v>
       </x:c>
       <x:c r="C686" s="1">
-        <x:v>25500</x:v>
+        <x:v>370033</x:v>
       </x:c>
       <x:c r="D686" s="1">
         <x:v>0</x:v>
@@ -26381,10 +26381,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F686" s="1">
-        <x:v>0</x:v>
+        <x:v>45850</x:v>
       </x:c>
       <x:c r="G686" s="1">
-        <x:v>25500</x:v>
+        <x:v>415883</x:v>
       </x:c>
     </x:row>
     <x:row r="687" spans="1:7">
@@ -29796,10 +29796,10 @@
         <x:v>885</x:v>
       </x:c>
       <x:c r="B835" s="1" t="s">
-        <x:v>256</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C835" s="1">
-        <x:v>3000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D835" s="1">
         <x:v>0</x:v>
@@ -29808,10 +29808,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F835" s="1">
-        <x:v>5950</x:v>
+        <x:v>14450</x:v>
       </x:c>
       <x:c r="G835" s="1">
-        <x:v>8950</x:v>
+        <x:v>14450</x:v>
       </x:c>
     </x:row>
     <x:row r="836" spans="1:7">
@@ -29819,10 +29819,10 @@
         <x:v>885</x:v>
       </x:c>
       <x:c r="B836" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="C836" s="1">
-        <x:v>0</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D836" s="1">
         <x:v>0</x:v>
@@ -29831,10 +29831,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F836" s="1">
-        <x:v>14450</x:v>
+        <x:v>5950</x:v>
       </x:c>
       <x:c r="G836" s="1">
-        <x:v>14450</x:v>
+        <x:v>8950</x:v>
       </x:c>
     </x:row>
     <x:row r="837" spans="1:7">
@@ -36190,10 +36190,10 @@
         <x:v>1158</x:v>
       </x:c>
       <x:c r="B1113" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C1113" s="1">
-        <x:v>752389</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1113" s="1">
         <x:v>0</x:v>
@@ -36202,10 +36202,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1113" s="1">
-        <x:v>418794</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="G1113" s="1">
-        <x:v>1171183</x:v>
+        <x:v>10000</x:v>
       </x:c>
     </x:row>
     <x:row r="1114" spans="1:7">
@@ -36213,10 +36213,10 @@
         <x:v>1158</x:v>
       </x:c>
       <x:c r="B1114" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1114" s="1">
-        <x:v>0</x:v>
+        <x:v>752389</x:v>
       </x:c>
       <x:c r="D1114" s="1">
         <x:v>0</x:v>
@@ -36225,10 +36225,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1114" s="1">
-        <x:v>10000</x:v>
+        <x:v>418794</x:v>
       </x:c>
       <x:c r="G1114" s="1">
-        <x:v>10000</x:v>
+        <x:v>1171183</x:v>
       </x:c>
     </x:row>
     <x:row r="1115" spans="1:7">
@@ -44608,10 +44608,10 @@
         <x:v>1519</x:v>
       </x:c>
       <x:c r="B1479" s="1" t="s">
-        <x:v>161</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C1479" s="1">
-        <x:v>82250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1479" s="1">
         <x:v>0</x:v>
@@ -44620,10 +44620,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1479" s="1">
-        <x:v>9000</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1479" s="1">
-        <x:v>91250</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="1480" spans="1:7">
@@ -44631,10 +44631,10 @@
         <x:v>1519</x:v>
       </x:c>
       <x:c r="B1480" s="1" t="s">
-        <x:v>165</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C1480" s="1">
-        <x:v>0</x:v>
+        <x:v>82250</x:v>
       </x:c>
       <x:c r="D1480" s="1">
         <x:v>0</x:v>
@@ -44643,10 +44643,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1480" s="1">
-        <x:v>1000</x:v>
+        <x:v>9000</x:v>
       </x:c>
       <x:c r="G1480" s="1">
-        <x:v>1000</x:v>
+        <x:v>91250</x:v>
       </x:c>
     </x:row>
     <x:row r="1481" spans="1:7">
@@ -45252,10 +45252,10 @@
         <x:v>1544</x:v>
       </x:c>
       <x:c r="B1507" s="1" t="s">
-        <x:v>410</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C1507" s="1">
-        <x:v>146700</x:v>
+        <x:v>8000</x:v>
       </x:c>
       <x:c r="D1507" s="1">
         <x:v>0</x:v>
@@ -45264,10 +45264,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1507" s="1">
-        <x:v>157050</x:v>
+        <x:v>66000</x:v>
       </x:c>
       <x:c r="G1507" s="1">
-        <x:v>303750</x:v>
+        <x:v>74000</x:v>
       </x:c>
     </x:row>
     <x:row r="1508" spans="1:7">
@@ -45275,10 +45275,10 @@
         <x:v>1544</x:v>
       </x:c>
       <x:c r="B1508" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="C1508" s="1">
-        <x:v>8000</x:v>
+        <x:v>146700</x:v>
       </x:c>
       <x:c r="D1508" s="1">
         <x:v>0</x:v>
@@ -45287,10 +45287,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1508" s="1">
-        <x:v>66000</x:v>
+        <x:v>157050</x:v>
       </x:c>
       <x:c r="G1508" s="1">
-        <x:v>74000</x:v>
+        <x:v>303750</x:v>
       </x:c>
     </x:row>
     <x:row r="1509" spans="1:7">
@@ -47897,10 +47897,10 @@
         <x:v>1657</x:v>
       </x:c>
       <x:c r="B1622" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C1622" s="1">
-        <x:v>0</x:v>
+        <x:v>27850</x:v>
       </x:c>
       <x:c r="D1622" s="1">
         <x:v>0</x:v>
@@ -47909,10 +47909,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1622" s="1">
-        <x:v>102225</x:v>
+        <x:v>19000</x:v>
       </x:c>
       <x:c r="G1622" s="1">
-        <x:v>102225</x:v>
+        <x:v>46850</x:v>
       </x:c>
     </x:row>
     <x:row r="1623" spans="1:7">
@@ -47920,10 +47920,10 @@
         <x:v>1657</x:v>
       </x:c>
       <x:c r="B1623" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C1623" s="1">
-        <x:v>27850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1623" s="1">
         <x:v>0</x:v>
@@ -47932,10 +47932,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1623" s="1">
-        <x:v>19000</x:v>
+        <x:v>102225</x:v>
       </x:c>
       <x:c r="G1623" s="1">
-        <x:v>46850</x:v>
+        <x:v>102225</x:v>
       </x:c>
     </x:row>
     <x:row r="1624" spans="1:7">
@@ -48909,7 +48909,7 @@
         <x:v>1699</x:v>
       </x:c>
       <x:c r="B1666" s="1" t="s">
-        <x:v>161</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C1666" s="1">
         <x:v>0</x:v>
@@ -48921,10 +48921,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1666" s="1">
-        <x:v>1000</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="G1666" s="1">
-        <x:v>1000</x:v>
+        <x:v>3000</x:v>
       </x:c>
     </x:row>
     <x:row r="1667" spans="1:7">
@@ -48932,7 +48932,7 @@
         <x:v>1699</x:v>
       </x:c>
       <x:c r="B1667" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C1667" s="1">
         <x:v>0</x:v>
@@ -48944,10 +48944,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1667" s="1">
-        <x:v>3000</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1667" s="1">
-        <x:v>3000</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="1668" spans="1:7">
@@ -57534,10 +57534,10 @@
         <x:v>2066</x:v>
       </x:c>
       <x:c r="B2041" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C2041" s="1">
-        <x:v>11000</x:v>
+        <x:v>960100</x:v>
       </x:c>
       <x:c r="D2041" s="1">
         <x:v>0</x:v>
@@ -57546,10 +57546,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2041" s="1">
-        <x:v>25550</x:v>
+        <x:v>882230</x:v>
       </x:c>
       <x:c r="G2041" s="1">
-        <x:v>36550</x:v>
+        <x:v>1842330</x:v>
       </x:c>
     </x:row>
     <x:row r="2042" spans="1:7">
@@ -57557,10 +57557,10 @@
         <x:v>2066</x:v>
       </x:c>
       <x:c r="B2042" s="1" t="s">
-        <x:v>188</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C2042" s="1">
-        <x:v>960100</x:v>
+        <x:v>11000</x:v>
       </x:c>
       <x:c r="D2042" s="1">
         <x:v>0</x:v>
@@ -57569,10 +57569,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2042" s="1">
-        <x:v>882230</x:v>
+        <x:v>25550</x:v>
       </x:c>
       <x:c r="G2042" s="1">
-        <x:v>1842330</x:v>
+        <x:v>36550</x:v>
       </x:c>
     </x:row>
     <x:row r="2043" spans="1:7">
@@ -69655,10 +69655,10 @@
         <x:v>2587</x:v>
       </x:c>
       <x:c r="B2568" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C2568" s="1">
-        <x:v>7000</x:v>
+        <x:v>139000</x:v>
       </x:c>
       <x:c r="D2568" s="1">
         <x:v>0</x:v>
@@ -69667,10 +69667,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2568" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G2568" s="1">
-        <x:v>7000</x:v>
+        <x:v>139500</x:v>
       </x:c>
     </x:row>
     <x:row r="2569" spans="1:7">
@@ -69678,10 +69678,10 @@
         <x:v>2587</x:v>
       </x:c>
       <x:c r="B2569" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="C2569" s="1">
-        <x:v>139000</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D2569" s="1">
         <x:v>0</x:v>
@@ -69690,10 +69690,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2569" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2569" s="1">
-        <x:v>139500</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="2570" spans="1:7">
@@ -72461,10 +72461,10 @@
         <x:v>2706</x:v>
       </x:c>
       <x:c r="B2690" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C2690" s="1">
-        <x:v>163800</x:v>
+        <x:v>206766</x:v>
       </x:c>
       <x:c r="D2690" s="1">
         <x:v>0</x:v>
@@ -72473,10 +72473,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2690" s="1">
-        <x:v>276645</x:v>
+        <x:v>286825</x:v>
       </x:c>
       <x:c r="G2690" s="1">
-        <x:v>440445</x:v>
+        <x:v>493591</x:v>
       </x:c>
     </x:row>
     <x:row r="2691" spans="1:7">
@@ -72484,10 +72484,10 @@
         <x:v>2706</x:v>
       </x:c>
       <x:c r="B2691" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C2691" s="1">
-        <x:v>206766</x:v>
+        <x:v>163800</x:v>
       </x:c>
       <x:c r="D2691" s="1">
         <x:v>0</x:v>
@@ -72496,10 +72496,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2691" s="1">
-        <x:v>286825</x:v>
+        <x:v>276645</x:v>
       </x:c>
       <x:c r="G2691" s="1">
-        <x:v>493591</x:v>
+        <x:v>440445</x:v>
       </x:c>
     </x:row>
     <x:row r="2692" spans="1:7">
@@ -73979,10 +73979,10 @@
         <x:v>2770</x:v>
       </x:c>
       <x:c r="B2756" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C2756" s="1">
-        <x:v>15000</x:v>
+        <x:v>102350</x:v>
       </x:c>
       <x:c r="D2756" s="1">
         <x:v>0</x:v>
@@ -73991,10 +73991,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2756" s="1">
-        <x:v>5000</x:v>
+        <x:v>106550</x:v>
       </x:c>
       <x:c r="G2756" s="1">
-        <x:v>20000</x:v>
+        <x:v>208900</x:v>
       </x:c>
     </x:row>
     <x:row r="2757" spans="1:7">
@@ -74002,10 +74002,10 @@
         <x:v>2770</x:v>
       </x:c>
       <x:c r="B2757" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C2757" s="1">
-        <x:v>102350</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D2757" s="1">
         <x:v>0</x:v>
@@ -74014,10 +74014,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2757" s="1">
-        <x:v>106550</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G2757" s="1">
-        <x:v>208900</x:v>
+        <x:v>20000</x:v>
       </x:c>
     </x:row>
     <x:row r="2758" spans="1:7">
@@ -75704,10 +75704,10 @@
         <x:v>2843</x:v>
       </x:c>
       <x:c r="B2831" s="1" t="s">
-        <x:v>165</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C2831" s="1">
-        <x:v>12000</x:v>
+        <x:v>99950</x:v>
       </x:c>
       <x:c r="D2831" s="1">
         <x:v>0</x:v>
@@ -75716,10 +75716,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2831" s="1">
-        <x:v>0</x:v>
+        <x:v>6650</x:v>
       </x:c>
       <x:c r="G2831" s="1">
-        <x:v>12000</x:v>
+        <x:v>106600</x:v>
       </x:c>
     </x:row>
     <x:row r="2832" spans="1:7">
@@ -75727,10 +75727,10 @@
         <x:v>2843</x:v>
       </x:c>
       <x:c r="B2832" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C2832" s="1">
-        <x:v>99950</x:v>
+        <x:v>12000</x:v>
       </x:c>
       <x:c r="D2832" s="1">
         <x:v>0</x:v>
@@ -75739,10 +75739,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2832" s="1">
-        <x:v>6650</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2832" s="1">
-        <x:v>106600</x:v>
+        <x:v>12000</x:v>
       </x:c>
     </x:row>
     <x:row r="2833" spans="1:7">
@@ -76371,10 +76371,10 @@
         <x:v>2871</x:v>
       </x:c>
       <x:c r="B2860" s="1" t="s">
-        <x:v>727</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C2860" s="1">
-        <x:v>284300</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D2860" s="1">
         <x:v>0</x:v>
@@ -76383,10 +76383,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2860" s="1">
-        <x:v>71650</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2860" s="1">
-        <x:v>355950</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="2861" spans="1:7">
@@ -76394,10 +76394,10 @@
         <x:v>2871</x:v>
       </x:c>
       <x:c r="B2861" s="1" t="s">
-        <x:v>165</x:v>
+        <x:v>727</x:v>
       </x:c>
       <x:c r="C2861" s="1">
-        <x:v>5000</x:v>
+        <x:v>284300</x:v>
       </x:c>
       <x:c r="D2861" s="1">
         <x:v>0</x:v>
@@ -76406,10 +76406,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2861" s="1">
-        <x:v>0</x:v>
+        <x:v>71650</x:v>
       </x:c>
       <x:c r="G2861" s="1">
-        <x:v>5000</x:v>
+        <x:v>355950</x:v>
       </x:c>
     </x:row>
     <x:row r="2862" spans="1:7">
@@ -78119,10 +78119,10 @@
         <x:v>2946</x:v>
       </x:c>
       <x:c r="B2936" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="C2936" s="1">
-        <x:v>71750</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D2936" s="1">
         <x:v>0</x:v>
@@ -78131,10 +78131,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2936" s="1">
-        <x:v>77150</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2936" s="1">
-        <x:v>148900</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="2937" spans="1:7">
@@ -78142,10 +78142,10 @@
         <x:v>2946</x:v>
       </x:c>
       <x:c r="B2937" s="1" t="s">
-        <x:v>254</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C2937" s="1">
-        <x:v>7000</x:v>
+        <x:v>71750</x:v>
       </x:c>
       <x:c r="D2937" s="1">
         <x:v>0</x:v>
@@ -78154,10 +78154,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2937" s="1">
-        <x:v>0</x:v>
+        <x:v>77150</x:v>
       </x:c>
       <x:c r="G2937" s="1">
-        <x:v>7000</x:v>
+        <x:v>148900</x:v>
       </x:c>
     </x:row>
     <x:row r="2938" spans="1:7">
@@ -80074,7 +80074,7 @@
         <x:v>3023</x:v>
       </x:c>
       <x:c r="B3021" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C3021" s="1">
         <x:v>0</x:v>
@@ -80086,10 +80086,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3021" s="1">
-        <x:v>24200</x:v>
+        <x:v>1100</x:v>
       </x:c>
       <x:c r="G3021" s="1">
-        <x:v>24200</x:v>
+        <x:v>1100</x:v>
       </x:c>
     </x:row>
     <x:row r="3022" spans="1:7">
@@ -80097,7 +80097,7 @@
         <x:v>3023</x:v>
       </x:c>
       <x:c r="B3022" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="C3022" s="1">
         <x:v>0</x:v>
@@ -80109,10 +80109,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3022" s="1">
-        <x:v>1100</x:v>
+        <x:v>24200</x:v>
       </x:c>
       <x:c r="G3022" s="1">
-        <x:v>1100</x:v>
+        <x:v>24200</x:v>
       </x:c>
     </x:row>
     <x:row r="3023" spans="1:7">
@@ -82328,10 +82328,10 @@
         <x:v>3115</x:v>
       </x:c>
       <x:c r="B3119" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C3119" s="1">
-        <x:v>34000</x:v>
+        <x:v>292600</x:v>
       </x:c>
       <x:c r="D3119" s="1">
         <x:v>0</x:v>
@@ -82340,10 +82340,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3119" s="1">
-        <x:v>0</x:v>
+        <x:v>222972</x:v>
       </x:c>
       <x:c r="G3119" s="1">
-        <x:v>34000</x:v>
+        <x:v>515572</x:v>
       </x:c>
     </x:row>
     <x:row r="3120" spans="1:7">
@@ -82351,10 +82351,10 @@
         <x:v>3115</x:v>
       </x:c>
       <x:c r="B3120" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="C3120" s="1">
-        <x:v>292600</x:v>
+        <x:v>34000</x:v>
       </x:c>
       <x:c r="D3120" s="1">
         <x:v>0</x:v>
@@ -82363,10 +82363,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3120" s="1">
-        <x:v>222972</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3120" s="1">
-        <x:v>515572</x:v>
+        <x:v>34000</x:v>
       </x:c>
     </x:row>
     <x:row r="3121" spans="1:7">
@@ -82512,10 +82512,10 @@
         <x:v>3122</x:v>
       </x:c>
       <x:c r="B3127" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C3127" s="1">
-        <x:v>0</x:v>
+        <x:v>29500</x:v>
       </x:c>
       <x:c r="D3127" s="1">
         <x:v>0</x:v>
@@ -82524,10 +82524,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3127" s="1">
-        <x:v>1000</x:v>
+        <x:v>12550</x:v>
       </x:c>
       <x:c r="G3127" s="1">
-        <x:v>1000</x:v>
+        <x:v>42050</x:v>
       </x:c>
     </x:row>
     <x:row r="3128" spans="1:7">
@@ -82535,10 +82535,10 @@
         <x:v>3122</x:v>
       </x:c>
       <x:c r="B3128" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C3128" s="1">
-        <x:v>29500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3128" s="1">
         <x:v>0</x:v>
@@ -82547,10 +82547,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3128" s="1">
-        <x:v>12550</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G3128" s="1">
-        <x:v>42050</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="3129" spans="1:7">
@@ -82719,10 +82719,10 @@
         <x:v>3130</x:v>
       </x:c>
       <x:c r="B3136" s="1" t="s">
-        <x:v>165</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C3136" s="1">
-        <x:v>25500</x:v>
+        <x:v>420650</x:v>
       </x:c>
       <x:c r="D3136" s="1">
         <x:v>0</x:v>
@@ -82731,10 +82731,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3136" s="1">
-        <x:v>0</x:v>
+        <x:v>448381</x:v>
       </x:c>
       <x:c r="G3136" s="1">
-        <x:v>25500</x:v>
+        <x:v>869031</x:v>
       </x:c>
     </x:row>
     <x:row r="3137" spans="1:7">
@@ -82742,10 +82742,10 @@
         <x:v>3130</x:v>
       </x:c>
       <x:c r="B3137" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C3137" s="1">
-        <x:v>420650</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D3137" s="1">
         <x:v>0</x:v>
@@ -82754,10 +82754,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3137" s="1">
-        <x:v>448381</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3137" s="1">
-        <x:v>869031</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="3138" spans="1:7">
@@ -84444,10 +84444,10 @@
         <x:v>3204</x:v>
       </x:c>
       <x:c r="B3211" s="1" t="s">
-        <x:v>254</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C3211" s="1">
-        <x:v>15000</x:v>
+        <x:v>332220</x:v>
       </x:c>
       <x:c r="D3211" s="1">
         <x:v>0</x:v>
@@ -84456,10 +84456,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3211" s="1">
-        <x:v>0</x:v>
+        <x:v>299023</x:v>
       </x:c>
       <x:c r="G3211" s="1">
-        <x:v>15000</x:v>
+        <x:v>631243</x:v>
       </x:c>
     </x:row>
     <x:row r="3212" spans="1:7">
@@ -84467,10 +84467,10 @@
         <x:v>3204</x:v>
       </x:c>
       <x:c r="B3212" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="C3212" s="1">
-        <x:v>332220</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D3212" s="1">
         <x:v>0</x:v>
@@ -84479,10 +84479,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3212" s="1">
-        <x:v>299023</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3212" s="1">
-        <x:v>631243</x:v>
+        <x:v>15000</x:v>
       </x:c>
     </x:row>
     <x:row r="3213" spans="1:7">
@@ -87250,10 +87250,10 @@
         <x:v>3316</x:v>
       </x:c>
       <x:c r="B3333" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="C3333" s="1">
-        <x:v>3000</x:v>
+        <x:v>429650</x:v>
       </x:c>
       <x:c r="D3333" s="1">
         <x:v>0</x:v>
@@ -87262,10 +87262,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3333" s="1">
-        <x:v>0</x:v>
+        <x:v>347550</x:v>
       </x:c>
       <x:c r="G3333" s="1">
-        <x:v>3000</x:v>
+        <x:v>777200</x:v>
       </x:c>
     </x:row>
     <x:row r="3334" spans="1:7">
@@ -87273,10 +87273,10 @@
         <x:v>3316</x:v>
       </x:c>
       <x:c r="B3334" s="1" t="s">
-        <x:v>410</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="C3334" s="1">
-        <x:v>429650</x:v>
+        <x:v>22500</x:v>
       </x:c>
       <x:c r="D3334" s="1">
         <x:v>0</x:v>
@@ -87285,10 +87285,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3334" s="1">
-        <x:v>347550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3334" s="1">
-        <x:v>777200</x:v>
+        <x:v>22500</x:v>
       </x:c>
     </x:row>
     <x:row r="3335" spans="1:7">
@@ -87296,10 +87296,10 @@
         <x:v>3316</x:v>
       </x:c>
       <x:c r="B3335" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C3335" s="1">
-        <x:v>22500</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D3335" s="1">
         <x:v>0</x:v>
@@ -87311,7 +87311,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G3335" s="1">
-        <x:v>22500</x:v>
+        <x:v>3000</x:v>
       </x:c>
     </x:row>
     <x:row r="3336" spans="1:7">
@@ -87917,10 +87917,10 @@
         <x:v>3343</x:v>
       </x:c>
       <x:c r="B3362" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C3362" s="1">
-        <x:v>0</x:v>
+        <x:v>119000</x:v>
       </x:c>
       <x:c r="D3362" s="1">
         <x:v>0</x:v>
@@ -87929,10 +87929,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3362" s="1">
-        <x:v>35750</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3362" s="1">
-        <x:v>35750</x:v>
+        <x:v>119000</x:v>
       </x:c>
     </x:row>
     <x:row r="3363" spans="1:7">
@@ -87940,10 +87940,10 @@
         <x:v>3343</x:v>
       </x:c>
       <x:c r="B3363" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C3363" s="1">
-        <x:v>119000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3363" s="1">
         <x:v>0</x:v>
@@ -87952,10 +87952,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3363" s="1">
-        <x:v>0</x:v>
+        <x:v>35750</x:v>
       </x:c>
       <x:c r="G3363" s="1">
-        <x:v>119000</x:v>
+        <x:v>35750</x:v>
       </x:c>
     </x:row>
     <x:row r="3364" spans="1:7">

--- a/reports/pro-oil/pro-oil-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-oil/pro-oil-candidate-lobby-lifetime-report.xlsx
@@ -19452,10 +19452,10 @@
         <x:v>421</x:v>
       </x:c>
       <x:c r="B367" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C367" s="1">
-        <x:v>107540</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D367" s="1">
         <x:v>0</x:v>
@@ -19464,10 +19464,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F367" s="1">
-        <x:v>59170</x:v>
+        <x:v>25150</x:v>
       </x:c>
       <x:c r="G367" s="1">
-        <x:v>166710</x:v>
+        <x:v>28150</x:v>
       </x:c>
     </x:row>
     <x:row r="368" spans="1:7">
@@ -19475,10 +19475,10 @@
         <x:v>421</x:v>
       </x:c>
       <x:c r="B368" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C368" s="1">
-        <x:v>3000</x:v>
+        <x:v>107540</x:v>
       </x:c>
       <x:c r="D368" s="1">
         <x:v>0</x:v>
@@ -19487,10 +19487,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F368" s="1">
-        <x:v>25150</x:v>
+        <x:v>59170</x:v>
       </x:c>
       <x:c r="G368" s="1">
-        <x:v>28150</x:v>
+        <x:v>166710</x:v>
       </x:c>
     </x:row>
     <x:row r="369" spans="1:7">
@@ -21108,11 +21108,11 @@
         <x:v>491</x:v>
       </x:c>
       <x:c r="B439" s="1" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C439" s="1">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="C439" s="1">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="D439" s="1">
         <x:v>0</x:v>
       </x:c>
@@ -21120,10 +21120,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F439" s="1">
-        <x:v>40350</x:v>
+        <x:v>13450</x:v>
       </x:c>
       <x:c r="G439" s="1">
-        <x:v>40350</x:v>
+        <x:v>13500</x:v>
       </x:c>
     </x:row>
     <x:row r="440" spans="1:7">
@@ -21131,10 +21131,10 @@
         <x:v>491</x:v>
       </x:c>
       <x:c r="B440" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C440" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D440" s="1">
         <x:v>0</x:v>
@@ -21143,10 +21143,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F440" s="1">
-        <x:v>13450</x:v>
+        <x:v>40350</x:v>
       </x:c>
       <x:c r="G440" s="1">
-        <x:v>13500</x:v>
+        <x:v>40350</x:v>
       </x:c>
     </x:row>
     <x:row r="441" spans="1:7">
@@ -30883,10 +30883,10 @@
         <x:v>914</x:v>
       </x:c>
       <x:c r="B864" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="C864" s="1">
-        <x:v>0</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D864" s="1">
         <x:v>0</x:v>
@@ -30895,10 +30895,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F864" s="1">
-        <x:v>14450</x:v>
+        <x:v>12950</x:v>
       </x:c>
       <x:c r="G864" s="1">
-        <x:v>14450</x:v>
+        <x:v>15950</x:v>
       </x:c>
     </x:row>
     <x:row r="865" spans="1:7">
@@ -30906,10 +30906,10 @@
         <x:v>914</x:v>
       </x:c>
       <x:c r="B865" s="1" t="s">
-        <x:v>260</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C865" s="1">
-        <x:v>3000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D865" s="1">
         <x:v>0</x:v>
@@ -30918,10 +30918,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F865" s="1">
-        <x:v>12950</x:v>
+        <x:v>14450</x:v>
       </x:c>
       <x:c r="G865" s="1">
-        <x:v>15950</x:v>
+        <x:v>14450</x:v>
       </x:c>
     </x:row>
     <x:row r="866" spans="1:7">
@@ -37714,10 +37714,10 @@
         <x:v>1205</x:v>
       </x:c>
       <x:c r="B1161" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1161" s="1">
-        <x:v>0</x:v>
+        <x:v>752389</x:v>
       </x:c>
       <x:c r="D1161" s="1">
         <x:v>0</x:v>
@@ -37726,10 +37726,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1161" s="1">
-        <x:v>10000</x:v>
+        <x:v>418794</x:v>
       </x:c>
       <x:c r="G1161" s="1">
-        <x:v>10000</x:v>
+        <x:v>1171183</x:v>
       </x:c>
     </x:row>
     <x:row r="1162" spans="1:7">
@@ -37737,10 +37737,10 @@
         <x:v>1205</x:v>
       </x:c>
       <x:c r="B1162" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C1162" s="1">
-        <x:v>752389</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1162" s="1">
         <x:v>0</x:v>
@@ -37749,10 +37749,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1162" s="1">
-        <x:v>418794</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="G1162" s="1">
-        <x:v>1171183</x:v>
+        <x:v>10000</x:v>
       </x:c>
     </x:row>
     <x:row r="1163" spans="1:7">
@@ -46546,10 +46546,10 @@
         <x:v>1584</x:v>
       </x:c>
       <x:c r="B1545" s="1" t="s">
-        <x:v>165</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C1545" s="1">
-        <x:v>82250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1545" s="1">
         <x:v>0</x:v>
@@ -46558,10 +46558,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1545" s="1">
-        <x:v>9000</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1545" s="1">
-        <x:v>91250</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="1546" spans="1:7">
@@ -46569,10 +46569,10 @@
         <x:v>1584</x:v>
       </x:c>
       <x:c r="B1546" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C1546" s="1">
-        <x:v>0</x:v>
+        <x:v>82250</x:v>
       </x:c>
       <x:c r="D1546" s="1">
         <x:v>0</x:v>
@@ -46581,10 +46581,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1546" s="1">
-        <x:v>1000</x:v>
+        <x:v>9000</x:v>
       </x:c>
       <x:c r="G1546" s="1">
-        <x:v>1000</x:v>
+        <x:v>91250</x:v>
       </x:c>
     </x:row>
     <x:row r="1547" spans="1:7">
@@ -47236,10 +47236,10 @@
         <x:v>1611</x:v>
       </x:c>
       <x:c r="B1575" s="1" t="s">
-        <x:v>419</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C1575" s="1">
-        <x:v>181700</x:v>
+        <x:v>8000</x:v>
       </x:c>
       <x:c r="D1575" s="1">
         <x:v>0</x:v>
@@ -47248,10 +47248,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1575" s="1">
-        <x:v>168050</x:v>
+        <x:v>66000</x:v>
       </x:c>
       <x:c r="G1575" s="1">
-        <x:v>349750</x:v>
+        <x:v>74000</x:v>
       </x:c>
     </x:row>
     <x:row r="1576" spans="1:7">
@@ -47259,10 +47259,10 @@
         <x:v>1611</x:v>
       </x:c>
       <x:c r="B1576" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="C1576" s="1">
-        <x:v>8000</x:v>
+        <x:v>181700</x:v>
       </x:c>
       <x:c r="D1576" s="1">
         <x:v>0</x:v>
@@ -47271,10 +47271,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1576" s="1">
-        <x:v>66000</x:v>
+        <x:v>168050</x:v>
       </x:c>
       <x:c r="G1576" s="1">
-        <x:v>74000</x:v>
+        <x:v>349750</x:v>
       </x:c>
     </x:row>
     <x:row r="1577" spans="1:7">
@@ -53009,10 +53009,10 @@
         <x:v>1856</x:v>
       </x:c>
       <x:c r="B1826" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C1826" s="1">
-        <x:v>-1000</x:v>
+        <x:v>147100</x:v>
       </x:c>
       <x:c r="D1826" s="1">
         <x:v>0</x:v>
@@ -53021,10 +53021,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1826" s="1">
-        <x:v>0</x:v>
+        <x:v>34550</x:v>
       </x:c>
       <x:c r="G1826" s="1">
-        <x:v>-1000</x:v>
+        <x:v>181650</x:v>
       </x:c>
     </x:row>
     <x:row r="1827" spans="1:7">
@@ -53032,10 +53032,10 @@
         <x:v>1856</x:v>
       </x:c>
       <x:c r="B1827" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C1827" s="1">
-        <x:v>147100</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="D1827" s="1">
         <x:v>0</x:v>
@@ -53044,10 +53044,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1827" s="1">
-        <x:v>34550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1827" s="1">
-        <x:v>181650</x:v>
+        <x:v>-1000</x:v>
       </x:c>
     </x:row>
     <x:row r="1828" spans="1:7">
@@ -56459,10 +56459,10 @@
         <x:v>2002</x:v>
       </x:c>
       <x:c r="B1976" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C1976" s="1">
-        <x:v>0</x:v>
+        <x:v>187150</x:v>
       </x:c>
       <x:c r="D1976" s="1">
         <x:v>31</x:v>
@@ -56471,10 +56471,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1976" s="1">
-        <x:v>0</x:v>
+        <x:v>6150</x:v>
       </x:c>
       <x:c r="G1976" s="1">
-        <x:v>31</x:v>
+        <x:v>193331</x:v>
       </x:c>
     </x:row>
     <x:row r="1977" spans="1:7">
@@ -56482,10 +56482,10 @@
         <x:v>2002</x:v>
       </x:c>
       <x:c r="B1977" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1977" s="1">
-        <x:v>187150</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1977" s="1">
         <x:v>31</x:v>
@@ -56494,10 +56494,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1977" s="1">
-        <x:v>6150</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1977" s="1">
-        <x:v>193331</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="1978" spans="1:7">
@@ -66993,10 +66993,10 @@
         <x:v>2455</x:v>
       </x:c>
       <x:c r="B2434" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C2434" s="1">
-        <x:v>0</x:v>
+        <x:v>4500</x:v>
       </x:c>
       <x:c r="D2434" s="1">
         <x:v>0</x:v>
@@ -67005,10 +67005,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2434" s="1">
-        <x:v>9005</x:v>
+        <x:v>54385</x:v>
       </x:c>
       <x:c r="G2434" s="1">
-        <x:v>9005</x:v>
+        <x:v>58885</x:v>
       </x:c>
     </x:row>
     <x:row r="2435" spans="1:7">
@@ -67016,10 +67016,10 @@
         <x:v>2455</x:v>
       </x:c>
       <x:c r="B2435" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C2435" s="1">
-        <x:v>4500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D2435" s="1">
         <x:v>0</x:v>
@@ -67028,10 +67028,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2435" s="1">
-        <x:v>54385</x:v>
+        <x:v>9005</x:v>
       </x:c>
       <x:c r="G2435" s="1">
-        <x:v>58885</x:v>
+        <x:v>9005</x:v>
       </x:c>
     </x:row>
     <x:row r="2436" spans="1:7">
@@ -72536,10 +72536,10 @@
         <x:v>2692</x:v>
       </x:c>
       <x:c r="B2675" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C2675" s="1">
-        <x:v>409250</x:v>
+        <x:v>7061</x:v>
       </x:c>
       <x:c r="D2675" s="1">
         <x:v>0</x:v>
@@ -72548,10 +72548,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2675" s="1">
-        <x:v>159800</x:v>
+        <x:v>23500</x:v>
       </x:c>
       <x:c r="G2675" s="1">
-        <x:v>569050</x:v>
+        <x:v>30561</x:v>
       </x:c>
     </x:row>
     <x:row r="2676" spans="1:7">
@@ -72559,10 +72559,10 @@
         <x:v>2692</x:v>
       </x:c>
       <x:c r="B2676" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C2676" s="1">
-        <x:v>7061</x:v>
+        <x:v>409250</x:v>
       </x:c>
       <x:c r="D2676" s="1">
         <x:v>0</x:v>
@@ -72571,10 +72571,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2676" s="1">
-        <x:v>23500</x:v>
+        <x:v>159800</x:v>
       </x:c>
       <x:c r="G2676" s="1">
-        <x:v>30561</x:v>
+        <x:v>569050</x:v>
       </x:c>
     </x:row>
     <x:row r="2677" spans="1:7">
@@ -72697,10 +72697,10 @@
         <x:v>2698</x:v>
       </x:c>
       <x:c r="B2682" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C2682" s="1">
-        <x:v>7000</x:v>
+        <x:v>139000</x:v>
       </x:c>
       <x:c r="D2682" s="1">
         <x:v>0</x:v>
@@ -72709,10 +72709,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2682" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G2682" s="1">
-        <x:v>7000</x:v>
+        <x:v>139500</x:v>
       </x:c>
     </x:row>
     <x:row r="2683" spans="1:7">
@@ -72720,10 +72720,10 @@
         <x:v>2698</x:v>
       </x:c>
       <x:c r="B2683" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="C2683" s="1">
-        <x:v>139000</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D2683" s="1">
         <x:v>0</x:v>
@@ -72732,10 +72732,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2683" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2683" s="1">
-        <x:v>139500</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="2684" spans="1:7">
@@ -75526,10 +75526,10 @@
         <x:v>2818</x:v>
       </x:c>
       <x:c r="B2805" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C2805" s="1">
-        <x:v>15000</x:v>
+        <x:v>163800</x:v>
       </x:c>
       <x:c r="D2805" s="1">
         <x:v>0</x:v>
@@ -75538,10 +75538,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2805" s="1">
-        <x:v>111650</x:v>
+        <x:v>277645</x:v>
       </x:c>
       <x:c r="G2805" s="1">
-        <x:v>126650</x:v>
+        <x:v>441445</x:v>
       </x:c>
     </x:row>
     <x:row r="2806" spans="1:7">
@@ -75549,10 +75549,10 @@
         <x:v>2818</x:v>
       </x:c>
       <x:c r="B2806" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C2806" s="1">
-        <x:v>163800</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D2806" s="1">
         <x:v>0</x:v>
@@ -75561,10 +75561,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2806" s="1">
-        <x:v>277645</x:v>
+        <x:v>111650</x:v>
       </x:c>
       <x:c r="G2806" s="1">
-        <x:v>441445</x:v>
+        <x:v>126650</x:v>
       </x:c>
     </x:row>
     <x:row r="2807" spans="1:7">
@@ -78815,10 +78815,10 @@
         <x:v>2957</x:v>
       </x:c>
       <x:c r="B2948" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C2948" s="1">
-        <x:v>12000</x:v>
+        <x:v>99950</x:v>
       </x:c>
       <x:c r="D2948" s="1">
         <x:v>0</x:v>
@@ -78827,10 +78827,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2948" s="1">
-        <x:v>0</x:v>
+        <x:v>6650</x:v>
       </x:c>
       <x:c r="G2948" s="1">
-        <x:v>12000</x:v>
+        <x:v>106600</x:v>
       </x:c>
     </x:row>
     <x:row r="2949" spans="1:7">
@@ -78838,10 +78838,10 @@
         <x:v>2957</x:v>
       </x:c>
       <x:c r="B2949" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C2949" s="1">
-        <x:v>99950</x:v>
+        <x:v>12000</x:v>
       </x:c>
       <x:c r="D2949" s="1">
         <x:v>0</x:v>
@@ -78850,10 +78850,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2949" s="1">
-        <x:v>6650</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2949" s="1">
-        <x:v>106600</x:v>
+        <x:v>12000</x:v>
       </x:c>
     </x:row>
     <x:row r="2950" spans="1:7">
@@ -81874,10 +81874,10 @@
         <x:v>3085</x:v>
       </x:c>
       <x:c r="B3081" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C3081" s="1">
-        <x:v>44000</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D3081" s="1">
         <x:v>0</x:v>
@@ -81886,10 +81886,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3081" s="1">
-        <x:v>2100</x:v>
+        <x:v>33600</x:v>
       </x:c>
       <x:c r="G3081" s="1">
-        <x:v>46100</x:v>
+        <x:v>38600</x:v>
       </x:c>
     </x:row>
     <x:row r="3082" spans="1:7">
@@ -81897,10 +81897,10 @@
         <x:v>3085</x:v>
       </x:c>
       <x:c r="B3082" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C3082" s="1">
-        <x:v>5000</x:v>
+        <x:v>10500</x:v>
       </x:c>
       <x:c r="D3082" s="1">
         <x:v>0</x:v>
@@ -81909,10 +81909,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3082" s="1">
-        <x:v>33600</x:v>
+        <x:v>31300</x:v>
       </x:c>
       <x:c r="G3082" s="1">
-        <x:v>38600</x:v>
+        <x:v>41800</x:v>
       </x:c>
     </x:row>
     <x:row r="3083" spans="1:7">
@@ -81920,10 +81920,10 @@
         <x:v>3085</x:v>
       </x:c>
       <x:c r="B3083" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C3083" s="1">
-        <x:v>10500</x:v>
+        <x:v>44000</x:v>
       </x:c>
       <x:c r="D3083" s="1">
         <x:v>0</x:v>
@@ -81932,10 +81932,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3083" s="1">
-        <x:v>31300</x:v>
+        <x:v>2100</x:v>
       </x:c>
       <x:c r="G3083" s="1">
-        <x:v>41800</x:v>
+        <x:v>46100</x:v>
       </x:c>
     </x:row>
     <x:row r="3084" spans="1:7">
@@ -82219,7 +82219,7 @@
         <x:v>3096</x:v>
       </x:c>
       <x:c r="B3096" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C3096" s="1">
         <x:v>1000</x:v>
@@ -82231,10 +82231,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3096" s="1">
-        <x:v>4750</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3096" s="1">
-        <x:v>5750</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="3097" spans="1:7">
@@ -82242,7 +82242,7 @@
         <x:v>3096</x:v>
       </x:c>
       <x:c r="B3097" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C3097" s="1">
         <x:v>1000</x:v>
@@ -82254,10 +82254,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3097" s="1">
-        <x:v>0</x:v>
+        <x:v>4750</x:v>
       </x:c>
       <x:c r="G3097" s="1">
-        <x:v>1000</x:v>
+        <x:v>5750</x:v>
       </x:c>
     </x:row>
     <x:row r="3098" spans="1:7">
@@ -83645,10 +83645,10 @@
         <x:v>3152</x:v>
       </x:c>
       <x:c r="B3158" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C3158" s="1">
-        <x:v>20000</x:v>
+        <x:v>157500</x:v>
       </x:c>
       <x:c r="D3158" s="1">
         <x:v>0</x:v>
@@ -83657,10 +83657,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3158" s="1">
-        <x:v>6000</x:v>
+        <x:v>45517</x:v>
       </x:c>
       <x:c r="G3158" s="1">
-        <x:v>26000</x:v>
+        <x:v>203017</x:v>
       </x:c>
     </x:row>
     <x:row r="3159" spans="1:7">
@@ -83668,10 +83668,10 @@
         <x:v>3152</x:v>
       </x:c>
       <x:c r="B3159" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C3159" s="1">
-        <x:v>157500</x:v>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="D3159" s="1">
         <x:v>0</x:v>
@@ -83680,10 +83680,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3159" s="1">
-        <x:v>45517</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="G3159" s="1">
-        <x:v>203017</x:v>
+        <x:v>26000</x:v>
       </x:c>
     </x:row>
     <x:row r="3160" spans="1:7">
@@ -85232,10 +85232,10 @@
         <x:v>3219</x:v>
       </x:c>
       <x:c r="B3227" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C3227" s="1">
-        <x:v>2300</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D3227" s="1">
         <x:v>0</x:v>
@@ -85244,10 +85244,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3227" s="1">
-        <x:v>8850</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="G3227" s="1">
-        <x:v>11150</x:v>
+        <x:v>9000</x:v>
       </x:c>
     </x:row>
     <x:row r="3228" spans="1:7">
@@ -85255,10 +85255,10 @@
         <x:v>3219</x:v>
       </x:c>
       <x:c r="B3228" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C3228" s="1">
-        <x:v>3000</x:v>
+        <x:v>2300</x:v>
       </x:c>
       <x:c r="D3228" s="1">
         <x:v>0</x:v>
@@ -85267,10 +85267,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3228" s="1">
-        <x:v>6000</x:v>
+        <x:v>8850</x:v>
       </x:c>
       <x:c r="G3228" s="1">
-        <x:v>9000</x:v>
+        <x:v>11150</x:v>
       </x:c>
     </x:row>
     <x:row r="3229" spans="1:7">
@@ -85531,22 +85531,22 @@
         <x:v>3230</x:v>
       </x:c>
       <x:c r="B3240" s="1" t="s">
-        <x:v>299</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C3240" s="1">
-        <x:v>536500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3240" s="1">
-        <x:v>295</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3240" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3240" s="1">
-        <x:v>230347</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3240" s="1">
-        <x:v>767142</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="3241" spans="1:7">
@@ -85554,22 +85554,22 @@
         <x:v>3230</x:v>
       </x:c>
       <x:c r="B3241" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="C3241" s="1">
-        <x:v>0</x:v>
+        <x:v>536500</x:v>
       </x:c>
       <x:c r="D3241" s="1">
-        <x:v>59</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E3241" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3241" s="1">
-        <x:v>0</x:v>
+        <x:v>230347</x:v>
       </x:c>
       <x:c r="G3241" s="1">
-        <x:v>59</x:v>
+        <x:v>767142</x:v>
       </x:c>
     </x:row>
     <x:row r="3242" spans="1:7">
@@ -86152,22 +86152,22 @@
         <x:v>3254</x:v>
       </x:c>
       <x:c r="B3267" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C3267" s="1">
-        <x:v>420650</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D3267" s="1">
-        <x:v>181</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3267" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3267" s="1">
-        <x:v>448881</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3267" s="1">
-        <x:v>869712</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="3268" spans="1:7">
@@ -86175,22 +86175,22 @@
         <x:v>3254</x:v>
       </x:c>
       <x:c r="B3268" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C3268" s="1">
-        <x:v>25500</x:v>
+        <x:v>420650</x:v>
       </x:c>
       <x:c r="D3268" s="1">
-        <x:v>0</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="E3268" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3268" s="1">
-        <x:v>0</x:v>
+        <x:v>448881</x:v>
       </x:c>
       <x:c r="G3268" s="1">
-        <x:v>25500</x:v>
+        <x:v>869712</x:v>
       </x:c>
     </x:row>
     <x:row r="3269" spans="1:7">
@@ -87969,22 +87969,22 @@
         <x:v>3332</x:v>
       </x:c>
       <x:c r="B3346" s="1" t="s">
-        <x:v>258</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C3346" s="1">
-        <x:v>15000</x:v>
+        <x:v>332220</x:v>
       </x:c>
       <x:c r="D3346" s="1">
-        <x:v>63</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3346" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3346" s="1">
-        <x:v>0</x:v>
+        <x:v>299023</x:v>
       </x:c>
       <x:c r="G3346" s="1">
-        <x:v>15063</x:v>
+        <x:v>631243</x:v>
       </x:c>
     </x:row>
     <x:row r="3347" spans="1:7">
@@ -87992,13 +87992,13 @@
         <x:v>3332</x:v>
       </x:c>
       <x:c r="B3347" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="C3347" s="1">
-        <x:v>0</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D3347" s="1">
-        <x:v>59</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E3347" s="1">
         <x:v>0</x:v>
@@ -88007,7 +88007,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G3347" s="1">
-        <x:v>59</x:v>
+        <x:v>15063</x:v>
       </x:c>
     </x:row>
     <x:row r="3348" spans="1:7">
@@ -88015,22 +88015,22 @@
         <x:v>3332</x:v>
       </x:c>
       <x:c r="B3348" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C3348" s="1">
-        <x:v>332220</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3348" s="1">
-        <x:v>0</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3348" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3348" s="1">
-        <x:v>299023</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3348" s="1">
-        <x:v>631243</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="3349" spans="1:7">
@@ -89188,10 +89188,10 @@
         <x:v>3380</x:v>
       </x:c>
       <x:c r="B3399" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="C3399" s="1">
-        <x:v>41550</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D3399" s="1">
         <x:v>0</x:v>
@@ -89200,10 +89200,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3399" s="1">
-        <x:v>6500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3399" s="1">
-        <x:v>48050</x:v>
+        <x:v>15000</x:v>
       </x:c>
     </x:row>
     <x:row r="3400" spans="1:7">
@@ -89211,10 +89211,10 @@
         <x:v>3380</x:v>
       </x:c>
       <x:c r="B3400" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C3400" s="1">
-        <x:v>15000</x:v>
+        <x:v>41550</x:v>
       </x:c>
       <x:c r="D3400" s="1">
         <x:v>0</x:v>
@@ -89223,10 +89223,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3400" s="1">
-        <x:v>0</x:v>
+        <x:v>6500</x:v>
       </x:c>
       <x:c r="G3400" s="1">
-        <x:v>15000</x:v>
+        <x:v>48050</x:v>
       </x:c>
     </x:row>
     <x:row r="3401" spans="1:7">
@@ -90545,10 +90545,10 @@
         <x:v>3433</x:v>
       </x:c>
       <x:c r="B3458" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C3458" s="1">
-        <x:v>500</x:v>
+        <x:v>19500</x:v>
       </x:c>
       <x:c r="D3458" s="1">
         <x:v>0</x:v>
@@ -90557,10 +90557,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3458" s="1">
-        <x:v>0</x:v>
+        <x:v>8650</x:v>
       </x:c>
       <x:c r="G3458" s="1">
-        <x:v>500</x:v>
+        <x:v>28150</x:v>
       </x:c>
     </x:row>
     <x:row r="3459" spans="1:7">
@@ -90568,10 +90568,10 @@
         <x:v>3433</x:v>
       </x:c>
       <x:c r="B3459" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C3459" s="1">
-        <x:v>19500</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="D3459" s="1">
         <x:v>0</x:v>
@@ -90580,10 +90580,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3459" s="1">
-        <x:v>8650</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3459" s="1">
-        <x:v>28150</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="3460" spans="1:7">
@@ -90683,22 +90683,22 @@
         <x:v>3438</x:v>
       </x:c>
       <x:c r="B3464" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C3464" s="1">
-        <x:v>47850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3464" s="1">
-        <x:v>0</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3464" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3464" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3464" s="1">
-        <x:v>52850</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="3465" spans="1:7">
@@ -90706,22 +90706,22 @@
         <x:v>3438</x:v>
       </x:c>
       <x:c r="B3465" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C3465" s="1">
-        <x:v>0</x:v>
+        <x:v>47850</x:v>
       </x:c>
       <x:c r="D3465" s="1">
-        <x:v>59</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3465" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3465" s="1">
-        <x:v>0</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G3465" s="1">
-        <x:v>59</x:v>
+        <x:v>52850</x:v>
       </x:c>
     </x:row>
     <x:row r="3466" spans="1:7">
@@ -92707,10 +92707,10 @@
         <x:v>3519</x:v>
       </x:c>
       <x:c r="B3552" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C3552" s="1">
-        <x:v>130750</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3552" s="1">
         <x:v>7</x:v>
@@ -92719,10 +92719,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3552" s="1">
-        <x:v>83750</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3552" s="1">
-        <x:v>214507</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="3553" spans="1:7">
@@ -92730,10 +92730,10 @@
         <x:v>3519</x:v>
       </x:c>
       <x:c r="B3553" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C3553" s="1">
-        <x:v>0</x:v>
+        <x:v>130750</x:v>
       </x:c>
       <x:c r="D3553" s="1">
         <x:v>7</x:v>
@@ -92742,10 +92742,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3553" s="1">
-        <x:v>0</x:v>
+        <x:v>83750</x:v>
       </x:c>
       <x:c r="G3553" s="1">
-        <x:v>7</x:v>
+        <x:v>214507</x:v>
       </x:c>
     </x:row>
     <x:row r="3554" spans="1:7">

--- a/reports/pro-oil/pro-oil-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-oil/pro-oil-candidate-lobby-lifetime-report.xlsx
@@ -16186,7 +16186,7 @@
         <x:v>279</x:v>
       </x:c>
       <x:c r="B225" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C225" s="1">
         <x:v>0</x:v>
@@ -16198,10 +16198,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F225" s="1">
-        <x:v>2300</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G225" s="1">
-        <x:v>2300</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="226" spans="1:7">
@@ -16209,7 +16209,7 @@
         <x:v>279</x:v>
       </x:c>
       <x:c r="B226" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C226" s="1">
         <x:v>0</x:v>
@@ -16221,10 +16221,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F226" s="1">
-        <x:v>1000</x:v>
+        <x:v>2300</x:v>
       </x:c>
       <x:c r="G226" s="1">
-        <x:v>1000</x:v>
+        <x:v>2300</x:v>
       </x:c>
     </x:row>
     <x:row r="227" spans="1:7">
@@ -19314,10 +19314,10 @@
         <x:v>415</x:v>
       </x:c>
       <x:c r="B361" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C361" s="1">
-        <x:v>15000</x:v>
+        <x:v>163000</x:v>
       </x:c>
       <x:c r="D361" s="1">
         <x:v>0</x:v>
@@ -19326,10 +19326,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F361" s="1">
-        <x:v>0</x:v>
+        <x:v>82550</x:v>
       </x:c>
       <x:c r="G361" s="1">
-        <x:v>15000</x:v>
+        <x:v>245550</x:v>
       </x:c>
     </x:row>
     <x:row r="362" spans="1:7">
@@ -19337,10 +19337,10 @@
         <x:v>415</x:v>
       </x:c>
       <x:c r="B362" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="C362" s="1">
-        <x:v>163000</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D362" s="1">
         <x:v>0</x:v>
@@ -19349,10 +19349,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F362" s="1">
-        <x:v>82550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G362" s="1">
-        <x:v>245550</x:v>
+        <x:v>15000</x:v>
       </x:c>
     </x:row>
     <x:row r="363" spans="1:7">
@@ -19452,10 +19452,10 @@
         <x:v>421</x:v>
       </x:c>
       <x:c r="B367" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C367" s="1">
-        <x:v>3000</x:v>
+        <x:v>107540</x:v>
       </x:c>
       <x:c r="D367" s="1">
         <x:v>0</x:v>
@@ -19464,10 +19464,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F367" s="1">
-        <x:v>25150</x:v>
+        <x:v>59170</x:v>
       </x:c>
       <x:c r="G367" s="1">
-        <x:v>28150</x:v>
+        <x:v>166710</x:v>
       </x:c>
     </x:row>
     <x:row r="368" spans="1:7">
@@ -19475,10 +19475,10 @@
         <x:v>421</x:v>
       </x:c>
       <x:c r="B368" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C368" s="1">
-        <x:v>107540</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D368" s="1">
         <x:v>0</x:v>
@@ -19487,10 +19487,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F368" s="1">
-        <x:v>59170</x:v>
+        <x:v>25150</x:v>
       </x:c>
       <x:c r="G368" s="1">
-        <x:v>166710</x:v>
+        <x:v>28150</x:v>
       </x:c>
     </x:row>
     <x:row r="369" spans="1:7">
@@ -21108,10 +21108,10 @@
         <x:v>491</x:v>
       </x:c>
       <x:c r="B439" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C439" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D439" s="1">
         <x:v>0</x:v>
@@ -21120,10 +21120,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F439" s="1">
-        <x:v>13450</x:v>
+        <x:v>40350</x:v>
       </x:c>
       <x:c r="G439" s="1">
-        <x:v>13500</x:v>
+        <x:v>40350</x:v>
       </x:c>
     </x:row>
     <x:row r="440" spans="1:7">
@@ -21131,11 +21131,11 @@
         <x:v>491</x:v>
       </x:c>
       <x:c r="B440" s="1" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C440" s="1">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="C440" s="1">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="D440" s="1">
         <x:v>0</x:v>
       </x:c>
@@ -21143,10 +21143,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F440" s="1">
-        <x:v>40350</x:v>
+        <x:v>13450</x:v>
       </x:c>
       <x:c r="G440" s="1">
-        <x:v>40350</x:v>
+        <x:v>13500</x:v>
       </x:c>
     </x:row>
     <x:row r="441" spans="1:7">
@@ -27295,22 +27295,22 @@
         <x:v>760</x:v>
       </x:c>
       <x:c r="B708" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>750</x:v>
       </x:c>
       <x:c r="C708" s="1">
-        <x:v>25500</x:v>
+        <x:v>418533</x:v>
       </x:c>
       <x:c r="D708" s="1">
-        <x:v>0</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E708" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F708" s="1">
-        <x:v>0</x:v>
+        <x:v>51350</x:v>
       </x:c>
       <x:c r="G708" s="1">
-        <x:v>25500</x:v>
+        <x:v>470001</x:v>
       </x:c>
     </x:row>
     <x:row r="709" spans="1:7">
@@ -27318,22 +27318,22 @@
         <x:v>760</x:v>
       </x:c>
       <x:c r="B709" s="1" t="s">
-        <x:v>750</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C709" s="1">
-        <x:v>418533</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D709" s="1">
-        <x:v>118</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E709" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F709" s="1">
-        <x:v>51350</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G709" s="1">
-        <x:v>470001</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="710" spans="1:7">
@@ -31481,22 +31481,22 @@
         <x:v>938</x:v>
       </x:c>
       <x:c r="B890" s="1" t="s">
-        <x:v>299</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C890" s="1">
-        <x:v>0</x:v>
+        <x:v>91000</x:v>
       </x:c>
       <x:c r="D890" s="1">
-        <x:v>59</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E890" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F890" s="1">
-        <x:v>0</x:v>
+        <x:v>26100</x:v>
       </x:c>
       <x:c r="G890" s="1">
-        <x:v>59</x:v>
+        <x:v>117218</x:v>
       </x:c>
     </x:row>
     <x:row r="891" spans="1:7">
@@ -31504,22 +31504,22 @@
         <x:v>938</x:v>
       </x:c>
       <x:c r="B891" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="C891" s="1">
-        <x:v>91000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D891" s="1">
-        <x:v>118</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E891" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F891" s="1">
-        <x:v>26100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G891" s="1">
-        <x:v>117218</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="892" spans="1:7">
@@ -37714,10 +37714,10 @@
         <x:v>1205</x:v>
       </x:c>
       <x:c r="B1161" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C1161" s="1">
-        <x:v>752389</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1161" s="1">
         <x:v>0</x:v>
@@ -37726,10 +37726,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1161" s="1">
-        <x:v>418794</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="G1161" s="1">
-        <x:v>1171183</x:v>
+        <x:v>10000</x:v>
       </x:c>
     </x:row>
     <x:row r="1162" spans="1:7">
@@ -37737,10 +37737,10 @@
         <x:v>1205</x:v>
       </x:c>
       <x:c r="B1162" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1162" s="1">
-        <x:v>0</x:v>
+        <x:v>752389</x:v>
       </x:c>
       <x:c r="D1162" s="1">
         <x:v>0</x:v>
@@ -37749,10 +37749,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1162" s="1">
-        <x:v>10000</x:v>
+        <x:v>418794</x:v>
       </x:c>
       <x:c r="G1162" s="1">
-        <x:v>10000</x:v>
+        <x:v>1171183</x:v>
       </x:c>
     </x:row>
     <x:row r="1163" spans="1:7">
@@ -50847,10 +50847,10 @@
         <x:v>1765</x:v>
       </x:c>
       <x:c r="B1732" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C1732" s="1">
-        <x:v>2500</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="D1732" s="1">
         <x:v>0</x:v>
@@ -50859,10 +50859,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1732" s="1">
-        <x:v>16350</x:v>
+        <x:v>72700</x:v>
       </x:c>
       <x:c r="G1732" s="1">
-        <x:v>18850</x:v>
+        <x:v>73185</x:v>
       </x:c>
     </x:row>
     <x:row r="1733" spans="1:7">
@@ -50870,10 +50870,10 @@
         <x:v>1765</x:v>
       </x:c>
       <x:c r="B1733" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1733" s="1">
-        <x:v>485</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1733" s="1">
         <x:v>0</x:v>
@@ -50882,10 +50882,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1733" s="1">
-        <x:v>72700</x:v>
+        <x:v>16350</x:v>
       </x:c>
       <x:c r="G1733" s="1">
-        <x:v>73185</x:v>
+        <x:v>18850</x:v>
       </x:c>
     </x:row>
     <x:row r="1734" spans="1:7">
@@ -66993,10 +66993,10 @@
         <x:v>2455</x:v>
       </x:c>
       <x:c r="B2434" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C2434" s="1">
-        <x:v>4500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D2434" s="1">
         <x:v>0</x:v>
@@ -67005,10 +67005,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2434" s="1">
-        <x:v>54385</x:v>
+        <x:v>9005</x:v>
       </x:c>
       <x:c r="G2434" s="1">
-        <x:v>58885</x:v>
+        <x:v>9005</x:v>
       </x:c>
     </x:row>
     <x:row r="2435" spans="1:7">
@@ -67016,10 +67016,10 @@
         <x:v>2455</x:v>
       </x:c>
       <x:c r="B2435" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C2435" s="1">
-        <x:v>0</x:v>
+        <x:v>4500</x:v>
       </x:c>
       <x:c r="D2435" s="1">
         <x:v>0</x:v>
@@ -67028,10 +67028,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2435" s="1">
-        <x:v>9005</x:v>
+        <x:v>54385</x:v>
       </x:c>
       <x:c r="G2435" s="1">
-        <x:v>9005</x:v>
+        <x:v>58885</x:v>
       </x:c>
     </x:row>
     <x:row r="2436" spans="1:7">
@@ -72536,10 +72536,10 @@
         <x:v>2692</x:v>
       </x:c>
       <x:c r="B2675" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C2675" s="1">
-        <x:v>7061</x:v>
+        <x:v>409250</x:v>
       </x:c>
       <x:c r="D2675" s="1">
         <x:v>0</x:v>
@@ -72548,10 +72548,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2675" s="1">
-        <x:v>23500</x:v>
+        <x:v>159800</x:v>
       </x:c>
       <x:c r="G2675" s="1">
-        <x:v>30561</x:v>
+        <x:v>569050</x:v>
       </x:c>
     </x:row>
     <x:row r="2676" spans="1:7">
@@ -72559,10 +72559,10 @@
         <x:v>2692</x:v>
       </x:c>
       <x:c r="B2676" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C2676" s="1">
-        <x:v>409250</x:v>
+        <x:v>7061</x:v>
       </x:c>
       <x:c r="D2676" s="1">
         <x:v>0</x:v>
@@ -72571,10 +72571,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2676" s="1">
-        <x:v>159800</x:v>
+        <x:v>23500</x:v>
       </x:c>
       <x:c r="G2676" s="1">
-        <x:v>569050</x:v>
+        <x:v>30561</x:v>
       </x:c>
     </x:row>
     <x:row r="2677" spans="1:7">
@@ -77044,10 +77044,10 @@
         <x:v>2882</x:v>
       </x:c>
       <x:c r="B2871" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C2871" s="1">
-        <x:v>15000</x:v>
+        <x:v>102350</x:v>
       </x:c>
       <x:c r="D2871" s="1">
         <x:v>0</x:v>
@@ -77056,10 +77056,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2871" s="1">
-        <x:v>5000</x:v>
+        <x:v>106550</x:v>
       </x:c>
       <x:c r="G2871" s="1">
-        <x:v>20000</x:v>
+        <x:v>208900</x:v>
       </x:c>
     </x:row>
     <x:row r="2872" spans="1:7">
@@ -77067,10 +77067,10 @@
         <x:v>2882</x:v>
       </x:c>
       <x:c r="B2872" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C2872" s="1">
-        <x:v>102350</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D2872" s="1">
         <x:v>0</x:v>
@@ -77079,10 +77079,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2872" s="1">
-        <x:v>106550</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G2872" s="1">
-        <x:v>208900</x:v>
+        <x:v>20000</x:v>
       </x:c>
     </x:row>
     <x:row r="2873" spans="1:7">
@@ -78815,10 +78815,10 @@
         <x:v>2957</x:v>
       </x:c>
       <x:c r="B2948" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C2948" s="1">
-        <x:v>99950</x:v>
+        <x:v>12000</x:v>
       </x:c>
       <x:c r="D2948" s="1">
         <x:v>0</x:v>
@@ -78827,10 +78827,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2948" s="1">
-        <x:v>6650</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2948" s="1">
-        <x:v>106600</x:v>
+        <x:v>12000</x:v>
       </x:c>
     </x:row>
     <x:row r="2949" spans="1:7">
@@ -78838,10 +78838,10 @@
         <x:v>2957</x:v>
       </x:c>
       <x:c r="B2949" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C2949" s="1">
-        <x:v>12000</x:v>
+        <x:v>99950</x:v>
       </x:c>
       <x:c r="D2949" s="1">
         <x:v>0</x:v>
@@ -78850,10 +78850,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2949" s="1">
-        <x:v>0</x:v>
+        <x:v>6650</x:v>
       </x:c>
       <x:c r="G2949" s="1">
-        <x:v>12000</x:v>
+        <x:v>106600</x:v>
       </x:c>
     </x:row>
     <x:row r="2950" spans="1:7">
@@ -79528,10 +79528,10 @@
         <x:v>2986</x:v>
       </x:c>
       <x:c r="B2979" s="1" t="s">
-        <x:v>750</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C2979" s="1">
-        <x:v>286800</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D2979" s="1">
         <x:v>0</x:v>
@@ -79540,10 +79540,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2979" s="1">
-        <x:v>75150</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2979" s="1">
-        <x:v>361950</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="2980" spans="1:7">
@@ -79551,10 +79551,10 @@
         <x:v>2986</x:v>
       </x:c>
       <x:c r="B2980" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>750</x:v>
       </x:c>
       <x:c r="C2980" s="1">
-        <x:v>5000</x:v>
+        <x:v>286800</x:v>
       </x:c>
       <x:c r="D2980" s="1">
         <x:v>0</x:v>
@@ -79563,10 +79563,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2980" s="1">
-        <x:v>0</x:v>
+        <x:v>75150</x:v>
       </x:c>
       <x:c r="G2980" s="1">
-        <x:v>5000</x:v>
+        <x:v>361950</x:v>
       </x:c>
     </x:row>
     <x:row r="2981" spans="1:7">
@@ -81299,22 +81299,22 @@
         <x:v>3061</x:v>
       </x:c>
       <x:c r="B3056" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="C3056" s="1">
-        <x:v>71750</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D3056" s="1">
-        <x:v>177</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3056" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3056" s="1">
-        <x:v>77150</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3056" s="1">
-        <x:v>149077</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="3057" spans="1:7">
@@ -81322,22 +81322,22 @@
         <x:v>3061</x:v>
       </x:c>
       <x:c r="B3057" s="1" t="s">
-        <x:v>258</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C3057" s="1">
-        <x:v>7000</x:v>
+        <x:v>71750</x:v>
       </x:c>
       <x:c r="D3057" s="1">
-        <x:v>0</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="E3057" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3057" s="1">
-        <x:v>0</x:v>
+        <x:v>77150</x:v>
       </x:c>
       <x:c r="G3057" s="1">
-        <x:v>7000</x:v>
+        <x:v>149077</x:v>
       </x:c>
     </x:row>
     <x:row r="3058" spans="1:7">
@@ -81874,10 +81874,10 @@
         <x:v>3085</x:v>
       </x:c>
       <x:c r="B3081" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C3081" s="1">
-        <x:v>5000</x:v>
+        <x:v>10500</x:v>
       </x:c>
       <x:c r="D3081" s="1">
         <x:v>0</x:v>
@@ -81886,10 +81886,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3081" s="1">
-        <x:v>33600</x:v>
+        <x:v>31300</x:v>
       </x:c>
       <x:c r="G3081" s="1">
-        <x:v>38600</x:v>
+        <x:v>41800</x:v>
       </x:c>
     </x:row>
     <x:row r="3082" spans="1:7">
@@ -81897,10 +81897,10 @@
         <x:v>3085</x:v>
       </x:c>
       <x:c r="B3082" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C3082" s="1">
-        <x:v>10500</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D3082" s="1">
         <x:v>0</x:v>
@@ -81909,10 +81909,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3082" s="1">
-        <x:v>31300</x:v>
+        <x:v>33600</x:v>
       </x:c>
       <x:c r="G3082" s="1">
-        <x:v>41800</x:v>
+        <x:v>38600</x:v>
       </x:c>
     </x:row>
     <x:row r="3083" spans="1:7">
@@ -82219,7 +82219,7 @@
         <x:v>3096</x:v>
       </x:c>
       <x:c r="B3096" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C3096" s="1">
         <x:v>1000</x:v>
@@ -82231,10 +82231,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3096" s="1">
-        <x:v>0</x:v>
+        <x:v>4750</x:v>
       </x:c>
       <x:c r="G3096" s="1">
-        <x:v>1000</x:v>
+        <x:v>5750</x:v>
       </x:c>
     </x:row>
     <x:row r="3097" spans="1:7">
@@ -82242,7 +82242,7 @@
         <x:v>3096</x:v>
       </x:c>
       <x:c r="B3097" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C3097" s="1">
         <x:v>1000</x:v>
@@ -82254,10 +82254,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3097" s="1">
-        <x:v>4750</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3097" s="1">
-        <x:v>5750</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="3098" spans="1:7">
@@ -82541,22 +82541,22 @@
         <x:v>3109</x:v>
       </x:c>
       <x:c r="B3110" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C3110" s="1">
-        <x:v>0</x:v>
+        <x:v>307450</x:v>
       </x:c>
       <x:c r="D3110" s="1">
-        <x:v>59</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3110" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3110" s="1">
-        <x:v>0</x:v>
+        <x:v>40550</x:v>
       </x:c>
       <x:c r="G3110" s="1">
-        <x:v>59</x:v>
+        <x:v>348000</x:v>
       </x:c>
     </x:row>
     <x:row r="3111" spans="1:7">
@@ -82564,22 +82564,22 @@
         <x:v>3109</x:v>
       </x:c>
       <x:c r="B3111" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C3111" s="1">
-        <x:v>307450</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3111" s="1">
-        <x:v>0</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3111" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3111" s="1">
-        <x:v>40550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3111" s="1">
-        <x:v>348000</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="3112" spans="1:7">
@@ -83645,10 +83645,10 @@
         <x:v>3152</x:v>
       </x:c>
       <x:c r="B3158" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C3158" s="1">
-        <x:v>157500</x:v>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="D3158" s="1">
         <x:v>0</x:v>
@@ -83657,10 +83657,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3158" s="1">
-        <x:v>45517</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="G3158" s="1">
-        <x:v>203017</x:v>
+        <x:v>26000</x:v>
       </x:c>
     </x:row>
     <x:row r="3159" spans="1:7">
@@ -83668,10 +83668,10 @@
         <x:v>3152</x:v>
       </x:c>
       <x:c r="B3159" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C3159" s="1">
-        <x:v>20000</x:v>
+        <x:v>157500</x:v>
       </x:c>
       <x:c r="D3159" s="1">
         <x:v>0</x:v>
@@ -83680,10 +83680,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3159" s="1">
-        <x:v>6000</x:v>
+        <x:v>45517</x:v>
       </x:c>
       <x:c r="G3159" s="1">
-        <x:v>26000</x:v>
+        <x:v>203017</x:v>
       </x:c>
     </x:row>
     <x:row r="3160" spans="1:7">
@@ -85531,22 +85531,22 @@
         <x:v>3230</x:v>
       </x:c>
       <x:c r="B3240" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="C3240" s="1">
-        <x:v>0</x:v>
+        <x:v>536500</x:v>
       </x:c>
       <x:c r="D3240" s="1">
-        <x:v>59</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E3240" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3240" s="1">
-        <x:v>0</x:v>
+        <x:v>230347</x:v>
       </x:c>
       <x:c r="G3240" s="1">
-        <x:v>59</x:v>
+        <x:v>767142</x:v>
       </x:c>
     </x:row>
     <x:row r="3241" spans="1:7">
@@ -85554,22 +85554,22 @@
         <x:v>3230</x:v>
       </x:c>
       <x:c r="B3241" s="1" t="s">
-        <x:v>299</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C3241" s="1">
-        <x:v>536500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3241" s="1">
-        <x:v>295</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3241" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3241" s="1">
-        <x:v>230347</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3241" s="1">
-        <x:v>767142</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="3242" spans="1:7">
@@ -85761,10 +85761,10 @@
         <x:v>3239</x:v>
       </x:c>
       <x:c r="B3250" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="C3250" s="1">
-        <x:v>343100</x:v>
+        <x:v>34000</x:v>
       </x:c>
       <x:c r="D3250" s="1">
         <x:v>0</x:v>
@@ -85773,10 +85773,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3250" s="1">
-        <x:v>244972</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3250" s="1">
-        <x:v>588072</x:v>
+        <x:v>34000</x:v>
       </x:c>
     </x:row>
     <x:row r="3251" spans="1:7">
@@ -85784,10 +85784,10 @@
         <x:v>3239</x:v>
       </x:c>
       <x:c r="B3251" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C3251" s="1">
-        <x:v>34000</x:v>
+        <x:v>343100</x:v>
       </x:c>
       <x:c r="D3251" s="1">
         <x:v>0</x:v>
@@ -85796,10 +85796,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3251" s="1">
-        <x:v>0</x:v>
+        <x:v>244972</x:v>
       </x:c>
       <x:c r="G3251" s="1">
-        <x:v>34000</x:v>
+        <x:v>588072</x:v>
       </x:c>
     </x:row>
     <x:row r="3252" spans="1:7">
@@ -85945,10 +85945,10 @@
         <x:v>3246</x:v>
       </x:c>
       <x:c r="B3258" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C3258" s="1">
-        <x:v>0</x:v>
+        <x:v>29500</x:v>
       </x:c>
       <x:c r="D3258" s="1">
         <x:v>0</x:v>
@@ -85957,10 +85957,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3258" s="1">
-        <x:v>1000</x:v>
+        <x:v>12550</x:v>
       </x:c>
       <x:c r="G3258" s="1">
-        <x:v>1000</x:v>
+        <x:v>42050</x:v>
       </x:c>
     </x:row>
     <x:row r="3259" spans="1:7">
@@ -85968,10 +85968,10 @@
         <x:v>3246</x:v>
       </x:c>
       <x:c r="B3259" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C3259" s="1">
-        <x:v>29500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3259" s="1">
         <x:v>0</x:v>
@@ -85980,10 +85980,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3259" s="1">
-        <x:v>12550</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G3259" s="1">
-        <x:v>42050</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="3260" spans="1:7">
@@ -86152,22 +86152,22 @@
         <x:v>3254</x:v>
       </x:c>
       <x:c r="B3267" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C3267" s="1">
-        <x:v>25500</x:v>
+        <x:v>420650</x:v>
       </x:c>
       <x:c r="D3267" s="1">
-        <x:v>0</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="E3267" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3267" s="1">
-        <x:v>0</x:v>
+        <x:v>448881</x:v>
       </x:c>
       <x:c r="G3267" s="1">
-        <x:v>25500</x:v>
+        <x:v>869712</x:v>
       </x:c>
     </x:row>
     <x:row r="3268" spans="1:7">
@@ -86175,22 +86175,22 @@
         <x:v>3254</x:v>
       </x:c>
       <x:c r="B3268" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C3268" s="1">
-        <x:v>420650</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D3268" s="1">
-        <x:v>181</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3268" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3268" s="1">
-        <x:v>448881</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3268" s="1">
-        <x:v>869712</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="3269" spans="1:7">
@@ -87969,22 +87969,22 @@
         <x:v>3332</x:v>
       </x:c>
       <x:c r="B3346" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C3346" s="1">
-        <x:v>332220</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3346" s="1">
-        <x:v>0</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3346" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3346" s="1">
-        <x:v>299023</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3346" s="1">
-        <x:v>631243</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="3347" spans="1:7">
@@ -87992,22 +87992,22 @@
         <x:v>3332</x:v>
       </x:c>
       <x:c r="B3347" s="1" t="s">
-        <x:v>258</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C3347" s="1">
-        <x:v>15000</x:v>
+        <x:v>332220</x:v>
       </x:c>
       <x:c r="D3347" s="1">
-        <x:v>63</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3347" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3347" s="1">
-        <x:v>0</x:v>
+        <x:v>299023</x:v>
       </x:c>
       <x:c r="G3347" s="1">
-        <x:v>15063</x:v>
+        <x:v>631243</x:v>
       </x:c>
     </x:row>
     <x:row r="3348" spans="1:7">
@@ -88015,13 +88015,13 @@
         <x:v>3332</x:v>
       </x:c>
       <x:c r="B3348" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="C3348" s="1">
-        <x:v>0</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D3348" s="1">
-        <x:v>59</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E3348" s="1">
         <x:v>0</x:v>
@@ -88030,7 +88030,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G3348" s="1">
-        <x:v>59</x:v>
+        <x:v>15063</x:v>
       </x:c>
     </x:row>
     <x:row r="3349" spans="1:7">
@@ -88084,22 +88084,22 @@
         <x:v>3334</x:v>
       </x:c>
       <x:c r="B3351" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C3351" s="1">
-        <x:v>7000</x:v>
+        <x:v>116050</x:v>
       </x:c>
       <x:c r="D3351" s="1">
-        <x:v>63</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="E3351" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3351" s="1">
-        <x:v>7000</x:v>
+        <x:v>47699</x:v>
       </x:c>
       <x:c r="G3351" s="1">
-        <x:v>14063</x:v>
+        <x:v>163985</x:v>
       </x:c>
     </x:row>
     <x:row r="3352" spans="1:7">
@@ -88107,22 +88107,22 @@
         <x:v>3334</x:v>
       </x:c>
       <x:c r="B3352" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C3352" s="1">
-        <x:v>116050</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D3352" s="1">
-        <x:v>236</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E3352" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3352" s="1">
-        <x:v>47699</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="G3352" s="1">
-        <x:v>163985</x:v>
+        <x:v>14063</x:v>
       </x:c>
     </x:row>
     <x:row r="3353" spans="1:7">
@@ -89188,10 +89188,10 @@
         <x:v>3380</x:v>
       </x:c>
       <x:c r="B3399" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C3399" s="1">
-        <x:v>15000</x:v>
+        <x:v>41550</x:v>
       </x:c>
       <x:c r="D3399" s="1">
         <x:v>0</x:v>
@@ -89200,10 +89200,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3399" s="1">
-        <x:v>0</x:v>
+        <x:v>6500</x:v>
       </x:c>
       <x:c r="G3399" s="1">
-        <x:v>15000</x:v>
+        <x:v>48050</x:v>
       </x:c>
     </x:row>
     <x:row r="3400" spans="1:7">
@@ -89211,10 +89211,10 @@
         <x:v>3380</x:v>
       </x:c>
       <x:c r="B3400" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="C3400" s="1">
-        <x:v>41550</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D3400" s="1">
         <x:v>0</x:v>
@@ -89223,10 +89223,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3400" s="1">
-        <x:v>6500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3400" s="1">
-        <x:v>48050</x:v>
+        <x:v>15000</x:v>
       </x:c>
     </x:row>
     <x:row r="3401" spans="1:7">
@@ -90453,22 +90453,22 @@
         <x:v>3430</x:v>
       </x:c>
       <x:c r="B3454" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C3454" s="1">
-        <x:v>0</x:v>
+        <x:v>72750</x:v>
       </x:c>
       <x:c r="D3454" s="1">
-        <x:v>59</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E3454" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3454" s="1">
-        <x:v>0</x:v>
+        <x:v>25450</x:v>
       </x:c>
       <x:c r="G3454" s="1">
-        <x:v>59</x:v>
+        <x:v>98495</x:v>
       </x:c>
     </x:row>
     <x:row r="3455" spans="1:7">
@@ -90476,22 +90476,22 @@
         <x:v>3430</x:v>
       </x:c>
       <x:c r="B3455" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C3455" s="1">
-        <x:v>72750</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3455" s="1">
-        <x:v>295</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3455" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3455" s="1">
-        <x:v>25450</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3455" s="1">
-        <x:v>98495</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="3456" spans="1:7">
@@ -90545,10 +90545,10 @@
         <x:v>3433</x:v>
       </x:c>
       <x:c r="B3458" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C3458" s="1">
-        <x:v>19500</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="D3458" s="1">
         <x:v>0</x:v>
@@ -90557,10 +90557,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3458" s="1">
-        <x:v>8650</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3458" s="1">
-        <x:v>28150</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="3459" spans="1:7">
@@ -90568,10 +90568,10 @@
         <x:v>3433</x:v>
       </x:c>
       <x:c r="B3459" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C3459" s="1">
-        <x:v>500</x:v>
+        <x:v>19500</x:v>
       </x:c>
       <x:c r="D3459" s="1">
         <x:v>0</x:v>
@@ -90580,10 +90580,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3459" s="1">
-        <x:v>0</x:v>
+        <x:v>8650</x:v>
       </x:c>
       <x:c r="G3459" s="1">
-        <x:v>500</x:v>
+        <x:v>28150</x:v>
       </x:c>
     </x:row>
     <x:row r="3460" spans="1:7">
@@ -90936,10 +90936,10 @@
         <x:v>3448</x:v>
       </x:c>
       <x:c r="B3475" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="C3475" s="1">
-        <x:v>3000</x:v>
+        <x:v>22500</x:v>
       </x:c>
       <x:c r="D3475" s="1">
         <x:v>0</x:v>
@@ -90951,7 +90951,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G3475" s="1">
-        <x:v>3000</x:v>
+        <x:v>22500</x:v>
       </x:c>
     </x:row>
     <x:row r="3476" spans="1:7">
@@ -90959,22 +90959,22 @@
         <x:v>3448</x:v>
       </x:c>
       <x:c r="B3476" s="1" t="s">
-        <x:v>419</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C3476" s="1">
-        <x:v>437150</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D3476" s="1">
-        <x:v>468</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3476" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3476" s="1">
-        <x:v>348550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3476" s="1">
-        <x:v>786168</x:v>
+        <x:v>3000</x:v>
       </x:c>
     </x:row>
     <x:row r="3477" spans="1:7">
@@ -90982,22 +90982,22 @@
         <x:v>3448</x:v>
       </x:c>
       <x:c r="B3477" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="C3477" s="1">
-        <x:v>22500</x:v>
+        <x:v>437150</x:v>
       </x:c>
       <x:c r="D3477" s="1">
-        <x:v>0</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="E3477" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3477" s="1">
-        <x:v>0</x:v>
+        <x:v>348550</x:v>
       </x:c>
       <x:c r="G3477" s="1">
-        <x:v>22500</x:v>
+        <x:v>786168</x:v>
       </x:c>
     </x:row>
     <x:row r="3478" spans="1:7">
@@ -92707,10 +92707,10 @@
         <x:v>3519</x:v>
       </x:c>
       <x:c r="B3552" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C3552" s="1">
-        <x:v>0</x:v>
+        <x:v>130750</x:v>
       </x:c>
       <x:c r="D3552" s="1">
         <x:v>7</x:v>
@@ -92719,10 +92719,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3552" s="1">
-        <x:v>0</x:v>
+        <x:v>83750</x:v>
       </x:c>
       <x:c r="G3552" s="1">
-        <x:v>7</x:v>
+        <x:v>214507</x:v>
       </x:c>
     </x:row>
     <x:row r="3553" spans="1:7">
@@ -92730,10 +92730,10 @@
         <x:v>3519</x:v>
       </x:c>
       <x:c r="B3553" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C3553" s="1">
-        <x:v>130750</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3553" s="1">
         <x:v>7</x:v>
@@ -92742,10 +92742,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3553" s="1">
-        <x:v>83750</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3553" s="1">
-        <x:v>214507</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="3554" spans="1:7">

--- a/reports/pro-oil/pro-oil-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-oil/pro-oil-candidate-lobby-lifetime-report.xlsx
@@ -16186,7 +16186,7 @@
         <x:v>279</x:v>
       </x:c>
       <x:c r="B225" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C225" s="1">
         <x:v>0</x:v>
@@ -16198,10 +16198,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F225" s="1">
-        <x:v>1000</x:v>
+        <x:v>2300</x:v>
       </x:c>
       <x:c r="G225" s="1">
-        <x:v>1000</x:v>
+        <x:v>2300</x:v>
       </x:c>
     </x:row>
     <x:row r="226" spans="1:7">
@@ -16209,7 +16209,7 @@
         <x:v>279</x:v>
       </x:c>
       <x:c r="B226" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C226" s="1">
         <x:v>0</x:v>
@@ -16221,10 +16221,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F226" s="1">
-        <x:v>2300</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G226" s="1">
-        <x:v>2300</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="227" spans="1:7">
@@ -31481,22 +31481,22 @@
         <x:v>938</x:v>
       </x:c>
       <x:c r="B890" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="C890" s="1">
-        <x:v>91000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D890" s="1">
-        <x:v>118</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E890" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F890" s="1">
-        <x:v>26100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G890" s="1">
-        <x:v>117218</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="891" spans="1:7">
@@ -31504,22 +31504,22 @@
         <x:v>938</x:v>
       </x:c>
       <x:c r="B891" s="1" t="s">
-        <x:v>299</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C891" s="1">
-        <x:v>0</x:v>
+        <x:v>91000</x:v>
       </x:c>
       <x:c r="D891" s="1">
-        <x:v>59</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E891" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F891" s="1">
-        <x:v>0</x:v>
+        <x:v>26100</x:v>
       </x:c>
       <x:c r="G891" s="1">
-        <x:v>59</x:v>
+        <x:v>117218</x:v>
       </x:c>
     </x:row>
     <x:row r="892" spans="1:7">
@@ -46546,10 +46546,10 @@
         <x:v>1584</x:v>
       </x:c>
       <x:c r="B1545" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C1545" s="1">
-        <x:v>0</x:v>
+        <x:v>82250</x:v>
       </x:c>
       <x:c r="D1545" s="1">
         <x:v>0</x:v>
@@ -46558,10 +46558,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1545" s="1">
-        <x:v>1000</x:v>
+        <x:v>9000</x:v>
       </x:c>
       <x:c r="G1545" s="1">
-        <x:v>1000</x:v>
+        <x:v>91250</x:v>
       </x:c>
     </x:row>
     <x:row r="1546" spans="1:7">
@@ -46569,10 +46569,10 @@
         <x:v>1584</x:v>
       </x:c>
       <x:c r="B1546" s="1" t="s">
-        <x:v>165</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C1546" s="1">
-        <x:v>82250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1546" s="1">
         <x:v>0</x:v>
@@ -46581,10 +46581,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1546" s="1">
-        <x:v>9000</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1546" s="1">
-        <x:v>91250</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="1547" spans="1:7">
@@ -47236,10 +47236,10 @@
         <x:v>1611</x:v>
       </x:c>
       <x:c r="B1575" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="C1575" s="1">
-        <x:v>8000</x:v>
+        <x:v>181700</x:v>
       </x:c>
       <x:c r="D1575" s="1">
         <x:v>0</x:v>
@@ -47248,10 +47248,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1575" s="1">
-        <x:v>66000</x:v>
+        <x:v>168050</x:v>
       </x:c>
       <x:c r="G1575" s="1">
-        <x:v>74000</x:v>
+        <x:v>349750</x:v>
       </x:c>
     </x:row>
     <x:row r="1576" spans="1:7">
@@ -47259,10 +47259,10 @@
         <x:v>1611</x:v>
       </x:c>
       <x:c r="B1576" s="1" t="s">
-        <x:v>419</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C1576" s="1">
-        <x:v>181700</x:v>
+        <x:v>8000</x:v>
       </x:c>
       <x:c r="D1576" s="1">
         <x:v>0</x:v>
@@ -47271,10 +47271,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1576" s="1">
-        <x:v>168050</x:v>
+        <x:v>66000</x:v>
       </x:c>
       <x:c r="G1576" s="1">
-        <x:v>349750</x:v>
+        <x:v>74000</x:v>
       </x:c>
     </x:row>
     <x:row r="1577" spans="1:7">
@@ -50847,10 +50847,10 @@
         <x:v>1765</x:v>
       </x:c>
       <x:c r="B1732" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1732" s="1">
-        <x:v>485</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1732" s="1">
         <x:v>0</x:v>
@@ -50859,10 +50859,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1732" s="1">
-        <x:v>72700</x:v>
+        <x:v>16350</x:v>
       </x:c>
       <x:c r="G1732" s="1">
-        <x:v>73185</x:v>
+        <x:v>18850</x:v>
       </x:c>
     </x:row>
     <x:row r="1733" spans="1:7">
@@ -50870,10 +50870,10 @@
         <x:v>1765</x:v>
       </x:c>
       <x:c r="B1733" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C1733" s="1">
-        <x:v>2500</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="D1733" s="1">
         <x:v>0</x:v>
@@ -50882,10 +50882,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1733" s="1">
-        <x:v>16350</x:v>
+        <x:v>72700</x:v>
       </x:c>
       <x:c r="G1733" s="1">
-        <x:v>18850</x:v>
+        <x:v>73185</x:v>
       </x:c>
     </x:row>
     <x:row r="1734" spans="1:7">
@@ -53009,10 +53009,10 @@
         <x:v>1856</x:v>
       </x:c>
       <x:c r="B1826" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C1826" s="1">
-        <x:v>147100</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="D1826" s="1">
         <x:v>0</x:v>
@@ -53021,10 +53021,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1826" s="1">
-        <x:v>34550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1826" s="1">
-        <x:v>181650</x:v>
+        <x:v>-1000</x:v>
       </x:c>
     </x:row>
     <x:row r="1827" spans="1:7">
@@ -53032,10 +53032,10 @@
         <x:v>1856</x:v>
       </x:c>
       <x:c r="B1827" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C1827" s="1">
-        <x:v>-1000</x:v>
+        <x:v>147100</x:v>
       </x:c>
       <x:c r="D1827" s="1">
         <x:v>0</x:v>
@@ -53044,10 +53044,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1827" s="1">
-        <x:v>0</x:v>
+        <x:v>34550</x:v>
       </x:c>
       <x:c r="G1827" s="1">
-        <x:v>-1000</x:v>
+        <x:v>181650</x:v>
       </x:c>
     </x:row>
     <x:row r="1828" spans="1:7">
@@ -56459,10 +56459,10 @@
         <x:v>2002</x:v>
       </x:c>
       <x:c r="B1976" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1976" s="1">
-        <x:v>187150</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1976" s="1">
         <x:v>31</x:v>
@@ -56471,10 +56471,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1976" s="1">
-        <x:v>6150</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1976" s="1">
-        <x:v>193331</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="1977" spans="1:7">
@@ -56482,10 +56482,10 @@
         <x:v>2002</x:v>
       </x:c>
       <x:c r="B1977" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C1977" s="1">
-        <x:v>0</x:v>
+        <x:v>187150</x:v>
       </x:c>
       <x:c r="D1977" s="1">
         <x:v>31</x:v>
@@ -56494,10 +56494,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1977" s="1">
-        <x:v>0</x:v>
+        <x:v>6150</x:v>
       </x:c>
       <x:c r="G1977" s="1">
-        <x:v>31</x:v>
+        <x:v>193331</x:v>
       </x:c>
     </x:row>
     <x:row r="1978" spans="1:7">
@@ -59955,10 +59955,10 @@
         <x:v>2150</x:v>
       </x:c>
       <x:c r="B2128" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="C2128" s="1">
-        <x:v>11000</x:v>
+        <x:v>960100</x:v>
       </x:c>
       <x:c r="D2128" s="1">
         <x:v>0</x:v>
@@ -59967,10 +59967,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2128" s="1">
-        <x:v>25550</x:v>
+        <x:v>882230</x:v>
       </x:c>
       <x:c r="G2128" s="1">
-        <x:v>36550</x:v>
+        <x:v>1842330</x:v>
       </x:c>
     </x:row>
     <x:row r="2129" spans="1:7">
@@ -59978,10 +59978,10 @@
         <x:v>2150</x:v>
       </x:c>
       <x:c r="B2129" s="1" t="s">
-        <x:v>193</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C2129" s="1">
-        <x:v>960100</x:v>
+        <x:v>11000</x:v>
       </x:c>
       <x:c r="D2129" s="1">
         <x:v>0</x:v>
@@ -59990,10 +59990,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2129" s="1">
-        <x:v>882230</x:v>
+        <x:v>25550</x:v>
       </x:c>
       <x:c r="G2129" s="1">
-        <x:v>1842330</x:v>
+        <x:v>36550</x:v>
       </x:c>
     </x:row>
     <x:row r="2130" spans="1:7">
@@ -60070,22 +60070,22 @@
         <x:v>2154</x:v>
       </x:c>
       <x:c r="B2133" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C2133" s="1">
+        <x:v>22450</x:v>
+      </x:c>
+      <x:c r="D2133" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E2133" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F2133" s="1">
         <x:v>250</x:v>
       </x:c>
-      <x:c r="D2133" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E2133" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F2133" s="1">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="G2133" s="1">
-        <x:v>250</x:v>
+        <x:v>22700</x:v>
       </x:c>
     </x:row>
     <x:row r="2134" spans="1:7">
@@ -60093,10 +60093,10 @@
         <x:v>2154</x:v>
       </x:c>
       <x:c r="B2134" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C2134" s="1">
-        <x:v>22450</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="D2134" s="1">
         <x:v>0</x:v>
@@ -60105,10 +60105,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2134" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G2134" s="1">
         <x:v>250</x:v>
-      </x:c>
-      <x:c r="G2134" s="1">
-        <x:v>22700</x:v>
       </x:c>
     </x:row>
     <x:row r="2135" spans="1:7">
@@ -72697,10 +72697,10 @@
         <x:v>2698</x:v>
       </x:c>
       <x:c r="B2682" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="C2682" s="1">
-        <x:v>139000</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D2682" s="1">
         <x:v>0</x:v>
@@ -72709,10 +72709,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2682" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2682" s="1">
-        <x:v>139500</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="2683" spans="1:7">
@@ -72720,10 +72720,10 @@
         <x:v>2698</x:v>
       </x:c>
       <x:c r="B2683" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C2683" s="1">
-        <x:v>7000</x:v>
+        <x:v>139000</x:v>
       </x:c>
       <x:c r="D2683" s="1">
         <x:v>0</x:v>
@@ -72732,10 +72732,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2683" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G2683" s="1">
-        <x:v>7000</x:v>
+        <x:v>139500</x:v>
       </x:c>
     </x:row>
     <x:row r="2684" spans="1:7">
@@ -78401,10 +78401,10 @@
         <x:v>2940</x:v>
       </x:c>
       <x:c r="B2930" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="C2930" s="1">
-        <x:v>206000</x:v>
+        <x:v>37500</x:v>
       </x:c>
       <x:c r="D2930" s="1">
         <x:v>0</x:v>
@@ -78413,10 +78413,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2930" s="1">
-        <x:v>45600</x:v>
+        <x:v>8000</x:v>
       </x:c>
       <x:c r="G2930" s="1">
-        <x:v>251600</x:v>
+        <x:v>45500</x:v>
       </x:c>
     </x:row>
     <x:row r="2931" spans="1:7">
@@ -78424,10 +78424,10 @@
         <x:v>2940</x:v>
       </x:c>
       <x:c r="B2931" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C2931" s="1">
-        <x:v>37500</x:v>
+        <x:v>206000</x:v>
       </x:c>
       <x:c r="D2931" s="1">
         <x:v>0</x:v>
@@ -78436,10 +78436,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2931" s="1">
-        <x:v>8000</x:v>
+        <x:v>45600</x:v>
       </x:c>
       <x:c r="G2931" s="1">
-        <x:v>45500</x:v>
+        <x:v>251600</x:v>
       </x:c>
     </x:row>
     <x:row r="2932" spans="1:7">
@@ -78815,10 +78815,10 @@
         <x:v>2957</x:v>
       </x:c>
       <x:c r="B2948" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C2948" s="1">
-        <x:v>12000</x:v>
+        <x:v>99950</x:v>
       </x:c>
       <x:c r="D2948" s="1">
         <x:v>0</x:v>
@@ -78827,10 +78827,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2948" s="1">
-        <x:v>0</x:v>
+        <x:v>6650</x:v>
       </x:c>
       <x:c r="G2948" s="1">
-        <x:v>12000</x:v>
+        <x:v>106600</x:v>
       </x:c>
     </x:row>
     <x:row r="2949" spans="1:7">
@@ -78838,10 +78838,10 @@
         <x:v>2957</x:v>
       </x:c>
       <x:c r="B2949" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C2949" s="1">
-        <x:v>99950</x:v>
+        <x:v>12000</x:v>
       </x:c>
       <x:c r="D2949" s="1">
         <x:v>0</x:v>
@@ -78850,10 +78850,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2949" s="1">
-        <x:v>6650</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2949" s="1">
-        <x:v>106600</x:v>
+        <x:v>12000</x:v>
       </x:c>
     </x:row>
     <x:row r="2950" spans="1:7">
@@ -79528,10 +79528,10 @@
         <x:v>2986</x:v>
       </x:c>
       <x:c r="B2979" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>750</x:v>
       </x:c>
       <x:c r="C2979" s="1">
-        <x:v>5000</x:v>
+        <x:v>286800</x:v>
       </x:c>
       <x:c r="D2979" s="1">
         <x:v>0</x:v>
@@ -79540,10 +79540,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2979" s="1">
-        <x:v>0</x:v>
+        <x:v>75150</x:v>
       </x:c>
       <x:c r="G2979" s="1">
-        <x:v>5000</x:v>
+        <x:v>361950</x:v>
       </x:c>
     </x:row>
     <x:row r="2980" spans="1:7">
@@ -79551,10 +79551,10 @@
         <x:v>2986</x:v>
       </x:c>
       <x:c r="B2980" s="1" t="s">
-        <x:v>750</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C2980" s="1">
-        <x:v>286800</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D2980" s="1">
         <x:v>0</x:v>
@@ -79563,10 +79563,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2980" s="1">
-        <x:v>75150</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2980" s="1">
-        <x:v>361950</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="2981" spans="1:7">
@@ -81299,22 +81299,22 @@
         <x:v>3061</x:v>
       </x:c>
       <x:c r="B3056" s="1" t="s">
-        <x:v>258</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C3056" s="1">
-        <x:v>7000</x:v>
+        <x:v>71750</x:v>
       </x:c>
       <x:c r="D3056" s="1">
-        <x:v>0</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="E3056" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3056" s="1">
-        <x:v>0</x:v>
+        <x:v>77150</x:v>
       </x:c>
       <x:c r="G3056" s="1">
-        <x:v>7000</x:v>
+        <x:v>149077</x:v>
       </x:c>
     </x:row>
     <x:row r="3057" spans="1:7">
@@ -81322,22 +81322,22 @@
         <x:v>3061</x:v>
       </x:c>
       <x:c r="B3057" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="C3057" s="1">
-        <x:v>71750</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D3057" s="1">
-        <x:v>177</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3057" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3057" s="1">
-        <x:v>77150</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3057" s="1">
-        <x:v>149077</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="3058" spans="1:7">
@@ -81874,10 +81874,10 @@
         <x:v>3085</x:v>
       </x:c>
       <x:c r="B3081" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C3081" s="1">
-        <x:v>10500</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D3081" s="1">
         <x:v>0</x:v>
@@ -81886,10 +81886,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3081" s="1">
-        <x:v>31300</x:v>
+        <x:v>33600</x:v>
       </x:c>
       <x:c r="G3081" s="1">
-        <x:v>41800</x:v>
+        <x:v>38600</x:v>
       </x:c>
     </x:row>
     <x:row r="3082" spans="1:7">
@@ -81897,10 +81897,10 @@
         <x:v>3085</x:v>
       </x:c>
       <x:c r="B3082" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C3082" s="1">
-        <x:v>5000</x:v>
+        <x:v>10500</x:v>
       </x:c>
       <x:c r="D3082" s="1">
         <x:v>0</x:v>
@@ -81909,10 +81909,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3082" s="1">
-        <x:v>33600</x:v>
+        <x:v>31300</x:v>
       </x:c>
       <x:c r="G3082" s="1">
-        <x:v>38600</x:v>
+        <x:v>41800</x:v>
       </x:c>
     </x:row>
     <x:row r="3083" spans="1:7">
@@ -82541,22 +82541,22 @@
         <x:v>3109</x:v>
       </x:c>
       <x:c r="B3110" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C3110" s="1">
-        <x:v>307450</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3110" s="1">
-        <x:v>0</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3110" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3110" s="1">
-        <x:v>40550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3110" s="1">
-        <x:v>348000</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="3111" spans="1:7">
@@ -82564,22 +82564,22 @@
         <x:v>3109</x:v>
       </x:c>
       <x:c r="B3111" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C3111" s="1">
-        <x:v>0</x:v>
+        <x:v>307450</x:v>
       </x:c>
       <x:c r="D3111" s="1">
-        <x:v>59</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3111" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3111" s="1">
-        <x:v>0</x:v>
+        <x:v>40550</x:v>
       </x:c>
       <x:c r="G3111" s="1">
-        <x:v>59</x:v>
+        <x:v>348000</x:v>
       </x:c>
     </x:row>
     <x:row r="3112" spans="1:7">
@@ -83645,10 +83645,10 @@
         <x:v>3152</x:v>
       </x:c>
       <x:c r="B3158" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C3158" s="1">
-        <x:v>20000</x:v>
+        <x:v>157500</x:v>
       </x:c>
       <x:c r="D3158" s="1">
         <x:v>0</x:v>
@@ -83657,10 +83657,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3158" s="1">
-        <x:v>6000</x:v>
+        <x:v>45517</x:v>
       </x:c>
       <x:c r="G3158" s="1">
-        <x:v>26000</x:v>
+        <x:v>203017</x:v>
       </x:c>
     </x:row>
     <x:row r="3159" spans="1:7">
@@ -83668,10 +83668,10 @@
         <x:v>3152</x:v>
       </x:c>
       <x:c r="B3159" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C3159" s="1">
-        <x:v>157500</x:v>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="D3159" s="1">
         <x:v>0</x:v>
@@ -83680,10 +83680,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3159" s="1">
-        <x:v>45517</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="G3159" s="1">
-        <x:v>203017</x:v>
+        <x:v>26000</x:v>
       </x:c>
     </x:row>
     <x:row r="3160" spans="1:7">
@@ -85232,10 +85232,10 @@
         <x:v>3219</x:v>
       </x:c>
       <x:c r="B3227" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C3227" s="1">
-        <x:v>3000</x:v>
+        <x:v>2300</x:v>
       </x:c>
       <x:c r="D3227" s="1">
         <x:v>0</x:v>
@@ -85244,10 +85244,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3227" s="1">
-        <x:v>6000</x:v>
+        <x:v>8850</x:v>
       </x:c>
       <x:c r="G3227" s="1">
-        <x:v>9000</x:v>
+        <x:v>11150</x:v>
       </x:c>
     </x:row>
     <x:row r="3228" spans="1:7">
@@ -85255,10 +85255,10 @@
         <x:v>3219</x:v>
       </x:c>
       <x:c r="B3228" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C3228" s="1">
-        <x:v>2300</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D3228" s="1">
         <x:v>0</x:v>
@@ -85267,10 +85267,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3228" s="1">
-        <x:v>8850</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="G3228" s="1">
-        <x:v>11150</x:v>
+        <x:v>9000</x:v>
       </x:c>
     </x:row>
     <x:row r="3229" spans="1:7">
@@ -85945,10 +85945,10 @@
         <x:v>3246</x:v>
       </x:c>
       <x:c r="B3258" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C3258" s="1">
-        <x:v>29500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3258" s="1">
         <x:v>0</x:v>
@@ -85957,10 +85957,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3258" s="1">
-        <x:v>12550</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G3258" s="1">
-        <x:v>42050</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="3259" spans="1:7">
@@ -85968,10 +85968,10 @@
         <x:v>3246</x:v>
       </x:c>
       <x:c r="B3259" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C3259" s="1">
-        <x:v>0</x:v>
+        <x:v>29500</x:v>
       </x:c>
       <x:c r="D3259" s="1">
         <x:v>0</x:v>
@@ -85980,10 +85980,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3259" s="1">
-        <x:v>1000</x:v>
+        <x:v>12550</x:v>
       </x:c>
       <x:c r="G3259" s="1">
-        <x:v>1000</x:v>
+        <x:v>42050</x:v>
       </x:c>
     </x:row>
     <x:row r="3260" spans="1:7">
@@ -87969,22 +87969,22 @@
         <x:v>3332</x:v>
       </x:c>
       <x:c r="B3346" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C3346" s="1">
-        <x:v>0</x:v>
+        <x:v>332220</x:v>
       </x:c>
       <x:c r="D3346" s="1">
-        <x:v>59</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3346" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3346" s="1">
-        <x:v>0</x:v>
+        <x:v>299023</x:v>
       </x:c>
       <x:c r="G3346" s="1">
-        <x:v>59</x:v>
+        <x:v>631243</x:v>
       </x:c>
     </x:row>
     <x:row r="3347" spans="1:7">
@@ -87992,22 +87992,22 @@
         <x:v>3332</x:v>
       </x:c>
       <x:c r="B3347" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="C3347" s="1">
-        <x:v>332220</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D3347" s="1">
-        <x:v>0</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E3347" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3347" s="1">
-        <x:v>299023</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3347" s="1">
-        <x:v>631243</x:v>
+        <x:v>15063</x:v>
       </x:c>
     </x:row>
     <x:row r="3348" spans="1:7">
@@ -88015,13 +88015,13 @@
         <x:v>3332</x:v>
       </x:c>
       <x:c r="B3348" s="1" t="s">
-        <x:v>258</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C3348" s="1">
-        <x:v>15000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3348" s="1">
-        <x:v>63</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3348" s="1">
         <x:v>0</x:v>
@@ -88030,7 +88030,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G3348" s="1">
-        <x:v>15063</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="3349" spans="1:7">
@@ -88084,22 +88084,22 @@
         <x:v>3334</x:v>
       </x:c>
       <x:c r="B3351" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C3351" s="1">
-        <x:v>116050</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D3351" s="1">
-        <x:v>236</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E3351" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3351" s="1">
-        <x:v>47699</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="G3351" s="1">
-        <x:v>163985</x:v>
+        <x:v>14063</x:v>
       </x:c>
     </x:row>
     <x:row r="3352" spans="1:7">
@@ -88107,22 +88107,22 @@
         <x:v>3334</x:v>
       </x:c>
       <x:c r="B3352" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C3352" s="1">
-        <x:v>7000</x:v>
+        <x:v>116050</x:v>
       </x:c>
       <x:c r="D3352" s="1">
-        <x:v>63</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="E3352" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3352" s="1">
-        <x:v>7000</x:v>
+        <x:v>47699</x:v>
       </x:c>
       <x:c r="G3352" s="1">
-        <x:v>14063</x:v>
+        <x:v>163985</x:v>
       </x:c>
     </x:row>
     <x:row r="3353" spans="1:7">
@@ -89901,22 +89901,22 @@
         <x:v>3408</x:v>
       </x:c>
       <x:c r="B3430" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C3430" s="1">
-        <x:v>38500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3430" s="1">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E3430" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3430" s="1">
-        <x:v>26250</x:v>
+        <x:v>10700</x:v>
       </x:c>
       <x:c r="G3430" s="1">
-        <x:v>64750</x:v>
+        <x:v>10701</x:v>
       </x:c>
     </x:row>
     <x:row r="3431" spans="1:7">
@@ -89924,22 +89924,22 @@
         <x:v>3408</x:v>
       </x:c>
       <x:c r="B3431" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C3431" s="1">
-        <x:v>0</x:v>
+        <x:v>38500</x:v>
       </x:c>
       <x:c r="D3431" s="1">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3431" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3431" s="1">
-        <x:v>10700</x:v>
+        <x:v>26250</x:v>
       </x:c>
       <x:c r="G3431" s="1">
-        <x:v>10701</x:v>
+        <x:v>64750</x:v>
       </x:c>
     </x:row>
     <x:row r="3432" spans="1:7">
@@ -90683,22 +90683,22 @@
         <x:v>3438</x:v>
       </x:c>
       <x:c r="B3464" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C3464" s="1">
-        <x:v>0</x:v>
+        <x:v>47850</x:v>
       </x:c>
       <x:c r="D3464" s="1">
-        <x:v>59</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3464" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3464" s="1">
-        <x:v>0</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G3464" s="1">
-        <x:v>59</x:v>
+        <x:v>52850</x:v>
       </x:c>
     </x:row>
     <x:row r="3465" spans="1:7">
@@ -90706,22 +90706,22 @@
         <x:v>3438</x:v>
       </x:c>
       <x:c r="B3465" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C3465" s="1">
-        <x:v>47850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3465" s="1">
-        <x:v>0</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3465" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3465" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3465" s="1">
-        <x:v>52850</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="3466" spans="1:7">
@@ -90936,10 +90936,10 @@
         <x:v>3448</x:v>
       </x:c>
       <x:c r="B3475" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C3475" s="1">
-        <x:v>22500</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D3475" s="1">
         <x:v>0</x:v>
@@ -90951,7 +90951,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G3475" s="1">
-        <x:v>22500</x:v>
+        <x:v>3000</x:v>
       </x:c>
     </x:row>
     <x:row r="3476" spans="1:7">
@@ -90959,22 +90959,22 @@
         <x:v>3448</x:v>
       </x:c>
       <x:c r="B3476" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="C3476" s="1">
-        <x:v>3000</x:v>
+        <x:v>437150</x:v>
       </x:c>
       <x:c r="D3476" s="1">
-        <x:v>0</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="E3476" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3476" s="1">
-        <x:v>0</x:v>
+        <x:v>348550</x:v>
       </x:c>
       <x:c r="G3476" s="1">
-        <x:v>3000</x:v>
+        <x:v>786168</x:v>
       </x:c>
     </x:row>
     <x:row r="3477" spans="1:7">
@@ -90982,22 +90982,22 @@
         <x:v>3448</x:v>
       </x:c>
       <x:c r="B3477" s="1" t="s">
-        <x:v>419</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="C3477" s="1">
-        <x:v>437150</x:v>
+        <x:v>22500</x:v>
       </x:c>
       <x:c r="D3477" s="1">
-        <x:v>468</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3477" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3477" s="1">
-        <x:v>348550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3477" s="1">
-        <x:v>786168</x:v>
+        <x:v>22500</x:v>
       </x:c>
     </x:row>
     <x:row r="3478" spans="1:7">
@@ -92707,10 +92707,10 @@
         <x:v>3519</x:v>
       </x:c>
       <x:c r="B3552" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C3552" s="1">
-        <x:v>130750</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3552" s="1">
         <x:v>7</x:v>
@@ -92719,10 +92719,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3552" s="1">
-        <x:v>83750</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3552" s="1">
-        <x:v>214507</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="3553" spans="1:7">
@@ -92730,10 +92730,10 @@
         <x:v>3519</x:v>
       </x:c>
       <x:c r="B3553" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C3553" s="1">
-        <x:v>0</x:v>
+        <x:v>130750</x:v>
       </x:c>
       <x:c r="D3553" s="1">
         <x:v>7</x:v>
@@ -92742,10 +92742,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3553" s="1">
-        <x:v>0</x:v>
+        <x:v>83750</x:v>
       </x:c>
       <x:c r="G3553" s="1">
-        <x:v>7</x:v>
+        <x:v>214507</x:v>
       </x:c>
     </x:row>
     <x:row r="3554" spans="1:7">

--- a/reports/pro-oil/pro-oil-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-oil/pro-oil-candidate-lobby-lifetime-report.xlsx
@@ -19452,10 +19452,10 @@
         <x:v>421</x:v>
       </x:c>
       <x:c r="B367" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C367" s="1">
-        <x:v>107540</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D367" s="1">
         <x:v>0</x:v>
@@ -19464,10 +19464,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F367" s="1">
-        <x:v>59170</x:v>
+        <x:v>25150</x:v>
       </x:c>
       <x:c r="G367" s="1">
-        <x:v>166710</x:v>
+        <x:v>28150</x:v>
       </x:c>
     </x:row>
     <x:row r="368" spans="1:7">
@@ -19475,10 +19475,10 @@
         <x:v>421</x:v>
       </x:c>
       <x:c r="B368" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C368" s="1">
-        <x:v>3000</x:v>
+        <x:v>107540</x:v>
       </x:c>
       <x:c r="D368" s="1">
         <x:v>0</x:v>
@@ -19487,10 +19487,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F368" s="1">
-        <x:v>25150</x:v>
+        <x:v>59170</x:v>
       </x:c>
       <x:c r="G368" s="1">
-        <x:v>28150</x:v>
+        <x:v>166710</x:v>
       </x:c>
     </x:row>
     <x:row r="369" spans="1:7">
@@ -27295,22 +27295,22 @@
         <x:v>760</x:v>
       </x:c>
       <x:c r="B708" s="1" t="s">
-        <x:v>750</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C708" s="1">
-        <x:v>418533</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D708" s="1">
-        <x:v>118</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E708" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F708" s="1">
-        <x:v>51350</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G708" s="1">
-        <x:v>470001</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="709" spans="1:7">
@@ -27318,22 +27318,22 @@
         <x:v>760</x:v>
       </x:c>
       <x:c r="B709" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>750</x:v>
       </x:c>
       <x:c r="C709" s="1">
-        <x:v>25500</x:v>
+        <x:v>418533</x:v>
       </x:c>
       <x:c r="D709" s="1">
-        <x:v>0</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E709" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F709" s="1">
-        <x:v>0</x:v>
+        <x:v>51350</x:v>
       </x:c>
       <x:c r="G709" s="1">
-        <x:v>25500</x:v>
+        <x:v>470001</x:v>
       </x:c>
     </x:row>
     <x:row r="710" spans="1:7">
@@ -30883,10 +30883,10 @@
         <x:v>914</x:v>
       </x:c>
       <x:c r="B864" s="1" t="s">
-        <x:v>260</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C864" s="1">
-        <x:v>3000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D864" s="1">
         <x:v>0</x:v>
@@ -30895,10 +30895,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F864" s="1">
-        <x:v>12950</x:v>
+        <x:v>14450</x:v>
       </x:c>
       <x:c r="G864" s="1">
-        <x:v>15950</x:v>
+        <x:v>14450</x:v>
       </x:c>
     </x:row>
     <x:row r="865" spans="1:7">
@@ -30906,10 +30906,10 @@
         <x:v>914</x:v>
       </x:c>
       <x:c r="B865" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="C865" s="1">
-        <x:v>0</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D865" s="1">
         <x:v>0</x:v>
@@ -30918,10 +30918,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F865" s="1">
-        <x:v>14450</x:v>
+        <x:v>12950</x:v>
       </x:c>
       <x:c r="G865" s="1">
-        <x:v>14450</x:v>
+        <x:v>15950</x:v>
       </x:c>
     </x:row>
     <x:row r="866" spans="1:7">
@@ -31481,22 +31481,22 @@
         <x:v>938</x:v>
       </x:c>
       <x:c r="B890" s="1" t="s">
-        <x:v>299</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C890" s="1">
-        <x:v>0</x:v>
+        <x:v>91000</x:v>
       </x:c>
       <x:c r="D890" s="1">
-        <x:v>59</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E890" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F890" s="1">
-        <x:v>0</x:v>
+        <x:v>26100</x:v>
       </x:c>
       <x:c r="G890" s="1">
-        <x:v>59</x:v>
+        <x:v>117218</x:v>
       </x:c>
     </x:row>
     <x:row r="891" spans="1:7">
@@ -31504,22 +31504,22 @@
         <x:v>938</x:v>
       </x:c>
       <x:c r="B891" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="C891" s="1">
-        <x:v>91000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D891" s="1">
-        <x:v>118</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E891" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F891" s="1">
-        <x:v>26100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G891" s="1">
-        <x:v>117218</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="892" spans="1:7">
@@ -38933,10 +38933,10 @@
         <x:v>1255</x:v>
       </x:c>
       <x:c r="B1214" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C1214" s="1">
-        <x:v>12000</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D1214" s="1">
         <x:v>0</x:v>
@@ -38945,10 +38945,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1214" s="1">
-        <x:v>12450</x:v>
+        <x:v>50751</x:v>
       </x:c>
       <x:c r="G1214" s="1">
-        <x:v>24450</x:v>
+        <x:v>53751</x:v>
       </x:c>
     </x:row>
     <x:row r="1215" spans="1:7">
@@ -38956,10 +38956,10 @@
         <x:v>1255</x:v>
       </x:c>
       <x:c r="B1215" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C1215" s="1">
-        <x:v>3000</x:v>
+        <x:v>12000</x:v>
       </x:c>
       <x:c r="D1215" s="1">
         <x:v>0</x:v>
@@ -38968,10 +38968,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1215" s="1">
-        <x:v>50751</x:v>
+        <x:v>12450</x:v>
       </x:c>
       <x:c r="G1215" s="1">
-        <x:v>53751</x:v>
+        <x:v>24450</x:v>
       </x:c>
     </x:row>
     <x:row r="1216" spans="1:7">
@@ -53009,10 +53009,10 @@
         <x:v>1856</x:v>
       </x:c>
       <x:c r="B1826" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C1826" s="1">
-        <x:v>-1000</x:v>
+        <x:v>147100</x:v>
       </x:c>
       <x:c r="D1826" s="1">
         <x:v>0</x:v>
@@ -53021,10 +53021,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1826" s="1">
-        <x:v>0</x:v>
+        <x:v>34550</x:v>
       </x:c>
       <x:c r="G1826" s="1">
-        <x:v>-1000</x:v>
+        <x:v>181650</x:v>
       </x:c>
     </x:row>
     <x:row r="1827" spans="1:7">
@@ -53032,10 +53032,10 @@
         <x:v>1856</x:v>
       </x:c>
       <x:c r="B1827" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C1827" s="1">
-        <x:v>147100</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="D1827" s="1">
         <x:v>0</x:v>
@@ -53044,10 +53044,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1827" s="1">
-        <x:v>34550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1827" s="1">
-        <x:v>181650</x:v>
+        <x:v>-1000</x:v>
       </x:c>
     </x:row>
     <x:row r="1828" spans="1:7">
@@ -53193,7 +53193,7 @@
         <x:v>1863</x:v>
       </x:c>
       <x:c r="B1834" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1834" s="1">
         <x:v>0</x:v>
@@ -53216,7 +53216,7 @@
         <x:v>1863</x:v>
       </x:c>
       <x:c r="B1835" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C1835" s="1">
         <x:v>0</x:v>
@@ -56459,10 +56459,10 @@
         <x:v>2002</x:v>
       </x:c>
       <x:c r="B1976" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C1976" s="1">
-        <x:v>0</x:v>
+        <x:v>187150</x:v>
       </x:c>
       <x:c r="D1976" s="1">
         <x:v>31</x:v>
@@ -56471,10 +56471,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1976" s="1">
-        <x:v>0</x:v>
+        <x:v>6150</x:v>
       </x:c>
       <x:c r="G1976" s="1">
-        <x:v>31</x:v>
+        <x:v>193331</x:v>
       </x:c>
     </x:row>
     <x:row r="1977" spans="1:7">
@@ -56482,10 +56482,10 @@
         <x:v>2002</x:v>
       </x:c>
       <x:c r="B1977" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1977" s="1">
-        <x:v>187150</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1977" s="1">
         <x:v>31</x:v>
@@ -56494,10 +56494,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1977" s="1">
-        <x:v>6150</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1977" s="1">
-        <x:v>193331</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="1978" spans="1:7">
@@ -59955,10 +59955,10 @@
         <x:v>2150</x:v>
       </x:c>
       <x:c r="B2128" s="1" t="s">
-        <x:v>193</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C2128" s="1">
-        <x:v>960100</x:v>
+        <x:v>11000</x:v>
       </x:c>
       <x:c r="D2128" s="1">
         <x:v>0</x:v>
@@ -59967,10 +59967,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2128" s="1">
-        <x:v>882230</x:v>
+        <x:v>25550</x:v>
       </x:c>
       <x:c r="G2128" s="1">
-        <x:v>1842330</x:v>
+        <x:v>36550</x:v>
       </x:c>
     </x:row>
     <x:row r="2129" spans="1:7">
@@ -59978,10 +59978,10 @@
         <x:v>2150</x:v>
       </x:c>
       <x:c r="B2129" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="C2129" s="1">
-        <x:v>11000</x:v>
+        <x:v>960100</x:v>
       </x:c>
       <x:c r="D2129" s="1">
         <x:v>0</x:v>
@@ -59990,10 +59990,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2129" s="1">
-        <x:v>25550</x:v>
+        <x:v>882230</x:v>
       </x:c>
       <x:c r="G2129" s="1">
-        <x:v>36550</x:v>
+        <x:v>1842330</x:v>
       </x:c>
     </x:row>
     <x:row r="2130" spans="1:7">
@@ -72536,10 +72536,10 @@
         <x:v>2692</x:v>
       </x:c>
       <x:c r="B2675" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C2675" s="1">
-        <x:v>409250</x:v>
+        <x:v>7061</x:v>
       </x:c>
       <x:c r="D2675" s="1">
         <x:v>0</x:v>
@@ -72548,10 +72548,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2675" s="1">
-        <x:v>159800</x:v>
+        <x:v>23500</x:v>
       </x:c>
       <x:c r="G2675" s="1">
-        <x:v>569050</x:v>
+        <x:v>30561</x:v>
       </x:c>
     </x:row>
     <x:row r="2676" spans="1:7">
@@ -72559,10 +72559,10 @@
         <x:v>2692</x:v>
       </x:c>
       <x:c r="B2676" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C2676" s="1">
-        <x:v>7061</x:v>
+        <x:v>409250</x:v>
       </x:c>
       <x:c r="D2676" s="1">
         <x:v>0</x:v>
@@ -72571,10 +72571,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2676" s="1">
-        <x:v>23500</x:v>
+        <x:v>159800</x:v>
       </x:c>
       <x:c r="G2676" s="1">
-        <x:v>30561</x:v>
+        <x:v>569050</x:v>
       </x:c>
     </x:row>
     <x:row r="2677" spans="1:7">
@@ -72697,10 +72697,10 @@
         <x:v>2698</x:v>
       </x:c>
       <x:c r="B2682" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C2682" s="1">
-        <x:v>7000</x:v>
+        <x:v>139000</x:v>
       </x:c>
       <x:c r="D2682" s="1">
         <x:v>0</x:v>
@@ -72709,10 +72709,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2682" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G2682" s="1">
-        <x:v>7000</x:v>
+        <x:v>139500</x:v>
       </x:c>
     </x:row>
     <x:row r="2683" spans="1:7">
@@ -72720,10 +72720,10 @@
         <x:v>2698</x:v>
       </x:c>
       <x:c r="B2683" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="C2683" s="1">
-        <x:v>139000</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D2683" s="1">
         <x:v>0</x:v>
@@ -72732,10 +72732,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2683" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2683" s="1">
-        <x:v>139500</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="2684" spans="1:7">
@@ -75503,10 +75503,10 @@
         <x:v>2818</x:v>
       </x:c>
       <x:c r="B2804" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C2804" s="1">
-        <x:v>206766</x:v>
+        <x:v>163800</x:v>
       </x:c>
       <x:c r="D2804" s="1">
         <x:v>0</x:v>
@@ -75515,10 +75515,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2804" s="1">
-        <x:v>286825</x:v>
+        <x:v>277645</x:v>
       </x:c>
       <x:c r="G2804" s="1">
-        <x:v>493591</x:v>
+        <x:v>441445</x:v>
       </x:c>
     </x:row>
     <x:row r="2805" spans="1:7">
@@ -75526,10 +75526,10 @@
         <x:v>2818</x:v>
       </x:c>
       <x:c r="B2805" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C2805" s="1">
-        <x:v>163800</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D2805" s="1">
         <x:v>0</x:v>
@@ -75538,10 +75538,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2805" s="1">
-        <x:v>277645</x:v>
+        <x:v>111650</x:v>
       </x:c>
       <x:c r="G2805" s="1">
-        <x:v>441445</x:v>
+        <x:v>126650</x:v>
       </x:c>
     </x:row>
     <x:row r="2806" spans="1:7">
@@ -75549,10 +75549,10 @@
         <x:v>2818</x:v>
       </x:c>
       <x:c r="B2806" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C2806" s="1">
-        <x:v>15000</x:v>
+        <x:v>206766</x:v>
       </x:c>
       <x:c r="D2806" s="1">
         <x:v>0</x:v>
@@ -75561,10 +75561,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2806" s="1">
-        <x:v>111650</x:v>
+        <x:v>286825</x:v>
       </x:c>
       <x:c r="G2806" s="1">
-        <x:v>126650</x:v>
+        <x:v>493591</x:v>
       </x:c>
     </x:row>
     <x:row r="2807" spans="1:7">
@@ -78861,22 +78861,22 @@
         <x:v>2958</x:v>
       </x:c>
       <x:c r="B2950" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="C2950" s="1">
-        <x:v>0</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="D2950" s="1">
-        <x:v>59</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E2950" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2950" s="1">
-        <x:v>0</x:v>
+        <x:v>4950</x:v>
       </x:c>
       <x:c r="G2950" s="1">
-        <x:v>59</x:v>
+        <x:v>14950</x:v>
       </x:c>
     </x:row>
     <x:row r="2951" spans="1:7">
@@ -78884,22 +78884,22 @@
         <x:v>2958</x:v>
       </x:c>
       <x:c r="B2951" s="1" t="s">
-        <x:v>260</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C2951" s="1">
-        <x:v>10000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D2951" s="1">
-        <x:v>0</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E2951" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2951" s="1">
-        <x:v>4950</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2951" s="1">
-        <x:v>14950</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="2952" spans="1:7">
@@ -79528,10 +79528,10 @@
         <x:v>2986</x:v>
       </x:c>
       <x:c r="B2979" s="1" t="s">
-        <x:v>750</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C2979" s="1">
-        <x:v>286800</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D2979" s="1">
         <x:v>0</x:v>
@@ -79540,10 +79540,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2979" s="1">
-        <x:v>75150</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2979" s="1">
-        <x:v>361950</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="2980" spans="1:7">
@@ -79551,10 +79551,10 @@
         <x:v>2986</x:v>
       </x:c>
       <x:c r="B2980" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>750</x:v>
       </x:c>
       <x:c r="C2980" s="1">
-        <x:v>5000</x:v>
+        <x:v>286800</x:v>
       </x:c>
       <x:c r="D2980" s="1">
         <x:v>0</x:v>
@@ -79563,10 +79563,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2980" s="1">
-        <x:v>0</x:v>
+        <x:v>75150</x:v>
       </x:c>
       <x:c r="G2980" s="1">
-        <x:v>5000</x:v>
+        <x:v>361950</x:v>
       </x:c>
     </x:row>
     <x:row r="2981" spans="1:7">
@@ -81874,10 +81874,10 @@
         <x:v>3085</x:v>
       </x:c>
       <x:c r="B3081" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C3081" s="1">
-        <x:v>5000</x:v>
+        <x:v>10500</x:v>
       </x:c>
       <x:c r="D3081" s="1">
         <x:v>0</x:v>
@@ -81886,10 +81886,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3081" s="1">
-        <x:v>33600</x:v>
+        <x:v>31300</x:v>
       </x:c>
       <x:c r="G3081" s="1">
-        <x:v>38600</x:v>
+        <x:v>41800</x:v>
       </x:c>
     </x:row>
     <x:row r="3082" spans="1:7">
@@ -81897,10 +81897,10 @@
         <x:v>3085</x:v>
       </x:c>
       <x:c r="B3082" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C3082" s="1">
-        <x:v>10500</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D3082" s="1">
         <x:v>0</x:v>
@@ -81909,10 +81909,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3082" s="1">
-        <x:v>31300</x:v>
+        <x:v>33600</x:v>
       </x:c>
       <x:c r="G3082" s="1">
-        <x:v>41800</x:v>
+        <x:v>38600</x:v>
       </x:c>
     </x:row>
     <x:row r="3083" spans="1:7">
@@ -82219,7 +82219,7 @@
         <x:v>3096</x:v>
       </x:c>
       <x:c r="B3096" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C3096" s="1">
         <x:v>1000</x:v>
@@ -82231,10 +82231,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3096" s="1">
-        <x:v>4750</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3096" s="1">
-        <x:v>5750</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="3097" spans="1:7">
@@ -82242,7 +82242,7 @@
         <x:v>3096</x:v>
       </x:c>
       <x:c r="B3097" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C3097" s="1">
         <x:v>1000</x:v>
@@ -82254,10 +82254,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3097" s="1">
-        <x:v>0</x:v>
+        <x:v>4750</x:v>
       </x:c>
       <x:c r="G3097" s="1">
-        <x:v>1000</x:v>
+        <x:v>5750</x:v>
       </x:c>
     </x:row>
     <x:row r="3098" spans="1:7">
@@ -82541,22 +82541,22 @@
         <x:v>3109</x:v>
       </x:c>
       <x:c r="B3110" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C3110" s="1">
-        <x:v>0</x:v>
+        <x:v>307450</x:v>
       </x:c>
       <x:c r="D3110" s="1">
-        <x:v>59</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3110" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3110" s="1">
-        <x:v>0</x:v>
+        <x:v>40550</x:v>
       </x:c>
       <x:c r="G3110" s="1">
-        <x:v>59</x:v>
+        <x:v>348000</x:v>
       </x:c>
     </x:row>
     <x:row r="3111" spans="1:7">
@@ -82564,22 +82564,22 @@
         <x:v>3109</x:v>
       </x:c>
       <x:c r="B3111" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C3111" s="1">
-        <x:v>307450</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3111" s="1">
-        <x:v>0</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3111" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3111" s="1">
-        <x:v>40550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3111" s="1">
-        <x:v>348000</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="3112" spans="1:7">
@@ -83277,10 +83277,10 @@
         <x:v>3140</x:v>
       </x:c>
       <x:c r="B3142" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="C3142" s="1">
-        <x:v>5000</x:v>
+        <x:v>48000</x:v>
       </x:c>
       <x:c r="D3142" s="1">
         <x:v>0</x:v>
@@ -83289,10 +83289,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3142" s="1">
-        <x:v>250</x:v>
+        <x:v>38300</x:v>
       </x:c>
       <x:c r="G3142" s="1">
-        <x:v>5250</x:v>
+        <x:v>86300</x:v>
       </x:c>
     </x:row>
     <x:row r="3143" spans="1:7">
@@ -83300,10 +83300,10 @@
         <x:v>3140</x:v>
       </x:c>
       <x:c r="B3143" s="1" t="s">
-        <x:v>156</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C3143" s="1">
-        <x:v>48000</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D3143" s="1">
         <x:v>0</x:v>
@@ -83312,10 +83312,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3143" s="1">
-        <x:v>38300</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G3143" s="1">
-        <x:v>86300</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="3144" spans="1:7">
@@ -83415,7 +83415,7 @@
         <x:v>3143</x:v>
       </x:c>
       <x:c r="B3148" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C3148" s="1">
         <x:v>0</x:v>
@@ -83427,10 +83427,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3148" s="1">
-        <x:v>4300</x:v>
+        <x:v>1100</x:v>
       </x:c>
       <x:c r="G3148" s="1">
-        <x:v>4300</x:v>
+        <x:v>1100</x:v>
       </x:c>
     </x:row>
     <x:row r="3149" spans="1:7">
@@ -83438,7 +83438,7 @@
         <x:v>3143</x:v>
       </x:c>
       <x:c r="B3149" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C3149" s="1">
         <x:v>0</x:v>
@@ -83450,10 +83450,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3149" s="1">
-        <x:v>1100</x:v>
+        <x:v>4300</x:v>
       </x:c>
       <x:c r="G3149" s="1">
-        <x:v>1100</x:v>
+        <x:v>4300</x:v>
       </x:c>
     </x:row>
     <x:row r="3150" spans="1:7">
@@ -83645,10 +83645,10 @@
         <x:v>3152</x:v>
       </x:c>
       <x:c r="B3158" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C3158" s="1">
-        <x:v>157500</x:v>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="D3158" s="1">
         <x:v>0</x:v>
@@ -83657,10 +83657,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3158" s="1">
-        <x:v>45517</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="G3158" s="1">
-        <x:v>203017</x:v>
+        <x:v>26000</x:v>
       </x:c>
     </x:row>
     <x:row r="3159" spans="1:7">
@@ -83668,10 +83668,10 @@
         <x:v>3152</x:v>
       </x:c>
       <x:c r="B3159" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C3159" s="1">
-        <x:v>20000</x:v>
+        <x:v>157500</x:v>
       </x:c>
       <x:c r="D3159" s="1">
         <x:v>0</x:v>
@@ -83680,10 +83680,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3159" s="1">
-        <x:v>6000</x:v>
+        <x:v>45517</x:v>
       </x:c>
       <x:c r="G3159" s="1">
-        <x:v>26000</x:v>
+        <x:v>203017</x:v>
       </x:c>
     </x:row>
     <x:row r="3160" spans="1:7">
@@ -85761,10 +85761,10 @@
         <x:v>3239</x:v>
       </x:c>
       <x:c r="B3250" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C3250" s="1">
-        <x:v>34000</x:v>
+        <x:v>343100</x:v>
       </x:c>
       <x:c r="D3250" s="1">
         <x:v>0</x:v>
@@ -85773,10 +85773,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3250" s="1">
-        <x:v>0</x:v>
+        <x:v>244972</x:v>
       </x:c>
       <x:c r="G3250" s="1">
-        <x:v>34000</x:v>
+        <x:v>588072</x:v>
       </x:c>
     </x:row>
     <x:row r="3251" spans="1:7">
@@ -85784,10 +85784,10 @@
         <x:v>3239</x:v>
       </x:c>
       <x:c r="B3251" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="C3251" s="1">
-        <x:v>343100</x:v>
+        <x:v>34000</x:v>
       </x:c>
       <x:c r="D3251" s="1">
         <x:v>0</x:v>
@@ -85796,10 +85796,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3251" s="1">
-        <x:v>244972</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3251" s="1">
-        <x:v>588072</x:v>
+        <x:v>34000</x:v>
       </x:c>
     </x:row>
     <x:row r="3252" spans="1:7">
@@ -85945,10 +85945,10 @@
         <x:v>3246</x:v>
       </x:c>
       <x:c r="B3258" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C3258" s="1">
-        <x:v>0</x:v>
+        <x:v>29500</x:v>
       </x:c>
       <x:c r="D3258" s="1">
         <x:v>0</x:v>
@@ -85957,10 +85957,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3258" s="1">
-        <x:v>1000</x:v>
+        <x:v>12550</x:v>
       </x:c>
       <x:c r="G3258" s="1">
-        <x:v>1000</x:v>
+        <x:v>42050</x:v>
       </x:c>
     </x:row>
     <x:row r="3259" spans="1:7">
@@ -85968,10 +85968,10 @@
         <x:v>3246</x:v>
       </x:c>
       <x:c r="B3259" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C3259" s="1">
-        <x:v>29500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3259" s="1">
         <x:v>0</x:v>
@@ -85980,10 +85980,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3259" s="1">
-        <x:v>12550</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G3259" s="1">
-        <x:v>42050</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="3260" spans="1:7">
@@ -86152,22 +86152,22 @@
         <x:v>3254</x:v>
       </x:c>
       <x:c r="B3267" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C3267" s="1">
-        <x:v>420650</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D3267" s="1">
-        <x:v>181</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3267" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3267" s="1">
-        <x:v>448881</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3267" s="1">
-        <x:v>869712</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="3268" spans="1:7">
@@ -86175,22 +86175,22 @@
         <x:v>3254</x:v>
       </x:c>
       <x:c r="B3268" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C3268" s="1">
-        <x:v>25500</x:v>
+        <x:v>420650</x:v>
       </x:c>
       <x:c r="D3268" s="1">
-        <x:v>0</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="E3268" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3268" s="1">
-        <x:v>0</x:v>
+        <x:v>448881</x:v>
       </x:c>
       <x:c r="G3268" s="1">
-        <x:v>25500</x:v>
+        <x:v>869712</x:v>
       </x:c>
     </x:row>
     <x:row r="3269" spans="1:7">
@@ -87969,22 +87969,22 @@
         <x:v>3332</x:v>
       </x:c>
       <x:c r="B3346" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C3346" s="1">
-        <x:v>332220</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3346" s="1">
-        <x:v>0</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3346" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3346" s="1">
-        <x:v>299023</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3346" s="1">
-        <x:v>631243</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="3347" spans="1:7">
@@ -88015,22 +88015,22 @@
         <x:v>3332</x:v>
       </x:c>
       <x:c r="B3348" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C3348" s="1">
-        <x:v>0</x:v>
+        <x:v>332220</x:v>
       </x:c>
       <x:c r="D3348" s="1">
-        <x:v>59</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3348" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3348" s="1">
-        <x:v>0</x:v>
+        <x:v>299023</x:v>
       </x:c>
       <x:c r="G3348" s="1">
-        <x:v>59</x:v>
+        <x:v>631243</x:v>
       </x:c>
     </x:row>
     <x:row r="3349" spans="1:7">
@@ -89188,10 +89188,10 @@
         <x:v>3380</x:v>
       </x:c>
       <x:c r="B3399" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="C3399" s="1">
-        <x:v>41550</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D3399" s="1">
         <x:v>0</x:v>
@@ -89200,10 +89200,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3399" s="1">
-        <x:v>6500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3399" s="1">
-        <x:v>48050</x:v>
+        <x:v>15000</x:v>
       </x:c>
     </x:row>
     <x:row r="3400" spans="1:7">
@@ -89211,10 +89211,10 @@
         <x:v>3380</x:v>
       </x:c>
       <x:c r="B3400" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C3400" s="1">
-        <x:v>15000</x:v>
+        <x:v>41550</x:v>
       </x:c>
       <x:c r="D3400" s="1">
         <x:v>0</x:v>
@@ -89223,10 +89223,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3400" s="1">
-        <x:v>0</x:v>
+        <x:v>6500</x:v>
       </x:c>
       <x:c r="G3400" s="1">
-        <x:v>15000</x:v>
+        <x:v>48050</x:v>
       </x:c>
     </x:row>
     <x:row r="3401" spans="1:7">
@@ -89901,22 +89901,22 @@
         <x:v>3408</x:v>
       </x:c>
       <x:c r="B3430" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C3430" s="1">
-        <x:v>0</x:v>
+        <x:v>38500</x:v>
       </x:c>
       <x:c r="D3430" s="1">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3430" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3430" s="1">
-        <x:v>10700</x:v>
+        <x:v>26250</x:v>
       </x:c>
       <x:c r="G3430" s="1">
-        <x:v>10701</x:v>
+        <x:v>64750</x:v>
       </x:c>
     </x:row>
     <x:row r="3431" spans="1:7">
@@ -89924,22 +89924,22 @@
         <x:v>3408</x:v>
       </x:c>
       <x:c r="B3431" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C3431" s="1">
-        <x:v>38500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3431" s="1">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E3431" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3431" s="1">
-        <x:v>26250</x:v>
+        <x:v>10700</x:v>
       </x:c>
       <x:c r="G3431" s="1">
-        <x:v>64750</x:v>
+        <x:v>10701</x:v>
       </x:c>
     </x:row>
     <x:row r="3432" spans="1:7">
@@ -90683,22 +90683,22 @@
         <x:v>3438</x:v>
       </x:c>
       <x:c r="B3464" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C3464" s="1">
-        <x:v>47850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3464" s="1">
-        <x:v>0</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3464" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3464" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3464" s="1">
-        <x:v>52850</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="3465" spans="1:7">
@@ -90706,22 +90706,22 @@
         <x:v>3438</x:v>
       </x:c>
       <x:c r="B3465" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C3465" s="1">
-        <x:v>0</x:v>
+        <x:v>47850</x:v>
       </x:c>
       <x:c r="D3465" s="1">
-        <x:v>59</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3465" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3465" s="1">
-        <x:v>0</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G3465" s="1">
-        <x:v>59</x:v>
+        <x:v>52850</x:v>
       </x:c>
     </x:row>
     <x:row r="3466" spans="1:7">
@@ -91695,22 +91695,22 @@
         <x:v>3478</x:v>
       </x:c>
       <x:c r="B3508" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C3508" s="1">
-        <x:v>0</x:v>
+        <x:v>265983</x:v>
       </x:c>
       <x:c r="D3508" s="1">
-        <x:v>59</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="E3508" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3508" s="1">
-        <x:v>44000</x:v>
+        <x:v>126150</x:v>
       </x:c>
       <x:c r="G3508" s="1">
-        <x:v>44059</x:v>
+        <x:v>392310</x:v>
       </x:c>
     </x:row>
     <x:row r="3509" spans="1:7">
@@ -91718,22 +91718,22 @@
         <x:v>3478</x:v>
       </x:c>
       <x:c r="B3509" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C3509" s="1">
-        <x:v>265983</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3509" s="1">
-        <x:v>177</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3509" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3509" s="1">
-        <x:v>126150</x:v>
+        <x:v>44000</x:v>
       </x:c>
       <x:c r="G3509" s="1">
-        <x:v>392310</x:v>
+        <x:v>44059</x:v>
       </x:c>
     </x:row>
     <x:row r="3510" spans="1:7">
@@ -92707,10 +92707,10 @@
         <x:v>3519</x:v>
       </x:c>
       <x:c r="B3552" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C3552" s="1">
-        <x:v>0</x:v>
+        <x:v>130750</x:v>
       </x:c>
       <x:c r="D3552" s="1">
         <x:v>7</x:v>
@@ -92719,10 +92719,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3552" s="1">
-        <x:v>0</x:v>
+        <x:v>83750</x:v>
       </x:c>
       <x:c r="G3552" s="1">
-        <x:v>7</x:v>
+        <x:v>214507</x:v>
       </x:c>
     </x:row>
     <x:row r="3553" spans="1:7">
@@ -92730,10 +92730,10 @@
         <x:v>3519</x:v>
       </x:c>
       <x:c r="B3553" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C3553" s="1">
-        <x:v>130750</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3553" s="1">
         <x:v>7</x:v>
@@ -92742,10 +92742,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3553" s="1">
-        <x:v>83750</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3553" s="1">
-        <x:v>214507</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="3554" spans="1:7">

--- a/reports/pro-oil/pro-oil-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-oil/pro-oil-candidate-lobby-lifetime-report.xlsx
@@ -16186,7 +16186,7 @@
         <x:v>279</x:v>
       </x:c>
       <x:c r="B225" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C225" s="1">
         <x:v>0</x:v>
@@ -16198,10 +16198,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F225" s="1">
-        <x:v>2300</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G225" s="1">
-        <x:v>2300</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="226" spans="1:7">
@@ -16209,7 +16209,7 @@
         <x:v>279</x:v>
       </x:c>
       <x:c r="B226" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C226" s="1">
         <x:v>0</x:v>
@@ -16221,10 +16221,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F226" s="1">
-        <x:v>1000</x:v>
+        <x:v>2300</x:v>
       </x:c>
       <x:c r="G226" s="1">
-        <x:v>1000</x:v>
+        <x:v>2300</x:v>
       </x:c>
     </x:row>
     <x:row r="227" spans="1:7">
@@ -19314,10 +19314,10 @@
         <x:v>415</x:v>
       </x:c>
       <x:c r="B361" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="C361" s="1">
-        <x:v>163000</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D361" s="1">
         <x:v>0</x:v>
@@ -19326,10 +19326,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F361" s="1">
-        <x:v>82550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G361" s="1">
-        <x:v>245550</x:v>
+        <x:v>15000</x:v>
       </x:c>
     </x:row>
     <x:row r="362" spans="1:7">
@@ -19337,10 +19337,10 @@
         <x:v>415</x:v>
       </x:c>
       <x:c r="B362" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C362" s="1">
-        <x:v>15000</x:v>
+        <x:v>163000</x:v>
       </x:c>
       <x:c r="D362" s="1">
         <x:v>0</x:v>
@@ -19349,10 +19349,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F362" s="1">
-        <x:v>0</x:v>
+        <x:v>82550</x:v>
       </x:c>
       <x:c r="G362" s="1">
-        <x:v>15000</x:v>
+        <x:v>245550</x:v>
       </x:c>
     </x:row>
     <x:row r="363" spans="1:7">
@@ -30883,10 +30883,10 @@
         <x:v>914</x:v>
       </x:c>
       <x:c r="B864" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="C864" s="1">
-        <x:v>0</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D864" s="1">
         <x:v>0</x:v>
@@ -30895,10 +30895,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F864" s="1">
-        <x:v>14450</x:v>
+        <x:v>12950</x:v>
       </x:c>
       <x:c r="G864" s="1">
-        <x:v>14450</x:v>
+        <x:v>15950</x:v>
       </x:c>
     </x:row>
     <x:row r="865" spans="1:7">
@@ -30906,10 +30906,10 @@
         <x:v>914</x:v>
       </x:c>
       <x:c r="B865" s="1" t="s">
-        <x:v>260</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C865" s="1">
-        <x:v>3000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D865" s="1">
         <x:v>0</x:v>
@@ -30918,10 +30918,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F865" s="1">
-        <x:v>12950</x:v>
+        <x:v>14450</x:v>
       </x:c>
       <x:c r="G865" s="1">
-        <x:v>15950</x:v>
+        <x:v>14450</x:v>
       </x:c>
     </x:row>
     <x:row r="866" spans="1:7">
@@ -31481,22 +31481,22 @@
         <x:v>938</x:v>
       </x:c>
       <x:c r="B890" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="C890" s="1">
-        <x:v>91000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D890" s="1">
-        <x:v>118</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E890" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F890" s="1">
-        <x:v>26100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G890" s="1">
-        <x:v>117218</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="891" spans="1:7">
@@ -31504,22 +31504,22 @@
         <x:v>938</x:v>
       </x:c>
       <x:c r="B891" s="1" t="s">
-        <x:v>299</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C891" s="1">
-        <x:v>0</x:v>
+        <x:v>91000</x:v>
       </x:c>
       <x:c r="D891" s="1">
-        <x:v>59</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E891" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F891" s="1">
-        <x:v>0</x:v>
+        <x:v>26100</x:v>
       </x:c>
       <x:c r="G891" s="1">
-        <x:v>59</x:v>
+        <x:v>117218</x:v>
       </x:c>
     </x:row>
     <x:row r="892" spans="1:7">
@@ -37714,10 +37714,10 @@
         <x:v>1205</x:v>
       </x:c>
       <x:c r="B1161" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1161" s="1">
-        <x:v>0</x:v>
+        <x:v>752389</x:v>
       </x:c>
       <x:c r="D1161" s="1">
         <x:v>0</x:v>
@@ -37726,10 +37726,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1161" s="1">
-        <x:v>10000</x:v>
+        <x:v>418794</x:v>
       </x:c>
       <x:c r="G1161" s="1">
-        <x:v>10000</x:v>
+        <x:v>1171183</x:v>
       </x:c>
     </x:row>
     <x:row r="1162" spans="1:7">
@@ -37737,10 +37737,10 @@
         <x:v>1205</x:v>
       </x:c>
       <x:c r="B1162" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C1162" s="1">
-        <x:v>752389</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1162" s="1">
         <x:v>0</x:v>
@@ -37749,10 +37749,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1162" s="1">
-        <x:v>418794</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="G1162" s="1">
-        <x:v>1171183</x:v>
+        <x:v>10000</x:v>
       </x:c>
     </x:row>
     <x:row r="1163" spans="1:7">
@@ -38933,10 +38933,10 @@
         <x:v>1255</x:v>
       </x:c>
       <x:c r="B1214" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C1214" s="1">
-        <x:v>3000</x:v>
+        <x:v>12000</x:v>
       </x:c>
       <x:c r="D1214" s="1">
         <x:v>0</x:v>
@@ -38945,10 +38945,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1214" s="1">
-        <x:v>50751</x:v>
+        <x:v>12450</x:v>
       </x:c>
       <x:c r="G1214" s="1">
-        <x:v>53751</x:v>
+        <x:v>24450</x:v>
       </x:c>
     </x:row>
     <x:row r="1215" spans="1:7">
@@ -38956,10 +38956,10 @@
         <x:v>1255</x:v>
       </x:c>
       <x:c r="B1215" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C1215" s="1">
-        <x:v>12000</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D1215" s="1">
         <x:v>0</x:v>
@@ -38968,10 +38968,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1215" s="1">
-        <x:v>12450</x:v>
+        <x:v>50751</x:v>
       </x:c>
       <x:c r="G1215" s="1">
-        <x:v>24450</x:v>
+        <x:v>53751</x:v>
       </x:c>
     </x:row>
     <x:row r="1216" spans="1:7">
@@ -47236,10 +47236,10 @@
         <x:v>1611</x:v>
       </x:c>
       <x:c r="B1575" s="1" t="s">
-        <x:v>419</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C1575" s="1">
-        <x:v>181700</x:v>
+        <x:v>8000</x:v>
       </x:c>
       <x:c r="D1575" s="1">
         <x:v>0</x:v>
@@ -47248,10 +47248,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1575" s="1">
-        <x:v>168050</x:v>
+        <x:v>66000</x:v>
       </x:c>
       <x:c r="G1575" s="1">
-        <x:v>349750</x:v>
+        <x:v>74000</x:v>
       </x:c>
     </x:row>
     <x:row r="1576" spans="1:7">
@@ -47259,10 +47259,10 @@
         <x:v>1611</x:v>
       </x:c>
       <x:c r="B1576" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="C1576" s="1">
-        <x:v>8000</x:v>
+        <x:v>181700</x:v>
       </x:c>
       <x:c r="D1576" s="1">
         <x:v>0</x:v>
@@ -47271,10 +47271,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1576" s="1">
-        <x:v>66000</x:v>
+        <x:v>168050</x:v>
       </x:c>
       <x:c r="G1576" s="1">
-        <x:v>74000</x:v>
+        <x:v>349750</x:v>
       </x:c>
     </x:row>
     <x:row r="1577" spans="1:7">
@@ -50847,10 +50847,10 @@
         <x:v>1765</x:v>
       </x:c>
       <x:c r="B1732" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C1732" s="1">
-        <x:v>2500</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="D1732" s="1">
         <x:v>0</x:v>
@@ -50859,10 +50859,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1732" s="1">
-        <x:v>16350</x:v>
+        <x:v>72700</x:v>
       </x:c>
       <x:c r="G1732" s="1">
-        <x:v>18850</x:v>
+        <x:v>73185</x:v>
       </x:c>
     </x:row>
     <x:row r="1733" spans="1:7">
@@ -50870,10 +50870,10 @@
         <x:v>1765</x:v>
       </x:c>
       <x:c r="B1733" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1733" s="1">
-        <x:v>485</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1733" s="1">
         <x:v>0</x:v>
@@ -50882,10 +50882,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1733" s="1">
-        <x:v>72700</x:v>
+        <x:v>16350</x:v>
       </x:c>
       <x:c r="G1733" s="1">
-        <x:v>73185</x:v>
+        <x:v>18850</x:v>
       </x:c>
     </x:row>
     <x:row r="1734" spans="1:7">
@@ -53193,7 +53193,7 @@
         <x:v>1863</x:v>
       </x:c>
       <x:c r="B1834" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C1834" s="1">
         <x:v>0</x:v>
@@ -53216,7 +53216,7 @@
         <x:v>1863</x:v>
       </x:c>
       <x:c r="B1835" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1835" s="1">
         <x:v>0</x:v>
@@ -55838,22 +55838,22 @@
         <x:v>1976</x:v>
       </x:c>
       <x:c r="B1949" s="1" t="s">
-        <x:v>156</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C1949" s="1">
-        <x:v>0</x:v>
+        <x:v>299950</x:v>
       </x:c>
       <x:c r="D1949" s="1">
-        <x:v>59</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E1949" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1949" s="1">
-        <x:v>0</x:v>
+        <x:v>178350</x:v>
       </x:c>
       <x:c r="G1949" s="1">
-        <x:v>59</x:v>
+        <x:v>478595</x:v>
       </x:c>
     </x:row>
     <x:row r="1950" spans="1:7">
@@ -55861,22 +55861,22 @@
         <x:v>1976</x:v>
       </x:c>
       <x:c r="B1950" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="C1950" s="1">
-        <x:v>299950</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1950" s="1">
-        <x:v>295</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E1950" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1950" s="1">
-        <x:v>178350</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1950" s="1">
-        <x:v>478595</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="1951" spans="1:7">
@@ -56459,10 +56459,10 @@
         <x:v>2002</x:v>
       </x:c>
       <x:c r="B1976" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1976" s="1">
-        <x:v>187150</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1976" s="1">
         <x:v>31</x:v>
@@ -56471,10 +56471,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1976" s="1">
-        <x:v>6150</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1976" s="1">
-        <x:v>193331</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="1977" spans="1:7">
@@ -56482,10 +56482,10 @@
         <x:v>2002</x:v>
       </x:c>
       <x:c r="B1977" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C1977" s="1">
-        <x:v>0</x:v>
+        <x:v>187150</x:v>
       </x:c>
       <x:c r="D1977" s="1">
         <x:v>31</x:v>
@@ -56494,10 +56494,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1977" s="1">
-        <x:v>0</x:v>
+        <x:v>6150</x:v>
       </x:c>
       <x:c r="G1977" s="1">
-        <x:v>31</x:v>
+        <x:v>193331</x:v>
       </x:c>
     </x:row>
     <x:row r="1978" spans="1:7">
@@ -72697,10 +72697,10 @@
         <x:v>2698</x:v>
       </x:c>
       <x:c r="B2682" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="C2682" s="1">
-        <x:v>139000</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D2682" s="1">
         <x:v>0</x:v>
@@ -72709,10 +72709,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2682" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2682" s="1">
-        <x:v>139500</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="2683" spans="1:7">
@@ -72720,10 +72720,10 @@
         <x:v>2698</x:v>
       </x:c>
       <x:c r="B2683" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C2683" s="1">
-        <x:v>7000</x:v>
+        <x:v>139000</x:v>
       </x:c>
       <x:c r="D2683" s="1">
         <x:v>0</x:v>
@@ -72732,10 +72732,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2683" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G2683" s="1">
-        <x:v>7000</x:v>
+        <x:v>139500</x:v>
       </x:c>
     </x:row>
     <x:row r="2684" spans="1:7">
@@ -75503,10 +75503,10 @@
         <x:v>2818</x:v>
       </x:c>
       <x:c r="B2804" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C2804" s="1">
-        <x:v>163800</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D2804" s="1">
         <x:v>0</x:v>
@@ -75515,10 +75515,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2804" s="1">
-        <x:v>277645</x:v>
+        <x:v>111650</x:v>
       </x:c>
       <x:c r="G2804" s="1">
-        <x:v>441445</x:v>
+        <x:v>126650</x:v>
       </x:c>
     </x:row>
     <x:row r="2805" spans="1:7">
@@ -75526,10 +75526,10 @@
         <x:v>2818</x:v>
       </x:c>
       <x:c r="B2805" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C2805" s="1">
-        <x:v>15000</x:v>
+        <x:v>206766</x:v>
       </x:c>
       <x:c r="D2805" s="1">
         <x:v>0</x:v>
@@ -75538,10 +75538,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2805" s="1">
-        <x:v>111650</x:v>
+        <x:v>286825</x:v>
       </x:c>
       <x:c r="G2805" s="1">
-        <x:v>126650</x:v>
+        <x:v>493591</x:v>
       </x:c>
     </x:row>
     <x:row r="2806" spans="1:7">
@@ -75549,10 +75549,10 @@
         <x:v>2818</x:v>
       </x:c>
       <x:c r="B2806" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C2806" s="1">
-        <x:v>206766</x:v>
+        <x:v>163800</x:v>
       </x:c>
       <x:c r="D2806" s="1">
         <x:v>0</x:v>
@@ -75561,10 +75561,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2806" s="1">
-        <x:v>286825</x:v>
+        <x:v>277645</x:v>
       </x:c>
       <x:c r="G2806" s="1">
-        <x:v>493591</x:v>
+        <x:v>441445</x:v>
       </x:c>
     </x:row>
     <x:row r="2807" spans="1:7">
@@ -77044,10 +77044,10 @@
         <x:v>2882</x:v>
       </x:c>
       <x:c r="B2871" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C2871" s="1">
-        <x:v>102350</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D2871" s="1">
         <x:v>0</x:v>
@@ -77056,10 +77056,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2871" s="1">
-        <x:v>106550</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G2871" s="1">
-        <x:v>208900</x:v>
+        <x:v>20000</x:v>
       </x:c>
     </x:row>
     <x:row r="2872" spans="1:7">
@@ -77067,10 +77067,10 @@
         <x:v>2882</x:v>
       </x:c>
       <x:c r="B2872" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C2872" s="1">
-        <x:v>15000</x:v>
+        <x:v>102350</x:v>
       </x:c>
       <x:c r="D2872" s="1">
         <x:v>0</x:v>
@@ -77079,10 +77079,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2872" s="1">
-        <x:v>5000</x:v>
+        <x:v>106550</x:v>
       </x:c>
       <x:c r="G2872" s="1">
-        <x:v>20000</x:v>
+        <x:v>208900</x:v>
       </x:c>
     </x:row>
     <x:row r="2873" spans="1:7">
@@ -81299,22 +81299,22 @@
         <x:v>3061</x:v>
       </x:c>
       <x:c r="B3056" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="C3056" s="1">
-        <x:v>71750</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D3056" s="1">
-        <x:v>177</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3056" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3056" s="1">
-        <x:v>77150</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3056" s="1">
-        <x:v>149077</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="3057" spans="1:7">
@@ -81322,22 +81322,22 @@
         <x:v>3061</x:v>
       </x:c>
       <x:c r="B3057" s="1" t="s">
-        <x:v>258</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C3057" s="1">
-        <x:v>7000</x:v>
+        <x:v>71750</x:v>
       </x:c>
       <x:c r="D3057" s="1">
-        <x:v>0</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="E3057" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3057" s="1">
-        <x:v>0</x:v>
+        <x:v>77150</x:v>
       </x:c>
       <x:c r="G3057" s="1">
-        <x:v>7000</x:v>
+        <x:v>149077</x:v>
       </x:c>
     </x:row>
     <x:row r="3058" spans="1:7">
@@ -81874,10 +81874,10 @@
         <x:v>3085</x:v>
       </x:c>
       <x:c r="B3081" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C3081" s="1">
-        <x:v>10500</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D3081" s="1">
         <x:v>0</x:v>
@@ -81886,10 +81886,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3081" s="1">
-        <x:v>31300</x:v>
+        <x:v>33600</x:v>
       </x:c>
       <x:c r="G3081" s="1">
-        <x:v>41800</x:v>
+        <x:v>38600</x:v>
       </x:c>
     </x:row>
     <x:row r="3082" spans="1:7">
@@ -81897,10 +81897,10 @@
         <x:v>3085</x:v>
       </x:c>
       <x:c r="B3082" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C3082" s="1">
-        <x:v>5000</x:v>
+        <x:v>10500</x:v>
       </x:c>
       <x:c r="D3082" s="1">
         <x:v>0</x:v>
@@ -81909,10 +81909,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3082" s="1">
-        <x:v>33600</x:v>
+        <x:v>31300</x:v>
       </x:c>
       <x:c r="G3082" s="1">
-        <x:v>38600</x:v>
+        <x:v>41800</x:v>
       </x:c>
     </x:row>
     <x:row r="3083" spans="1:7">
@@ -82219,7 +82219,7 @@
         <x:v>3096</x:v>
       </x:c>
       <x:c r="B3096" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C3096" s="1">
         <x:v>1000</x:v>
@@ -82231,10 +82231,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3096" s="1">
-        <x:v>0</x:v>
+        <x:v>4750</x:v>
       </x:c>
       <x:c r="G3096" s="1">
-        <x:v>1000</x:v>
+        <x:v>5750</x:v>
       </x:c>
     </x:row>
     <x:row r="3097" spans="1:7">
@@ -82242,7 +82242,7 @@
         <x:v>3096</x:v>
       </x:c>
       <x:c r="B3097" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C3097" s="1">
         <x:v>1000</x:v>
@@ -82254,10 +82254,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3097" s="1">
-        <x:v>4750</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3097" s="1">
-        <x:v>5750</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="3098" spans="1:7">
@@ -83277,10 +83277,10 @@
         <x:v>3140</x:v>
       </x:c>
       <x:c r="B3142" s="1" t="s">
-        <x:v>156</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C3142" s="1">
-        <x:v>48000</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D3142" s="1">
         <x:v>0</x:v>
@@ -83289,10 +83289,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3142" s="1">
-        <x:v>38300</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G3142" s="1">
-        <x:v>86300</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="3143" spans="1:7">
@@ -83300,10 +83300,10 @@
         <x:v>3140</x:v>
       </x:c>
       <x:c r="B3143" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="C3143" s="1">
-        <x:v>5000</x:v>
+        <x:v>48000</x:v>
       </x:c>
       <x:c r="D3143" s="1">
         <x:v>0</x:v>
@@ -83312,10 +83312,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3143" s="1">
-        <x:v>250</x:v>
+        <x:v>38300</x:v>
       </x:c>
       <x:c r="G3143" s="1">
-        <x:v>5250</x:v>
+        <x:v>86300</x:v>
       </x:c>
     </x:row>
     <x:row r="3144" spans="1:7">
@@ -83415,7 +83415,7 @@
         <x:v>3143</x:v>
       </x:c>
       <x:c r="B3148" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C3148" s="1">
         <x:v>0</x:v>
@@ -83427,10 +83427,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3148" s="1">
-        <x:v>1100</x:v>
+        <x:v>4300</x:v>
       </x:c>
       <x:c r="G3148" s="1">
-        <x:v>1100</x:v>
+        <x:v>4300</x:v>
       </x:c>
     </x:row>
     <x:row r="3149" spans="1:7">
@@ -83438,7 +83438,7 @@
         <x:v>3143</x:v>
       </x:c>
       <x:c r="B3149" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C3149" s="1">
         <x:v>0</x:v>
@@ -83450,10 +83450,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3149" s="1">
-        <x:v>4300</x:v>
+        <x:v>1100</x:v>
       </x:c>
       <x:c r="G3149" s="1">
-        <x:v>4300</x:v>
+        <x:v>1100</x:v>
       </x:c>
     </x:row>
     <x:row r="3150" spans="1:7">
@@ -83645,10 +83645,10 @@
         <x:v>3152</x:v>
       </x:c>
       <x:c r="B3158" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C3158" s="1">
-        <x:v>20000</x:v>
+        <x:v>157500</x:v>
       </x:c>
       <x:c r="D3158" s="1">
         <x:v>0</x:v>
@@ -83657,10 +83657,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3158" s="1">
-        <x:v>6000</x:v>
+        <x:v>45517</x:v>
       </x:c>
       <x:c r="G3158" s="1">
-        <x:v>26000</x:v>
+        <x:v>203017</x:v>
       </x:c>
     </x:row>
     <x:row r="3159" spans="1:7">
@@ -83668,10 +83668,10 @@
         <x:v>3152</x:v>
       </x:c>
       <x:c r="B3159" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C3159" s="1">
-        <x:v>157500</x:v>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="D3159" s="1">
         <x:v>0</x:v>
@@ -83680,10 +83680,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3159" s="1">
-        <x:v>45517</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="G3159" s="1">
-        <x:v>203017</x:v>
+        <x:v>26000</x:v>
       </x:c>
     </x:row>
     <x:row r="3160" spans="1:7">
@@ -85945,10 +85945,10 @@
         <x:v>3246</x:v>
       </x:c>
       <x:c r="B3258" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C3258" s="1">
-        <x:v>29500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3258" s="1">
         <x:v>0</x:v>
@@ -85957,10 +85957,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3258" s="1">
-        <x:v>12550</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G3258" s="1">
-        <x:v>42050</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="3259" spans="1:7">
@@ -85968,10 +85968,10 @@
         <x:v>3246</x:v>
       </x:c>
       <x:c r="B3259" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C3259" s="1">
-        <x:v>0</x:v>
+        <x:v>29500</x:v>
       </x:c>
       <x:c r="D3259" s="1">
         <x:v>0</x:v>
@@ -85980,10 +85980,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3259" s="1">
-        <x:v>1000</x:v>
+        <x:v>12550</x:v>
       </x:c>
       <x:c r="G3259" s="1">
-        <x:v>1000</x:v>
+        <x:v>42050</x:v>
       </x:c>
     </x:row>
     <x:row r="3260" spans="1:7">
@@ -87969,22 +87969,22 @@
         <x:v>3332</x:v>
       </x:c>
       <x:c r="B3346" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C3346" s="1">
-        <x:v>0</x:v>
+        <x:v>332220</x:v>
       </x:c>
       <x:c r="D3346" s="1">
-        <x:v>59</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3346" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3346" s="1">
-        <x:v>0</x:v>
+        <x:v>299023</x:v>
       </x:c>
       <x:c r="G3346" s="1">
-        <x:v>59</x:v>
+        <x:v>631243</x:v>
       </x:c>
     </x:row>
     <x:row r="3347" spans="1:7">
@@ -88015,22 +88015,22 @@
         <x:v>3332</x:v>
       </x:c>
       <x:c r="B3348" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C3348" s="1">
-        <x:v>332220</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3348" s="1">
-        <x:v>0</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3348" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3348" s="1">
-        <x:v>299023</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3348" s="1">
-        <x:v>631243</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="3349" spans="1:7">
@@ -88084,22 +88084,22 @@
         <x:v>3334</x:v>
       </x:c>
       <x:c r="B3351" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C3351" s="1">
-        <x:v>7000</x:v>
+        <x:v>116050</x:v>
       </x:c>
       <x:c r="D3351" s="1">
-        <x:v>63</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="E3351" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3351" s="1">
-        <x:v>7000</x:v>
+        <x:v>47699</x:v>
       </x:c>
       <x:c r="G3351" s="1">
-        <x:v>14063</x:v>
+        <x:v>163985</x:v>
       </x:c>
     </x:row>
     <x:row r="3352" spans="1:7">
@@ -88107,22 +88107,22 @@
         <x:v>3334</x:v>
       </x:c>
       <x:c r="B3352" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C3352" s="1">
-        <x:v>116050</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D3352" s="1">
-        <x:v>236</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E3352" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3352" s="1">
-        <x:v>47699</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="G3352" s="1">
-        <x:v>163985</x:v>
+        <x:v>14063</x:v>
       </x:c>
     </x:row>
     <x:row r="3353" spans="1:7">
@@ -89188,10 +89188,10 @@
         <x:v>3380</x:v>
       </x:c>
       <x:c r="B3399" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C3399" s="1">
-        <x:v>15000</x:v>
+        <x:v>41550</x:v>
       </x:c>
       <x:c r="D3399" s="1">
         <x:v>0</x:v>
@@ -89200,10 +89200,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3399" s="1">
-        <x:v>0</x:v>
+        <x:v>6500</x:v>
       </x:c>
       <x:c r="G3399" s="1">
-        <x:v>15000</x:v>
+        <x:v>48050</x:v>
       </x:c>
     </x:row>
     <x:row r="3400" spans="1:7">
@@ -89211,10 +89211,10 @@
         <x:v>3380</x:v>
       </x:c>
       <x:c r="B3400" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="C3400" s="1">
-        <x:v>41550</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D3400" s="1">
         <x:v>0</x:v>
@@ -89223,10 +89223,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3400" s="1">
-        <x:v>6500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3400" s="1">
-        <x:v>48050</x:v>
+        <x:v>15000</x:v>
       </x:c>
     </x:row>
     <x:row r="3401" spans="1:7">
@@ -90453,22 +90453,22 @@
         <x:v>3430</x:v>
       </x:c>
       <x:c r="B3454" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C3454" s="1">
-        <x:v>72750</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3454" s="1">
-        <x:v>295</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3454" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3454" s="1">
-        <x:v>25450</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3454" s="1">
-        <x:v>98495</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="3455" spans="1:7">
@@ -90476,22 +90476,22 @@
         <x:v>3430</x:v>
       </x:c>
       <x:c r="B3455" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C3455" s="1">
-        <x:v>0</x:v>
+        <x:v>72750</x:v>
       </x:c>
       <x:c r="D3455" s="1">
-        <x:v>59</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E3455" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3455" s="1">
-        <x:v>0</x:v>
+        <x:v>25450</x:v>
       </x:c>
       <x:c r="G3455" s="1">
-        <x:v>59</x:v>
+        <x:v>98495</x:v>
       </x:c>
     </x:row>
     <x:row r="3456" spans="1:7">
@@ -90683,22 +90683,22 @@
         <x:v>3438</x:v>
       </x:c>
       <x:c r="B3464" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C3464" s="1">
-        <x:v>0</x:v>
+        <x:v>47850</x:v>
       </x:c>
       <x:c r="D3464" s="1">
-        <x:v>59</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3464" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3464" s="1">
-        <x:v>0</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G3464" s="1">
-        <x:v>59</x:v>
+        <x:v>52850</x:v>
       </x:c>
     </x:row>
     <x:row r="3465" spans="1:7">
@@ -90706,22 +90706,22 @@
         <x:v>3438</x:v>
       </x:c>
       <x:c r="B3465" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C3465" s="1">
-        <x:v>47850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3465" s="1">
-        <x:v>0</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3465" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3465" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3465" s="1">
-        <x:v>52850</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="3466" spans="1:7">
@@ -90936,10 +90936,10 @@
         <x:v>3448</x:v>
       </x:c>
       <x:c r="B3475" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="C3475" s="1">
-        <x:v>3000</x:v>
+        <x:v>22500</x:v>
       </x:c>
       <x:c r="D3475" s="1">
         <x:v>0</x:v>
@@ -90951,7 +90951,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G3475" s="1">
-        <x:v>3000</x:v>
+        <x:v>22500</x:v>
       </x:c>
     </x:row>
     <x:row r="3476" spans="1:7">
@@ -90959,22 +90959,22 @@
         <x:v>3448</x:v>
       </x:c>
       <x:c r="B3476" s="1" t="s">
-        <x:v>419</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C3476" s="1">
-        <x:v>437150</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D3476" s="1">
-        <x:v>468</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3476" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3476" s="1">
-        <x:v>348550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3476" s="1">
-        <x:v>786168</x:v>
+        <x:v>3000</x:v>
       </x:c>
     </x:row>
     <x:row r="3477" spans="1:7">
@@ -90982,22 +90982,22 @@
         <x:v>3448</x:v>
       </x:c>
       <x:c r="B3477" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="C3477" s="1">
-        <x:v>22500</x:v>
+        <x:v>437150</x:v>
       </x:c>
       <x:c r="D3477" s="1">
-        <x:v>0</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="E3477" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3477" s="1">
-        <x:v>0</x:v>
+        <x:v>348550</x:v>
       </x:c>
       <x:c r="G3477" s="1">
-        <x:v>22500</x:v>
+        <x:v>786168</x:v>
       </x:c>
     </x:row>
     <x:row r="3478" spans="1:7">
@@ -91695,22 +91695,22 @@
         <x:v>3478</x:v>
       </x:c>
       <x:c r="B3508" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C3508" s="1">
-        <x:v>265983</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3508" s="1">
-        <x:v>177</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3508" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3508" s="1">
-        <x:v>126150</x:v>
+        <x:v>44000</x:v>
       </x:c>
       <x:c r="G3508" s="1">
-        <x:v>392310</x:v>
+        <x:v>44059</x:v>
       </x:c>
     </x:row>
     <x:row r="3509" spans="1:7">
@@ -91718,22 +91718,22 @@
         <x:v>3478</x:v>
       </x:c>
       <x:c r="B3509" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C3509" s="1">
-        <x:v>0</x:v>
+        <x:v>265983</x:v>
       </x:c>
       <x:c r="D3509" s="1">
-        <x:v>59</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="E3509" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3509" s="1">
-        <x:v>44000</x:v>
+        <x:v>126150</x:v>
       </x:c>
       <x:c r="G3509" s="1">
-        <x:v>44059</x:v>
+        <x:v>392310</x:v>
       </x:c>
     </x:row>
     <x:row r="3510" spans="1:7">
@@ -92132,22 +92132,22 @@
         <x:v>3495</x:v>
       </x:c>
       <x:c r="B3527" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="C3527" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D3527" s="1">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3527" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3527" s="1">
-        <x:v>0</x:v>
+        <x:v>11300</x:v>
       </x:c>
       <x:c r="G3527" s="1">
-        <x:v>3</x:v>
+        <x:v>12300</x:v>
       </x:c>
     </x:row>
     <x:row r="3528" spans="1:7">
@@ -92155,22 +92155,22 @@
         <x:v>3495</x:v>
       </x:c>
       <x:c r="B3528" s="1" t="s">
-        <x:v>260</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C3528" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3528" s="1">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E3528" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3528" s="1">
-        <x:v>11300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3528" s="1">
-        <x:v>12300</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="3529" spans="1:7">

--- a/reports/pro-oil/pro-oil-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-oil/pro-oil-candidate-lobby-lifetime-report.xlsx
@@ -16186,7 +16186,7 @@
         <x:v>279</x:v>
       </x:c>
       <x:c r="B225" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C225" s="1">
         <x:v>0</x:v>
@@ -16198,10 +16198,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F225" s="1">
-        <x:v>1000</x:v>
+        <x:v>2300</x:v>
       </x:c>
       <x:c r="G225" s="1">
-        <x:v>1000</x:v>
+        <x:v>2300</x:v>
       </x:c>
     </x:row>
     <x:row r="226" spans="1:7">
@@ -16209,7 +16209,7 @@
         <x:v>279</x:v>
       </x:c>
       <x:c r="B226" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C226" s="1">
         <x:v>0</x:v>
@@ -16221,10 +16221,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F226" s="1">
-        <x:v>2300</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G226" s="1">
-        <x:v>2300</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="227" spans="1:7">
@@ -19314,10 +19314,10 @@
         <x:v>415</x:v>
       </x:c>
       <x:c r="B361" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C361" s="1">
-        <x:v>15000</x:v>
+        <x:v>163000</x:v>
       </x:c>
       <x:c r="D361" s="1">
         <x:v>0</x:v>
@@ -19326,10 +19326,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F361" s="1">
-        <x:v>0</x:v>
+        <x:v>82550</x:v>
       </x:c>
       <x:c r="G361" s="1">
-        <x:v>15000</x:v>
+        <x:v>245550</x:v>
       </x:c>
     </x:row>
     <x:row r="362" spans="1:7">
@@ -19337,10 +19337,10 @@
         <x:v>415</x:v>
       </x:c>
       <x:c r="B362" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="C362" s="1">
-        <x:v>163000</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D362" s="1">
         <x:v>0</x:v>
@@ -19349,10 +19349,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F362" s="1">
-        <x:v>82550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G362" s="1">
-        <x:v>245550</x:v>
+        <x:v>15000</x:v>
       </x:c>
     </x:row>
     <x:row r="363" spans="1:7">
@@ -19452,10 +19452,10 @@
         <x:v>421</x:v>
       </x:c>
       <x:c r="B367" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C367" s="1">
-        <x:v>3000</x:v>
+        <x:v>107540</x:v>
       </x:c>
       <x:c r="D367" s="1">
         <x:v>0</x:v>
@@ -19464,10 +19464,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F367" s="1">
-        <x:v>25150</x:v>
+        <x:v>59170</x:v>
       </x:c>
       <x:c r="G367" s="1">
-        <x:v>28150</x:v>
+        <x:v>166710</x:v>
       </x:c>
     </x:row>
     <x:row r="368" spans="1:7">
@@ -19475,10 +19475,10 @@
         <x:v>421</x:v>
       </x:c>
       <x:c r="B368" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C368" s="1">
-        <x:v>107540</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D368" s="1">
         <x:v>0</x:v>
@@ -19487,10 +19487,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F368" s="1">
-        <x:v>59170</x:v>
+        <x:v>25150</x:v>
       </x:c>
       <x:c r="G368" s="1">
-        <x:v>166710</x:v>
+        <x:v>28150</x:v>
       </x:c>
     </x:row>
     <x:row r="369" spans="1:7">
@@ -21108,11 +21108,11 @@
         <x:v>491</x:v>
       </x:c>
       <x:c r="B439" s="1" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C439" s="1">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="C439" s="1">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="D439" s="1">
         <x:v>0</x:v>
       </x:c>
@@ -21120,10 +21120,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F439" s="1">
-        <x:v>40350</x:v>
+        <x:v>13450</x:v>
       </x:c>
       <x:c r="G439" s="1">
-        <x:v>40350</x:v>
+        <x:v>13500</x:v>
       </x:c>
     </x:row>
     <x:row r="440" spans="1:7">
@@ -21131,10 +21131,10 @@
         <x:v>491</x:v>
       </x:c>
       <x:c r="B440" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C440" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D440" s="1">
         <x:v>0</x:v>
@@ -21143,10 +21143,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F440" s="1">
-        <x:v>13450</x:v>
+        <x:v>40350</x:v>
       </x:c>
       <x:c r="G440" s="1">
-        <x:v>13500</x:v>
+        <x:v>40350</x:v>
       </x:c>
     </x:row>
     <x:row r="441" spans="1:7">
@@ -27295,22 +27295,22 @@
         <x:v>760</x:v>
       </x:c>
       <x:c r="B708" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>750</x:v>
       </x:c>
       <x:c r="C708" s="1">
-        <x:v>25500</x:v>
+        <x:v>418533</x:v>
       </x:c>
       <x:c r="D708" s="1">
-        <x:v>0</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E708" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F708" s="1">
-        <x:v>0</x:v>
+        <x:v>51350</x:v>
       </x:c>
       <x:c r="G708" s="1">
-        <x:v>25500</x:v>
+        <x:v>470001</x:v>
       </x:c>
     </x:row>
     <x:row r="709" spans="1:7">
@@ -27318,22 +27318,22 @@
         <x:v>760</x:v>
       </x:c>
       <x:c r="B709" s="1" t="s">
-        <x:v>750</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C709" s="1">
-        <x:v>418533</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D709" s="1">
-        <x:v>118</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E709" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F709" s="1">
-        <x:v>51350</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G709" s="1">
-        <x:v>470001</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="710" spans="1:7">
@@ -31481,22 +31481,22 @@
         <x:v>938</x:v>
       </x:c>
       <x:c r="B890" s="1" t="s">
-        <x:v>299</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C890" s="1">
-        <x:v>0</x:v>
+        <x:v>91000</x:v>
       </x:c>
       <x:c r="D890" s="1">
-        <x:v>59</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E890" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F890" s="1">
-        <x:v>0</x:v>
+        <x:v>26100</x:v>
       </x:c>
       <x:c r="G890" s="1">
-        <x:v>59</x:v>
+        <x:v>117218</x:v>
       </x:c>
     </x:row>
     <x:row r="891" spans="1:7">
@@ -31504,22 +31504,22 @@
         <x:v>938</x:v>
       </x:c>
       <x:c r="B891" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="C891" s="1">
-        <x:v>91000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D891" s="1">
-        <x:v>118</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E891" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F891" s="1">
-        <x:v>26100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G891" s="1">
-        <x:v>117218</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="892" spans="1:7">
@@ -47236,10 +47236,10 @@
         <x:v>1611</x:v>
       </x:c>
       <x:c r="B1575" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="C1575" s="1">
-        <x:v>8000</x:v>
+        <x:v>181700</x:v>
       </x:c>
       <x:c r="D1575" s="1">
         <x:v>0</x:v>
@@ -47248,10 +47248,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1575" s="1">
-        <x:v>66000</x:v>
+        <x:v>168050</x:v>
       </x:c>
       <x:c r="G1575" s="1">
-        <x:v>74000</x:v>
+        <x:v>349750</x:v>
       </x:c>
     </x:row>
     <x:row r="1576" spans="1:7">
@@ -47259,10 +47259,10 @@
         <x:v>1611</x:v>
       </x:c>
       <x:c r="B1576" s="1" t="s">
-        <x:v>419</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C1576" s="1">
-        <x:v>181700</x:v>
+        <x:v>8000</x:v>
       </x:c>
       <x:c r="D1576" s="1">
         <x:v>0</x:v>
@@ -47271,10 +47271,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1576" s="1">
-        <x:v>168050</x:v>
+        <x:v>66000</x:v>
       </x:c>
       <x:c r="G1576" s="1">
-        <x:v>349750</x:v>
+        <x:v>74000</x:v>
       </x:c>
     </x:row>
     <x:row r="1577" spans="1:7">
@@ -50847,10 +50847,10 @@
         <x:v>1765</x:v>
       </x:c>
       <x:c r="B1732" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1732" s="1">
-        <x:v>485</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1732" s="1">
         <x:v>0</x:v>
@@ -50859,10 +50859,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1732" s="1">
-        <x:v>72700</x:v>
+        <x:v>16350</x:v>
       </x:c>
       <x:c r="G1732" s="1">
-        <x:v>73185</x:v>
+        <x:v>18850</x:v>
       </x:c>
     </x:row>
     <x:row r="1733" spans="1:7">
@@ -50870,10 +50870,10 @@
         <x:v>1765</x:v>
       </x:c>
       <x:c r="B1733" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C1733" s="1">
-        <x:v>2500</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="D1733" s="1">
         <x:v>0</x:v>
@@ -50882,10 +50882,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1733" s="1">
-        <x:v>16350</x:v>
+        <x:v>72700</x:v>
       </x:c>
       <x:c r="G1733" s="1">
-        <x:v>18850</x:v>
+        <x:v>73185</x:v>
       </x:c>
     </x:row>
     <x:row r="1734" spans="1:7">
@@ -53009,10 +53009,10 @@
         <x:v>1856</x:v>
       </x:c>
       <x:c r="B1826" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C1826" s="1">
-        <x:v>147100</x:v>
+        <x:v>-1000</x:v>
       </x:c>
       <x:c r="D1826" s="1">
         <x:v>0</x:v>
@@ -53021,10 +53021,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1826" s="1">
-        <x:v>34550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1826" s="1">
-        <x:v>181650</x:v>
+        <x:v>-1000</x:v>
       </x:c>
     </x:row>
     <x:row r="1827" spans="1:7">
@@ -53032,10 +53032,10 @@
         <x:v>1856</x:v>
       </x:c>
       <x:c r="B1827" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C1827" s="1">
-        <x:v>-1000</x:v>
+        <x:v>147100</x:v>
       </x:c>
       <x:c r="D1827" s="1">
         <x:v>0</x:v>
@@ -53044,10 +53044,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1827" s="1">
-        <x:v>0</x:v>
+        <x:v>34550</x:v>
       </x:c>
       <x:c r="G1827" s="1">
-        <x:v>-1000</x:v>
+        <x:v>181650</x:v>
       </x:c>
     </x:row>
     <x:row r="1828" spans="1:7">
@@ -55838,22 +55838,22 @@
         <x:v>1976</x:v>
       </x:c>
       <x:c r="B1949" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="C1949" s="1">
-        <x:v>299950</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1949" s="1">
-        <x:v>295</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E1949" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1949" s="1">
-        <x:v>178350</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1949" s="1">
-        <x:v>478595</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="1950" spans="1:7">
@@ -55861,22 +55861,22 @@
         <x:v>1976</x:v>
       </x:c>
       <x:c r="B1950" s="1" t="s">
-        <x:v>156</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C1950" s="1">
-        <x:v>0</x:v>
+        <x:v>299950</x:v>
       </x:c>
       <x:c r="D1950" s="1">
-        <x:v>59</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E1950" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1950" s="1">
-        <x:v>0</x:v>
+        <x:v>178350</x:v>
       </x:c>
       <x:c r="G1950" s="1">
-        <x:v>59</x:v>
+        <x:v>478595</x:v>
       </x:c>
     </x:row>
     <x:row r="1951" spans="1:7">
@@ -56459,10 +56459,10 @@
         <x:v>2002</x:v>
       </x:c>
       <x:c r="B1976" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C1976" s="1">
-        <x:v>0</x:v>
+        <x:v>187150</x:v>
       </x:c>
       <x:c r="D1976" s="1">
         <x:v>31</x:v>
@@ -56471,10 +56471,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1976" s="1">
-        <x:v>0</x:v>
+        <x:v>6150</x:v>
       </x:c>
       <x:c r="G1976" s="1">
-        <x:v>31</x:v>
+        <x:v>193331</x:v>
       </x:c>
     </x:row>
     <x:row r="1977" spans="1:7">
@@ -56482,10 +56482,10 @@
         <x:v>2002</x:v>
       </x:c>
       <x:c r="B1977" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1977" s="1">
-        <x:v>187150</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1977" s="1">
         <x:v>31</x:v>
@@ -56494,10 +56494,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1977" s="1">
-        <x:v>6150</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1977" s="1">
-        <x:v>193331</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="1978" spans="1:7">
@@ -59955,10 +59955,10 @@
         <x:v>2150</x:v>
       </x:c>
       <x:c r="B2128" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="C2128" s="1">
-        <x:v>11000</x:v>
+        <x:v>960100</x:v>
       </x:c>
       <x:c r="D2128" s="1">
         <x:v>0</x:v>
@@ -59967,10 +59967,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2128" s="1">
-        <x:v>25550</x:v>
+        <x:v>882230</x:v>
       </x:c>
       <x:c r="G2128" s="1">
-        <x:v>36550</x:v>
+        <x:v>1842330</x:v>
       </x:c>
     </x:row>
     <x:row r="2129" spans="1:7">
@@ -59978,10 +59978,10 @@
         <x:v>2150</x:v>
       </x:c>
       <x:c r="B2129" s="1" t="s">
-        <x:v>193</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C2129" s="1">
-        <x:v>960100</x:v>
+        <x:v>11000</x:v>
       </x:c>
       <x:c r="D2129" s="1">
         <x:v>0</x:v>
@@ -59990,10 +59990,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2129" s="1">
-        <x:v>882230</x:v>
+        <x:v>25550</x:v>
       </x:c>
       <x:c r="G2129" s="1">
-        <x:v>1842330</x:v>
+        <x:v>36550</x:v>
       </x:c>
     </x:row>
     <x:row r="2130" spans="1:7">
@@ -60070,10 +60070,10 @@
         <x:v>2154</x:v>
       </x:c>
       <x:c r="B2133" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C2133" s="1">
-        <x:v>22450</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="D2133" s="1">
         <x:v>0</x:v>
@@ -60082,10 +60082,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2133" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G2133" s="1">
         <x:v>250</x:v>
-      </x:c>
-      <x:c r="G2133" s="1">
-        <x:v>22700</x:v>
       </x:c>
     </x:row>
     <x:row r="2134" spans="1:7">
@@ -60093,22 +60093,22 @@
         <x:v>2154</x:v>
       </x:c>
       <x:c r="B2134" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C2134" s="1">
+        <x:v>22450</x:v>
+      </x:c>
+      <x:c r="D2134" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E2134" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F2134" s="1">
         <x:v>250</x:v>
       </x:c>
-      <x:c r="D2134" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E2134" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F2134" s="1">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="G2134" s="1">
-        <x:v>250</x:v>
+        <x:v>22700</x:v>
       </x:c>
     </x:row>
     <x:row r="2135" spans="1:7">
@@ -72536,10 +72536,10 @@
         <x:v>2692</x:v>
       </x:c>
       <x:c r="B2675" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C2675" s="1">
-        <x:v>7061</x:v>
+        <x:v>409250</x:v>
       </x:c>
       <x:c r="D2675" s="1">
         <x:v>0</x:v>
@@ -72548,10 +72548,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2675" s="1">
-        <x:v>23500</x:v>
+        <x:v>159800</x:v>
       </x:c>
       <x:c r="G2675" s="1">
-        <x:v>30561</x:v>
+        <x:v>569050</x:v>
       </x:c>
     </x:row>
     <x:row r="2676" spans="1:7">
@@ -72559,10 +72559,10 @@
         <x:v>2692</x:v>
       </x:c>
       <x:c r="B2676" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C2676" s="1">
-        <x:v>409250</x:v>
+        <x:v>7061</x:v>
       </x:c>
       <x:c r="D2676" s="1">
         <x:v>0</x:v>
@@ -72571,10 +72571,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2676" s="1">
-        <x:v>159800</x:v>
+        <x:v>23500</x:v>
       </x:c>
       <x:c r="G2676" s="1">
-        <x:v>569050</x:v>
+        <x:v>30561</x:v>
       </x:c>
     </x:row>
     <x:row r="2677" spans="1:7">
@@ -75503,10 +75503,10 @@
         <x:v>2818</x:v>
       </x:c>
       <x:c r="B2804" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C2804" s="1">
-        <x:v>15000</x:v>
+        <x:v>206766</x:v>
       </x:c>
       <x:c r="D2804" s="1">
         <x:v>0</x:v>
@@ -75515,10 +75515,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2804" s="1">
-        <x:v>111650</x:v>
+        <x:v>286825</x:v>
       </x:c>
       <x:c r="G2804" s="1">
-        <x:v>126650</x:v>
+        <x:v>493591</x:v>
       </x:c>
     </x:row>
     <x:row r="2805" spans="1:7">
@@ -75526,10 +75526,10 @@
         <x:v>2818</x:v>
       </x:c>
       <x:c r="B2805" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C2805" s="1">
-        <x:v>206766</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D2805" s="1">
         <x:v>0</x:v>
@@ -75538,10 +75538,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2805" s="1">
-        <x:v>286825</x:v>
+        <x:v>111650</x:v>
       </x:c>
       <x:c r="G2805" s="1">
-        <x:v>493591</x:v>
+        <x:v>126650</x:v>
       </x:c>
     </x:row>
     <x:row r="2806" spans="1:7">
@@ -77044,10 +77044,10 @@
         <x:v>2882</x:v>
       </x:c>
       <x:c r="B2871" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C2871" s="1">
-        <x:v>15000</x:v>
+        <x:v>102350</x:v>
       </x:c>
       <x:c r="D2871" s="1">
         <x:v>0</x:v>
@@ -77056,10 +77056,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2871" s="1">
-        <x:v>5000</x:v>
+        <x:v>106550</x:v>
       </x:c>
       <x:c r="G2871" s="1">
-        <x:v>20000</x:v>
+        <x:v>208900</x:v>
       </x:c>
     </x:row>
     <x:row r="2872" spans="1:7">
@@ -77067,10 +77067,10 @@
         <x:v>2882</x:v>
       </x:c>
       <x:c r="B2872" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C2872" s="1">
-        <x:v>102350</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D2872" s="1">
         <x:v>0</x:v>
@@ -77079,10 +77079,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2872" s="1">
-        <x:v>106550</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G2872" s="1">
-        <x:v>208900</x:v>
+        <x:v>20000</x:v>
       </x:c>
     </x:row>
     <x:row r="2873" spans="1:7">
@@ -78815,10 +78815,10 @@
         <x:v>2957</x:v>
       </x:c>
       <x:c r="B2948" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C2948" s="1">
-        <x:v>99950</x:v>
+        <x:v>12000</x:v>
       </x:c>
       <x:c r="D2948" s="1">
         <x:v>0</x:v>
@@ -78827,10 +78827,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2948" s="1">
-        <x:v>6650</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2948" s="1">
-        <x:v>106600</x:v>
+        <x:v>12000</x:v>
       </x:c>
     </x:row>
     <x:row r="2949" spans="1:7">
@@ -78838,10 +78838,10 @@
         <x:v>2957</x:v>
       </x:c>
       <x:c r="B2949" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C2949" s="1">
-        <x:v>12000</x:v>
+        <x:v>99950</x:v>
       </x:c>
       <x:c r="D2949" s="1">
         <x:v>0</x:v>
@@ -78850,10 +78850,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2949" s="1">
-        <x:v>0</x:v>
+        <x:v>6650</x:v>
       </x:c>
       <x:c r="G2949" s="1">
-        <x:v>12000</x:v>
+        <x:v>106600</x:v>
       </x:c>
     </x:row>
     <x:row r="2950" spans="1:7">
@@ -78861,22 +78861,22 @@
         <x:v>2958</x:v>
       </x:c>
       <x:c r="B2950" s="1" t="s">
-        <x:v>260</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C2950" s="1">
-        <x:v>10000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D2950" s="1">
-        <x:v>0</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E2950" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2950" s="1">
-        <x:v>4950</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2950" s="1">
-        <x:v>14950</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="2951" spans="1:7">
@@ -78884,22 +78884,22 @@
         <x:v>2958</x:v>
       </x:c>
       <x:c r="B2951" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="C2951" s="1">
-        <x:v>0</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="D2951" s="1">
-        <x:v>59</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E2951" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2951" s="1">
-        <x:v>0</x:v>
+        <x:v>4950</x:v>
       </x:c>
       <x:c r="G2951" s="1">
-        <x:v>59</x:v>
+        <x:v>14950</x:v>
       </x:c>
     </x:row>
     <x:row r="2952" spans="1:7">
@@ -81874,10 +81874,10 @@
         <x:v>3085</x:v>
       </x:c>
       <x:c r="B3081" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C3081" s="1">
-        <x:v>5000</x:v>
+        <x:v>10500</x:v>
       </x:c>
       <x:c r="D3081" s="1">
         <x:v>0</x:v>
@@ -81886,10 +81886,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3081" s="1">
-        <x:v>33600</x:v>
+        <x:v>31300</x:v>
       </x:c>
       <x:c r="G3081" s="1">
-        <x:v>38600</x:v>
+        <x:v>41800</x:v>
       </x:c>
     </x:row>
     <x:row r="3082" spans="1:7">
@@ -81897,10 +81897,10 @@
         <x:v>3085</x:v>
       </x:c>
       <x:c r="B3082" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C3082" s="1">
-        <x:v>10500</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D3082" s="1">
         <x:v>0</x:v>
@@ -81909,10 +81909,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3082" s="1">
-        <x:v>31300</x:v>
+        <x:v>33600</x:v>
       </x:c>
       <x:c r="G3082" s="1">
-        <x:v>41800</x:v>
+        <x:v>38600</x:v>
       </x:c>
     </x:row>
     <x:row r="3083" spans="1:7">
@@ -82219,7 +82219,7 @@
         <x:v>3096</x:v>
       </x:c>
       <x:c r="B3096" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C3096" s="1">
         <x:v>1000</x:v>
@@ -82231,10 +82231,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3096" s="1">
-        <x:v>4750</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3096" s="1">
-        <x:v>5750</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="3097" spans="1:7">
@@ -82242,7 +82242,7 @@
         <x:v>3096</x:v>
       </x:c>
       <x:c r="B3097" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C3097" s="1">
         <x:v>1000</x:v>
@@ -82254,10 +82254,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3097" s="1">
-        <x:v>0</x:v>
+        <x:v>4750</x:v>
       </x:c>
       <x:c r="G3097" s="1">
-        <x:v>1000</x:v>
+        <x:v>5750</x:v>
       </x:c>
     </x:row>
     <x:row r="3098" spans="1:7">
@@ -82541,22 +82541,22 @@
         <x:v>3109</x:v>
       </x:c>
       <x:c r="B3110" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C3110" s="1">
-        <x:v>307450</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3110" s="1">
-        <x:v>0</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3110" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3110" s="1">
-        <x:v>40550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3110" s="1">
-        <x:v>348000</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="3111" spans="1:7">
@@ -82564,22 +82564,22 @@
         <x:v>3109</x:v>
       </x:c>
       <x:c r="B3111" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C3111" s="1">
-        <x:v>0</x:v>
+        <x:v>307450</x:v>
       </x:c>
       <x:c r="D3111" s="1">
-        <x:v>59</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3111" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3111" s="1">
-        <x:v>0</x:v>
+        <x:v>40550</x:v>
       </x:c>
       <x:c r="G3111" s="1">
-        <x:v>59</x:v>
+        <x:v>348000</x:v>
       </x:c>
     </x:row>
     <x:row r="3112" spans="1:7">
@@ -83277,10 +83277,10 @@
         <x:v>3140</x:v>
       </x:c>
       <x:c r="B3142" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="C3142" s="1">
-        <x:v>5000</x:v>
+        <x:v>48000</x:v>
       </x:c>
       <x:c r="D3142" s="1">
         <x:v>0</x:v>
@@ -83289,10 +83289,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3142" s="1">
-        <x:v>250</x:v>
+        <x:v>38300</x:v>
       </x:c>
       <x:c r="G3142" s="1">
-        <x:v>5250</x:v>
+        <x:v>86300</x:v>
       </x:c>
     </x:row>
     <x:row r="3143" spans="1:7">
@@ -83300,10 +83300,10 @@
         <x:v>3140</x:v>
       </x:c>
       <x:c r="B3143" s="1" t="s">
-        <x:v>156</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C3143" s="1">
-        <x:v>48000</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D3143" s="1">
         <x:v>0</x:v>
@@ -83312,10 +83312,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3143" s="1">
-        <x:v>38300</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G3143" s="1">
-        <x:v>86300</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="3144" spans="1:7">
@@ -85232,10 +85232,10 @@
         <x:v>3219</x:v>
       </x:c>
       <x:c r="B3227" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C3227" s="1">
-        <x:v>2300</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D3227" s="1">
         <x:v>0</x:v>
@@ -85244,10 +85244,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3227" s="1">
-        <x:v>8850</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="G3227" s="1">
-        <x:v>11150</x:v>
+        <x:v>9000</x:v>
       </x:c>
     </x:row>
     <x:row r="3228" spans="1:7">
@@ -85255,10 +85255,10 @@
         <x:v>3219</x:v>
       </x:c>
       <x:c r="B3228" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C3228" s="1">
-        <x:v>3000</x:v>
+        <x:v>2300</x:v>
       </x:c>
       <x:c r="D3228" s="1">
         <x:v>0</x:v>
@@ -85267,10 +85267,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3228" s="1">
-        <x:v>6000</x:v>
+        <x:v>8850</x:v>
       </x:c>
       <x:c r="G3228" s="1">
-        <x:v>9000</x:v>
+        <x:v>11150</x:v>
       </x:c>
     </x:row>
     <x:row r="3229" spans="1:7">
@@ -85761,10 +85761,10 @@
         <x:v>3239</x:v>
       </x:c>
       <x:c r="B3250" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="C3250" s="1">
-        <x:v>343100</x:v>
+        <x:v>34000</x:v>
       </x:c>
       <x:c r="D3250" s="1">
         <x:v>0</x:v>
@@ -85773,10 +85773,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3250" s="1">
-        <x:v>244972</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3250" s="1">
-        <x:v>588072</x:v>
+        <x:v>34000</x:v>
       </x:c>
     </x:row>
     <x:row r="3251" spans="1:7">
@@ -85784,10 +85784,10 @@
         <x:v>3239</x:v>
       </x:c>
       <x:c r="B3251" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C3251" s="1">
-        <x:v>34000</x:v>
+        <x:v>343100</x:v>
       </x:c>
       <x:c r="D3251" s="1">
         <x:v>0</x:v>
@@ -85796,10 +85796,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3251" s="1">
-        <x:v>0</x:v>
+        <x:v>244972</x:v>
       </x:c>
       <x:c r="G3251" s="1">
-        <x:v>34000</x:v>
+        <x:v>588072</x:v>
       </x:c>
     </x:row>
     <x:row r="3252" spans="1:7">
@@ -86152,22 +86152,22 @@
         <x:v>3254</x:v>
       </x:c>
       <x:c r="B3267" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C3267" s="1">
-        <x:v>25500</x:v>
+        <x:v>420650</x:v>
       </x:c>
       <x:c r="D3267" s="1">
-        <x:v>0</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="E3267" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3267" s="1">
-        <x:v>0</x:v>
+        <x:v>448881</x:v>
       </x:c>
       <x:c r="G3267" s="1">
-        <x:v>25500</x:v>
+        <x:v>869712</x:v>
       </x:c>
     </x:row>
     <x:row r="3268" spans="1:7">
@@ -86175,22 +86175,22 @@
         <x:v>3254</x:v>
       </x:c>
       <x:c r="B3268" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C3268" s="1">
-        <x:v>420650</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D3268" s="1">
-        <x:v>181</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3268" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3268" s="1">
-        <x:v>448881</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3268" s="1">
-        <x:v>869712</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="3269" spans="1:7">
@@ -87969,22 +87969,22 @@
         <x:v>3332</x:v>
       </x:c>
       <x:c r="B3346" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="C3346" s="1">
-        <x:v>332220</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="D3346" s="1">
-        <x:v>0</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E3346" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3346" s="1">
-        <x:v>299023</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3346" s="1">
-        <x:v>631243</x:v>
+        <x:v>15063</x:v>
       </x:c>
     </x:row>
     <x:row r="3347" spans="1:7">
@@ -87992,13 +87992,13 @@
         <x:v>3332</x:v>
       </x:c>
       <x:c r="B3347" s="1" t="s">
-        <x:v>258</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C3347" s="1">
-        <x:v>15000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3347" s="1">
-        <x:v>63</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3347" s="1">
         <x:v>0</x:v>
@@ -88007,7 +88007,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G3347" s="1">
-        <x:v>15063</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="3348" spans="1:7">
@@ -88015,22 +88015,22 @@
         <x:v>3332</x:v>
       </x:c>
       <x:c r="B3348" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C3348" s="1">
-        <x:v>0</x:v>
+        <x:v>332220</x:v>
       </x:c>
       <x:c r="D3348" s="1">
-        <x:v>59</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3348" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3348" s="1">
-        <x:v>0</x:v>
+        <x:v>299023</x:v>
       </x:c>
       <x:c r="G3348" s="1">
-        <x:v>59</x:v>
+        <x:v>631243</x:v>
       </x:c>
     </x:row>
     <x:row r="3349" spans="1:7">
@@ -88084,22 +88084,22 @@
         <x:v>3334</x:v>
       </x:c>
       <x:c r="B3351" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C3351" s="1">
-        <x:v>116050</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D3351" s="1">
-        <x:v>236</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E3351" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3351" s="1">
-        <x:v>47699</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="G3351" s="1">
-        <x:v>163985</x:v>
+        <x:v>14063</x:v>
       </x:c>
     </x:row>
     <x:row r="3352" spans="1:7">
@@ -88107,22 +88107,22 @@
         <x:v>3334</x:v>
       </x:c>
       <x:c r="B3352" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C3352" s="1">
-        <x:v>7000</x:v>
+        <x:v>116050</x:v>
       </x:c>
       <x:c r="D3352" s="1">
-        <x:v>63</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="E3352" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3352" s="1">
-        <x:v>7000</x:v>
+        <x:v>47699</x:v>
       </x:c>
       <x:c r="G3352" s="1">
-        <x:v>14063</x:v>
+        <x:v>163985</x:v>
       </x:c>
     </x:row>
     <x:row r="3353" spans="1:7">
@@ -90453,22 +90453,22 @@
         <x:v>3430</x:v>
       </x:c>
       <x:c r="B3454" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C3454" s="1">
-        <x:v>0</x:v>
+        <x:v>72750</x:v>
       </x:c>
       <x:c r="D3454" s="1">
-        <x:v>59</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="E3454" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3454" s="1">
-        <x:v>0</x:v>
+        <x:v>25450</x:v>
       </x:c>
       <x:c r="G3454" s="1">
-        <x:v>59</x:v>
+        <x:v>98495</x:v>
       </x:c>
     </x:row>
     <x:row r="3455" spans="1:7">
@@ -90476,22 +90476,22 @@
         <x:v>3430</x:v>
       </x:c>
       <x:c r="B3455" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C3455" s="1">
-        <x:v>72750</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3455" s="1">
-        <x:v>295</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3455" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3455" s="1">
-        <x:v>25450</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3455" s="1">
-        <x:v>98495</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="3456" spans="1:7">
@@ -90683,22 +90683,22 @@
         <x:v>3438</x:v>
       </x:c>
       <x:c r="B3464" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C3464" s="1">
-        <x:v>47850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3464" s="1">
-        <x:v>0</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3464" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3464" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3464" s="1">
-        <x:v>52850</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="3465" spans="1:7">
@@ -90706,22 +90706,22 @@
         <x:v>3438</x:v>
       </x:c>
       <x:c r="B3465" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C3465" s="1">
-        <x:v>0</x:v>
+        <x:v>47850</x:v>
       </x:c>
       <x:c r="D3465" s="1">
-        <x:v>59</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3465" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3465" s="1">
-        <x:v>0</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G3465" s="1">
-        <x:v>59</x:v>
+        <x:v>52850</x:v>
       </x:c>
     </x:row>
     <x:row r="3466" spans="1:7">
@@ -90936,10 +90936,10 @@
         <x:v>3448</x:v>
       </x:c>
       <x:c r="B3475" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C3475" s="1">
-        <x:v>22500</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D3475" s="1">
         <x:v>0</x:v>
@@ -90951,7 +90951,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G3475" s="1">
-        <x:v>22500</x:v>
+        <x:v>3000</x:v>
       </x:c>
     </x:row>
     <x:row r="3476" spans="1:7">
@@ -90959,22 +90959,22 @@
         <x:v>3448</x:v>
       </x:c>
       <x:c r="B3476" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="C3476" s="1">
-        <x:v>3000</x:v>
+        <x:v>437150</x:v>
       </x:c>
       <x:c r="D3476" s="1">
-        <x:v>0</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="E3476" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3476" s="1">
-        <x:v>0</x:v>
+        <x:v>348550</x:v>
       </x:c>
       <x:c r="G3476" s="1">
-        <x:v>3000</x:v>
+        <x:v>786168</x:v>
       </x:c>
     </x:row>
     <x:row r="3477" spans="1:7">
@@ -90982,22 +90982,22 @@
         <x:v>3448</x:v>
       </x:c>
       <x:c r="B3477" s="1" t="s">
-        <x:v>419</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="C3477" s="1">
-        <x:v>437150</x:v>
+        <x:v>22500</x:v>
       </x:c>
       <x:c r="D3477" s="1">
-        <x:v>468</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3477" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3477" s="1">
-        <x:v>348550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3477" s="1">
-        <x:v>786168</x:v>
+        <x:v>22500</x:v>
       </x:c>
     </x:row>
     <x:row r="3478" spans="1:7">
@@ -92132,22 +92132,22 @@
         <x:v>3495</x:v>
       </x:c>
       <x:c r="B3527" s="1" t="s">
-        <x:v>260</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C3527" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3527" s="1">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E3527" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3527" s="1">
-        <x:v>11300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3527" s="1">
-        <x:v>12300</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="3528" spans="1:7">
@@ -92155,22 +92155,22 @@
         <x:v>3495</x:v>
       </x:c>
       <x:c r="B3528" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="C3528" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D3528" s="1">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3528" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3528" s="1">
-        <x:v>0</x:v>
+        <x:v>11300</x:v>
       </x:c>
       <x:c r="G3528" s="1">
-        <x:v>3</x:v>
+        <x:v>12300</x:v>
       </x:c>
     </x:row>
     <x:row r="3529" spans="1:7">
@@ -92707,10 +92707,10 @@
         <x:v>3519</x:v>
       </x:c>
       <x:c r="B3552" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C3552" s="1">
-        <x:v>130750</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D3552" s="1">
         <x:v>7</x:v>
@@ -92719,10 +92719,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3552" s="1">
-        <x:v>83750</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3552" s="1">
-        <x:v>214507</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="3553" spans="1:7">
@@ -92730,10 +92730,10 @@
         <x:v>3519</x:v>
       </x:c>
       <x:c r="B3553" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C3553" s="1">
-        <x:v>0</x:v>
+        <x:v>130750</x:v>
       </x:c>
       <x:c r="D3553" s="1">
         <x:v>7</x:v>
@@ -92742,10 +92742,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3553" s="1">
-        <x:v>0</x:v>
+        <x:v>83750</x:v>
       </x:c>
       <x:c r="G3553" s="1">
-        <x:v>7</x:v>
+        <x:v>214507</x:v>
       </x:c>
     </x:row>
     <x:row r="3554" spans="1:7">
